--- a/Result/checksun_type/整體解決方案.xlsx
+++ b/Result/checksun_type/整體解決方案.xlsx
@@ -878,12 +878,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-2.4</t>
+          <t>-1.21</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>332.0</t>
+          <t>303.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>20.6</t>
+          <t>20.35</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -908,12 +908,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-2.55</t>
+          <t>-1.6</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>32.53</t>
+          <t>26.90</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-28.22</t>
+          <t>-29.09</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -988,17 +988,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-3.15</t>
+          <t>-1.96</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>332</t>
+          <t>303</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
@@ -1029,57 +1029,57 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-4.81</t>
+          <t>-4.01</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-2.89</t>
+          <t>-4.23</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-5.58</t>
+          <t>-5.74</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-6.75</t>
+          <t>-7.02</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>21.64</t>
+          <t>21.2</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>22.28</t>
+          <t>22.14</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>23.6</t>
+          <t>23.48</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>25.31</t>
+          <t>25.26</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-7.22</t>
+          <t>-13.86</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-0.67</t>
+          <t>-0.74</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-0.62</t>
+          <t>-0.65</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-120.48</t>
+          <t>-121.22</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1099,41 +1099,41 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>65953.37012987013</t>
+          <t>65871.74567723343</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>6909.0</t>
+          <t>6204.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>6954.2</t>
+          <t>6690.2</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>5247.3</t>
+          <t>5272.2</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>8221.3</t>
+          <t>8019.26</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>1706</t>
+          <t>1418</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-460.9308758926027</t>
+          <t>-359.6353005633848</t>
         </is>
       </c>
       <c r="BC2" t="n">
-        <v>212.97</v>
+        <v>197.49</v>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>-16.43</t>
+          <t>-17.44</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -1197,22 +1197,22 @@
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>2.18</t>
+          <t>2.21</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="BX2" t="inlineStr">
         <is>
-          <t>84.03</t>
+          <t>84.12</t>
         </is>
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>2068</t>
+          <t>2043</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
@@ -1262,22 +1262,22 @@
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>20.85</t>
+          <t>20.7</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>21.3</t>
+          <t>20.8</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>20.55</t>
+          <t>20.3</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>20.6</t>
+          <t>20.35</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
@@ -1309,12 +1309,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-1.85</t>
+          <t>-2.4</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>432.0</t>
+          <t>332.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1324,7 +1324,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>21.1</t>
+          <t>20.6</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1334,17 +1334,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-2.43</t>
+          <t>-1.23</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-2.55</t>
+          <t>-1.6</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>18.25</t>
+          <t>32.53</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1409,7 +1409,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-26.48</t>
+          <t>-28.22</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1419,17 +1419,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-3.08</t>
+          <t>-3.15</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1440,12 +1440,12 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>332</t>
+          <t>303</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
@@ -1455,62 +1455,62 @@
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>29.41</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-3.74</t>
+          <t>-4.81</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-2.07</t>
+          <t>-2.89</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-5.61</t>
+          <t>-5.58</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-6.48</t>
+          <t>-6.75</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>21.92</t>
+          <t>21.64</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>22.38</t>
+          <t>22.28</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>23.71</t>
+          <t>23.6</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>25.35</t>
+          <t>25.31</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>2.19</t>
+          <t>-7.22</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-0.60</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>-0.62</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-120.11</t>
+          <t>-120.48</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,41 +1530,41 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>65953.37012987013</t>
+          <t>65871.74567723343</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>9271.0</t>
+          <t>6909.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>6118.4</t>
+          <t>6954.2</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>5174.1</t>
+          <t>5247.3</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>8359.92</t>
+          <t>8221.3</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>944</t>
+          <t>1706</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-583.4590404799573</t>
+          <t>-460.9308758926027</t>
         </is>
       </c>
       <c r="BC3" t="n">
-        <v>151.95</v>
+        <v>212.97</v>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>-14.40</t>
+          <t>-16.43</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -1628,22 +1628,22 @@
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>2.18</t>
+          <t>2.21</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
@@ -1668,12 +1668,12 @@
       </c>
       <c r="BX3" t="inlineStr">
         <is>
-          <t>84.03</t>
+          <t>84.12</t>
         </is>
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>2068</t>
+          <t>2043</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
@@ -1693,22 +1693,22 @@
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>21.6</t>
+          <t>20.85</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>21.75</t>
+          <t>21.3</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>21.1</t>
+          <t>20.55</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>21.1</t>
+          <t>20.6</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
@@ -1740,12 +1740,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-4.23</t>
+          <t>-1.85</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>277.0</t>
+          <t>432.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1755,7 +1755,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>21.5</t>
+          <t>21.1</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1765,17 +1765,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-4.37</t>
+          <t>-3.69</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-2.55</t>
+          <t>-1.6</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>4.44</t>
+          <t>18.25</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-25.09</t>
+          <t>-26.48</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1850,17 +1850,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-5.58</t>
+          <t>-3.08</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1871,12 +1871,12 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>332</t>
+          <t>303</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
@@ -1886,62 +1886,62 @@
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>62.75</t>
+          <t>29.41</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-2.58</t>
+          <t>-3.74</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-1.75</t>
+          <t>-2.07</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-5.62</t>
+          <t>-5.61</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-6.25</t>
+          <t>-6.48</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>22.07</t>
+          <t>21.92</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>22.46</t>
+          <t>22.38</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>23.8</t>
+          <t>23.71</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>25.39</t>
+          <t>25.35</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>10.30</t>
+          <t>2.19</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-0.55</t>
+          <t>-0.60</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-0.62</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1951,7 +1951,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-120.22</t>
+          <t>-120.11</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1961,41 +1961,41 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>65953.37012987013</t>
+          <t>65871.74567723343</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>6118.0</t>
+          <t>9271.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>4827.0</t>
+          <t>6118.4</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>4621.6</t>
+          <t>5174.1</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>8529.86</t>
+          <t>8359.92</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>205</t>
+          <t>944</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-717.1700700201001</t>
+          <t>-583.4590404799573</t>
         </is>
       </c>
       <c r="BC4" t="n">
-        <v>-193.72</v>
+        <v>151.95</v>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
@@ -2014,7 +2014,7 @@
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>-12.78</t>
+          <t>-14.40</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -2059,7 +2059,7 @@
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
@@ -2069,12 +2069,12 @@
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>2.18</t>
+          <t>2.21</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
@@ -2099,12 +2099,12 @@
       </c>
       <c r="BX4" t="inlineStr">
         <is>
-          <t>84.03</t>
+          <t>84.12</t>
         </is>
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>2068</t>
+          <t>2043</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
@@ -2124,22 +2124,22 @@
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>22.45</t>
+          <t>21.6</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>22.7</t>
+          <t>21.75</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>21.5</t>
+          <t>21.1</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>21.5</t>
+          <t>21.1</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-0.44</t>
+          <t>-4.23</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>220.0</t>
+          <t>277.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2186,7 +2186,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>22.45</t>
+          <t>21.5</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2196,17 +2196,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-8.98</t>
+          <t>-5.65</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-2.55</t>
+          <t>-1.6</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-3.88</t>
+          <t>4.44</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-21.78</t>
+          <t>-25.09</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2281,17 +2281,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>-5.58</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2302,77 +2302,77 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>332</t>
+          <t>303</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>88.24</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>78.13</t>
+          <t>62.75</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>-2.58</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-1.50</t>
+          <t>-1.75</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-5.75</t>
+          <t>-5.62</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-6.03</t>
+          <t>-6.25</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>22.18</t>
+          <t>22.07</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>22.52</t>
+          <t>22.46</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>23.89</t>
+          <t>23.8</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>25.42</t>
+          <t>25.39</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>16.80</t>
+          <t>10.30</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-0.53</t>
+          <t>-0.55</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-0.63</t>
+          <t>-0.62</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-120.74</t>
+          <t>-120.22</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2392,41 +2392,41 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>65953.37012987013</t>
+          <t>65871.74567723343</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>4949.0</t>
+          <t>6118.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>4249.0</t>
+          <t>4827.0</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>4420.6</t>
+          <t>4621.6</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>8793.4</t>
+          <t>8529.86</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-171</t>
+          <t>205</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-812.3425340488951</t>
+          <t>-717.1700700201001</t>
         </is>
       </c>
       <c r="BC5" t="n">
-        <v>-342.8</v>
+        <v>-193.72</v>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
@@ -2445,7 +2445,7 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>-8.92</t>
+          <t>-12.78</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
@@ -2490,22 +2490,22 @@
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>2.18</t>
+          <t>2.21</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="BX5" t="inlineStr">
         <is>
-          <t>84.03</t>
+          <t>84.12</t>
         </is>
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>2068</t>
+          <t>2043</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
@@ -2555,22 +2555,22 @@
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>22.65</t>
+          <t>22.45</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>22.8</t>
+          <t>22.7</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>22.25</t>
+          <t>21.5</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>22.45</t>
+          <t>21.5</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
@@ -2602,12 +2602,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2.48</t>
+          <t>-0.44</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>335.0</t>
+          <t>220.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2617,7 +2617,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>22.55</t>
+          <t>22.45</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2627,17 +2627,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-9.47</t>
+          <t>-10.32</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-2.55</t>
+          <t>-1.6</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-13.24</t>
+          <t>-3.88</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2702,7 +2702,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-21.43</t>
+          <t>-21.78</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2712,17 +2712,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2733,47 +2733,47 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>332</t>
+          <t>303</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>88.24</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>53.98</t>
+          <t>78.13</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>2.17</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-2.02</t>
+          <t>-1.50</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-6.11</t>
+          <t>-5.75</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-5.72</t>
+          <t>-6.03</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>22.07</t>
+          <t>22.18</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
@@ -2783,27 +2783,27 @@
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>23.99</t>
+          <t>23.89</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>25.44</t>
+          <t>25.42</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>11.82</t>
+          <t>16.80</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>-0.53</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>-0.63</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2813,7 +2813,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-121.61</t>
+          <t>-120.74</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2823,41 +2823,41 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>65953.37012987013</t>
+          <t>65871.74567723343</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>7524.0</t>
+          <t>4949.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>3854.2</t>
+          <t>4249.0</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>4442.4</t>
+          <t>4420.6</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>9497.76</t>
+          <t>8793.4</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-588</t>
+          <t>-171</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-897.713861172273</t>
+          <t>-812.3425340488951</t>
         </is>
       </c>
       <c r="BC6" t="n">
-        <v>-418.28</v>
+        <v>-342.8</v>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>-8.52</t>
+          <t>-8.92</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
@@ -2921,7 +2921,7 @@
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>2.18</t>
+          <t>2.21</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BX6" t="inlineStr">
         <is>
-          <t>84.03</t>
+          <t>84.12</t>
         </is>
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>2068</t>
+          <t>2043</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CC6" t="inlineStr">
         <is>
-          <t>22.2</t>
+          <t>22.65</t>
         </is>
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>22.85</t>
+          <t>22.8</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>22.15</t>
+          <t>22.25</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>22.55</t>
+          <t>22.45</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>2.48</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>124.0</t>
+          <t>335.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>22.0</t>
+          <t>22.55</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-6.8</t>
+          <t>-10.81</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-2.55</t>
+          <t>-1.6</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-15.90</t>
+          <t>-13.24</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-23.34</t>
+          <t>-21.43</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,77 +3164,77 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>332</t>
+          <t>303</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>46.15</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>30.79</t>
+          <t>53.98</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>2.17</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-2.65</t>
+          <t>-2.02</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-6.54</t>
+          <t>-6.11</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-5.35</t>
+          <t>-5.72</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>21.93</t>
+          <t>22.07</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>22.53</t>
+          <t>22.52</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>24.1</t>
+          <t>23.99</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>25.47</t>
+          <t>25.44</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>3.77</t>
+          <t>11.82</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>-0.58</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-0.68</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3244,7 +3244,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-122.25</t>
+          <t>-121.61</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3254,41 +3254,41 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>65953.37012987013</t>
+          <t>65871.74567723343</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>2730.0</t>
+          <t>7524.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>3540.4</t>
+          <t>3854.2</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>4209.9</t>
+          <t>4442.4</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>10262.8</t>
+          <t>9497.76</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-669</t>
+          <t>-588</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-984.8842059189067</t>
+          <t>-897.713861172273</t>
         </is>
       </c>
       <c r="BC7" t="n">
-        <v>-787.0599999999999</v>
+        <v>-418.28</v>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
@@ -3307,7 +3307,7 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>-10.75</t>
+          <t>-8.52</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -3352,7 +3352,7 @@
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
@@ -3362,12 +3362,12 @@
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>0.81</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>2.18</t>
+          <t>2.21</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="BX7" t="inlineStr">
         <is>
-          <t>84.03</t>
+          <t>84.12</t>
         </is>
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>2068</t>
+          <t>2043</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
@@ -3417,22 +3417,22 @@
       </c>
       <c r="CC7" t="inlineStr">
         <is>
-          <t>21.8</t>
+          <t>22.2</t>
         </is>
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>22.2</t>
+          <t>22.85</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>21.65</t>
+          <t>22.15</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>22.0</t>
+          <t>22.55</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
@@ -3464,12 +3464,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>124.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>21.85</t>
+          <t>22.0</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3489,17 +3489,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-6.07</t>
+          <t>-8.11</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-2.55</t>
+          <t>-1.6</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-6.91</t>
+          <t>-15.90</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3564,7 +3564,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-23.87</t>
+          <t>-23.34</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3574,12 +3574,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -3595,79 +3595,79 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>332</t>
+          <t>303</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>15.79</t>
+          <t>46.15</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>19.85</t>
+          <t>30.79</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-3.18</t>
+          <t>-2.65</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-6.73</t>
+          <t>-6.54</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-5.01</t>
+          <t>-5.35</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>21.87</t>
+          <t>21.93</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>22.59</t>
+          <t>22.53</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>24.22</t>
+          <t>24.1</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>25.49</t>
+          <t>25.47</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>3.77</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
+          <t>-0.65</t>
+        </is>
+      </c>
+      <c r="AR8" t="inlineStr">
+        <is>
           <t>-0.68</t>
         </is>
       </c>
-      <c r="AR8" t="inlineStr">
-        <is>
-          <t>-0.68</t>
-        </is>
-      </c>
       <c r="AS8" t="inlineStr">
         <is>
           <t>3.04</t>
@@ -3675,7 +3675,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-122.46</t>
+          <t>-122.25</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3685,41 +3685,41 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>65953.37012987013</t>
+          <t>65871.74567723343</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>2814.0</t>
+          <t>2730.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>4229.8</t>
+          <t>3540.4</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>4544.0</t>
+          <t>4209.9</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>10674.9</t>
+          <t>10262.8</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-314</t>
+          <t>-669</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-1020.853105276921</t>
+          <t>-984.8842059189067</t>
         </is>
       </c>
       <c r="BC8" t="n">
-        <v>-772.13</v>
+        <v>-787.0599999999999</v>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
@@ -3738,7 +3738,7 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>-11.36</t>
+          <t>-10.75</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -3783,7 +3783,7 @@
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
@@ -3793,12 +3793,12 @@
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>0.80</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>2.18</t>
+          <t>2.21</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
@@ -3823,12 +3823,12 @@
       </c>
       <c r="BX8" t="inlineStr">
         <is>
-          <t>84.03</t>
+          <t>84.12</t>
         </is>
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>2068</t>
+          <t>2043</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
@@ -3848,22 +3848,22 @@
       </c>
       <c r="CC8" t="inlineStr">
         <is>
-          <t>22.05</t>
+          <t>21.8</t>
         </is>
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>22.05</t>
+          <t>22.2</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>21.5</t>
+          <t>21.65</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>21.85</t>
+          <t>22.0</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>148.0</t>
+          <t>130.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3910,7 +3910,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>22.05</t>
+          <t>21.85</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3920,17 +3920,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-7.04</t>
+          <t>-7.37</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-2.55</t>
+          <t>-1.6</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-4.35</t>
+          <t>-6.91</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3995,7 +3995,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-23.17</t>
+          <t>-23.87</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4005,17 +4005,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2.32</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4026,77 +4026,77 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>332</t>
+          <t>303</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>30.43</t>
+          <t>15.79</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>17.15</t>
+          <t>19.85</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>0.36</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-3.13</t>
+          <t>-3.18</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-6.77</t>
+          <t>-6.73</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-4.69</t>
+          <t>-5.01</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>21.97</t>
+          <t>21.87</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>22.68</t>
+          <t>22.59</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>24.33</t>
+          <t>24.22</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>25.52</t>
+          <t>25.49</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-0.69</t>
+          <t>-0.68</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-0.69</t>
+          <t>-0.68</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-122.51</t>
+          <t>-122.46</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4116,41 +4116,41 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>65953.37012987013</t>
+          <t>65871.74567723343</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>3228.0</t>
+          <t>2814.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>4416.2</t>
+          <t>4229.8</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>4616.9</t>
+          <t>4544.0</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>11023.46</t>
+          <t>10674.9</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-200</t>
+          <t>-314</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-1066.075593375926</t>
+          <t>-1020.853105276921</t>
         </is>
       </c>
       <c r="BC9" t="n">
-        <v>-732.23</v>
+        <v>-772.13</v>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>-10.55</t>
+          <t>-11.36</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -4224,12 +4224,12 @@
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>0.81</t>
+          <t>0.80</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>2.18</t>
+          <t>2.21</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="BX9" t="inlineStr">
         <is>
-          <t>84.03</t>
+          <t>84.12</t>
         </is>
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>2068</t>
+          <t>2043</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
@@ -4279,7 +4279,7 @@
       </c>
       <c r="CC9" t="inlineStr">
         <is>
-          <t>21.55</t>
+          <t>22.05</t>
         </is>
       </c>
       <c r="CD9" t="inlineStr">
@@ -4289,12 +4289,12 @@
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>21.55</t>
+          <t>21.5</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>22.05</t>
+          <t>21.85</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
@@ -4326,12 +4326,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>135.0</t>
+          <t>148.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4341,7 +4341,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>21.9</t>
+          <t>22.05</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4351,17 +4351,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-6.31</t>
+          <t>-8.35</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-2.55</t>
+          <t>-1.6</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-3.19</t>
+          <t>-4.35</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4426,7 +4426,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-23.69</t>
+          <t>-23.17</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4436,17 +4436,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-0.45</t>
+          <t>2.32</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4457,77 +4457,77 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>332</t>
+          <t>303</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>13.33</t>
+          <t>30.43</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>7.01</t>
+          <t>17.15</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>0.36</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-3.27</t>
+          <t>-3.13</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-6.82</t>
+          <t>-6.77</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-4.33</t>
+          <t>-4.69</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>22.03</t>
+          <t>21.97</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>22.78</t>
+          <t>22.68</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>24.44</t>
+          <t>24.33</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>25.55</t>
+          <t>25.52</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-3.18</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>-0.69</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-0.68</t>
+          <t>-0.69</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4537,7 +4537,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-122.50</t>
+          <t>-122.51</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4547,41 +4547,41 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>65953.37012987013</t>
+          <t>65871.74567723343</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>2975.0</t>
+          <t>3228.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>4592.2</t>
+          <t>4416.2</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>4743.6</t>
+          <t>4616.9</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>11440.2</t>
+          <t>11023.46</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-151</t>
+          <t>-200</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-1126.774657034685</t>
+          <t>-1066.075593375926</t>
         </is>
       </c>
       <c r="BC10" t="n">
-        <v>-693.4400000000001</v>
+        <v>-732.23</v>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
@@ -4600,7 +4600,7 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>-11.16</t>
+          <t>-10.55</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -4645,7 +4645,7 @@
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
@@ -4660,7 +4660,7 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>2.18</t>
+          <t>2.21</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="BX10" t="inlineStr">
         <is>
-          <t>84.03</t>
+          <t>84.12</t>
         </is>
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>2068</t>
+          <t>2043</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
@@ -4710,22 +4710,22 @@
       </c>
       <c r="CC10" t="inlineStr">
         <is>
-          <t>21.95</t>
+          <t>21.55</t>
         </is>
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>22.1</t>
+          <t>22.05</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>21.8</t>
+          <t>21.55</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>21.9</t>
+          <t>22.05</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>275.0</t>
+          <t>135.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4772,7 +4772,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>21.85</t>
+          <t>21.9</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4782,17 +4782,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-6.07</t>
+          <t>-7.62</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-2.55</t>
+          <t>-1.6</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>-3.19</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4857,7 +4857,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-23.87</t>
+          <t>-23.69</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4867,17 +4867,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>-0.45</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4888,67 +4888,67 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>332</t>
+          <t>303</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>7.69</t>
+          <t>13.33</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>3.8</t>
+          <t>7.01</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-1.18</t>
+          <t>-0.59</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-3.42</t>
+          <t>-3.27</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-6.76</t>
+          <t>-6.82</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-4.01</t>
+          <t>-4.33</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>22.11</t>
+          <t>22.03</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>22.89</t>
+          <t>22.78</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>24.55</t>
+          <t>24.44</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>25.58</t>
+          <t>25.55</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-4.15</t>
+          <t>-3.18</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
@@ -4968,7 +4968,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-122.32</t>
+          <t>-122.50</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4978,41 +4978,41 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>65953.37012987013</t>
+          <t>65871.74567723343</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>5955.0</t>
+          <t>2975.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>5030.6</t>
+          <t>4592.2</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>5007.2</t>
+          <t>4743.6</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>12014.98</t>
+          <t>11440.2</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>-151</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-1205.563016958922</t>
+          <t>-1126.774657034685</t>
         </is>
       </c>
       <c r="BC11" t="n">
-        <v>-586.15</v>
+        <v>-693.4400000000001</v>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
@@ -5031,7 +5031,7 @@
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>-11.36</t>
+          <t>-11.16</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
@@ -5076,7 +5076,7 @@
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
@@ -5086,12 +5086,12 @@
       </c>
       <c r="BR11" t="inlineStr">
         <is>
-          <t>0.80</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>2.18</t>
+          <t>2.21</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="BX11" t="inlineStr">
         <is>
-          <t>84.03</t>
+          <t>84.12</t>
         </is>
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>2068</t>
+          <t>2043</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
@@ -5141,22 +5141,22 @@
       </c>
       <c r="CC11" t="inlineStr">
         <is>
-          <t>21.5</t>
+          <t>21.95</t>
         </is>
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>22.2</t>
+          <t>22.1</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>21.25</t>
+          <t>21.8</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>21.85</t>
+          <t>21.9</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
@@ -5188,12 +5188,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-2.91</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>281.0</t>
+          <t>275.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5203,7 +5203,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>21.7</t>
+          <t>21.85</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5213,17 +5213,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-5.34</t>
+          <t>-7.37</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-2.55</t>
+          <t>-1.6</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-9.98</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5288,7 +5288,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-24.39</t>
+          <t>-23.87</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5298,17 +5298,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-3.46</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5319,77 +5319,77 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>332</t>
+          <t>303</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.69</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>3.8</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-2.56</t>
+          <t>-1.18</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-3.21</t>
+          <t>-3.42</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-6.71</t>
+          <t>-6.76</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-3.73</t>
+          <t>-4.01</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>22.27</t>
+          <t>22.11</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>23.01</t>
+          <t>22.89</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>24.66</t>
+          <t>24.55</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>25.62</t>
+          <t>25.58</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-3.12</t>
+          <t>-4.15</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-0.69</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-0.67</t>
+          <t>-0.68</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5399,7 +5399,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-122.09</t>
+          <t>-122.32</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5409,41 +5409,41 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>65953.37012987013</t>
+          <t>65871.74567723343</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>6177.0</t>
+          <t>5955.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>4879.4</t>
+          <t>5030.6</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>5420.1</t>
+          <t>5007.2</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>12696.6</t>
+          <t>12014.98</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-540</t>
+          <t>23</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-1318.183814463578</t>
+          <t>-1205.563016958922</t>
         </is>
       </c>
       <c r="BC12" t="n">
-        <v>-731.23</v>
+        <v>-586.15</v>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
@@ -5462,7 +5462,7 @@
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>-11.97</t>
+          <t>-11.36</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
@@ -5507,7 +5507,7 @@
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
@@ -5522,7 +5522,7 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>2.18</t>
+          <t>2.21</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
@@ -5547,12 +5547,12 @@
       </c>
       <c r="BX12" t="inlineStr">
         <is>
-          <t>84.03</t>
+          <t>84.12</t>
         </is>
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>2068</t>
+          <t>2043</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
@@ -5572,22 +5572,22 @@
       </c>
       <c r="CC12" t="inlineStr">
         <is>
-          <t>22.3</t>
+          <t>21.5</t>
         </is>
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>22.45</t>
+          <t>22.2</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>21.7</t>
+          <t>21.25</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>21.7</t>
+          <t>21.85</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
@@ -5619,12 +5619,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-2.85</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1335.0</t>
+          <t>895.0</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5649,12 +5649,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-2.24</t>
+          <t>-0.74</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>16.46</t>
+          <t>12.01</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5729,17 +5729,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>3.07</t>
+          <t>2.06</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>-2.42</t>
+          <t>-1.11</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5750,12 +5750,12 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>14</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>1335</t>
+          <t>895</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
@@ -5770,57 +5770,57 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>-3.58</t>
+          <t>-2.30</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>-6.18</t>
+          <t>-6.61</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>-5.88</t>
+          <t>-6.32</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>-2.72</t>
+          <t>-2.89</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>64.3</t>
+          <t>63.46</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>68.54</t>
+          <t>67.95</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>72.82</t>
+          <t>72.53</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>74.85</t>
+          <t>74.69</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>-22.21</t>
+          <t>-21.64</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>-2.63</t>
+          <t>-2.77</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>-2.15</t>
+          <t>-2.28</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -5830,7 +5830,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-121.33</t>
+          <t>-122.55</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5840,41 +5840,41 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>1184371.385281385</t>
+          <t>1182784.869596542</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>83495.0</t>
+          <t>55553.0</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>81963.0</t>
+          <t>76033.4</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>70377.3</t>
+          <t>67880.8</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>140394.08</t>
+          <t>139203.84</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>11585</t>
+          <t>8152</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>-8019.516559500055</t>
+          <t>-7525.606587032868</t>
         </is>
       </c>
       <c r="BC13" t="n">
-        <v>-3807.28</v>
+        <v>-4809.1</v>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
@@ -5918,7 +5918,7 @@
       </c>
       <c r="BL13" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="BM13" t="inlineStr">
@@ -5978,7 +5978,7 @@
       </c>
       <c r="BX13" t="inlineStr">
         <is>
-          <t>84.03</t>
+          <t>84.12</t>
         </is>
       </c>
       <c r="BY13" t="inlineStr">
@@ -6003,7 +6003,7 @@
       </c>
       <c r="CC13" t="inlineStr">
         <is>
-          <t>63.2</t>
+          <t>62.5</t>
         </is>
       </c>
       <c r="CD13" t="inlineStr">
@@ -6013,7 +6013,7 @@
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>62.0</t>
+          <t>61.2</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
@@ -6050,12 +6050,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>-2.85</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>905.0</t>
+          <t>1335.0</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6065,7 +6065,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>63.8</t>
+          <t>62.0</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6075,17 +6075,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-2.9</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-2.24</t>
+          <t>-0.74</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2.33</t>
+          <t>16.46</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6150,7 +6150,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>-17.89</t>
+          <t>-20.21</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6160,17 +6160,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>3.07</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>-0.62</t>
+          <t>-2.42</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6181,12 +6181,12 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>14</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>1335</t>
+          <t>895</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
@@ -6201,57 +6201,57 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>-2.39</t>
+          <t>-3.58</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>-5.34</t>
+          <t>-6.18</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>-5.56</t>
+          <t>-5.88</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>-2.47</t>
+          <t>-2.72</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>65.36</t>
+          <t>64.3</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>69.04</t>
+          <t>68.54</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>73.11</t>
+          <t>72.82</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>74.96</t>
+          <t>74.85</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>-18.88</t>
+          <t>-22.21</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>-2.42</t>
+          <t>-2.63</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>-2.03</t>
+          <t>-2.15</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -6261,7 +6261,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-120.15</t>
+          <t>-121.33</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6271,41 +6271,41 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>1184371.385281385</t>
+          <t>1182784.869596542</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>57904.0</t>
+          <t>83495.0</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>74558.6</t>
+          <t>81963.0</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>72860.9</t>
+          <t>70377.3</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>140798.66</t>
+          <t>140394.08</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>1697</t>
+          <t>11585</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>-8785.377460999793</t>
+          <t>-8019.516559500055</t>
         </is>
       </c>
       <c r="BC14" t="n">
-        <v>-5233.92</v>
+        <v>-3807.28</v>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
@@ -6324,7 +6324,7 @@
       </c>
       <c r="BG14" t="inlineStr">
         <is>
-          <t>-15.50</t>
+          <t>-17.88</t>
         </is>
       </c>
       <c r="BH14" t="inlineStr">
@@ -6349,7 +6349,7 @@
       </c>
       <c r="BL14" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="BM14" t="inlineStr">
@@ -6369,7 +6369,7 @@
       </c>
       <c r="BP14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ14" t="inlineStr">
@@ -6379,7 +6379,7 @@
       </c>
       <c r="BR14" t="inlineStr">
         <is>
-          <t>3.78</t>
+          <t>3.67</t>
         </is>
       </c>
       <c r="BS14" t="inlineStr">
@@ -6409,7 +6409,7 @@
       </c>
       <c r="BX14" t="inlineStr">
         <is>
-          <t>84.03</t>
+          <t>84.12</t>
         </is>
       </c>
       <c r="BY14" t="inlineStr">
@@ -6434,22 +6434,22 @@
       </c>
       <c r="CC14" t="inlineStr">
         <is>
-          <t>64.3</t>
+          <t>63.2</t>
         </is>
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>64.5</t>
+          <t>63.5</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>63.5</t>
+          <t>62.0</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>63.8</t>
+          <t>62.0</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
@@ -6481,12 +6481,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-1.41</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>981.0</t>
+          <t>905.0</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6496,7 +6496,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>64.3</t>
+          <t>63.8</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6506,17 +6506,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-3.71</t>
+          <t>-2.9</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-2.24</t>
+          <t>-0.74</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>-3.13</t>
+          <t>2.33</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6581,7 +6581,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>-17.25</t>
+          <t>-17.89</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -6591,17 +6591,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>2.26</t>
+          <t>2.08</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>-1.09</t>
+          <t>-0.62</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6612,12 +6612,12 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>14</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>1335</t>
+          <t>895</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
@@ -6632,57 +6632,57 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>-2.63</t>
+          <t>-2.39</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>-5.00</t>
+          <t>-5.34</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>-5.25</t>
+          <t>-5.56</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>-2.20</t>
+          <t>-2.47</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>66.03999999999999</t>
+          <t>65.36</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>69.52</t>
+          <t>69.04</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>73.37</t>
+          <t>73.11</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>75.02</t>
+          <t>74.96</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>-18.32</t>
+          <t>-18.88</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>-2.29</t>
+          <t>-2.42</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>-1.94</t>
+          <t>-2.03</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -6692,7 +6692,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-119.20</t>
+          <t>-120.15</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6702,41 +6702,41 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>1184371.385281385</t>
+          <t>1182784.869596542</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>63333.0</t>
+          <t>57904.0</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>73690.8</t>
+          <t>74558.6</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>76070.6</t>
+          <t>72860.9</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>142749.4</t>
+          <t>140798.66</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>-2379</t>
+          <t>1697</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>-9431.096754263934</t>
+          <t>-8785.377460999793</t>
         </is>
       </c>
       <c r="BC15" t="n">
-        <v>-4343.16</v>
+        <v>-5233.92</v>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
@@ -6755,7 +6755,7 @@
       </c>
       <c r="BG15" t="inlineStr">
         <is>
-          <t>-14.83</t>
+          <t>-15.50</t>
         </is>
       </c>
       <c r="BH15" t="inlineStr">
@@ -6780,7 +6780,7 @@
       </c>
       <c r="BL15" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="BM15" t="inlineStr">
@@ -6800,7 +6800,7 @@
       </c>
       <c r="BP15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ15" t="inlineStr">
@@ -6810,7 +6810,7 @@
       </c>
       <c r="BR15" t="inlineStr">
         <is>
-          <t>3.81</t>
+          <t>3.78</t>
         </is>
       </c>
       <c r="BS15" t="inlineStr">
@@ -6840,7 +6840,7 @@
       </c>
       <c r="BX15" t="inlineStr">
         <is>
-          <t>84.03</t>
+          <t>84.12</t>
         </is>
       </c>
       <c r="BY15" t="inlineStr">
@@ -6865,22 +6865,22 @@
       </c>
       <c r="CC15" t="inlineStr">
         <is>
-          <t>64.0</t>
+          <t>64.3</t>
         </is>
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>65.3</t>
+          <t>64.5</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>64.0</t>
+          <t>63.5</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>64.3</t>
+          <t>63.8</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
@@ -6912,12 +6912,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-1.51</t>
+          <t>-1.41</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1830.0</t>
+          <t>981.0</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -6927,7 +6927,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>65.2</t>
+          <t>64.3</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6937,17 +6937,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-5.16</t>
+          <t>-3.71</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-2.24</t>
+          <t>-0.74</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>-3.13</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -7012,7 +7012,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>-16.09</t>
+          <t>-17.25</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7022,17 +7022,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>4.22</t>
+          <t>2.26</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>-1.07</t>
+          <t>-1.09</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7043,12 +7043,12 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>14</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>1335</t>
+          <t>895</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
@@ -7058,62 +7058,62 @@
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>-2.13</t>
+          <t>-2.63</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>-4.85</t>
+          <t>-5.00</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>-4.89</t>
+          <t>-5.25</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>-1.92</t>
+          <t>-2.20</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>66.62</t>
+          <t>66.03999999999999</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>70.02</t>
+          <t>69.52</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>73.62</t>
+          <t>73.37</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>75.06</t>
+          <t>75.02</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>-16.33</t>
+          <t>-18.32</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>-2.15</t>
+          <t>-2.29</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>-1.85</t>
+          <t>-1.94</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -7123,7 +7123,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-118.32</t>
+          <t>-119.20</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7133,41 +7133,41 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>1184371.385281385</t>
+          <t>1182784.869596542</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>119882.0</t>
+          <t>63333.0</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>74184.2</t>
+          <t>73690.8</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>74218.8</t>
+          <t>76070.6</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>146686.82</t>
+          <t>142749.4</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>-34</t>
+          <t>-2379</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>-10356.17625329185</t>
+          <t>-9431.096754263934</t>
         </is>
       </c>
       <c r="BC16" t="n">
-        <v>-3497.21</v>
+        <v>-4343.16</v>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
@@ -7186,7 +7186,7 @@
       </c>
       <c r="BG16" t="inlineStr">
         <is>
-          <t>-13.64</t>
+          <t>-14.83</t>
         </is>
       </c>
       <c r="BH16" t="inlineStr">
@@ -7211,7 +7211,7 @@
       </c>
       <c r="BL16" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="BM16" t="inlineStr">
@@ -7231,7 +7231,7 @@
       </c>
       <c r="BP16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ16" t="inlineStr">
@@ -7241,7 +7241,7 @@
       </c>
       <c r="BR16" t="inlineStr">
         <is>
-          <t>3.86</t>
+          <t>3.81</t>
         </is>
       </c>
       <c r="BS16" t="inlineStr">
@@ -7271,7 +7271,7 @@
       </c>
       <c r="BX16" t="inlineStr">
         <is>
-          <t>84.03</t>
+          <t>84.12</t>
         </is>
       </c>
       <c r="BY16" t="inlineStr">
@@ -7296,22 +7296,22 @@
       </c>
       <c r="CC16" t="inlineStr">
         <is>
-          <t>66.2</t>
+          <t>64.0</t>
         </is>
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>66.2</t>
+          <t>65.3</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>64.9</t>
+          <t>64.0</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>65.2</t>
+          <t>64.3</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
@@ -7343,12 +7343,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-1.63</t>
+          <t>-1.51</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1280.0</t>
+          <t>1830.0</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7358,7 +7358,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>66.2</t>
+          <t>65.2</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7368,17 +7368,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-6.77</t>
+          <t>-5.16</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-2.24</t>
+          <t>-0.74</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>-14.46</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7443,7 +7443,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>-14.80</t>
+          <t>-16.09</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -7453,17 +7453,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>2.95</t>
+          <t>4.22</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>-1.81</t>
+          <t>-1.07</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7474,12 +7474,12 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>14</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>1335</t>
+          <t>895</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
@@ -7494,57 +7494,57 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>-1.58</t>
+          <t>-2.13</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>-4.45</t>
+          <t>-4.85</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>-4.75</t>
+          <t>-4.89</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>-1.57</t>
+          <t>-1.92</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>67.26</t>
+          <t>66.62</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>70.4</t>
+          <t>70.02</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>73.91</t>
+          <t>73.62</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>75.09</t>
+          <t>75.06</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>-14.48</t>
+          <t>-16.33</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>-2.03</t>
+          <t>-2.15</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>-1.77</t>
+          <t>-1.85</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -7554,7 +7554,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-117.57</t>
+          <t>-118.32</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7564,41 +7564,41 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>1184371.385281385</t>
+          <t>1182784.869596542</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>85201.0</t>
+          <t>119882.0</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>59728.2</t>
+          <t>74184.2</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>69820.9</t>
+          <t>74218.8</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>148731.72</t>
+          <t>146686.82</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>-10092</t>
+          <t>-34</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>-11603.26133037079</t>
+          <t>-10356.17625329185</t>
         </is>
       </c>
       <c r="BC17" t="n">
-        <v>-8222.629999999999</v>
+        <v>-3497.21</v>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
@@ -7617,7 +7617,7 @@
       </c>
       <c r="BG17" t="inlineStr">
         <is>
-          <t>-12.32</t>
+          <t>-13.64</t>
         </is>
       </c>
       <c r="BH17" t="inlineStr">
@@ -7642,7 +7642,7 @@
       </c>
       <c r="BL17" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="BM17" t="inlineStr">
@@ -7662,7 +7662,7 @@
       </c>
       <c r="BP17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ17" t="inlineStr">
@@ -7672,7 +7672,7 @@
       </c>
       <c r="BR17" t="inlineStr">
         <is>
-          <t>3.92</t>
+          <t>3.86</t>
         </is>
       </c>
       <c r="BS17" t="inlineStr">
@@ -7702,7 +7702,7 @@
       </c>
       <c r="BX17" t="inlineStr">
         <is>
-          <t>84.03</t>
+          <t>84.12</t>
         </is>
       </c>
       <c r="BY17" t="inlineStr">
@@ -7727,22 +7727,22 @@
       </c>
       <c r="CC17" t="inlineStr">
         <is>
-          <t>67.6</t>
+          <t>66.2</t>
         </is>
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>67.8</t>
+          <t>66.2</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>65.8</t>
+          <t>64.9</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>66.2</t>
+          <t>65.2</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
@@ -7774,12 +7774,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>-1.63</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>685.0</t>
+          <t>1280.0</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7789,7 +7789,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>67.3</t>
+          <t>66.2</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7799,17 +7799,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-8.55</t>
+          <t>-6.77</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-2.24</t>
+          <t>-0.74</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>-12.53</t>
+          <t>-14.46</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7874,7 +7874,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>-13.38</t>
+          <t>-14.80</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -7884,17 +7884,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>2.95</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>-1.49</t>
+          <t>-1.81</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7905,17 +7905,17 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>14</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>1335</t>
+          <t>895</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>3.23</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
@@ -7925,37 +7925,37 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>-0.68</t>
+          <t>-1.58</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>-4.08</t>
+          <t>-4.45</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>-4.79</t>
+          <t>-4.75</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>-1.19</t>
+          <t>-1.57</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>67.76</t>
+          <t>67.26</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>70.64</t>
+          <t>70.4</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>74.19</t>
+          <t>73.91</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
@@ -7965,17 +7965,17 @@
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>-13.99</t>
+          <t>-14.48</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>-1.95</t>
+          <t>-2.03</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>-1.71</t>
+          <t>-1.77</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -7985,7 +7985,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-116.93</t>
+          <t>-117.57</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -7995,41 +7995,41 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>1184371.385281385</t>
+          <t>1182784.869596542</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>46473.0</t>
+          <t>85201.0</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>58791.6</t>
+          <t>59728.2</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>67214.7</t>
+          <t>69820.9</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>153057.4</t>
+          <t>148731.72</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>-8423</t>
+          <t>-10092</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>-12217.92197691516</t>
+          <t>-11603.26133037079</t>
         </is>
       </c>
       <c r="BC18" t="n">
-        <v>-10963.74</v>
+        <v>-8222.629999999999</v>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
@@ -8048,7 +8048,7 @@
       </c>
       <c r="BG18" t="inlineStr">
         <is>
-          <t>-10.86</t>
+          <t>-12.32</t>
         </is>
       </c>
       <c r="BH18" t="inlineStr">
@@ -8073,7 +8073,7 @@
       </c>
       <c r="BL18" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="BM18" t="inlineStr">
@@ -8093,7 +8093,7 @@
       </c>
       <c r="BP18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ18" t="inlineStr">
@@ -8103,7 +8103,7 @@
       </c>
       <c r="BR18" t="inlineStr">
         <is>
-          <t>3.99</t>
+          <t>3.92</t>
         </is>
       </c>
       <c r="BS18" t="inlineStr">
@@ -8133,7 +8133,7 @@
       </c>
       <c r="BX18" t="inlineStr">
         <is>
-          <t>84.03</t>
+          <t>84.12</t>
         </is>
       </c>
       <c r="BY18" t="inlineStr">
@@ -8158,22 +8158,22 @@
       </c>
       <c r="CC18" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>67.6</t>
         </is>
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>68.3</t>
+          <t>67.8</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>67.3</t>
+          <t>65.8</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>67.3</t>
+          <t>66.2</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
@@ -8205,12 +8205,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>799.0</t>
+          <t>685.0</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8220,7 +8220,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>67.2</t>
+          <t>67.3</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8230,17 +8230,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-8.39</t>
+          <t>-8.55</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-2.24</t>
+          <t>-0.74</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>-12.53</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8305,7 +8305,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>-13.51</t>
+          <t>-13.38</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -8315,17 +8315,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>1.84</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>-1.49</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8336,77 +8336,77 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>14</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>1335</t>
+          <t>895</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.23</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>4.3</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>-1.03</t>
+          <t>-0.68</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>-4.28</t>
+          <t>-4.08</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>-4.73</t>
+          <t>-4.79</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>-0.82</t>
+          <t>-1.19</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>67.9</t>
+          <t>67.76</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>70.93</t>
+          <t>70.64</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>74.46</t>
+          <t>74.19</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>75.07</t>
+          <t>75.09</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>-16.85</t>
+          <t>-13.99</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>-1.93</t>
+          <t>-1.95</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>-1.65</t>
+          <t>-1.71</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -8416,7 +8416,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-116.34</t>
+          <t>-116.93</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8426,41 +8426,41 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>1184371.385281385</t>
+          <t>1182784.869596542</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>53565.0</t>
+          <t>46473.0</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>71163.2</t>
+          <t>58791.6</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>70542.6</t>
+          <t>67214.7</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>156765.32</t>
+          <t>153057.4</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>620</t>
+          <t>-8423</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>-12445.95501356898</t>
+          <t>-12217.92197691516</t>
         </is>
       </c>
       <c r="BC19" t="n">
-        <v>-10338.62</v>
+        <v>-10963.74</v>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
@@ -8479,7 +8479,7 @@
       </c>
       <c r="BG19" t="inlineStr">
         <is>
-          <t>-10.99</t>
+          <t>-10.86</t>
         </is>
       </c>
       <c r="BH19" t="inlineStr">
@@ -8504,7 +8504,7 @@
       </c>
       <c r="BL19" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="BM19" t="inlineStr">
@@ -8524,7 +8524,7 @@
       </c>
       <c r="BP19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ19" t="inlineStr">
@@ -8534,7 +8534,7 @@
       </c>
       <c r="BR19" t="inlineStr">
         <is>
-          <t>3.98</t>
+          <t>3.99</t>
         </is>
       </c>
       <c r="BS19" t="inlineStr">
@@ -8564,7 +8564,7 @@
       </c>
       <c r="BX19" t="inlineStr">
         <is>
-          <t>84.03</t>
+          <t>84.12</t>
         </is>
       </c>
       <c r="BY19" t="inlineStr">
@@ -8589,22 +8589,22 @@
       </c>
       <c r="CC19" t="inlineStr">
         <is>
-          <t>67.2</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>67.7</t>
+          <t>68.3</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>66.6</t>
+          <t>67.3</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>67.2</t>
+          <t>67.3</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
@@ -8636,12 +8636,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-1.76</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>979.0</t>
+          <t>799.0</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8666,12 +8666,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-2.24</t>
+          <t>-0.74</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8746,17 +8746,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>1.84</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>-0.44</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8767,12 +8767,12 @@
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>14</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>1335</t>
+          <t>895</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
@@ -8782,62 +8782,62 @@
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>10.13</t>
+          <t>4.3</t>
         </is>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>-1.73</t>
+          <t>-1.03</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>-3.95</t>
+          <t>-4.28</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>-4.72</t>
+          <t>-4.73</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>-0.46</t>
+          <t>-0.82</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>68.38000000000001</t>
+          <t>67.9</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>71.19</t>
+          <t>70.93</t>
         </is>
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>74.72</t>
+          <t>74.46</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>75.06</t>
+          <t>75.07</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>-17.89</t>
+          <t>-16.85</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>-1.86</t>
+          <t>-1.93</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>-1.58</t>
+          <t>-1.65</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -8847,7 +8847,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-115.65</t>
+          <t>-116.34</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8857,41 +8857,41 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>1184371.385281385</t>
+          <t>1182784.869596542</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>65800.0</t>
+          <t>53565.0</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>78450.4</t>
+          <t>71163.2</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>77571.5</t>
+          <t>70542.6</t>
         </is>
       </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>159725.04</t>
+          <t>156765.32</t>
         </is>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>878</t>
+          <t>620</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>-12829.10600648209</t>
+          <t>-12445.95501356898</t>
         </is>
       </c>
       <c r="BC20" t="n">
-        <v>-9836.219999999999</v>
+        <v>-10338.62</v>
       </c>
       <c r="BD20" t="inlineStr">
         <is>
@@ -8935,7 +8935,7 @@
       </c>
       <c r="BL20" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="BM20" t="inlineStr">
@@ -8955,7 +8955,7 @@
       </c>
       <c r="BP20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ20" t="inlineStr">
@@ -8995,7 +8995,7 @@
       </c>
       <c r="BX20" t="inlineStr">
         <is>
-          <t>84.03</t>
+          <t>84.12</t>
         </is>
       </c>
       <c r="BY20" t="inlineStr">
@@ -9020,12 +9020,12 @@
       </c>
       <c r="CC20" t="inlineStr">
         <is>
-          <t>68.1</t>
+          <t>67.2</t>
         </is>
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>68.1</t>
+          <t>67.7</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
@@ -9067,12 +9067,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>-1.76</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>693.0</t>
+          <t>979.0</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9082,7 +9082,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>68.4</t>
+          <t>67.2</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9092,17 +9092,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-10.32</t>
+          <t>-8.39</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-2.24</t>
+          <t>-0.74</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>-14.50</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9167,7 +9167,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>-11.97</t>
+          <t>-13.51</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -9177,17 +9177,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>-1.46</t>
+          <t>-0.44</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9198,17 +9198,17 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>14</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>1335</t>
+          <t>895</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>12.9</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr">
@@ -9218,57 +9218,57 @@
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>-0.87</t>
+          <t>-1.73</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>-3.49</t>
+          <t>-3.95</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>-4.66</t>
+          <t>-4.72</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>-0.46</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>68.38000000000001</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>71.5</t>
+          <t>71.19</t>
         </is>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>74.99</t>
+          <t>74.72</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>75.02</t>
+          <t>75.06</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>-16.12</t>
+          <t>-17.89</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>-1.75</t>
+          <t>-1.86</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>-1.51</t>
+          <t>-1.58</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -9278,7 +9278,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-114.95</t>
+          <t>-115.65</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9288,41 +9288,41 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>1184371.385281385</t>
+          <t>1182784.869596542</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>47602.0</t>
+          <t>65800.0</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>74253.4</t>
+          <t>78450.4</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>86849.0</t>
+          <t>77571.5</t>
         </is>
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>165185.86</t>
+          <t>159725.04</t>
         </is>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>-12595</t>
+          <t>878</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>-13373.26661799914</t>
+          <t>-12829.10600648209</t>
         </is>
       </c>
       <c r="BC21" t="n">
-        <v>-10078.1</v>
+        <v>-9836.219999999999</v>
       </c>
       <c r="BD21" t="inlineStr">
         <is>
@@ -9341,7 +9341,7 @@
       </c>
       <c r="BG21" t="inlineStr">
         <is>
-          <t>-9.40</t>
+          <t>-10.99</t>
         </is>
       </c>
       <c r="BH21" t="inlineStr">
@@ -9366,7 +9366,7 @@
       </c>
       <c r="BL21" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="BM21" t="inlineStr">
@@ -9396,7 +9396,7 @@
       </c>
       <c r="BR21" t="inlineStr">
         <is>
-          <t>4.05</t>
+          <t>3.98</t>
         </is>
       </c>
       <c r="BS21" t="inlineStr">
@@ -9426,7 +9426,7 @@
       </c>
       <c r="BX21" t="inlineStr">
         <is>
-          <t>84.03</t>
+          <t>84.12</t>
         </is>
       </c>
       <c r="BY21" t="inlineStr">
@@ -9451,22 +9451,22 @@
       </c>
       <c r="CC21" t="inlineStr">
         <is>
-          <t>69.1</t>
+          <t>68.1</t>
         </is>
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>69.5</t>
+          <t>68.1</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>68.3</t>
+          <t>66.6</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>68.4</t>
+          <t>67.2</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
@@ -9498,12 +9498,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1181.0</t>
+          <t>693.0</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9513,7 +9513,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>68.7</t>
+          <t>68.4</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9523,17 +9523,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-10.81</t>
+          <t>-10.32</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-2.24</t>
+          <t>-0.74</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>-12.08</t>
+          <t>-14.50</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9598,7 +9598,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>-11.58</t>
+          <t>-11.97</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -9608,17 +9608,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>2.72</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2.87</t>
+          <t>-1.46</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9629,77 +9629,77 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>14</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>1335</t>
+          <t>895</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>17.5</t>
+          <t>12.9</t>
         </is>
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>5.83</t>
+          <t>10.13</t>
         </is>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>-0.89</t>
+          <t>-0.87</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>-3.44</t>
+          <t>-3.49</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>-4.52</t>
+          <t>-4.66</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>69.32</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>71.79</t>
+          <t>71.5</t>
         </is>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>75.19</t>
+          <t>74.99</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>74.97</t>
+          <t>75.02</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>-17.99</t>
+          <t>-16.12</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>-1.71</t>
+          <t>-1.75</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>-1.45</t>
+          <t>-1.51</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -9709,7 +9709,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-114.35</t>
+          <t>-114.95</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9719,41 +9719,41 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>1184371.385281385</t>
+          <t>1182784.869596542</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>80518.0</t>
+          <t>47602.0</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>79913.6</t>
+          <t>74253.4</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>90895.1</t>
+          <t>86849.0</t>
         </is>
       </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>172580.1</t>
+          <t>165185.86</t>
         </is>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>-10981</t>
+          <t>-12595</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>-13972.3869447237</t>
+          <t>-13373.26661799914</t>
         </is>
       </c>
       <c r="BC22" t="n">
-        <v>-8113.93</v>
+        <v>-10078.1</v>
       </c>
       <c r="BD22" t="inlineStr">
         <is>
@@ -9772,7 +9772,7 @@
       </c>
       <c r="BG22" t="inlineStr">
         <is>
-          <t>-9.01</t>
+          <t>-9.40</t>
         </is>
       </c>
       <c r="BH22" t="inlineStr">
@@ -9797,7 +9797,7 @@
       </c>
       <c r="BL22" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="BM22" t="inlineStr">
@@ -9827,7 +9827,7 @@
       </c>
       <c r="BR22" t="inlineStr">
         <is>
-          <t>4.07</t>
+          <t>4.05</t>
         </is>
       </c>
       <c r="BS22" t="inlineStr">
@@ -9857,7 +9857,7 @@
       </c>
       <c r="BX22" t="inlineStr">
         <is>
-          <t>84.03</t>
+          <t>84.12</t>
         </is>
       </c>
       <c r="BY22" t="inlineStr">
@@ -9882,22 +9882,22 @@
       </c>
       <c r="CC22" t="inlineStr">
         <is>
-          <t>67.2</t>
+          <t>69.1</t>
         </is>
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>69.5</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>66.5</t>
+          <t>68.3</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>68.7</t>
+          <t>68.4</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
@@ -9929,12 +9929,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-2.29</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1578.0</t>
+          <t>1181.0</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -9944,7 +9944,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>68.7</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -9954,17 +9954,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-9.68</t>
+          <t>-10.81</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-2.24</t>
+          <t>-0.74</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>-20.39</t>
+          <t>-12.08</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -10029,7 +10029,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>-12.48</t>
+          <t>-11.58</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -10039,17 +10039,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>3.63</t>
+          <t>2.72</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>-3.24</t>
+          <t>2.87</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10060,77 +10060,77 @@
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>14</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>1335</t>
+          <t>895</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>17.5</t>
         </is>
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>5.83</t>
         </is>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>-2.41</t>
+          <t>-0.89</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>-3.24</t>
+          <t>-3.44</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>-4.54</t>
+          <t>-4.52</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>69.67999999999999</t>
+          <t>69.32</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>72.01</t>
+          <t>71.79</t>
         </is>
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>75.44</t>
+          <t>75.19</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>74.86</t>
+          <t>74.97</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>-19.92</t>
+          <t>-17.99</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>-1.66</t>
+          <t>-1.71</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>-1.38</t>
+          <t>-1.45</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -10140,7 +10140,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-113.71</t>
+          <t>-114.35</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10150,41 +10150,41 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>1184371.385281385</t>
+          <t>1182784.869596542</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>108331.0</t>
+          <t>80518.0</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>75637.8</t>
+          <t>79913.6</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>95013.8</t>
+          <t>90895.1</t>
         </is>
       </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>190051.54</t>
+          <t>172580.1</t>
         </is>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>-19376</t>
+          <t>-10981</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>-15037.56043283963</t>
+          <t>-13972.3869447237</t>
         </is>
       </c>
       <c r="BC23" t="n">
-        <v>-8544.9</v>
+        <v>-8113.93</v>
       </c>
       <c r="BD23" t="inlineStr">
         <is>
@@ -10203,7 +10203,7 @@
       </c>
       <c r="BG23" t="inlineStr">
         <is>
-          <t>-9.93</t>
+          <t>-9.01</t>
         </is>
       </c>
       <c r="BH23" t="inlineStr">
@@ -10228,7 +10228,7 @@
       </c>
       <c r="BL23" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="BM23" t="inlineStr">
@@ -10248,7 +10248,7 @@
       </c>
       <c r="BP23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ23" t="inlineStr">
@@ -10258,7 +10258,7 @@
       </c>
       <c r="BR23" t="inlineStr">
         <is>
-          <t>4.03</t>
+          <t>4.07</t>
         </is>
       </c>
       <c r="BS23" t="inlineStr">
@@ -10288,7 +10288,7 @@
       </c>
       <c r="BX23" t="inlineStr">
         <is>
-          <t>84.03</t>
+          <t>84.12</t>
         </is>
       </c>
       <c r="BY23" t="inlineStr">
@@ -10313,22 +10313,22 @@
       </c>
       <c r="CC23" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>67.2</t>
         </is>
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>70.2</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>66.5</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>68.7</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">
@@ -10360,12 +10360,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>-3.22</t>
+          <t>-1.06</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>13342.0</t>
+          <t>6296.0</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -10375,7 +10375,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>84.6</t>
+          <t>83.7</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -10390,12 +10390,12 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>-2.88</t>
+          <t>-4.0</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>-37.63</t>
+          <t>-18.50</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -10460,7 +10460,7 @@
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>-29.21</t>
+          <t>-29.96</t>
         </is>
       </c>
       <c r="X24" t="inlineStr">
@@ -10470,17 +10470,17 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>11.86</t>
+          <t>5.59</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>-2.54</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
@@ -10491,12 +10491,12 @@
       <c r="AC24" t="inlineStr"/>
       <c r="AD24" t="inlineStr">
         <is>
-          <t>129</t>
+          <t>76</t>
         </is>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
-          <t>13342</t>
+          <t>6296</t>
         </is>
       </c>
       <c r="AF24" t="inlineStr">
@@ -10506,62 +10506,62 @@
       </c>
       <c r="AG24" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
-          <t>-5.07</t>
+          <t>-4.21</t>
         </is>
       </c>
       <c r="AI24" t="inlineStr">
         <is>
-          <t>-4.14</t>
+          <t>-4.98</t>
         </is>
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>-12.22</t>
+          <t>-12.44</t>
         </is>
       </c>
       <c r="AK24" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="AL24" t="inlineStr">
         <is>
-          <t>89.12</t>
+          <t>87.38000000000001</t>
         </is>
       </c>
       <c r="AM24" t="inlineStr">
         <is>
-          <t>92.97</t>
+          <t>91.96</t>
         </is>
       </c>
       <c r="AN24" t="inlineStr">
         <is>
-          <t>105.91</t>
+          <t>105.02</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>102.73</t>
+          <t>102.93</t>
         </is>
       </c>
       <c r="AP24" t="inlineStr">
         <is>
-          <t>-3.45</t>
+          <t>-6.45</t>
         </is>
       </c>
       <c r="AQ24" t="inlineStr">
         <is>
-          <t>-4.77</t>
+          <t>-4.99</t>
         </is>
       </c>
       <c r="AR24" t="inlineStr">
         <is>
-          <t>-4.61</t>
+          <t>-4.69</t>
         </is>
       </c>
       <c r="AS24" t="inlineStr">
@@ -10571,7 +10571,7 @@
       </c>
       <c r="AT24" t="inlineStr">
         <is>
-          <t>-138.45</t>
+          <t>-139.08</t>
         </is>
       </c>
       <c r="AU24" t="inlineStr">
@@ -10581,41 +10581,41 @@
       </c>
       <c r="AV24" t="inlineStr">
         <is>
-          <t>1188956.751082251</t>
+          <t>1188385.067723343</t>
         </is>
       </c>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>1136155.0</t>
+          <t>528139.0</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>931861.8</t>
+          <t>854615.4</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr">
         <is>
-          <t>1494189.3</t>
+          <t>1048562.9</t>
         </is>
       </c>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>2699451.5</t>
+          <t>2414824.58</t>
         </is>
       </c>
       <c r="BA24" t="inlineStr">
         <is>
-          <t>-562327</t>
+          <t>-193947</t>
         </is>
       </c>
       <c r="BB24" t="inlineStr">
         <is>
-          <t>-156934.2348995581</t>
+          <t>-172876.6337917207</t>
         </is>
       </c>
       <c r="BC24" t="n">
-        <v>-233639.39</v>
+        <v>-260559.83</v>
       </c>
       <c r="BD24" t="inlineStr">
         <is>
@@ -10634,7 +10634,7 @@
       </c>
       <c r="BG24" t="inlineStr">
         <is>
-          <t>24.41</t>
+          <t>23.09</t>
         </is>
       </c>
       <c r="BH24" t="inlineStr">
@@ -10679,22 +10679,22 @@
       </c>
       <c r="BP24" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ24" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR24" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="BS24" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="BT24" t="inlineStr">
@@ -10704,7 +10704,7 @@
       </c>
       <c r="BU24" t="inlineStr">
         <is>
-          <t>90.97</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="BV24" t="inlineStr">
@@ -10719,12 +10719,12 @@
       </c>
       <c r="BX24" t="inlineStr">
         <is>
-          <t>84.03</t>
+          <t>84.12</t>
         </is>
       </c>
       <c r="BY24" t="inlineStr">
         <is>
-          <t>33077</t>
+          <t>32725</t>
         </is>
       </c>
       <c r="BZ24" t="inlineStr">
@@ -10744,22 +10744,22 @@
       </c>
       <c r="CC24" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>84.6</t>
         </is>
       </c>
       <c r="CD24" t="inlineStr">
         <is>
-          <t>88.8</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="CE24" t="inlineStr">
         <is>
-          <t>82.6</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="CF24" t="inlineStr">
         <is>
-          <t>84.6</t>
+          <t>83.7</t>
         </is>
       </c>
       <c r="CG24" t="inlineStr">
@@ -10791,12 +10791,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>-2.44</t>
+          <t>-3.22</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>9024.0</t>
+          <t>13342.0</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -10806,7 +10806,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>87.4</t>
+          <t>84.6</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -10816,17 +10816,17 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>-3.31</t>
+          <t>-1.08</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>-2.88</t>
+          <t>-4.0</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>-50.54</t>
+          <t>-37.63</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -10891,7 +10891,7 @@
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>-26.86</t>
+          <t>-29.21</t>
         </is>
       </c>
       <c r="X25" t="inlineStr">
@@ -10901,17 +10901,17 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>8.02</t>
+          <t>11.86</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>-1.93</t>
+          <t>-2.54</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
@@ -10922,12 +10922,12 @@
       <c r="AC25" t="inlineStr"/>
       <c r="AD25" t="inlineStr">
         <is>
-          <t>129</t>
+          <t>76</t>
         </is>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
-          <t>13342</t>
+          <t>6296</t>
         </is>
       </c>
       <c r="AF25" t="inlineStr">
@@ -10937,162 +10937,162 @@
       </c>
       <c r="AG25" t="inlineStr">
         <is>
-          <t>12.79</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
-          <t>-3.47</t>
+          <t>-5.07</t>
         </is>
       </c>
       <c r="AI25" t="inlineStr">
         <is>
-          <t>-3.54</t>
+          <t>-4.14</t>
         </is>
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>-12.14</t>
+          <t>-12.22</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
         <is>
-          <t>4.27</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="AL25" t="inlineStr">
         <is>
-          <t>90.53999999999999</t>
+          <t>89.12</t>
         </is>
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>93.86</t>
+          <t>92.97</t>
         </is>
       </c>
       <c r="AN25" t="inlineStr">
         <is>
-          <t>106.84</t>
+          <t>105.91</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>102.46</t>
+          <t>102.73</t>
         </is>
       </c>
       <c r="AP25" t="inlineStr">
         <is>
+          <t>-3.45</t>
+        </is>
+      </c>
+      <c r="AQ25" t="inlineStr">
+        <is>
+          <t>-4.77</t>
+        </is>
+      </c>
+      <c r="AR25" t="inlineStr">
+        <is>
+          <t>-4.61</t>
+        </is>
+      </c>
+      <c r="AS25" t="inlineStr">
+        <is>
+          <t>12.0</t>
+        </is>
+      </c>
+      <c r="AT25" t="inlineStr">
+        <is>
+          <t>-138.45</t>
+        </is>
+      </c>
+      <c r="AU25" t="inlineStr">
+        <is>
+          <t>2025/11/12</t>
+        </is>
+      </c>
+      <c r="AV25" t="inlineStr">
+        <is>
+          <t>1188385.067723343</t>
+        </is>
+      </c>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>1136155.0</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>931861.8</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr">
+        <is>
+          <t>1494189.3</t>
+        </is>
+      </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>2699451.5</t>
+        </is>
+      </c>
+      <c r="BA25" t="inlineStr">
+        <is>
+          <t>-562327</t>
+        </is>
+      </c>
+      <c r="BB25" t="inlineStr">
+        <is>
+          <t>-156934.2348995581</t>
+        </is>
+      </c>
+      <c r="BC25" t="n">
+        <v>-233639.39</v>
+      </c>
+      <c r="BD25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BE25" t="inlineStr">
+        <is>
+          <t>68.0</t>
+        </is>
+      </c>
+      <c r="BF25" t="inlineStr">
+        <is>
+          <t>2025/07/28</t>
+        </is>
+      </c>
+      <c r="BG25" t="inlineStr">
+        <is>
+          <t>24.41</t>
+        </is>
+      </c>
+      <c r="BH25" t="inlineStr">
+        <is>
+          <t>中光電</t>
+        </is>
+      </c>
+      <c r="BI25" t="inlineStr">
+        <is>
+          <t>中光電</t>
+        </is>
+      </c>
+      <c r="BJ25" t="inlineStr">
+        <is>
+          <t>光電業</t>
+        </is>
+      </c>
+      <c r="BK25" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BL25" t="inlineStr">
+        <is>
           <t>1.27</t>
         </is>
       </c>
-      <c r="AQ25" t="inlineStr">
-        <is>
-          <t>-4.52</t>
-        </is>
-      </c>
-      <c r="AR25" t="inlineStr">
-        <is>
-          <t>-4.57</t>
-        </is>
-      </c>
-      <c r="AS25" t="inlineStr">
-        <is>
-          <t>12.0</t>
-        </is>
-      </c>
-      <c r="AT25" t="inlineStr">
-        <is>
-          <t>-138.11</t>
-        </is>
-      </c>
-      <c r="AU25" t="inlineStr">
-        <is>
-          <t>2025/11/12</t>
-        </is>
-      </c>
-      <c r="AV25" t="inlineStr">
-        <is>
-          <t>1188956.751082251</t>
-        </is>
-      </c>
-      <c r="AW25" t="inlineStr">
-        <is>
-          <t>789636.0</t>
-        </is>
-      </c>
-      <c r="AX25" t="inlineStr">
-        <is>
-          <t>941766.6</t>
-        </is>
-      </c>
-      <c r="AY25" t="inlineStr">
-        <is>
-          <t>1903952.8</t>
-        </is>
-      </c>
-      <c r="AZ25" t="inlineStr">
-        <is>
-          <t>2858383.84</t>
-        </is>
-      </c>
-      <c r="BA25" t="inlineStr">
-        <is>
-          <t>-962186</t>
-        </is>
-      </c>
-      <c r="BB25" t="inlineStr">
-        <is>
-          <t>-142987.8434661122</t>
-        </is>
-      </c>
-      <c r="BC25" t="n">
-        <v>-251981.92</v>
-      </c>
-      <c r="BD25" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BE25" t="inlineStr">
-        <is>
-          <t>68.0</t>
-        </is>
-      </c>
-      <c r="BF25" t="inlineStr">
-        <is>
-          <t>2025/07/28</t>
-        </is>
-      </c>
-      <c r="BG25" t="inlineStr">
-        <is>
-          <t>28.53</t>
-        </is>
-      </c>
-      <c r="BH25" t="inlineStr">
-        <is>
-          <t>中光電</t>
-        </is>
-      </c>
-      <c r="BI25" t="inlineStr">
-        <is>
-          <t>中光電</t>
-        </is>
-      </c>
-      <c r="BJ25" t="inlineStr">
-        <is>
-          <t>光電業</t>
-        </is>
-      </c>
-      <c r="BK25" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BL25" t="inlineStr">
-        <is>
-          <t>1.27</t>
-        </is>
-      </c>
       <c r="BM25" t="inlineStr">
         <is>
           <t>10.52226299517467</t>
@@ -11110,22 +11110,22 @@
       </c>
       <c r="BP25" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ25" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR25" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="BS25" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="BT25" t="inlineStr">
@@ -11135,7 +11135,7 @@
       </c>
       <c r="BU25" t="inlineStr">
         <is>
-          <t>90.97</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="BV25" t="inlineStr">
@@ -11150,12 +11150,12 @@
       </c>
       <c r="BX25" t="inlineStr">
         <is>
-          <t>84.03</t>
+          <t>84.12</t>
         </is>
       </c>
       <c r="BY25" t="inlineStr">
         <is>
-          <t>33077</t>
+          <t>32725</t>
         </is>
       </c>
       <c r="BZ25" t="inlineStr">
@@ -11175,22 +11175,22 @@
       </c>
       <c r="CC25" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="CD25" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>88.8</t>
         </is>
       </c>
       <c r="CE25" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>82.6</t>
         </is>
       </c>
       <c r="CF25" t="inlineStr">
         <is>
-          <t>87.4</t>
+          <t>84.6</t>
         </is>
       </c>
       <c r="CG25" t="inlineStr">
@@ -11222,12 +11222,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>-2.21</t>
+          <t>-2.44</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>12279.0</t>
+          <t>9024.0</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -11237,7 +11237,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>89.6</t>
+          <t>87.4</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -11247,17 +11247,17 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>-5.91</t>
+          <t>-4.42</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>-2.88</t>
+          <t>-4.0</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>-50.98</t>
+          <t>-50.54</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -11322,7 +11322,7 @@
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>-25.02</t>
+          <t>-26.86</t>
         </is>
       </c>
       <c r="X26" t="inlineStr">
@@ -11332,17 +11332,17 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>10.91</t>
+          <t>8.02</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>-4.01</t>
+          <t>-1.93</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
@@ -11353,77 +11353,77 @@
       <c r="AC26" t="inlineStr"/>
       <c r="AD26" t="inlineStr">
         <is>
-          <t>129</t>
+          <t>76</t>
         </is>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
-          <t>13342</t>
+          <t>6296</t>
         </is>
       </c>
       <c r="AF26" t="inlineStr">
         <is>
-          <t>5.48</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG26" t="inlineStr">
         <is>
-          <t>30.76</t>
+          <t>12.79</t>
         </is>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
-          <t>-1.43</t>
+          <t>-3.47</t>
         </is>
       </c>
       <c r="AI26" t="inlineStr">
         <is>
-          <t>-4.01</t>
+          <t>-3.54</t>
         </is>
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>-11.89</t>
+          <t>-12.14</t>
         </is>
       </c>
       <c r="AK26" t="inlineStr">
         <is>
-          <t>5.27</t>
+          <t>4.27</t>
         </is>
       </c>
       <c r="AL26" t="inlineStr">
         <is>
-          <t>90.9</t>
+          <t>90.53999999999999</t>
         </is>
       </c>
       <c r="AM26" t="inlineStr">
         <is>
-          <t>94.7</t>
+          <t>93.86</t>
         </is>
       </c>
       <c r="AN26" t="inlineStr">
         <is>
-          <t>107.48</t>
+          <t>106.84</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>102.1</t>
+          <t>102.46</t>
         </is>
       </c>
       <c r="AP26" t="inlineStr">
         <is>
-          <t>3.95</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="AQ26" t="inlineStr">
         <is>
-          <t>-4.41</t>
+          <t>-4.52</t>
         </is>
       </c>
       <c r="AR26" t="inlineStr">
         <is>
-          <t>-4.59</t>
+          <t>-4.57</t>
         </is>
       </c>
       <c r="AS26" t="inlineStr">
@@ -11433,7 +11433,7 @@
       </c>
       <c r="AT26" t="inlineStr">
         <is>
-          <t>-138.24</t>
+          <t>-138.11</t>
         </is>
       </c>
       <c r="AU26" t="inlineStr">
@@ -11443,41 +11443,41 @@
       </c>
       <c r="AV26" t="inlineStr">
         <is>
-          <t>1188956.751082251</t>
+          <t>1188385.067723343</t>
         </is>
       </c>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>1116375.0</t>
+          <t>789636.0</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>997608.4</t>
+          <t>941766.6</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr">
         <is>
-          <t>2034960.6</t>
+          <t>1903952.8</t>
         </is>
       </c>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>2909917.96</t>
+          <t>2858383.84</t>
         </is>
       </c>
       <c r="BA26" t="inlineStr">
         <is>
-          <t>-1037352</t>
+          <t>-962186</t>
         </is>
       </c>
       <c r="BB26" t="inlineStr">
         <is>
-          <t>-123170.7379044272</t>
+          <t>-142987.8434661122</t>
         </is>
       </c>
       <c r="BC26" t="n">
-        <v>-232059.16</v>
+        <v>-251981.92</v>
       </c>
       <c r="BD26" t="inlineStr">
         <is>
@@ -11496,7 +11496,7 @@
       </c>
       <c r="BG26" t="inlineStr">
         <is>
-          <t>31.76</t>
+          <t>28.53</t>
         </is>
       </c>
       <c r="BH26" t="inlineStr">
@@ -11541,22 +11541,22 @@
       </c>
       <c r="BP26" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ26" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR26" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="BS26" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="BT26" t="inlineStr">
@@ -11566,7 +11566,7 @@
       </c>
       <c r="BU26" t="inlineStr">
         <is>
-          <t>90.97</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="BV26" t="inlineStr">
@@ -11581,12 +11581,12 @@
       </c>
       <c r="BX26" t="inlineStr">
         <is>
-          <t>84.03</t>
+          <t>84.12</t>
         </is>
       </c>
       <c r="BY26" t="inlineStr">
         <is>
-          <t>33077</t>
+          <t>32725</t>
         </is>
       </c>
       <c r="BZ26" t="inlineStr">
@@ -11606,22 +11606,22 @@
       </c>
       <c r="CC26" t="inlineStr">
         <is>
-          <t>90.5</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="CD26" t="inlineStr">
         <is>
-          <t>93.8</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="CE26" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="CF26" t="inlineStr">
         <is>
-          <t>89.6</t>
+          <t>87.4</t>
         </is>
       </c>
       <c r="CG26" t="inlineStr">
@@ -11653,12 +11653,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>-0.87</t>
+          <t>-2.21</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>7698.0</t>
+          <t>12279.0</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -11668,7 +11668,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>91.6</t>
+          <t>89.6</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -11678,17 +11678,17 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>-8.27</t>
+          <t>-7.05</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>-2.88</t>
+          <t>-4.0</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>-48.49</t>
+          <t>-50.98</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -11753,7 +11753,7 @@
       </c>
       <c r="W27" t="inlineStr">
         <is>
-          <t>-23.35</t>
+          <t>-25.02</t>
         </is>
       </c>
       <c r="X27" t="inlineStr">
@@ -11763,17 +11763,17 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>6.84</t>
+          <t>10.91</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>0.90</t>
+          <t>-4.01</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
@@ -11784,77 +11784,77 @@
       <c r="AC27" t="inlineStr"/>
       <c r="AD27" t="inlineStr">
         <is>
-          <t>129</t>
+          <t>76</t>
         </is>
       </c>
       <c r="AE27" t="inlineStr">
         <is>
-          <t>13342</t>
+          <t>6296</t>
         </is>
       </c>
       <c r="AF27" t="inlineStr">
         <is>
-          <t>32.88</t>
+          <t>5.48</t>
         </is>
       </c>
       <c r="AG27" t="inlineStr">
         <is>
-          <t>44.29</t>
+          <t>30.76</t>
         </is>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>-1.43</t>
         </is>
       </c>
       <c r="AI27" t="inlineStr">
         <is>
-          <t>-4.58</t>
+          <t>-4.01</t>
         </is>
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>-11.45</t>
+          <t>-11.89</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
         <is>
-          <t>6.20</t>
+          <t>5.27</t>
         </is>
       </c>
       <c r="AL27" t="inlineStr">
         <is>
-          <t>91.28</t>
+          <t>90.9</t>
         </is>
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>95.66</t>
+          <t>94.7</t>
         </is>
       </c>
       <c r="AN27" t="inlineStr">
         <is>
-          <t>108.04</t>
+          <t>107.48</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>101.72</t>
+          <t>102.1</t>
         </is>
       </c>
       <c r="AP27" t="inlineStr">
         <is>
-          <t>4.43</t>
+          <t>3.95</t>
         </is>
       </c>
       <c r="AQ27" t="inlineStr">
         <is>
-          <t>-4.43</t>
+          <t>-4.41</t>
         </is>
       </c>
       <c r="AR27" t="inlineStr">
         <is>
-          <t>-4.63</t>
+          <t>-4.59</t>
         </is>
       </c>
       <c r="AS27" t="inlineStr">
@@ -11864,7 +11864,7 @@
       </c>
       <c r="AT27" t="inlineStr">
         <is>
-          <t>-138.61</t>
+          <t>-138.24</t>
         </is>
       </c>
       <c r="AU27" t="inlineStr">
@@ -11874,41 +11874,41 @@
       </c>
       <c r="AV27" t="inlineStr">
         <is>
-          <t>1188956.751082251</t>
+          <t>1188385.067723343</t>
         </is>
       </c>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>702772.0</t>
+          <t>1116375.0</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>1032573.8</t>
+          <t>997608.4</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr">
         <is>
-          <t>2004573.2</t>
+          <t>2034960.6</t>
         </is>
       </c>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>3051992.38</t>
+          <t>2909917.96</t>
         </is>
       </c>
       <c r="BA27" t="inlineStr">
         <is>
-          <t>-971999</t>
+          <t>-1037352</t>
         </is>
       </c>
       <c r="BB27" t="inlineStr">
         <is>
-          <t>-103372.8434950374</t>
+          <t>-123170.7379044272</t>
         </is>
       </c>
       <c r="BC27" t="n">
-        <v>-230317.98</v>
+        <v>-232059.16</v>
       </c>
       <c r="BD27" t="inlineStr">
         <is>
@@ -11927,7 +11927,7 @@
       </c>
       <c r="BG27" t="inlineStr">
         <is>
-          <t>34.71</t>
+          <t>31.76</t>
         </is>
       </c>
       <c r="BH27" t="inlineStr">
@@ -11972,22 +11972,22 @@
       </c>
       <c r="BP27" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
         </is>
       </c>
       <c r="BQ27" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BR27" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="BS27" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="BT27" t="inlineStr">
@@ -11997,7 +11997,7 @@
       </c>
       <c r="BU27" t="inlineStr">
         <is>
-          <t>90.97</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="BV27" t="inlineStr">
@@ -12012,12 +12012,12 @@
       </c>
       <c r="BX27" t="inlineStr">
         <is>
-          <t>84.03</t>
+          <t>84.12</t>
         </is>
       </c>
       <c r="BY27" t="inlineStr">
         <is>
-          <t>33077</t>
+          <t>32725</t>
         </is>
       </c>
       <c r="BZ27" t="inlineStr">
@@ -12037,22 +12037,22 @@
       </c>
       <c r="CC27" t="inlineStr">
         <is>
-          <t>91.6</t>
+          <t>90.5</t>
         </is>
       </c>
       <c r="CD27" t="inlineStr">
         <is>
-          <t>92.2</t>
+          <t>93.8</t>
         </is>
       </c>
       <c r="CE27" t="inlineStr">
         <is>
-          <t>90.2</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="CF27" t="inlineStr">
         <is>
-          <t>91.6</t>
+          <t>89.6</t>
         </is>
       </c>
       <c r="CG27" t="inlineStr">
@@ -12084,12 +12084,12 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>-0.87</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>9952.0</t>
+          <t>7698.0</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -12099,7 +12099,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>92.4</t>
+          <t>91.6</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -12109,17 +12109,17 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>-9.22</t>
+          <t>-9.44</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>-2.88</t>
+          <t>-4.0</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>-38.84</t>
+          <t>-48.49</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -12184,7 +12184,7 @@
       </c>
       <c r="W28" t="inlineStr">
         <is>
-          <t>-22.68</t>
+          <t>-23.35</t>
         </is>
       </c>
       <c r="X28" t="inlineStr">
@@ -12194,17 +12194,17 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>8.84</t>
+          <t>6.84</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>0.90</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
@@ -12215,77 +12215,77 @@
       <c r="AC28" t="inlineStr"/>
       <c r="AD28" t="inlineStr">
         <is>
-          <t>129</t>
+          <t>76</t>
         </is>
       </c>
       <c r="AE28" t="inlineStr">
         <is>
-          <t>13342</t>
+          <t>6296</t>
         </is>
       </c>
       <c r="AF28" t="inlineStr">
         <is>
-          <t>53.93</t>
+          <t>32.88</t>
         </is>
       </c>
       <c r="AG28" t="inlineStr">
         <is>
-          <t>39.33</t>
+          <t>44.29</t>
         </is>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="AI28" t="inlineStr">
         <is>
-          <t>-4.40</t>
+          <t>-4.58</t>
         </is>
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>-11.44</t>
+          <t>-11.45</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
         <is>
-          <t>7.27</t>
+          <t>6.20</t>
         </is>
       </c>
       <c r="AL28" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>91.28</t>
         </is>
       </c>
       <c r="AM28" t="inlineStr">
         <is>
-          <t>96.23</t>
+          <t>95.66</t>
         </is>
       </c>
       <c r="AN28" t="inlineStr">
         <is>
-          <t>108.66</t>
+          <t>108.04</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>101.3</t>
+          <t>101.72</t>
         </is>
       </c>
       <c r="AP28" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>4.43</t>
         </is>
       </c>
       <c r="AQ28" t="inlineStr">
         <is>
-          <t>-4.59</t>
+          <t>-4.43</t>
         </is>
       </c>
       <c r="AR28" t="inlineStr">
         <is>
-          <t>-4.68</t>
+          <t>-4.63</t>
         </is>
       </c>
       <c r="AS28" t="inlineStr">
@@ -12295,7 +12295,7 @@
       </c>
       <c r="AT28" t="inlineStr">
         <is>
-          <t>-139.04</t>
+          <t>-138.61</t>
         </is>
       </c>
       <c r="AU28" t="inlineStr">
@@ -12305,41 +12305,41 @@
       </c>
       <c r="AV28" t="inlineStr">
         <is>
-          <t>1188956.751082251</t>
+          <t>1188385.067723343</t>
         </is>
       </c>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>914371.0</t>
+          <t>702772.0</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>1242510.4</t>
+          <t>1032573.8</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr">
         <is>
-          <t>2031632.2</t>
+          <t>2004573.2</t>
         </is>
       </c>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>3137803.82</t>
+          <t>3051992.38</t>
         </is>
       </c>
       <c r="BA28" t="inlineStr">
         <is>
-          <t>-789121</t>
+          <t>-971999</t>
         </is>
       </c>
       <c r="BB28" t="inlineStr">
         <is>
-          <t>-80291.90875880011</t>
+          <t>-103372.8434950374</t>
         </is>
       </c>
       <c r="BC28" t="n">
-        <v>-175290.35</v>
+        <v>-230317.98</v>
       </c>
       <c r="BD28" t="inlineStr">
         <is>
@@ -12358,7 +12358,7 @@
       </c>
       <c r="BG28" t="inlineStr">
         <is>
-          <t>35.88</t>
+          <t>34.71</t>
         </is>
       </c>
       <c r="BH28" t="inlineStr">
@@ -12403,22 +12403,22 @@
       </c>
       <c r="BP28" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ28" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR28" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="BS28" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="BT28" t="inlineStr">
@@ -12428,7 +12428,7 @@
       </c>
       <c r="BU28" t="inlineStr">
         <is>
-          <t>90.97</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="BV28" t="inlineStr">
@@ -12443,12 +12443,12 @@
       </c>
       <c r="BX28" t="inlineStr">
         <is>
-          <t>84.03</t>
+          <t>84.12</t>
         </is>
       </c>
       <c r="BY28" t="inlineStr">
         <is>
-          <t>33077</t>
+          <t>32725</t>
         </is>
       </c>
       <c r="BZ28" t="inlineStr">
@@ -12468,22 +12468,22 @@
       </c>
       <c r="CC28" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>91.6</t>
         </is>
       </c>
       <c r="CD28" t="inlineStr">
         <is>
-          <t>93.4</t>
+          <t>92.2</t>
         </is>
       </c>
       <c r="CE28" t="inlineStr">
         <is>
-          <t>90.5</t>
+          <t>90.2</t>
         </is>
       </c>
       <c r="CF28" t="inlineStr">
         <is>
-          <t>92.4</t>
+          <t>91.6</t>
         </is>
       </c>
       <c r="CG28" t="inlineStr">
@@ -12515,12 +12515,12 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>2.78</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>12899.0</t>
+          <t>9952.0</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -12530,7 +12530,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>91.7</t>
+          <t>92.4</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -12540,17 +12540,17 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>-8.39</t>
+          <t>-10.39</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>-2.88</t>
+          <t>-4.0</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>-5.80</t>
+          <t>-38.84</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -12615,7 +12615,7 @@
       </c>
       <c r="W29" t="inlineStr">
         <is>
-          <t>-23.26</t>
+          <t>-22.68</t>
         </is>
       </c>
       <c r="X29" t="inlineStr">
@@ -12625,17 +12625,17 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>11.46</t>
+          <t>8.84</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
@@ -12646,77 +12646,77 @@
       <c r="AC29" t="inlineStr"/>
       <c r="AD29" t="inlineStr">
         <is>
-          <t>129</t>
+          <t>76</t>
         </is>
       </c>
       <c r="AE29" t="inlineStr">
         <is>
-          <t>13342</t>
+          <t>6296</t>
         </is>
       </c>
       <c r="AF29" t="inlineStr">
         <is>
-          <t>46.07</t>
+          <t>53.93</t>
         </is>
       </c>
       <c r="AG29" t="inlineStr">
         <is>
-          <t>35.96</t>
+          <t>39.33</t>
         </is>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
-          <t>-1.21</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="AI29" t="inlineStr">
         <is>
-          <t>-4.18</t>
+          <t>-4.40</t>
         </is>
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>-11.33</t>
+          <t>-11.44</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
         <is>
-          <t>8.29</t>
+          <t>7.27</t>
         </is>
       </c>
       <c r="AL29" t="inlineStr">
         <is>
-          <t>92.82000000000001</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>96.86</t>
+          <t>96.23</t>
         </is>
       </c>
       <c r="AN29" t="inlineStr">
         <is>
-          <t>109.24</t>
+          <t>108.66</t>
         </is>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>100.87</t>
+          <t>101.3</t>
         </is>
       </c>
       <c r="AP29" t="inlineStr">
         <is>
-          <t>-2.43</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="AQ29" t="inlineStr">
         <is>
-          <t>-4.82</t>
+          <t>-4.59</t>
         </is>
       </c>
       <c r="AR29" t="inlineStr">
         <is>
-          <t>-4.71</t>
+          <t>-4.68</t>
         </is>
       </c>
       <c r="AS29" t="inlineStr">
@@ -12726,7 +12726,7 @@
       </c>
       <c r="AT29" t="inlineStr">
         <is>
-          <t>-139.23</t>
+          <t>-139.04</t>
         </is>
       </c>
       <c r="AU29" t="inlineStr">
@@ -12736,41 +12736,41 @@
       </c>
       <c r="AV29" t="inlineStr">
         <is>
-          <t>1188956.751082251</t>
+          <t>1188385.067723343</t>
         </is>
       </c>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>1185679.0</t>
+          <t>914371.0</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>2056516.8</t>
+          <t>1242510.4</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr">
         <is>
-          <t>2183123.9</t>
+          <t>2031632.2</t>
         </is>
       </c>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>3222248.96</t>
+          <t>3137803.82</t>
         </is>
       </c>
       <c r="BA29" t="inlineStr">
         <is>
-          <t>-126607</t>
+          <t>-789121</t>
         </is>
       </c>
       <c r="BB29" t="inlineStr">
         <is>
-          <t>-63019.46568749043</t>
+          <t>-80291.90875880011</t>
         </is>
       </c>
       <c r="BC29" t="n">
-        <v>-113090.38</v>
+        <v>-175290.35</v>
       </c>
       <c r="BD29" t="inlineStr">
         <is>
@@ -12789,7 +12789,7 @@
       </c>
       <c r="BG29" t="inlineStr">
         <is>
-          <t>34.85</t>
+          <t>35.88</t>
         </is>
       </c>
       <c r="BH29" t="inlineStr">
@@ -12834,7 +12834,7 @@
       </c>
       <c r="BP29" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ29" t="inlineStr">
@@ -12844,12 +12844,12 @@
       </c>
       <c r="BR29" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="BS29" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="BT29" t="inlineStr">
@@ -12859,7 +12859,7 @@
       </c>
       <c r="BU29" t="inlineStr">
         <is>
-          <t>90.97</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="BV29" t="inlineStr">
@@ -12874,12 +12874,12 @@
       </c>
       <c r="BX29" t="inlineStr">
         <is>
-          <t>84.03</t>
+          <t>84.12</t>
         </is>
       </c>
       <c r="BY29" t="inlineStr">
         <is>
-          <t>33077</t>
+          <t>32725</t>
         </is>
       </c>
       <c r="BZ29" t="inlineStr">
@@ -12899,7 +12899,7 @@
       </c>
       <c r="CC29" t="inlineStr">
         <is>
-          <t>89.9</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="CD29" t="inlineStr">
@@ -12909,12 +12909,12 @@
       </c>
       <c r="CE29" t="inlineStr">
         <is>
-          <t>89.1</t>
+          <t>90.5</t>
         </is>
       </c>
       <c r="CF29" t="inlineStr">
         <is>
-          <t>91.7</t>
+          <t>92.4</t>
         </is>
       </c>
       <c r="CG29" t="inlineStr">
@@ -12946,12 +12946,12 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>-2.54</t>
+          <t>2.78</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>11977.0</t>
+          <t>12899.0</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -12961,7 +12961,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>91.7</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -12971,17 +12971,17 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>-5.44</t>
+          <t>-9.56</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>-2.88</t>
+          <t>-4.0</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>23.54</t>
+          <t>-5.80</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -13046,7 +13046,7 @@
       </c>
       <c r="W30" t="inlineStr">
         <is>
-          <t>-25.36</t>
+          <t>-23.26</t>
         </is>
       </c>
       <c r="X30" t="inlineStr">
@@ -13056,17 +13056,17 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>10.64</t>
+          <t>11.46</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>-1.44</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
@@ -13077,77 +13077,77 @@
       <c r="AC30" t="inlineStr"/>
       <c r="AD30" t="inlineStr">
         <is>
-          <t>129</t>
+          <t>76</t>
         </is>
       </c>
       <c r="AE30" t="inlineStr">
         <is>
-          <t>13342</t>
+          <t>6296</t>
         </is>
       </c>
       <c r="AF30" t="inlineStr">
         <is>
-          <t>17.98</t>
+          <t>46.07</t>
         </is>
       </c>
       <c r="AG30" t="inlineStr">
         <is>
-          <t>37.6</t>
+          <t>35.96</t>
         </is>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
-          <t>-4.62</t>
+          <t>-1.21</t>
         </is>
       </c>
       <c r="AI30" t="inlineStr">
         <is>
-          <t>-4.67</t>
+          <t>-4.18</t>
         </is>
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>-10.71</t>
+          <t>-11.33</t>
         </is>
       </c>
       <c r="AK30" t="inlineStr">
         <is>
-          <t>9.39</t>
+          <t>8.29</t>
         </is>
       </c>
       <c r="AL30" t="inlineStr">
         <is>
-          <t>93.52000000000001</t>
+          <t>92.82000000000001</t>
         </is>
       </c>
       <c r="AM30" t="inlineStr">
         <is>
-          <t>98.1</t>
+          <t>96.86</t>
         </is>
       </c>
       <c r="AN30" t="inlineStr">
         <is>
-          <t>109.87</t>
+          <t>109.24</t>
         </is>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>100.44</t>
+          <t>100.87</t>
         </is>
       </c>
       <c r="AP30" t="inlineStr">
         <is>
-          <t>-6.22</t>
+          <t>-2.43</t>
         </is>
       </c>
       <c r="AQ30" t="inlineStr">
         <is>
-          <t>-4.97</t>
+          <t>-4.82</t>
         </is>
       </c>
       <c r="AR30" t="inlineStr">
         <is>
-          <t>-4.68</t>
+          <t>-4.71</t>
         </is>
       </c>
       <c r="AS30" t="inlineStr">
@@ -13157,7 +13157,7 @@
       </c>
       <c r="AT30" t="inlineStr">
         <is>
-          <t>-138.99</t>
+          <t>-139.23</t>
         </is>
       </c>
       <c r="AU30" t="inlineStr">
@@ -13167,41 +13167,41 @@
       </c>
       <c r="AV30" t="inlineStr">
         <is>
-          <t>1188956.751082251</t>
+          <t>1188385.067723343</t>
         </is>
       </c>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>1068845.0</t>
+          <t>1185679.0</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>2866139.0</t>
+          <t>2056516.8</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr">
         <is>
-          <t>2320044.7</t>
+          <t>2183123.9</t>
         </is>
       </c>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>3369664.12</t>
+          <t>3222248.96</t>
         </is>
       </c>
       <c r="BA30" t="inlineStr">
         <is>
-          <t>546094</t>
+          <t>-126607</t>
         </is>
       </c>
       <c r="BB30" t="inlineStr">
         <is>
-          <t>-53915.6621966216</t>
+          <t>-63019.46568749043</t>
         </is>
       </c>
       <c r="BC30" t="n">
-        <v>-49263.07</v>
+        <v>-113090.38</v>
       </c>
       <c r="BD30" t="inlineStr">
         <is>
@@ -13220,7 +13220,7 @@
       </c>
       <c r="BG30" t="inlineStr">
         <is>
-          <t>31.18</t>
+          <t>34.85</t>
         </is>
       </c>
       <c r="BH30" t="inlineStr">
@@ -13265,22 +13265,22 @@
       </c>
       <c r="BP30" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ30" t="inlineStr">
         <is>
-          <t>價跌量縮</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BR30" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="BS30" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="BT30" t="inlineStr">
@@ -13290,7 +13290,7 @@
       </c>
       <c r="BU30" t="inlineStr">
         <is>
-          <t>90.97</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="BV30" t="inlineStr">
@@ -13305,12 +13305,12 @@
       </c>
       <c r="BX30" t="inlineStr">
         <is>
-          <t>84.03</t>
+          <t>84.12</t>
         </is>
       </c>
       <c r="BY30" t="inlineStr">
         <is>
-          <t>33077</t>
+          <t>32725</t>
         </is>
       </c>
       <c r="BZ30" t="inlineStr">
@@ -13330,22 +13330,22 @@
       </c>
       <c r="CC30" t="inlineStr">
         <is>
-          <t>90.6</t>
+          <t>89.9</t>
         </is>
       </c>
       <c r="CD30" t="inlineStr">
         <is>
+          <t>93.4</t>
+        </is>
+      </c>
+      <c r="CE30" t="inlineStr">
+        <is>
+          <t>89.1</t>
+        </is>
+      </c>
+      <c r="CF30" t="inlineStr">
+        <is>
           <t>91.7</t>
-        </is>
-      </c>
-      <c r="CE30" t="inlineStr">
-        <is>
-          <t>88.0</t>
-        </is>
-      </c>
-      <c r="CF30" t="inlineStr">
-        <is>
-          <t>89.2</t>
         </is>
       </c>
       <c r="CG30" t="inlineStr">
@@ -13377,12 +13377,12 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>-3.89</t>
+          <t>-2.54</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>14012.0</t>
+          <t>11977.0</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -13392,7 +13392,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>91.5</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -13402,17 +13402,17 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>-8.16</t>
+          <t>-6.57</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>-2.88</t>
+          <t>-4.0</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>32.19</t>
+          <t>23.54</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -13477,7 +13477,7 @@
       </c>
       <c r="W31" t="inlineStr">
         <is>
-          <t>-23.43</t>
+          <t>-25.36</t>
         </is>
       </c>
       <c r="X31" t="inlineStr">
@@ -13487,17 +13487,17 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>12.45</t>
+          <t>10.64</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>-3.59</t>
+          <t>-1.44</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
@@ -13508,77 +13508,77 @@
       <c r="AC31" t="inlineStr"/>
       <c r="AD31" t="inlineStr">
         <is>
-          <t>129</t>
+          <t>76</t>
         </is>
       </c>
       <c r="AE31" t="inlineStr">
         <is>
-          <t>13342</t>
+          <t>6296</t>
         </is>
       </c>
       <c r="AF31" t="inlineStr">
         <is>
-          <t>43.82</t>
+          <t>17.98</t>
         </is>
       </c>
       <c r="AG31" t="inlineStr">
         <is>
-          <t>51.52</t>
+          <t>37.6</t>
         </is>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
-          <t>-2.54</t>
+          <t>-4.62</t>
         </is>
       </c>
       <c r="AI31" t="inlineStr">
         <is>
-          <t>-5.57</t>
+          <t>-4.67</t>
         </is>
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>-10.03</t>
+          <t>-10.71</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
         <is>
-          <t>10.48</t>
+          <t>9.39</t>
         </is>
       </c>
       <c r="AL31" t="inlineStr">
         <is>
-          <t>93.88</t>
+          <t>93.52000000000001</t>
         </is>
       </c>
       <c r="AM31" t="inlineStr">
         <is>
-          <t>99.42</t>
+          <t>98.1</t>
         </is>
       </c>
       <c r="AN31" t="inlineStr">
         <is>
-          <t>110.5</t>
+          <t>109.87</t>
         </is>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>100.02</t>
+          <t>100.44</t>
         </is>
       </c>
       <c r="AP31" t="inlineStr">
         <is>
-          <t>-4.91</t>
+          <t>-6.22</t>
         </is>
       </c>
       <c r="AQ31" t="inlineStr">
         <is>
-          <t>-4.83</t>
+          <t>-4.97</t>
         </is>
       </c>
       <c r="AR31" t="inlineStr">
         <is>
-          <t>-4.61</t>
+          <t>-4.68</t>
         </is>
       </c>
       <c r="AS31" t="inlineStr">
@@ -13588,7 +13588,7 @@
       </c>
       <c r="AT31" t="inlineStr">
         <is>
-          <t>-138.38</t>
+          <t>-138.99</t>
         </is>
       </c>
       <c r="AU31" t="inlineStr">
@@ -13598,41 +13598,41 @@
       </c>
       <c r="AV31" t="inlineStr">
         <is>
-          <t>1188956.751082251</t>
+          <t>1188385.067723343</t>
         </is>
       </c>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>1291202.0</t>
+          <t>1068845.0</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>3072312.8</t>
+          <t>2866139.0</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr">
         <is>
-          <t>2324244.4</t>
+          <t>2320044.7</t>
         </is>
       </c>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>3618472.68</t>
+          <t>3369664.12</t>
         </is>
       </c>
       <c r="BA31" t="inlineStr">
         <is>
-          <t>748068</t>
+          <t>546094</t>
         </is>
       </c>
       <c r="BB31" t="inlineStr">
         <is>
-          <t>-54761.58804141716</t>
+          <t>-53915.6621966216</t>
         </is>
       </c>
       <c r="BC31" t="n">
-        <v>56196.13</v>
+        <v>-49263.07</v>
       </c>
       <c r="BD31" t="inlineStr">
         <is>
@@ -13651,7 +13651,7 @@
       </c>
       <c r="BG31" t="inlineStr">
         <is>
-          <t>34.56</t>
+          <t>31.18</t>
         </is>
       </c>
       <c r="BH31" t="inlineStr">
@@ -13696,7 +13696,7 @@
       </c>
       <c r="BP31" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ31" t="inlineStr">
@@ -13706,12 +13706,12 @@
       </c>
       <c r="BR31" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="BS31" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="BT31" t="inlineStr">
@@ -13721,7 +13721,7 @@
       </c>
       <c r="BU31" t="inlineStr">
         <is>
-          <t>90.97</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="BV31" t="inlineStr">
@@ -13736,12 +13736,12 @@
       </c>
       <c r="BX31" t="inlineStr">
         <is>
-          <t>84.03</t>
+          <t>84.12</t>
         </is>
       </c>
       <c r="BY31" t="inlineStr">
         <is>
-          <t>33077</t>
+          <t>32725</t>
         </is>
       </c>
       <c r="BZ31" t="inlineStr">
@@ -13761,22 +13761,22 @@
       </c>
       <c r="CC31" t="inlineStr">
         <is>
-          <t>95.2</t>
+          <t>90.6</t>
         </is>
       </c>
       <c r="CD31" t="inlineStr">
         <is>
-          <t>95.8</t>
+          <t>91.7</t>
         </is>
       </c>
       <c r="CE31" t="inlineStr">
         <is>
-          <t>90.5</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="CF31" t="inlineStr">
         <is>
-          <t>91.5</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="CG31" t="inlineStr">
@@ -13808,12 +13808,12 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>-1.35</t>
+          <t>-3.89</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>18516.0</t>
+          <t>14012.0</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -13823,7 +13823,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>95.2</t>
+          <t>91.5</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -13833,17 +13833,17 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>-12.53</t>
+          <t>-9.32</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>-2.88</t>
+          <t>-4.0</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>29.85</t>
+          <t>32.19</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -13908,7 +13908,7 @@
       </c>
       <c r="W32" t="inlineStr">
         <is>
-          <t>-20.33</t>
+          <t>-23.43</t>
         </is>
       </c>
       <c r="X32" t="inlineStr">
@@ -13918,17 +13918,17 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>16.45</t>
+          <t>12.45</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>-3.59</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
@@ -13939,77 +13939,77 @@
       <c r="AC32" t="inlineStr"/>
       <c r="AD32" t="inlineStr">
         <is>
-          <t>129</t>
+          <t>76</t>
         </is>
       </c>
       <c r="AE32" t="inlineStr">
         <is>
-          <t>13342</t>
+          <t>6296</t>
         </is>
       </c>
       <c r="AF32" t="inlineStr">
         <is>
-          <t>51.01</t>
+          <t>43.82</t>
         </is>
       </c>
       <c r="AG32" t="inlineStr">
         <is>
-          <t>53.91</t>
+          <t>51.52</t>
         </is>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
-          <t>2.26</t>
+          <t>-2.54</t>
         </is>
       </c>
       <c r="AI32" t="inlineStr">
         <is>
-          <t>-7.57</t>
+          <t>-5.57</t>
         </is>
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>-9.2</t>
+          <t>-10.03</t>
         </is>
       </c>
       <c r="AK32" t="inlineStr">
         <is>
-          <t>11.40</t>
+          <t>10.48</t>
         </is>
       </c>
       <c r="AL32" t="inlineStr">
         <is>
-          <t>93.1</t>
+          <t>93.88</t>
         </is>
       </c>
       <c r="AM32" t="inlineStr">
         <is>
-          <t>100.72</t>
+          <t>99.42</t>
         </is>
       </c>
       <c r="AN32" t="inlineStr">
         <is>
-          <t>110.93</t>
+          <t>110.5</t>
         </is>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>99.57</t>
+          <t>100.02</t>
         </is>
       </c>
       <c r="AP32" t="inlineStr">
         <is>
-          <t>-5.95</t>
+          <t>-4.91</t>
         </is>
       </c>
       <c r="AQ32" t="inlineStr">
         <is>
-          <t>-4.82</t>
+          <t>-4.83</t>
         </is>
       </c>
       <c r="AR32" t="inlineStr">
         <is>
-          <t>-4.55</t>
+          <t>-4.61</t>
         </is>
       </c>
       <c r="AS32" t="inlineStr">
@@ -14019,7 +14019,7 @@
       </c>
       <c r="AT32" t="inlineStr">
         <is>
-          <t>-137.91</t>
+          <t>-138.38</t>
         </is>
       </c>
       <c r="AU32" t="inlineStr">
@@ -14029,41 +14029,41 @@
       </c>
       <c r="AV32" t="inlineStr">
         <is>
-          <t>1188956.751082251</t>
+          <t>1188385.067723343</t>
         </is>
       </c>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>1752455.0</t>
+          <t>1291202.0</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>2976572.6</t>
+          <t>3072312.8</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr">
         <is>
-          <t>2292309.0</t>
+          <t>2324244.4</t>
         </is>
       </c>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>3718207.26</t>
+          <t>3618472.68</t>
         </is>
       </c>
       <c r="BA32" t="inlineStr">
         <is>
-          <t>684263</t>
+          <t>748068</t>
         </is>
       </c>
       <c r="BB32" t="inlineStr">
         <is>
-          <t>-74935.71899780657</t>
+          <t>-54761.58804141716</t>
         </is>
       </c>
       <c r="BC32" t="n">
-        <v>181021.17</v>
+        <v>56196.13</v>
       </c>
       <c r="BD32" t="inlineStr">
         <is>
@@ -14082,7 +14082,7 @@
       </c>
       <c r="BG32" t="inlineStr">
         <is>
-          <t>40.00</t>
+          <t>34.56</t>
         </is>
       </c>
       <c r="BH32" t="inlineStr">
@@ -14127,22 +14127,22 @@
       </c>
       <c r="BP32" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ32" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR32" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="BS32" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="BT32" t="inlineStr">
@@ -14152,7 +14152,7 @@
       </c>
       <c r="BU32" t="inlineStr">
         <is>
-          <t>90.97</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="BV32" t="inlineStr">
@@ -14167,12 +14167,12 @@
       </c>
       <c r="BX32" t="inlineStr">
         <is>
-          <t>84.03</t>
+          <t>84.12</t>
         </is>
       </c>
       <c r="BY32" t="inlineStr">
         <is>
-          <t>33077</t>
+          <t>32725</t>
         </is>
       </c>
       <c r="BZ32" t="inlineStr">
@@ -14192,22 +14192,22 @@
       </c>
       <c r="CC32" t="inlineStr">
         <is>
-          <t>96.2</t>
+          <t>95.2</t>
         </is>
       </c>
       <c r="CD32" t="inlineStr">
         <is>
-          <t>96.2</t>
+          <t>95.8</t>
         </is>
       </c>
       <c r="CE32" t="inlineStr">
         <is>
-          <t>93.5</t>
+          <t>90.5</t>
         </is>
       </c>
       <c r="CF32" t="inlineStr">
         <is>
-          <t>95.2</t>
+          <t>91.5</t>
         </is>
       </c>
       <c r="CG32" t="inlineStr">
@@ -14239,12 +14239,12 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>-1.35</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>51617.0</t>
+          <t>18516.0</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -14254,7 +14254,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>96.5</t>
+          <t>95.2</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -14264,17 +14264,17 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>-14.07</t>
+          <t>-13.74</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>-2.88</t>
+          <t>-4.0</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>24.75</t>
+          <t>29.85</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -14339,7 +14339,7 @@
       </c>
       <c r="W33" t="inlineStr">
         <is>
-          <t>-19.25</t>
+          <t>-20.33</t>
         </is>
       </c>
       <c r="X33" t="inlineStr">
@@ -14349,17 +14349,17 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>45.86</t>
+          <t>16.45</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2.24</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
@@ -14370,77 +14370,77 @@
       <c r="AC33" t="inlineStr"/>
       <c r="AD33" t="inlineStr">
         <is>
-          <t>129</t>
+          <t>76</t>
         </is>
       </c>
       <c r="AE33" t="inlineStr">
         <is>
-          <t>13342</t>
+          <t>6296</t>
         </is>
       </c>
       <c r="AF33" t="inlineStr">
         <is>
-          <t>59.73</t>
+          <t>51.01</t>
         </is>
       </c>
       <c r="AG33" t="inlineStr">
         <is>
-          <t>43.82</t>
+          <t>53.91</t>
         </is>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
-          <t>5.26</t>
+          <t>2.26</t>
         </is>
       </c>
       <c r="AI33" t="inlineStr">
         <is>
-          <t>-10.04</t>
+          <t>-7.57</t>
         </is>
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>-8.26</t>
+          <t>-9.2</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
         <is>
-          <t>12.13</t>
+          <t>11.40</t>
         </is>
       </c>
       <c r="AL33" t="inlineStr">
         <is>
-          <t>91.67999999999999</t>
+          <t>93.1</t>
         </is>
       </c>
       <c r="AM33" t="inlineStr">
         <is>
-          <t>101.91</t>
+          <t>100.72</t>
         </is>
       </c>
       <c r="AN33" t="inlineStr">
         <is>
-          <t>111.08</t>
+          <t>110.93</t>
         </is>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>99.07</t>
+          <t>99.57</t>
         </is>
       </c>
       <c r="AP33" t="inlineStr">
         <is>
-          <t>-14.05</t>
+          <t>-5.95</t>
         </is>
       </c>
       <c r="AQ33" t="inlineStr">
         <is>
-          <t>-5.11</t>
+          <t>-4.82</t>
         </is>
       </c>
       <c r="AR33" t="inlineStr">
         <is>
-          <t>-4.48</t>
+          <t>-4.55</t>
         </is>
       </c>
       <c r="AS33" t="inlineStr">
@@ -14450,7 +14450,7 @@
       </c>
       <c r="AT33" t="inlineStr">
         <is>
-          <t>-137.35</t>
+          <t>-137.91</t>
         </is>
       </c>
       <c r="AU33" t="inlineStr">
@@ -14460,41 +14460,41 @@
       </c>
       <c r="AV33" t="inlineStr">
         <is>
-          <t>1188956.751082251</t>
+          <t>1188385.067723343</t>
         </is>
       </c>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>4984403.0</t>
+          <t>1752455.0</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>2820754.0</t>
+          <t>2976572.6</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr">
         <is>
-          <t>2261178.2</t>
+          <t>2292309.0</t>
         </is>
       </c>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>3861738.8</t>
+          <t>3718207.26</t>
         </is>
       </c>
       <c r="BA33" t="inlineStr">
         <is>
-          <t>559575</t>
+          <t>684263</t>
         </is>
       </c>
       <c r="BB33" t="inlineStr">
         <is>
-          <t>-121473.3345341895</t>
+          <t>-74935.71899780657</t>
         </is>
       </c>
       <c r="BC33" t="n">
-        <v>303457.64</v>
+        <v>181021.17</v>
       </c>
       <c r="BD33" t="inlineStr">
         <is>
@@ -14513,7 +14513,7 @@
       </c>
       <c r="BG33" t="inlineStr">
         <is>
-          <t>41.91</t>
+          <t>40.00</t>
         </is>
       </c>
       <c r="BH33" t="inlineStr">
@@ -14558,7 +14558,7 @@
       </c>
       <c r="BP33" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ33" t="inlineStr">
@@ -14568,12 +14568,12 @@
       </c>
       <c r="BR33" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="BS33" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="BT33" t="inlineStr">
@@ -14583,7 +14583,7 @@
       </c>
       <c r="BU33" t="inlineStr">
         <is>
-          <t>90.97</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="BV33" t="inlineStr">
@@ -14598,12 +14598,12 @@
       </c>
       <c r="BX33" t="inlineStr">
         <is>
-          <t>84.03</t>
+          <t>84.12</t>
         </is>
       </c>
       <c r="BY33" t="inlineStr">
         <is>
-          <t>33077</t>
+          <t>32725</t>
         </is>
       </c>
       <c r="BZ33" t="inlineStr">
@@ -14623,22 +14623,22 @@
       </c>
       <c r="CC33" t="inlineStr">
         <is>
-          <t>92.2</t>
+          <t>96.2</t>
         </is>
       </c>
       <c r="CD33" t="inlineStr">
         <is>
-          <t>99.5</t>
+          <t>96.2</t>
         </is>
       </c>
       <c r="CE33" t="inlineStr">
         <is>
-          <t>91.6</t>
+          <t>93.5</t>
         </is>
       </c>
       <c r="CF33" t="inlineStr">
         <is>
-          <t>96.5</t>
+          <t>95.2</t>
         </is>
       </c>
       <c r="CG33" t="inlineStr">
@@ -14670,12 +14670,12 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>4.59</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>54542.0</t>
+          <t>51617.0</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -14685,7 +14685,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>95.2</t>
+          <t>96.5</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -14695,17 +14695,17 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>-12.53</t>
+          <t>-15.29</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>-2.88</t>
+          <t>-4.0</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>25.23</t>
+          <t>24.75</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -14770,7 +14770,7 @@
       </c>
       <c r="W34" t="inlineStr">
         <is>
-          <t>-20.33</t>
+          <t>-19.25</t>
         </is>
       </c>
       <c r="X34" t="inlineStr">
@@ -14780,17 +14780,17 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>48.46</t>
+          <t>45.86</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>-0.47</t>
+          <t>2.24</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
@@ -14801,77 +14801,77 @@
       <c r="AC34" t="inlineStr"/>
       <c r="AD34" t="inlineStr">
         <is>
-          <t>129</t>
+          <t>76</t>
         </is>
       </c>
       <c r="AE34" t="inlineStr">
         <is>
-          <t>13342</t>
+          <t>6296</t>
         </is>
       </c>
       <c r="AF34" t="inlineStr">
         <is>
-          <t>51.01</t>
+          <t>59.73</t>
         </is>
       </c>
       <c r="AG34" t="inlineStr">
         <is>
-          <t>23.91</t>
+          <t>43.82</t>
         </is>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
-          <t>5.59</t>
+          <t>5.26</t>
         </is>
       </c>
       <c r="AI34" t="inlineStr">
         <is>
-          <t>-12.37</t>
+          <t>-10.04</t>
         </is>
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>-7.53</t>
+          <t>-8.26</t>
         </is>
       </c>
       <c r="AK34" t="inlineStr">
         <is>
-          <t>12.89</t>
+          <t>12.13</t>
         </is>
       </c>
       <c r="AL34" t="inlineStr">
         <is>
-          <t>90.16</t>
+          <t>91.67999999999999</t>
         </is>
       </c>
       <c r="AM34" t="inlineStr">
         <is>
-          <t>102.88</t>
+          <t>101.91</t>
         </is>
       </c>
       <c r="AN34" t="inlineStr">
         <is>
-          <t>111.26</t>
+          <t>111.08</t>
         </is>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>98.56</t>
+          <t>99.07</t>
         </is>
       </c>
       <c r="AP34" t="inlineStr">
         <is>
-          <t>-28.15</t>
+          <t>-14.05</t>
         </is>
       </c>
       <c r="AQ34" t="inlineStr">
         <is>
-          <t>-5.54</t>
+          <t>-5.11</t>
         </is>
       </c>
       <c r="AR34" t="inlineStr">
         <is>
-          <t>-4.32</t>
+          <t>-4.48</t>
         </is>
       </c>
       <c r="AS34" t="inlineStr">
@@ -14881,7 +14881,7 @@
       </c>
       <c r="AT34" t="inlineStr">
         <is>
-          <t>-136.04</t>
+          <t>-137.35</t>
         </is>
       </c>
       <c r="AU34" t="inlineStr">
@@ -14891,41 +14891,41 @@
       </c>
       <c r="AV34" t="inlineStr">
         <is>
-          <t>1188956.751082251</t>
+          <t>1188385.067723343</t>
         </is>
       </c>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>5233790.0</t>
+          <t>4984403.0</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>2309731.0</t>
+          <t>2820754.0</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr">
         <is>
-          <t>1844425.0</t>
+          <t>2261178.2</t>
         </is>
       </c>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>3953879.86</t>
+          <t>3861738.8</t>
         </is>
       </c>
       <c r="BA34" t="inlineStr">
         <is>
-          <t>465306</t>
+          <t>559575</t>
         </is>
       </c>
       <c r="BB34" t="inlineStr">
         <is>
-          <t>-198733.5113556983</t>
+          <t>-121473.3345341895</t>
         </is>
       </c>
       <c r="BC34" t="n">
-        <v>121248.97</v>
+        <v>303457.64</v>
       </c>
       <c r="BD34" t="inlineStr">
         <is>
@@ -14944,7 +14944,7 @@
       </c>
       <c r="BG34" t="inlineStr">
         <is>
-          <t>40.00</t>
+          <t>41.91</t>
         </is>
       </c>
       <c r="BH34" t="inlineStr">
@@ -14989,7 +14989,7 @@
       </c>
       <c r="BP34" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BQ34" t="inlineStr">
@@ -14999,12 +14999,12 @@
       </c>
       <c r="BR34" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="BS34" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="BT34" t="inlineStr">
@@ -15014,7 +15014,7 @@
       </c>
       <c r="BU34" t="inlineStr">
         <is>
-          <t>90.97</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="BV34" t="inlineStr">
@@ -15029,12 +15029,12 @@
       </c>
       <c r="BX34" t="inlineStr">
         <is>
-          <t>84.03</t>
+          <t>84.12</t>
         </is>
       </c>
       <c r="BY34" t="inlineStr">
         <is>
-          <t>33077</t>
+          <t>32725</t>
         </is>
       </c>
       <c r="BZ34" t="inlineStr">
@@ -15054,22 +15054,22 @@
       </c>
       <c r="CC34" t="inlineStr">
         <is>
+          <t>92.2</t>
+        </is>
+      </c>
+      <c r="CD34" t="inlineStr">
+        <is>
+          <t>99.5</t>
+        </is>
+      </c>
+      <c r="CE34" t="inlineStr">
+        <is>
           <t>91.6</t>
         </is>
       </c>
-      <c r="CD34" t="inlineStr">
-        <is>
-          <t>99.5</t>
-        </is>
-      </c>
-      <c r="CE34" t="inlineStr">
-        <is>
-          <t>91.5</t>
-        </is>
-      </c>
       <c r="CF34" t="inlineStr">
         <is>
-          <t>95.2</t>
+          <t>96.5</t>
         </is>
       </c>
       <c r="CG34" t="inlineStr">

--- a/Result/checksun_type/整體解決方案.xlsx
+++ b/Result/checksun_type/整體解決方案.xlsx
@@ -873,7 +873,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1057,15 +1057,11 @@
           <t>20.51</t>
         </is>
       </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>21.47</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>22.97</t>
-        </is>
+      <c r="AM2" t="n">
+        <v>21.47</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>22.97</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
@@ -1112,20 +1108,16 @@
           <t>10516.0</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>6553.2</t>
-        </is>
+      <c r="AX2" t="n">
+        <v>6553.2</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
           <t>6621.7</t>
         </is>
       </c>
-      <c r="AZ2" t="inlineStr">
-        <is>
-          <t>7055.1</t>
-        </is>
+      <c r="AZ2" t="n">
+        <v>7055.1</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
@@ -1142,8 +1134,10 @@
           <t>451.8476631753983</t>
         </is>
       </c>
-      <c r="BD2" t="n">
-        <v>10516</v>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>10516.0</t>
+        </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1309,7 +1303,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1493,15 +1487,11 @@
           <t>20.33</t>
         </is>
       </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>21.54</t>
-        </is>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>23.05</t>
-        </is>
+      <c r="AM3" t="n">
+        <v>21.54</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>23.05</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
@@ -1548,20 +1538,16 @@
           <t>5964.0</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>5690.8</t>
-        </is>
+      <c r="AX3" t="n">
+        <v>5690.8</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
           <t>6322.5</t>
         </is>
       </c>
-      <c r="AZ3" t="inlineStr">
-        <is>
-          <t>7140.5</t>
-        </is>
+      <c r="AZ3" t="n">
+        <v>7140.5</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
@@ -1578,8 +1564,10 @@
           <t>126.0489308279157</t>
         </is>
       </c>
-      <c r="BD3" t="n">
-        <v>5964</v>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>5964.0</t>
+        </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1745,7 +1733,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1929,15 +1917,11 @@
           <t>20.37</t>
         </is>
       </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>21.66</t>
-        </is>
-      </c>
-      <c r="AN4" t="inlineStr">
-        <is>
-          <t>23.16</t>
-        </is>
+      <c r="AM4" t="n">
+        <v>21.66</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>23.16</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
@@ -1984,20 +1968,16 @@
           <t>7205.0</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>5879.8</t>
-        </is>
+      <c r="AX4" t="n">
+        <v>5879.8</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
           <t>5999.1</t>
         </is>
       </c>
-      <c r="AZ4" t="inlineStr">
-        <is>
-          <t>7311.98</t>
-        </is>
+      <c r="AZ4" t="n">
+        <v>7311.98</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
@@ -2014,8 +1994,10 @@
           <t>143.8347085162286</t>
         </is>
       </c>
-      <c r="BD4" t="n">
-        <v>7205</v>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>7205.0</t>
+        </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2181,7 +2163,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2365,15 +2347,11 @@
           <t>20.5</t>
         </is>
       </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>21.8</t>
-        </is>
-      </c>
-      <c r="AN5" t="inlineStr">
-        <is>
-          <t>23.27</t>
-        </is>
+      <c r="AM5" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>23.27</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
@@ -2420,20 +2398,16 @@
           <t>7576.0</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>6293.0</t>
-        </is>
+      <c r="AX5" t="n">
+        <v>6293</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
           <t>5560.0</t>
         </is>
       </c>
-      <c r="AZ5" t="inlineStr">
-        <is>
-          <t>7585.92</t>
-        </is>
+      <c r="AZ5" t="n">
+        <v>7585.92</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
@@ -2450,8 +2424,10 @@
           <t>31.14172276681074</t>
         </is>
       </c>
-      <c r="BD5" t="n">
-        <v>7576</v>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>7576.0</t>
+        </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2617,7 +2593,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2801,15 +2777,11 @@
           <t>20.82</t>
         </is>
       </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>21.99</t>
-        </is>
-      </c>
-      <c r="AN6" t="inlineStr">
-        <is>
-          <t>23.38</t>
-        </is>
+      <c r="AM6" t="n">
+        <v>21.99</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>23.38</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
@@ -2856,20 +2828,16 @@
           <t>1505.0</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>6001.4</t>
-        </is>
+      <c r="AX6" t="n">
+        <v>6001.4</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
           <t>5125.2</t>
         </is>
       </c>
-      <c r="AZ6" t="inlineStr">
-        <is>
-          <t>7728.1</t>
-        </is>
+      <c r="AZ6" t="n">
+        <v>7728.1</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
@@ -2886,8 +2854,10 @@
           <t>-170.7104612597432</t>
         </is>
       </c>
-      <c r="BD6" t="n">
-        <v>1505</v>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>1505.0</t>
+        </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -3053,7 +3023,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3237,15 +3207,11 @@
           <t>21.2</t>
         </is>
       </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>22.14</t>
-        </is>
-      </c>
-      <c r="AN7" t="inlineStr">
-        <is>
-          <t>23.48</t>
-        </is>
+      <c r="AM7" t="n">
+        <v>22.14</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>23.48</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
@@ -3292,20 +3258,16 @@
           <t>6204.0</t>
         </is>
       </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>6690.2</t>
-        </is>
+      <c r="AX7" t="n">
+        <v>6690.2</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
           <t>5272.2</t>
         </is>
       </c>
-      <c r="AZ7" t="inlineStr">
-        <is>
-          <t>8019.26</t>
-        </is>
+      <c r="AZ7" t="n">
+        <v>8019.26</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
@@ -3322,8 +3284,10 @@
           <t>197.4903637473135</t>
         </is>
       </c>
-      <c r="BD7" t="n">
-        <v>6204</v>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>6204.0</t>
+        </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3489,7 +3453,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3673,15 +3637,11 @@
           <t>21.64</t>
         </is>
       </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>22.28</t>
-        </is>
-      </c>
-      <c r="AN8" t="inlineStr">
-        <is>
-          <t>23.6</t>
-        </is>
+      <c r="AM8" t="n">
+        <v>22.28</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>23.6</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
@@ -3728,20 +3688,16 @@
           <t>6909.0</t>
         </is>
       </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>6954.2</t>
-        </is>
+      <c r="AX8" t="n">
+        <v>6954.2</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
           <t>5247.3</t>
         </is>
       </c>
-      <c r="AZ8" t="inlineStr">
-        <is>
-          <t>8221.3</t>
-        </is>
+      <c r="AZ8" t="n">
+        <v>8221.299999999999</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
@@ -3758,8 +3714,10 @@
           <t>212.9740293378472</t>
         </is>
       </c>
-      <c r="BD8" t="n">
-        <v>6909</v>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>6909.0</t>
+        </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3925,7 +3883,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -4109,15 +4067,11 @@
           <t>21.92</t>
         </is>
       </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>22.38</t>
-        </is>
-      </c>
-      <c r="AN9" t="inlineStr">
-        <is>
-          <t>23.71</t>
-        </is>
+      <c r="AM9" t="n">
+        <v>22.38</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>23.71</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
@@ -4164,20 +4118,16 @@
           <t>9271.0</t>
         </is>
       </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>6118.4</t>
-        </is>
+      <c r="AX9" t="n">
+        <v>6118.4</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
           <t>5174.1</t>
         </is>
       </c>
-      <c r="AZ9" t="inlineStr">
-        <is>
-          <t>8359.92</t>
-        </is>
+      <c r="AZ9" t="n">
+        <v>8359.92</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
@@ -4194,8 +4144,10 @@
           <t>151.9516219908282</t>
         </is>
       </c>
-      <c r="BD9" t="n">
-        <v>9271</v>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>9271.0</t>
+        </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4361,7 +4313,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4545,15 +4497,11 @@
           <t>22.07</t>
         </is>
       </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>22.46</t>
-        </is>
-      </c>
-      <c r="AN10" t="inlineStr">
-        <is>
-          <t>23.8</t>
-        </is>
+      <c r="AM10" t="n">
+        <v>22.46</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>23.8</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
@@ -4600,20 +4548,16 @@
           <t>6118.0</t>
         </is>
       </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>4827.0</t>
-        </is>
+      <c r="AX10" t="n">
+        <v>4827</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
           <t>4621.6</t>
         </is>
       </c>
-      <c r="AZ10" t="inlineStr">
-        <is>
-          <t>8529.86</t>
-        </is>
+      <c r="AZ10" t="n">
+        <v>8529.860000000001</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
@@ -4630,8 +4574,10 @@
           <t>-193.7215178617271</t>
         </is>
       </c>
-      <c r="BD10" t="n">
-        <v>6118</v>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>6118.0</t>
+        </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4797,7 +4743,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -4981,15 +4927,11 @@
           <t>22.18</t>
         </is>
       </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>22.52</t>
-        </is>
-      </c>
-      <c r="AN11" t="inlineStr">
-        <is>
-          <t>23.89</t>
-        </is>
+      <c r="AM11" t="n">
+        <v>22.52</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>23.89</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
@@ -5036,20 +4978,16 @@
           <t>4949.0</t>
         </is>
       </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>4249.0</t>
-        </is>
+      <c r="AX11" t="n">
+        <v>4249</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
           <t>4420.6</t>
         </is>
       </c>
-      <c r="AZ11" t="inlineStr">
-        <is>
-          <t>8793.4</t>
-        </is>
+      <c r="AZ11" t="n">
+        <v>8793.4</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
@@ -5066,8 +5004,10 @@
           <t>-342.8002348703167</t>
         </is>
       </c>
-      <c r="BD11" t="n">
-        <v>4949</v>
+      <c r="BD11" t="inlineStr">
+        <is>
+          <t>4949.0</t>
+        </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5233,7 +5173,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5417,15 +5357,11 @@
           <t>22.07</t>
         </is>
       </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>22.52</t>
-        </is>
-      </c>
-      <c r="AN12" t="inlineStr">
-        <is>
-          <t>23.99</t>
-        </is>
+      <c r="AM12" t="n">
+        <v>22.52</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>23.99</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
@@ -5472,20 +5408,16 @@
           <t>7524.0</t>
         </is>
       </c>
-      <c r="AX12" t="inlineStr">
-        <is>
-          <t>3854.2</t>
-        </is>
+      <c r="AX12" t="n">
+        <v>3854.2</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
           <t>4442.4</t>
         </is>
       </c>
-      <c r="AZ12" t="inlineStr">
-        <is>
-          <t>9497.76</t>
-        </is>
+      <c r="AZ12" t="n">
+        <v>9497.76</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
@@ -5502,8 +5434,10 @@
           <t>-418.2769650657883</t>
         </is>
       </c>
-      <c r="BD12" t="n">
-        <v>7524</v>
+      <c r="BD12" t="inlineStr">
+        <is>
+          <t>7524.0</t>
+        </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5669,7 +5603,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -5853,15 +5787,11 @@
           <t>62.06</t>
         </is>
       </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>65.53</t>
-        </is>
-      </c>
-      <c r="AN13" t="inlineStr">
-        <is>
-          <t>71.05</t>
-        </is>
+      <c r="AM13" t="n">
+        <v>65.53</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>71.05</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
@@ -5908,20 +5838,16 @@
           <t>64137.0</t>
         </is>
       </c>
-      <c r="AX13" t="inlineStr">
-        <is>
-          <t>56110.8</t>
-        </is>
+      <c r="AX13" t="n">
+        <v>56110.8</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
           <t>66072.1</t>
         </is>
       </c>
-      <c r="AZ13" t="inlineStr">
-        <is>
-          <t>131071.42</t>
-        </is>
+      <c r="AZ13" t="n">
+        <v>131071.42</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
@@ -5938,8 +5864,10 @@
           <t>-5046.292096739809</t>
         </is>
       </c>
-      <c r="BD13" t="n">
-        <v>64137</v>
+      <c r="BD13" t="inlineStr">
+        <is>
+          <t>64137.0</t>
+        </is>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
@@ -6105,7 +6033,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -6289,15 +6217,11 @@
           <t>61.86</t>
         </is>
       </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>65.9</t>
-        </is>
-      </c>
-      <c r="AN14" t="inlineStr">
-        <is>
-          <t>71.32</t>
-        </is>
+      <c r="AM14" t="n">
+        <v>65.90000000000001</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>71.31999999999999</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
@@ -6344,20 +6268,16 @@
           <t>40116.0</t>
         </is>
       </c>
-      <c r="AX14" t="inlineStr">
-        <is>
-          <t>54394.0</t>
-        </is>
+      <c r="AX14" t="n">
+        <v>54394</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
           <t>68178.5</t>
         </is>
       </c>
-      <c r="AZ14" t="inlineStr">
-        <is>
-          <t>133670.02</t>
-        </is>
+      <c r="AZ14" t="n">
+        <v>133670.02</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
@@ -6374,8 +6294,10 @@
           <t>-6045.859222618266</t>
         </is>
       </c>
-      <c r="BD14" t="n">
-        <v>40116</v>
+      <c r="BD14" t="inlineStr">
+        <is>
+          <t>40116.0</t>
+        </is>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
@@ -6541,7 +6463,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -6725,15 +6647,11 @@
           <t>61.88</t>
         </is>
       </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>66.34</t>
-        </is>
-      </c>
-      <c r="AN15" t="inlineStr">
-        <is>
-          <t>71.65</t>
-        </is>
+      <c r="AM15" t="n">
+        <v>66.34</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>71.65000000000001</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
@@ -6780,20 +6698,16 @@
           <t>66567.0</t>
         </is>
       </c>
-      <c r="AX15" t="inlineStr">
-        <is>
-          <t>63069.8</t>
-        </is>
+      <c r="AX15" t="n">
+        <v>63069.8</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
           <t>68814.2</t>
         </is>
       </c>
-      <c r="AZ15" t="inlineStr">
-        <is>
-          <t>136082.22</t>
-        </is>
+      <c r="AZ15" t="n">
+        <v>136082.22</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
@@ -6810,8 +6724,10 @@
           <t>-4684.210144493976</t>
         </is>
       </c>
-      <c r="BD15" t="n">
-        <v>66567</v>
+      <c r="BD15" t="inlineStr">
+        <is>
+          <t>66567.0</t>
+        </is>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
@@ -6977,7 +6893,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -7161,15 +7077,11 @@
           <t>62.21999999999999</t>
         </is>
       </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>66.79</t>
-        </is>
-      </c>
-      <c r="AN16" t="inlineStr">
-        <is>
-          <t>71.95</t>
-        </is>
+      <c r="AM16" t="n">
+        <v>66.79000000000001</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>71.95</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
@@ -7216,20 +7128,16 @@
           <t>68921.0</t>
         </is>
       </c>
-      <c r="AX16" t="inlineStr">
-        <is>
-          <t>61337.2</t>
-        </is>
+      <c r="AX16" t="n">
+        <v>61337.2</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
           <t>67514.0</t>
         </is>
       </c>
-      <c r="AZ16" t="inlineStr">
-        <is>
-          <t>137842.84</t>
-        </is>
+      <c r="AZ16" t="n">
+        <v>137842.84</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
@@ -7246,8 +7154,10 @@
           <t>-5405.739670584488</t>
         </is>
       </c>
-      <c r="BD16" t="n">
-        <v>68921</v>
+      <c r="BD16" t="inlineStr">
+        <is>
+          <t>68921.0</t>
+        </is>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
@@ -7413,7 +7323,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -7597,15 +7507,11 @@
           <t>63.0</t>
         </is>
       </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>67.37</t>
-        </is>
-      </c>
-      <c r="AN17" t="inlineStr">
-        <is>
-          <t>72.27</t>
-        </is>
+      <c r="AM17" t="n">
+        <v>67.37</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>72.27</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
@@ -7652,20 +7558,16 @@
           <t>40813.0</t>
         </is>
       </c>
-      <c r="AX17" t="inlineStr">
-        <is>
-          <t>60219.6</t>
-        </is>
+      <c r="AX17" t="n">
+        <v>60219.6</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
           <t>67201.9</t>
         </is>
       </c>
-      <c r="AZ17" t="inlineStr">
-        <is>
-          <t>138237.78</t>
-        </is>
+      <c r="AZ17" t="n">
+        <v>138237.78</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
@@ -7682,8 +7584,10 @@
           <t>-6495.648291050042</t>
         </is>
       </c>
-      <c r="BD17" t="n">
-        <v>40813</v>
+      <c r="BD17" t="inlineStr">
+        <is>
+          <t>40813.0</t>
+        </is>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
@@ -7849,7 +7753,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -8033,15 +7937,11 @@
           <t>63.46</t>
         </is>
       </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>67.95</t>
-        </is>
-      </c>
-      <c r="AN18" t="inlineStr">
-        <is>
-          <t>72.53</t>
-        </is>
+      <c r="AM18" t="n">
+        <v>67.95</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>72.53</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
@@ -8088,20 +7988,16 @@
           <t>55553.0</t>
         </is>
       </c>
-      <c r="AX18" t="inlineStr">
-        <is>
-          <t>76033.4</t>
-        </is>
+      <c r="AX18" t="n">
+        <v>76033.39999999999</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
           <t>67880.8</t>
         </is>
       </c>
-      <c r="AZ18" t="inlineStr">
-        <is>
-          <t>139203.84</t>
-        </is>
+      <c r="AZ18" t="n">
+        <v>139203.84</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
@@ -8118,8 +8014,10 @@
           <t>-4809.101738463331</t>
         </is>
       </c>
-      <c r="BD18" t="n">
-        <v>55553</v>
+      <c r="BD18" t="inlineStr">
+        <is>
+          <t>55553.0</t>
+        </is>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
@@ -8285,7 +8183,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -8469,15 +8367,11 @@
           <t>64.3</t>
         </is>
       </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>68.54</t>
-        </is>
-      </c>
-      <c r="AN19" t="inlineStr">
-        <is>
-          <t>72.82</t>
-        </is>
+      <c r="AM19" t="n">
+        <v>68.54000000000001</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>72.81999999999999</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
@@ -8524,20 +8418,16 @@
           <t>83495.0</t>
         </is>
       </c>
-      <c r="AX19" t="inlineStr">
-        <is>
-          <t>81963.0</t>
-        </is>
+      <c r="AX19" t="n">
+        <v>81963</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
           <t>70377.3</t>
         </is>
       </c>
-      <c r="AZ19" t="inlineStr">
-        <is>
-          <t>140394.08</t>
-        </is>
+      <c r="AZ19" t="n">
+        <v>140394.08</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
@@ -8554,8 +8444,10 @@
           <t>-3807.281601251496</t>
         </is>
       </c>
-      <c r="BD19" t="n">
-        <v>83495</v>
+      <c r="BD19" t="inlineStr">
+        <is>
+          <t>83495.0</t>
+        </is>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
@@ -8721,7 +8613,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -8905,15 +8797,11 @@
           <t>65.36</t>
         </is>
       </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>69.04</t>
-        </is>
-      </c>
-      <c r="AN20" t="inlineStr">
-        <is>
-          <t>73.11</t>
-        </is>
+      <c r="AM20" t="n">
+        <v>69.04000000000001</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>73.11</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
@@ -8960,20 +8848,16 @@
           <t>57904.0</t>
         </is>
       </c>
-      <c r="AX20" t="inlineStr">
-        <is>
-          <t>74558.6</t>
-        </is>
+      <c r="AX20" t="n">
+        <v>74558.60000000001</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
           <t>72860.9</t>
         </is>
       </c>
-      <c r="AZ20" t="inlineStr">
-        <is>
-          <t>140798.66</t>
-        </is>
+      <c r="AZ20" t="n">
+        <v>140798.66</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
@@ -8990,8 +8874,10 @@
           <t>-5233.921348047021</t>
         </is>
       </c>
-      <c r="BD20" t="n">
-        <v>57904</v>
+      <c r="BD20" t="inlineStr">
+        <is>
+          <t>57904.0</t>
+        </is>
       </c>
       <c r="BE20" t="inlineStr">
         <is>
@@ -9157,7 +9043,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -9341,15 +9227,11 @@
           <t>66.03999999999999</t>
         </is>
       </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>69.52</t>
-        </is>
-      </c>
-      <c r="AN21" t="inlineStr">
-        <is>
-          <t>73.37</t>
-        </is>
+      <c r="AM21" t="n">
+        <v>69.52</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>73.37</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
@@ -9396,20 +9278,16 @@
           <t>63333.0</t>
         </is>
       </c>
-      <c r="AX21" t="inlineStr">
-        <is>
-          <t>73690.8</t>
-        </is>
+      <c r="AX21" t="n">
+        <v>73690.8</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
           <t>76070.6</t>
         </is>
       </c>
-      <c r="AZ21" t="inlineStr">
-        <is>
-          <t>142749.4</t>
-        </is>
+      <c r="AZ21" t="n">
+        <v>142749.4</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
@@ -9426,8 +9304,10 @@
           <t>-4343.159509610385</t>
         </is>
       </c>
-      <c r="BD21" t="n">
-        <v>63333</v>
+      <c r="BD21" t="inlineStr">
+        <is>
+          <t>63333.0</t>
+        </is>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
@@ -9593,7 +9473,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -9777,15 +9657,11 @@
           <t>66.62</t>
         </is>
       </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>70.02</t>
-        </is>
-      </c>
-      <c r="AN22" t="inlineStr">
-        <is>
-          <t>73.62</t>
-        </is>
+      <c r="AM22" t="n">
+        <v>70.02</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>73.62</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
@@ -9832,20 +9708,16 @@
           <t>119882.0</t>
         </is>
       </c>
-      <c r="AX22" t="inlineStr">
-        <is>
-          <t>74184.2</t>
-        </is>
+      <c r="AX22" t="n">
+        <v>74184.2</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
           <t>74218.8</t>
         </is>
       </c>
-      <c r="AZ22" t="inlineStr">
-        <is>
-          <t>146686.82</t>
-        </is>
+      <c r="AZ22" t="n">
+        <v>146686.82</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
@@ -9862,8 +9734,10 @@
           <t>-3497.208329357687</t>
         </is>
       </c>
-      <c r="BD22" t="n">
-        <v>119882</v>
+      <c r="BD22" t="inlineStr">
+        <is>
+          <t>119882.0</t>
+        </is>
       </c>
       <c r="BE22" t="inlineStr">
         <is>
@@ -10029,7 +9903,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -10213,15 +10087,11 @@
           <t>67.26</t>
         </is>
       </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>70.4</t>
-        </is>
-      </c>
-      <c r="AN23" t="inlineStr">
-        <is>
-          <t>73.91</t>
-        </is>
+      <c r="AM23" t="n">
+        <v>70.40000000000001</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>73.91</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
@@ -10268,20 +10138,16 @@
           <t>85201.0</t>
         </is>
       </c>
-      <c r="AX23" t="inlineStr">
-        <is>
-          <t>59728.2</t>
-        </is>
+      <c r="AX23" t="n">
+        <v>59728.2</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
           <t>69820.9</t>
         </is>
       </c>
-      <c r="AZ23" t="inlineStr">
-        <is>
-          <t>148731.72</t>
-        </is>
+      <c r="AZ23" t="n">
+        <v>148731.72</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
@@ -10298,8 +10164,10 @@
           <t>-8222.627774376771</t>
         </is>
       </c>
-      <c r="BD23" t="n">
-        <v>85201</v>
+      <c r="BD23" t="inlineStr">
+        <is>
+          <t>85201.0</t>
+        </is>
       </c>
       <c r="BE23" t="inlineStr">
         <is>
@@ -10465,7 +10333,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -10649,15 +10517,11 @@
           <t>88.82</t>
         </is>
       </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>89.97</t>
-        </is>
-      </c>
-      <c r="AN24" t="inlineStr">
-        <is>
-          <t>101.54</t>
-        </is>
+      <c r="AM24" t="n">
+        <v>89.97</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>101.54</v>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
@@ -10704,20 +10568,16 @@
           <t>1496761.0</t>
         </is>
       </c>
-      <c r="AX24" t="inlineStr">
-        <is>
-          <t>1187172.6</t>
-        </is>
+      <c r="AX24" t="n">
+        <v>1187172.6</v>
       </c>
       <c r="AY24" t="inlineStr">
         <is>
           <t>1020894.0</t>
         </is>
       </c>
-      <c r="AZ24" t="inlineStr">
-        <is>
-          <t>2058125.44</t>
-        </is>
+      <c r="AZ24" t="n">
+        <v>2058125.44</v>
       </c>
       <c r="BA24" t="inlineStr">
         <is>
@@ -10734,8 +10594,10 @@
           <t>-65418.32762892707</t>
         </is>
       </c>
-      <c r="BD24" t="n">
-        <v>1496761</v>
+      <c r="BD24" t="inlineStr">
+        <is>
+          <t>1496761.0</t>
+        </is>
       </c>
       <c r="BE24" t="inlineStr">
         <is>
@@ -10901,7 +10763,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -11085,15 +10947,11 @@
           <t>85.55999999999999</t>
         </is>
       </c>
-      <c r="AM25" t="inlineStr">
-        <is>
-          <t>89.42</t>
-        </is>
-      </c>
-      <c r="AN25" t="inlineStr">
-        <is>
-          <t>101.99</t>
-        </is>
+      <c r="AM25" t="n">
+        <v>89.42</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>101.99</v>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
@@ -11140,20 +10998,16 @@
           <t>2115557.0</t>
         </is>
       </c>
-      <c r="AX25" t="inlineStr">
-        <is>
-          <t>993448.2</t>
-        </is>
+      <c r="AX25" t="n">
+        <v>993448.2</v>
       </c>
       <c r="AY25" t="inlineStr">
         <is>
           <t>962655.0</t>
         </is>
       </c>
-      <c r="AZ25" t="inlineStr">
-        <is>
-          <t>2145653.4</t>
-        </is>
+      <c r="AZ25" t="n">
+        <v>2145653.4</v>
       </c>
       <c r="BA25" t="inlineStr">
         <is>
@@ -11170,8 +11024,10 @@
           <t>-98962.45567306643</t>
         </is>
       </c>
-      <c r="BD25" t="n">
-        <v>2115557</v>
+      <c r="BD25" t="inlineStr">
+        <is>
+          <t>2115557.0</t>
+        </is>
       </c>
       <c r="BE25" t="inlineStr">
         <is>
@@ -11337,7 +11193,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -11521,15 +11377,11 @@
           <t>84.28</t>
         </is>
       </c>
-      <c r="AM26" t="inlineStr">
-        <is>
-          <t>89.54</t>
-        </is>
-      </c>
-      <c r="AN26" t="inlineStr">
-        <is>
-          <t>102.79</t>
-        </is>
+      <c r="AM26" t="n">
+        <v>89.54000000000001</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>102.79</v>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
@@ -11576,20 +11428,16 @@
           <t>1396196.0</t>
         </is>
       </c>
-      <c r="AX26" t="inlineStr">
-        <is>
-          <t>797567.8</t>
-        </is>
+      <c r="AX26" t="n">
+        <v>797567.8</v>
       </c>
       <c r="AY26" t="inlineStr">
         <is>
           <t>869667.2</t>
         </is>
       </c>
-      <c r="AZ26" t="inlineStr">
-        <is>
-          <t>2222751.52</t>
-        </is>
+      <c r="AZ26" t="n">
+        <v>2222751.52</v>
       </c>
       <c r="BA26" t="inlineStr">
         <is>
@@ -11606,8 +11454,10 @@
           <t>-209647.8366049416</t>
         </is>
       </c>
-      <c r="BD26" t="n">
-        <v>1396196</v>
+      <c r="BD26" t="inlineStr">
+        <is>
+          <t>1396196.0</t>
+        </is>
       </c>
       <c r="BE26" t="inlineStr">
         <is>
@@ -11773,7 +11623,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -11957,15 +11807,11 @@
           <t>84.74</t>
         </is>
       </c>
-      <c r="AM27" t="inlineStr">
-        <is>
-          <t>90.4</t>
-        </is>
-      </c>
-      <c r="AN27" t="inlineStr">
-        <is>
-          <t>103.48</t>
-        </is>
+      <c r="AM27" t="n">
+        <v>90.40000000000001</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>103.48</v>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
@@ -12012,20 +11858,16 @@
           <t>446832.0</t>
         </is>
       </c>
-      <c r="AX27" t="inlineStr">
-        <is>
-          <t>676255.8</t>
-        </is>
+      <c r="AX27" t="n">
+        <v>676255.8</v>
       </c>
       <c r="AY27" t="inlineStr">
         <is>
           <t>836932.1</t>
         </is>
       </c>
-      <c r="AZ27" t="inlineStr">
-        <is>
-          <t>2237649.02</t>
-        </is>
+      <c r="AZ27" t="n">
+        <v>2237649.02</v>
       </c>
       <c r="BA27" t="inlineStr">
         <is>
@@ -12042,8 +11884,10 @@
           <t>-283207.9937717296</t>
         </is>
       </c>
-      <c r="BD27" t="n">
-        <v>446832</v>
+      <c r="BD27" t="inlineStr">
+        <is>
+          <t>446832.0</t>
+        </is>
       </c>
       <c r="BE27" t="inlineStr">
         <is>
@@ -12209,7 +12053,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -12393,15 +12237,11 @@
           <t>86.17999999999999</t>
         </is>
       </c>
-      <c r="AM28" t="inlineStr">
-        <is>
-          <t>91.23</t>
-        </is>
-      </c>
-      <c r="AN28" t="inlineStr">
-        <is>
-          <t>104.22</t>
-        </is>
+      <c r="AM28" t="n">
+        <v>91.23</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>104.22</v>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
@@ -12448,20 +12288,16 @@
           <t>480517.0</t>
         </is>
       </c>
-      <c r="AX28" t="inlineStr">
-        <is>
-          <t>810164.4</t>
-        </is>
+      <c r="AX28" t="n">
+        <v>810164.4</v>
       </c>
       <c r="AY28" t="inlineStr">
         <is>
           <t>921369.1</t>
         </is>
       </c>
-      <c r="AZ28" t="inlineStr">
-        <is>
-          <t>2333587.64</t>
-        </is>
+      <c r="AZ28" t="n">
+        <v>2333587.64</v>
       </c>
       <c r="BA28" t="inlineStr">
         <is>
@@ -12478,8 +12314,10 @@
           <t>-276461.7899467224</t>
         </is>
       </c>
-      <c r="BD28" t="n">
-        <v>480517</v>
+      <c r="BD28" t="inlineStr">
+        <is>
+          <t>480517.0</t>
+        </is>
       </c>
       <c r="BE28" t="inlineStr">
         <is>
@@ -12645,7 +12483,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -12829,15 +12667,11 @@
           <t>87.38000000000001</t>
         </is>
       </c>
-      <c r="AM29" t="inlineStr">
-        <is>
-          <t>91.96</t>
-        </is>
-      </c>
-      <c r="AN29" t="inlineStr">
-        <is>
-          <t>105.02</t>
-        </is>
+      <c r="AM29" t="n">
+        <v>91.95999999999999</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>105.02</v>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
@@ -12884,20 +12718,16 @@
           <t>528139.0</t>
         </is>
       </c>
-      <c r="AX29" t="inlineStr">
-        <is>
-          <t>854615.4</t>
-        </is>
+      <c r="AX29" t="n">
+        <v>854615.4</v>
       </c>
       <c r="AY29" t="inlineStr">
         <is>
           <t>1048562.9</t>
         </is>
       </c>
-      <c r="AZ29" t="inlineStr">
-        <is>
-          <t>2414824.58</t>
-        </is>
+      <c r="AZ29" t="n">
+        <v>2414824.58</v>
       </c>
       <c r="BA29" t="inlineStr">
         <is>
@@ -12914,8 +12744,10 @@
           <t>-260559.8276986149</t>
         </is>
       </c>
-      <c r="BD29" t="n">
-        <v>528139</v>
+      <c r="BD29" t="inlineStr">
+        <is>
+          <t>528139.0</t>
+        </is>
       </c>
       <c r="BE29" t="inlineStr">
         <is>
@@ -13081,7 +12913,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -13265,15 +13097,11 @@
           <t>89.12</t>
         </is>
       </c>
-      <c r="AM30" t="inlineStr">
-        <is>
-          <t>92.97</t>
-        </is>
-      </c>
-      <c r="AN30" t="inlineStr">
-        <is>
-          <t>105.91</t>
-        </is>
+      <c r="AM30" t="n">
+        <v>92.97</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>105.91</v>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
@@ -13320,20 +13148,16 @@
           <t>1136155.0</t>
         </is>
       </c>
-      <c r="AX30" t="inlineStr">
-        <is>
-          <t>931861.8</t>
-        </is>
+      <c r="AX30" t="n">
+        <v>931861.8</v>
       </c>
       <c r="AY30" t="inlineStr">
         <is>
           <t>1494189.3</t>
         </is>
       </c>
-      <c r="AZ30" t="inlineStr">
-        <is>
-          <t>2699451.5</t>
-        </is>
+      <c r="AZ30" t="n">
+        <v>2699451.5</v>
       </c>
       <c r="BA30" t="inlineStr">
         <is>
@@ -13350,8 +13174,10 @@
           <t>-233639.3877835108</t>
         </is>
       </c>
-      <c r="BD30" t="n">
-        <v>1136155</v>
+      <c r="BD30" t="inlineStr">
+        <is>
+          <t>1136155.0</t>
+        </is>
       </c>
       <c r="BE30" t="inlineStr">
         <is>
@@ -13517,7 +13343,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -13701,15 +13527,11 @@
           <t>90.53999999999999</t>
         </is>
       </c>
-      <c r="AM31" t="inlineStr">
-        <is>
-          <t>93.86</t>
-        </is>
-      </c>
-      <c r="AN31" t="inlineStr">
-        <is>
-          <t>106.84</t>
-        </is>
+      <c r="AM31" t="n">
+        <v>93.86</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>106.84</v>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
@@ -13756,20 +13578,16 @@
           <t>789636.0</t>
         </is>
       </c>
-      <c r="AX31" t="inlineStr">
-        <is>
-          <t>941766.6</t>
-        </is>
+      <c r="AX31" t="n">
+        <v>941766.6</v>
       </c>
       <c r="AY31" t="inlineStr">
         <is>
           <t>1903952.8</t>
         </is>
       </c>
-      <c r="AZ31" t="inlineStr">
-        <is>
-          <t>2858383.84</t>
-        </is>
+      <c r="AZ31" t="n">
+        <v>2858383.84</v>
       </c>
       <c r="BA31" t="inlineStr">
         <is>
@@ -13786,8 +13604,10 @@
           <t>-251981.9240553796</t>
         </is>
       </c>
-      <c r="BD31" t="n">
-        <v>789636</v>
+      <c r="BD31" t="inlineStr">
+        <is>
+          <t>789636.0</t>
+        </is>
       </c>
       <c r="BE31" t="inlineStr">
         <is>
@@ -13953,7 +13773,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -14137,15 +13957,11 @@
           <t>90.9</t>
         </is>
       </c>
-      <c r="AM32" t="inlineStr">
-        <is>
-          <t>94.7</t>
-        </is>
-      </c>
-      <c r="AN32" t="inlineStr">
-        <is>
-          <t>107.48</t>
-        </is>
+      <c r="AM32" t="n">
+        <v>94.7</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>107.48</v>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
@@ -14192,20 +14008,16 @@
           <t>1116375.0</t>
         </is>
       </c>
-      <c r="AX32" t="inlineStr">
-        <is>
-          <t>997608.4</t>
-        </is>
+      <c r="AX32" t="n">
+        <v>997608.4</v>
       </c>
       <c r="AY32" t="inlineStr">
         <is>
           <t>2034960.6</t>
         </is>
       </c>
-      <c r="AZ32" t="inlineStr">
-        <is>
-          <t>2909917.96</t>
-        </is>
+      <c r="AZ32" t="n">
+        <v>2909917.96</v>
       </c>
       <c r="BA32" t="inlineStr">
         <is>
@@ -14222,8 +14034,10 @@
           <t>-232059.1571560712</t>
         </is>
       </c>
-      <c r="BD32" t="n">
-        <v>1116375</v>
+      <c r="BD32" t="inlineStr">
+        <is>
+          <t>1116375.0</t>
+        </is>
       </c>
       <c r="BE32" t="inlineStr">
         <is>
@@ -14389,7 +14203,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -14573,15 +14387,11 @@
           <t>91.28</t>
         </is>
       </c>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>95.66</t>
-        </is>
-      </c>
-      <c r="AN33" t="inlineStr">
-        <is>
-          <t>108.04</t>
-        </is>
+      <c r="AM33" t="n">
+        <v>95.66</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>108.04</v>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
@@ -14628,20 +14438,16 @@
           <t>702772.0</t>
         </is>
       </c>
-      <c r="AX33" t="inlineStr">
-        <is>
-          <t>1032573.8</t>
-        </is>
+      <c r="AX33" t="n">
+        <v>1032573.8</v>
       </c>
       <c r="AY33" t="inlineStr">
         <is>
           <t>2004573.2</t>
         </is>
       </c>
-      <c r="AZ33" t="inlineStr">
-        <is>
-          <t>3051992.38</t>
-        </is>
+      <c r="AZ33" t="n">
+        <v>3051992.38</v>
       </c>
       <c r="BA33" t="inlineStr">
         <is>
@@ -14658,8 +14464,10 @@
           <t>-230317.9845443424</t>
         </is>
       </c>
-      <c r="BD33" t="n">
-        <v>702772</v>
+      <c r="BD33" t="inlineStr">
+        <is>
+          <t>702772.0</t>
+        </is>
       </c>
       <c r="BE33" t="inlineStr">
         <is>
@@ -14825,7 +14633,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -15009,15 +14817,11 @@
           <t>92.0</t>
         </is>
       </c>
-      <c r="AM34" t="inlineStr">
-        <is>
-          <t>96.23</t>
-        </is>
-      </c>
-      <c r="AN34" t="inlineStr">
-        <is>
-          <t>108.66</t>
-        </is>
+      <c r="AM34" t="n">
+        <v>96.23</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>108.66</v>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
@@ -15064,20 +14868,16 @@
           <t>914371.0</t>
         </is>
       </c>
-      <c r="AX34" t="inlineStr">
-        <is>
-          <t>1242510.4</t>
-        </is>
+      <c r="AX34" t="n">
+        <v>1242510.4</v>
       </c>
       <c r="AY34" t="inlineStr">
         <is>
           <t>2031632.2</t>
         </is>
       </c>
-      <c r="AZ34" t="inlineStr">
-        <is>
-          <t>3137803.82</t>
-        </is>
+      <c r="AZ34" t="n">
+        <v>3137803.82</v>
       </c>
       <c r="BA34" t="inlineStr">
         <is>
@@ -15094,8 +14894,10 @@
           <t>-175290.3456510033</t>
         </is>
       </c>
-      <c r="BD34" t="n">
-        <v>914371</v>
+      <c r="BD34" t="inlineStr">
+        <is>
+          <t>914371.0</t>
+        </is>
       </c>
       <c r="BE34" t="inlineStr">
         <is>

--- a/Result/checksun_type/整體解決方案.xlsx
+++ b/Result/checksun_type/整體解決方案.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CW34"/>
+  <dimension ref="A1:CW31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -948,12 +948,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>9.85</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>7091.0</t>
+          <t>3968.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -963,7 +963,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>26.3</t>
+          <t>28.05</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -978,12 +978,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.86</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>33.09</t>
+          <t>40.41</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -993,7 +993,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -1048,7 +1048,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-8.36</t>
+          <t>-2.26</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -1073,7 +1073,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -1123,33 +1123,33 @@
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>26.74</t>
+          <t>14.96</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>-2.65</t>
+          <t>11.09</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr"/>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>34</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>7091</t>
+          <t>3968</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1159,51 +1159,51 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>93.21</t>
+          <t>89.74</t>
         </is>
       </c>
       <c r="AU2" t="n">
-        <v>5.92</v>
+        <v>7.97</v>
       </c>
       <c r="AV2" t="n">
-        <v>9.119999999999999</v>
+        <v>11.48</v>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>1.99</t>
+          <t>3.68</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>-4.57</t>
+          <t>-3.74</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>24.83</t>
+          <t>25.98</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>22.76</v>
+        <v>23.3</v>
       </c>
       <c r="BA2" t="n">
-        <v>22.31</v>
+        <v>22.48</v>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>23.38</t>
+          <t>23.35</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>92.01</t>
+          <t>70.30</t>
         </is>
       </c>
       <c r="BD2" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.22</v>
       </c>
       <c r="BE2" t="n">
-        <v>0.49</v>
+        <v>0.72</v>
       </c>
       <c r="BF2" t="inlineStr">
         <is>
@@ -1212,7 +1212,7 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>-83.89</t>
+          <t>-76.48</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -1222,43 +1222,43 @@
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>65071.44150417828</t>
+          <t>65233.4125</t>
         </is>
       </c>
       <c r="BJ2" t="inlineStr">
         <is>
-          <t>188298.0</t>
+          <t>108973.0</t>
         </is>
       </c>
       <c r="BK2" t="n">
-        <v>79224.39999999999</v>
+        <v>99912.8</v>
       </c>
       <c r="BL2" t="inlineStr">
         <is>
-          <t>59526.8</t>
+          <t>71156.8</t>
         </is>
       </c>
       <c r="BM2" t="n">
-        <v>16223.06</v>
+        <v>19249.48</v>
       </c>
       <c r="BN2" t="inlineStr">
         <is>
-          <t>19697</t>
+          <t>28756</t>
         </is>
       </c>
       <c r="BO2" t="inlineStr">
         <is>
-          <t>7356.297981212065</t>
+          <t>9965.6333372948</t>
         </is>
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>20216.36191111003</t>
+          <t>16886.72296234135</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>188298.0</t>
+          <t>108973.0</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1278,7 +1278,7 @@
       </c>
       <c r="BU2" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>7.06</t>
         </is>
       </c>
       <c r="BV2" t="inlineStr">
@@ -1303,7 +1303,7 @@
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1323,22 +1323,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議關注買點&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;2&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1363,12 +1363,12 @@
       </c>
       <c r="CL2" t="inlineStr">
         <is>
-          <t>94.46</t>
+          <t>93.4</t>
         </is>
       </c>
       <c r="CM2" t="inlineStr">
         <is>
-          <t>2640</t>
+          <t>2816</t>
         </is>
       </c>
       <c r="CN2" t="inlineStr">
@@ -1388,22 +1388,22 @@
       </c>
       <c r="CQ2" t="inlineStr">
         <is>
-          <t>26.45</t>
+          <t>25.9</t>
         </is>
       </c>
       <c r="CR2" t="inlineStr">
         <is>
-          <t>27.3</t>
+          <t>28.05</t>
         </is>
       </c>
       <c r="CS2" t="inlineStr">
         <is>
-          <t>26.0</t>
+          <t>25.25</t>
         </is>
       </c>
       <c r="CT2" t="inlineStr">
         <is>
-          <t>26.3</t>
+          <t>28.05</t>
         </is>
       </c>
       <c r="CU2" t="inlineStr">
@@ -1435,12 +1435,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>9.4</t>
+          <t>-3.09</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>4853.0</t>
+          <t>2162.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1450,7 +1450,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>26.2</t>
+          <t>25.5</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1460,17 +1460,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>9.09</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.86</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>36.79</t>
+          <t>26.73</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1480,7 +1480,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -1535,7 +1535,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-8.71</t>
+          <t>-11.15</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1560,7 +1560,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -1610,17 +1610,17 @@
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-24</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>18.30</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>4.80</t>
+          <t>-2.35</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
@@ -1631,66 +1631,66 @@
       <c r="AP3" t="inlineStr"/>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>34</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>7091</t>
+          <t>3968</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>69.23</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>86.43</t>
+          <t>89.74</t>
         </is>
       </c>
       <c r="AU3" t="n">
-        <v>7.16</v>
+        <v>1.47</v>
       </c>
       <c r="AV3" t="n">
-        <v>8.859999999999999</v>
+        <v>9.42</v>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>2.68</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>-4.90</t>
+          <t>-4.17</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>24.45</t>
+          <t>25.13</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>22.46</v>
+        <v>22.97</v>
       </c>
       <c r="BA3" t="n">
-        <v>22.25</v>
+        <v>22.37</v>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>23.39</t>
+          <t>23.34</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>107.93</t>
+          <t>67.67</t>
         </is>
       </c>
       <c r="BD3" t="n">
-        <v>0.78</v>
+        <v>0.99</v>
       </c>
       <c r="BE3" t="n">
-        <v>0.38</v>
+        <v>0.59</v>
       </c>
       <c r="BF3" t="inlineStr">
         <is>
@@ -1699,7 +1699,7 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>-87.60</t>
+          <t>-80.61</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -1709,43 +1709,43 @@
       </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>65071.44150417828</t>
+          <t>65233.4125</t>
         </is>
       </c>
       <c r="BJ3" t="inlineStr">
         <is>
-          <t>126542.0</t>
+          <t>55535.0</t>
         </is>
       </c>
       <c r="BK3" t="n">
-        <v>56408.2</v>
+        <v>81577.39999999999</v>
       </c>
       <c r="BL3" t="inlineStr">
         <is>
-          <t>41235.7</t>
+          <t>64373.5</t>
         </is>
       </c>
       <c r="BM3" t="n">
-        <v>12661.38</v>
+        <v>17193.38</v>
       </c>
       <c r="BN3" t="inlineStr">
         <is>
-          <t>15172</t>
+          <t>17203</t>
         </is>
       </c>
       <c r="BO3" t="inlineStr">
         <is>
-          <t>5018.104539412434</t>
+          <t>8707.253405468153</t>
         </is>
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>11096.67566033239</t>
+          <t>16137.50823887664</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>126542.0</t>
+          <t>55535.0</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1765,7 +1765,7 @@
       </c>
       <c r="BU3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-2.67</t>
         </is>
       </c>
       <c r="BV3" t="inlineStr">
@@ -1790,7 +1790,7 @@
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1810,22 +1810,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議關注買點&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;2&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1850,12 +1850,12 @@
       </c>
       <c r="CL3" t="inlineStr">
         <is>
-          <t>94.46</t>
+          <t>93.4</t>
         </is>
       </c>
       <c r="CM3" t="inlineStr">
         <is>
-          <t>2640</t>
+          <t>2816</t>
         </is>
       </c>
       <c r="CN3" t="inlineStr">
@@ -1875,7 +1875,7 @@
       </c>
       <c r="CQ3" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>25.85</t>
         </is>
       </c>
       <c r="CR3" t="inlineStr">
@@ -1885,12 +1885,12 @@
       </c>
       <c r="CS3" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>25.4</t>
         </is>
       </c>
       <c r="CT3" t="inlineStr">
         <is>
-          <t>26.2</t>
+          <t>25.5</t>
         </is>
       </c>
       <c r="CU3" t="inlineStr">
@@ -1912,7 +1912,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>【d1】</t>
+          <t>【b1】</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>843.0</t>
+          <t>7091.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1937,7 +1937,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>23.85</t>
+          <t>26.3</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1947,17 +1947,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>9.32</t>
+          <t>6.24</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.86</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>21.91</t>
+          <t>33.09</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1967,7 +1967,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -2022,7 +2022,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-16.90</t>
+          <t>-8.36</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -2047,7 +2047,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -2097,87 +2097,87 @@
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>2025-12-19</t>
+          <t>2025-12-23</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>3.18</t>
+          <t>26.74</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>-1.24</t>
+          <t>-2.65</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr"/>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>34</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>7091</t>
+          <t>3968</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>79.63</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>82.13</t>
+          <t>93.21</t>
         </is>
       </c>
       <c r="AU4" t="n">
-        <v>-0.42</v>
+        <v>5.92</v>
       </c>
       <c r="AV4" t="n">
-        <v>8.02</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>1.99</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>-5.17</t>
+          <t>-4.57</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>23.95</t>
+          <t>24.83</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>22.17</v>
+        <v>22.76</v>
       </c>
       <c r="BA4" t="n">
-        <v>22.2</v>
+        <v>22.31</v>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>23.41</t>
+          <t>23.38</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>111.88</t>
+          <t>92.01</t>
         </is>
       </c>
       <c r="BD4" t="n">
-        <v>0.58</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="BE4" t="n">
-        <v>0.28</v>
+        <v>0.49</v>
       </c>
       <c r="BF4" t="inlineStr">
         <is>
@@ -2186,7 +2186,7 @@
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>-90.95</t>
+          <t>-83.89</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -2196,43 +2196,43 @@
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>65071.44150417828</t>
+          <t>65233.4125</t>
         </is>
       </c>
       <c r="BJ4" t="inlineStr">
         <is>
-          <t>20216.0</t>
+          <t>188298.0</t>
         </is>
       </c>
       <c r="BK4" t="n">
-        <v>35180.4</v>
+        <v>79224.39999999999</v>
       </c>
       <c r="BL4" t="inlineStr">
         <is>
-          <t>28857.5</t>
+          <t>59526.8</t>
         </is>
       </c>
       <c r="BM4" t="n">
-        <v>10271.14</v>
+        <v>16223.06</v>
       </c>
       <c r="BN4" t="inlineStr">
         <is>
-          <t>6322</t>
+          <t>19697</t>
         </is>
       </c>
       <c r="BO4" t="inlineStr">
         <is>
-          <t>3912.909790154261</t>
+          <t>7356.297981212065</t>
         </is>
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>4288.956885638152</t>
+          <t>20216.36191111003</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>20216.0</t>
+          <t>188298.0</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2252,7 +2252,7 @@
       </c>
       <c r="BU4" t="inlineStr">
         <is>
-          <t>-8.97</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="BV4" t="inlineStr">
@@ -2277,7 +2277,7 @@
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2297,22 +2297,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>0.97</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="CL4" t="inlineStr">
         <is>
-          <t>94.46</t>
+          <t>93.4</t>
         </is>
       </c>
       <c r="CM4" t="inlineStr">
         <is>
-          <t>2640</t>
+          <t>2816</t>
         </is>
       </c>
       <c r="CN4" t="inlineStr">
@@ -2362,22 +2362,22 @@
       </c>
       <c r="CQ4" t="inlineStr">
         <is>
-          <t>24.05</t>
+          <t>26.45</t>
         </is>
       </c>
       <c r="CR4" t="inlineStr">
         <is>
-          <t>24.45</t>
+          <t>27.3</t>
         </is>
       </c>
       <c r="CS4" t="inlineStr">
         <is>
-          <t>23.55</t>
+          <t>26.0</t>
         </is>
       </c>
       <c r="CT4" t="inlineStr">
         <is>
-          <t>23.85</t>
+          <t>26.3</t>
         </is>
       </c>
       <c r="CU4" t="inlineStr">
@@ -2399,7 +2399,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>【d1】</t>
+          <t>【b1】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2409,12 +2409,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-0.84</t>
+          <t>9.4</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>732.0</t>
+          <t>4853.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2424,7 +2424,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>23.8</t>
+          <t>26.2</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2434,17 +2434,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>9.51</t>
+          <t>6.6</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.86</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>56.47</t>
+          <t>36.79</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2454,7 +2454,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -2509,7 +2509,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-17.07</t>
+          <t>-8.71</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2534,7 +2534,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -2584,87 +2584,87 @@
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>2.76</t>
+          <t>18.30</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>2.38</t>
+          <t>4.80</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr"/>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>34</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>7091</t>
+          <t>3968</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>79.66</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>88.92</t>
+          <t>86.43</t>
         </is>
       </c>
       <c r="AU5" t="n">
-        <v>-1.04</v>
+        <v>7.16</v>
       </c>
       <c r="AV5" t="n">
-        <v>9.44</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>-1.01</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>-5.36</t>
+          <t>-4.90</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>24.05</t>
+          <t>24.45</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>21.98</v>
+        <v>22.46</v>
       </c>
       <c r="BA5" t="n">
-        <v>22.2</v>
+        <v>22.25</v>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>23.46</t>
+          <t>23.39</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>181.23</t>
+          <t>107.93</t>
         </is>
       </c>
       <c r="BD5" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.78</v>
       </c>
       <c r="BE5" t="n">
-        <v>0.2</v>
+        <v>0.38</v>
       </c>
       <c r="BF5" t="inlineStr">
         <is>
@@ -2673,7 +2673,7 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>-93.48</t>
+          <t>-87.60</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
@@ -2683,43 +2683,43 @@
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>65071.44150417828</t>
+          <t>65233.4125</t>
         </is>
       </c>
       <c r="BJ5" t="inlineStr">
         <is>
-          <t>17296.0</t>
+          <t>126542.0</t>
         </is>
       </c>
       <c r="BK5" t="n">
-        <v>42400.8</v>
+        <v>56408.2</v>
       </c>
       <c r="BL5" t="inlineStr">
         <is>
-          <t>27099.0</t>
+          <t>41235.7</t>
         </is>
       </c>
       <c r="BM5" t="n">
-        <v>10048.64</v>
+        <v>12661.38</v>
       </c>
       <c r="BN5" t="inlineStr">
         <is>
-          <t>15301</t>
+          <t>15172</t>
         </is>
       </c>
       <c r="BO5" t="inlineStr">
         <is>
-          <t>3844.537590975371</t>
+          <t>5018.104539412434</t>
         </is>
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>5802.538747302169</t>
+          <t>11096.67566033239</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>17296.0</t>
+          <t>126542.0</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2739,7 +2739,7 @@
       </c>
       <c r="BU5" t="inlineStr">
         <is>
-          <t>-9.16</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="BV5" t="inlineStr">
@@ -2764,7 +2764,7 @@
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2784,22 +2784,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議關注買點&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;2&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>0.97</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2824,12 +2824,12 @@
       </c>
       <c r="CL5" t="inlineStr">
         <is>
-          <t>94.46</t>
+          <t>93.4</t>
         </is>
       </c>
       <c r="CM5" t="inlineStr">
         <is>
-          <t>2640</t>
+          <t>2816</t>
         </is>
       </c>
       <c r="CN5" t="inlineStr">
@@ -2849,22 +2849,22 @@
       </c>
       <c r="CQ5" t="inlineStr">
         <is>
-          <t>23.75</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="CR5" t="inlineStr">
         <is>
-          <t>23.85</t>
+          <t>26.2</t>
         </is>
       </c>
       <c r="CS5" t="inlineStr">
         <is>
-          <t>23.2</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="CT5" t="inlineStr">
         <is>
-          <t>23.8</t>
+          <t>26.2</t>
         </is>
       </c>
       <c r="CU5" t="inlineStr">
@@ -2896,12 +2896,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-1.63</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1808.0</t>
+          <t>843.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>24.0</t>
+          <t>23.85</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2921,17 +2921,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>8.75</t>
+          <t>14.97</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.86</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>82.48</t>
+          <t>21.91</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2941,7 +2941,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -2996,7 +2996,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-16.38</t>
+          <t>-16.90</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -3021,7 +3021,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -3071,17 +3071,17 @@
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2025-12-19</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>6.82</t>
+          <t>3.18</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>-1.41</t>
+          <t>-1.24</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
@@ -3092,66 +3092,66 @@
       <c r="AP6" t="inlineStr"/>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>34</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>7091</t>
+          <t>3968</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>87.1</t>
+          <t>79.63</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>88.6</t>
+          <t>82.13</t>
         </is>
       </c>
       <c r="AU6" t="n">
-        <v>0.17</v>
+        <v>-0.42</v>
       </c>
       <c r="AV6" t="n">
-        <v>9.85</v>
+        <v>8.02</v>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>-1.79</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>-5.50</t>
+          <t>-5.17</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>23.96</t>
+          <t>23.95</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>21.81</v>
+        <v>22.17</v>
       </c>
       <c r="BA6" t="n">
-        <v>22.21</v>
+        <v>22.2</v>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>23.5</t>
+          <t>23.41</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>381.30</t>
+          <t>111.88</t>
         </is>
       </c>
       <c r="BD6" t="n">
-        <v>0.52</v>
+        <v>0.58</v>
       </c>
       <c r="BE6" t="n">
-        <v>0.11</v>
+        <v>0.28</v>
       </c>
       <c r="BF6" t="inlineStr">
         <is>
@@ -3160,7 +3160,7 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>-96.43</t>
+          <t>-90.95</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
@@ -3170,43 +3170,43 @@
       </c>
       <c r="BI6" t="inlineStr">
         <is>
-          <t>65071.44150417828</t>
+          <t>65233.4125</t>
         </is>
       </c>
       <c r="BJ6" t="inlineStr">
         <is>
-          <t>43770.0</t>
+          <t>20216.0</t>
         </is>
       </c>
       <c r="BK6" t="n">
-        <v>47169.6</v>
+        <v>35180.4</v>
       </c>
       <c r="BL6" t="inlineStr">
         <is>
-          <t>25849.0</t>
+          <t>28857.5</t>
         </is>
       </c>
       <c r="BM6" t="n">
-        <v>9818.92</v>
+        <v>10271.14</v>
       </c>
       <c r="BN6" t="inlineStr">
         <is>
-          <t>21320</t>
+          <t>6322</t>
         </is>
       </c>
       <c r="BO6" t="inlineStr">
         <is>
-          <t>3488.537380734135</t>
+          <t>3912.909790154261</t>
         </is>
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>8070.422165847122</t>
+          <t>4288.956885638152</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>43770.0</t>
+          <t>20216.0</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="BU6" t="inlineStr">
         <is>
-          <t>-8.40</t>
+          <t>-8.97</t>
         </is>
       </c>
       <c r="BV6" t="inlineStr">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -3271,12 +3271,12 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3311,12 +3311,12 @@
       </c>
       <c r="CL6" t="inlineStr">
         <is>
-          <t>94.46</t>
+          <t>93.4</t>
         </is>
       </c>
       <c r="CM6" t="inlineStr">
         <is>
-          <t>2640</t>
+          <t>2816</t>
         </is>
       </c>
       <c r="CN6" t="inlineStr">
@@ -3336,22 +3336,22 @@
       </c>
       <c r="CQ6" t="inlineStr">
         <is>
-          <t>24.55</t>
+          <t>24.05</t>
         </is>
       </c>
       <c r="CR6" t="inlineStr">
         <is>
-          <t>24.85</t>
+          <t>24.45</t>
         </is>
       </c>
       <c r="CS6" t="inlineStr">
         <is>
-          <t>23.5</t>
+          <t>23.55</t>
         </is>
       </c>
       <c r="CT6" t="inlineStr">
         <is>
-          <t>24.0</t>
+          <t>23.85</t>
         </is>
       </c>
       <c r="CU6" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2.79</t>
+          <t>-0.84</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>3021.0</t>
+          <t>732.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3398,7 +3398,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>24.4</t>
+          <t>23.8</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3408,17 +3408,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>7.22</t>
+          <t>15.15</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.86</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>81.49</t>
+          <t>56.47</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3428,7 +3428,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -3483,7 +3483,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-14.98</t>
+          <t>-17.07</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3508,7 +3508,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -3558,17 +3558,17 @@
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>11.39</t>
+          <t>2.76</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>-2.42</t>
+          <t>2.38</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
@@ -3579,66 +3579,66 @@
       <c r="AP7" t="inlineStr"/>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>34</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>7091</t>
+          <t>3968</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>79.66</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>92.9</t>
+          <t>88.92</t>
         </is>
       </c>
       <c r="AU7" t="n">
-        <v>3.7</v>
+        <v>-1.04</v>
       </c>
       <c r="AV7" t="n">
-        <v>8.779999999999999</v>
+        <v>9.44</v>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>-2.62</t>
+          <t>-1.01</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>-5.66</t>
+          <t>-5.36</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>23.53</t>
+          <t>24.05</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>21.63</v>
+        <v>21.98</v>
       </c>
       <c r="BA7" t="n">
-        <v>22.21</v>
+        <v>22.2</v>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>23.54</t>
+          <t>23.46</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>8743.35</t>
+          <t>181.23</t>
         </is>
       </c>
       <c r="BD7" t="n">
-        <v>0.45</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BE7" t="n">
-        <v>0.01</v>
+        <v>0.2</v>
       </c>
       <c r="BF7" t="inlineStr">
         <is>
@@ -3647,7 +3647,7 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>-99.83</t>
+          <t>-93.48</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -3657,43 +3657,43 @@
       </c>
       <c r="BI7" t="inlineStr">
         <is>
-          <t>65071.44150417828</t>
+          <t>65233.4125</t>
         </is>
       </c>
       <c r="BJ7" t="inlineStr">
         <is>
-          <t>74217.0</t>
+          <t>17296.0</t>
         </is>
       </c>
       <c r="BK7" t="n">
-        <v>39829.2</v>
+        <v>42400.8</v>
       </c>
       <c r="BL7" t="inlineStr">
         <is>
-          <t>21946.2</t>
+          <t>27099.0</t>
         </is>
       </c>
       <c r="BM7" t="n">
-        <v>9166.76</v>
+        <v>10048.64</v>
       </c>
       <c r="BN7" t="inlineStr">
         <is>
-          <t>17883</t>
+          <t>15301</t>
         </is>
       </c>
       <c r="BO7" t="inlineStr">
         <is>
-          <t>2655.4674198045</t>
+          <t>3844.537590975371</t>
         </is>
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>8185.526257845377</t>
+          <t>5802.538747302169</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>74217.0</t>
+          <t>17296.0</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -3713,7 +3713,7 @@
       </c>
       <c r="BU7" t="inlineStr">
         <is>
-          <t>-6.87</t>
+          <t>-9.16</t>
         </is>
       </c>
       <c r="BV7" t="inlineStr">
@@ -3738,7 +3738,7 @@
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3758,22 +3758,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>0.90</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3798,12 +3798,12 @@
       </c>
       <c r="CL7" t="inlineStr">
         <is>
-          <t>94.46</t>
+          <t>93.4</t>
         </is>
       </c>
       <c r="CM7" t="inlineStr">
         <is>
-          <t>2640</t>
+          <t>2816</t>
         </is>
       </c>
       <c r="CN7" t="inlineStr">
@@ -3823,22 +3823,22 @@
       </c>
       <c r="CQ7" t="inlineStr">
         <is>
-          <t>25.05</t>
+          <t>23.75</t>
         </is>
       </c>
       <c r="CR7" t="inlineStr">
         <is>
-          <t>25.45</t>
+          <t>23.85</t>
         </is>
       </c>
       <c r="CS7" t="inlineStr">
         <is>
-          <t>23.95</t>
+          <t>23.2</t>
         </is>
       </c>
       <c r="CT7" t="inlineStr">
         <is>
-          <t>24.4</t>
+          <t>23.8</t>
         </is>
       </c>
       <c r="CU7" t="inlineStr">
@@ -3870,12 +3870,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-2.7</t>
+          <t>-1.63</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>854.0</t>
+          <t>1808.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3885,84 +3885,84 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
+          <t>24.0</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>14.44</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1.86</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>82.48</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>2025-07-28 00:00:00</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>2025-08-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>2025-07-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>2025-07-22 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>25.6</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>28.7</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>24.25</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
           <t>23.7</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>9.89</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1.32</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>73.03</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>-40.0</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>2025-07-28 00:00:00</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>2025-08-14 00:00:00</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>2025-07-11 00:00:00</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>2025-07-22 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>25.6</t>
-        </is>
-      </c>
-      <c r="R8" t="inlineStr">
-        <is>
-          <t>28.7</t>
-        </is>
-      </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>24.25</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>23.7</t>
-        </is>
-      </c>
       <c r="V8" t="inlineStr">
         <is>
           <t>0</t>
@@ -3970,7 +3970,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-17.42</t>
+          <t>-16.38</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3995,7 +3995,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -4045,17 +4045,17 @@
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>3.22</t>
+          <t>6.82</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>-2.53</t>
+          <t>-1.41</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
@@ -4066,66 +4066,66 @@
       <c r="AP8" t="inlineStr"/>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>34</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>7091</t>
+          <t>3968</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>78.69</t>
+          <t>87.1</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>92.9</t>
+          <t>88.6</t>
         </is>
       </c>
       <c r="AU8" t="n">
-        <v>3.09</v>
+        <v>0.17</v>
       </c>
       <c r="AV8" t="n">
-        <v>7.23</v>
+        <v>9.85</v>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>-3.47</t>
+          <t>-1.79</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>-5.81</t>
+          <t>-5.50</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>22.99</t>
+          <t>23.96</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>21.44</v>
+        <v>21.81</v>
       </c>
       <c r="BA8" t="n">
         <v>22.21</v>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>23.58</t>
+          <t>23.5</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>390.65</t>
+          <t>381.30</t>
         </is>
       </c>
       <c r="BD8" t="n">
-        <v>0.31</v>
+        <v>0.52</v>
       </c>
       <c r="BE8" t="n">
-        <v>-0.11</v>
+        <v>0.11</v>
       </c>
       <c r="BF8" t="inlineStr">
         <is>
@@ -4134,7 +4134,7 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>-103.48</t>
+          <t>-96.43</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -4144,43 +4144,43 @@
       </c>
       <c r="BI8" t="inlineStr">
         <is>
-          <t>65071.44150417828</t>
+          <t>65233.4125</t>
         </is>
       </c>
       <c r="BJ8" t="inlineStr">
         <is>
-          <t>20403.0</t>
+          <t>43770.0</t>
         </is>
       </c>
       <c r="BK8" t="n">
-        <v>26063.2</v>
+        <v>47169.6</v>
       </c>
       <c r="BL8" t="inlineStr">
         <is>
-          <t>15063.2</t>
+          <t>25849.0</t>
         </is>
       </c>
       <c r="BM8" t="n">
-        <v>7895.76</v>
+        <v>9818.92</v>
       </c>
       <c r="BN8" t="inlineStr">
         <is>
-          <t>11000</t>
+          <t>21320</t>
         </is>
       </c>
       <c r="BO8" t="inlineStr">
         <is>
-          <t>1650.002176524341</t>
+          <t>3488.537380734135</t>
         </is>
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>4795.441880062685</t>
+          <t>8070.422165847122</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>20403.0</t>
+          <t>43770.0</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
@@ -4200,7 +4200,7 @@
       </c>
       <c r="BU8" t="inlineStr">
         <is>
-          <t>-9.54</t>
+          <t>-8.40</t>
         </is>
       </c>
       <c r="BV8" t="inlineStr">
@@ -4225,7 +4225,7 @@
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -4250,17 +4250,17 @@
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -4285,12 +4285,12 @@
       </c>
       <c r="CL8" t="inlineStr">
         <is>
-          <t>94.46</t>
+          <t>93.4</t>
         </is>
       </c>
       <c r="CM8" t="inlineStr">
         <is>
-          <t>2640</t>
+          <t>2816</t>
         </is>
       </c>
       <c r="CN8" t="inlineStr">
@@ -4310,22 +4310,22 @@
       </c>
       <c r="CQ8" t="inlineStr">
         <is>
-          <t>24.1</t>
+          <t>24.55</t>
         </is>
       </c>
       <c r="CR8" t="inlineStr">
         <is>
-          <t>24.3</t>
+          <t>24.85</t>
         </is>
       </c>
       <c r="CS8" t="inlineStr">
         <is>
-          <t>23.7</t>
+          <t>23.5</t>
         </is>
       </c>
       <c r="CT8" t="inlineStr">
         <is>
-          <t>23.7</t>
+          <t>24.0</t>
         </is>
       </c>
       <c r="CU8" t="inlineStr">
@@ -4357,12 +4357,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>4.13</t>
+          <t>2.79</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2341.0</t>
+          <t>3021.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -4372,7 +4372,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>24.35</t>
+          <t>24.4</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -4382,17 +4382,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>7.41</t>
+          <t>13.01</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.86</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>66.36</t>
+          <t>81.49</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -4402,7 +4402,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -4457,7 +4457,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-15.16</t>
+          <t>-14.98</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4482,7 +4482,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -4532,17 +4532,17 @@
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>8.83</t>
+          <t>11.39</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>-2.42</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
@@ -4553,12 +4553,12 @@
       <c r="AP9" t="inlineStr"/>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>34</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>7091</t>
+          <t>3968</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4568,51 +4568,51 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>92.9</t>
         </is>
       </c>
       <c r="AU9" t="n">
-        <v>8.029999999999999</v>
+        <v>3.7</v>
       </c>
       <c r="AV9" t="n">
-        <v>5.77</v>
+        <v>8.779999999999999</v>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>-4.13</t>
+          <t>-2.62</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>-5.98</t>
+          <t>-5.66</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>22.54</t>
+          <t>23.53</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>21.31</v>
+        <v>21.63</v>
       </c>
       <c r="BA9" t="n">
-        <v>22.23</v>
+        <v>22.21</v>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>23.64</t>
+          <t>23.54</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>192.87</t>
+          <t>8743.35</t>
         </is>
       </c>
       <c r="BD9" t="n">
-        <v>0.19</v>
+        <v>0.45</v>
       </c>
       <c r="BE9" t="n">
-        <v>-0.21</v>
+        <v>0.01</v>
       </c>
       <c r="BF9" t="inlineStr">
         <is>
@@ -4621,7 +4621,7 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>-106.88</t>
+          <t>-99.83</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -4631,43 +4631,43 @@
       </c>
       <c r="BI9" t="inlineStr">
         <is>
-          <t>65071.44150417828</t>
+          <t>65233.4125</t>
         </is>
       </c>
       <c r="BJ9" t="inlineStr">
         <is>
-          <t>56318.0</t>
+          <t>74217.0</t>
         </is>
       </c>
       <c r="BK9" t="n">
-        <v>22534.6</v>
+        <v>39829.2</v>
       </c>
       <c r="BL9" t="inlineStr">
         <is>
-          <t>13545.3</t>
+          <t>21946.2</t>
         </is>
       </c>
       <c r="BM9" t="n">
-        <v>7743.9</v>
+        <v>9166.76</v>
       </c>
       <c r="BN9" t="inlineStr">
         <is>
-          <t>8989</t>
+          <t>17883</t>
         </is>
       </c>
       <c r="BO9" t="inlineStr">
         <is>
-          <t>1078.104048608279</t>
+          <t>2655.4674198045</t>
         </is>
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>5546.984130370882</t>
+          <t>8185.526257845377</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>56318.0</t>
+          <t>74217.0</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
@@ -4687,7 +4687,7 @@
       </c>
       <c r="BU9" t="inlineStr">
         <is>
-          <t>-7.06</t>
+          <t>-6.87</t>
         </is>
       </c>
       <c r="BV9" t="inlineStr">
@@ -4712,7 +4712,7 @@
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4732,7 +4732,7 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
@@ -4747,7 +4747,7 @@
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4772,12 +4772,12 @@
       </c>
       <c r="CL9" t="inlineStr">
         <is>
-          <t>94.46</t>
+          <t>93.4</t>
         </is>
       </c>
       <c r="CM9" t="inlineStr">
         <is>
-          <t>2640</t>
+          <t>2816</t>
         </is>
       </c>
       <c r="CN9" t="inlineStr">
@@ -4797,22 +4797,22 @@
       </c>
       <c r="CQ9" t="inlineStr">
         <is>
-          <t>24.2</t>
+          <t>25.05</t>
         </is>
       </c>
       <c r="CR9" t="inlineStr">
         <is>
-          <t>24.7</t>
+          <t>25.45</t>
         </is>
       </c>
       <c r="CS9" t="inlineStr">
         <is>
-          <t>23.7</t>
+          <t>23.95</t>
         </is>
       </c>
       <c r="CT9" t="inlineStr">
         <is>
-          <t>24.35</t>
+          <t>24.4</t>
         </is>
       </c>
       <c r="CU9" t="inlineStr">
@@ -4844,12 +4844,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>6.73</t>
+          <t>-2.7</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1792.0</t>
+          <t>854.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4859,7 +4859,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>23.35</t>
+          <t>23.7</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4869,17 +4869,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>11.22</t>
+          <t>15.51</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.86</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>37.16</t>
+          <t>73.03</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4889,7 +4889,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -4944,7 +4944,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-18.64</t>
+          <t>-17.42</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4969,7 +4969,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -5019,17 +5019,17 @@
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>6.76</t>
+          <t>3.22</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>5.49</t>
+          <t>-2.53</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
@@ -5040,66 +5040,66 @@
       <c r="AP10" t="inlineStr"/>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>34</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>7091</t>
+          <t>3968</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>78.69</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>92.9</t>
         </is>
       </c>
       <c r="AU10" t="n">
-        <v>6.48</v>
+        <v>3.09</v>
       </c>
       <c r="AV10" t="n">
-        <v>3.6</v>
+        <v>7.23</v>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>-4.77</t>
+          <t>-3.47</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>-6.24</t>
+          <t>-5.81</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>21.93</t>
+          <t>22.99</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>21.17</v>
+        <v>21.44</v>
       </c>
       <c r="BA10" t="n">
-        <v>22.23</v>
+        <v>22.21</v>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>23.71</t>
+          <t>23.58</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>93.76</t>
+          <t>390.65</t>
         </is>
       </c>
       <c r="BD10" t="n">
-        <v>-0.02</v>
+        <v>0.31</v>
       </c>
       <c r="BE10" t="n">
-        <v>-0.31</v>
+        <v>-0.11</v>
       </c>
       <c r="BF10" t="inlineStr">
         <is>
@@ -5108,7 +5108,7 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>-110.19</t>
+          <t>-103.48</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -5118,43 +5118,43 @@
       </c>
       <c r="BI10" t="inlineStr">
         <is>
-          <t>65071.44150417828</t>
+          <t>65233.4125</t>
         </is>
       </c>
       <c r="BJ10" t="inlineStr">
         <is>
-          <t>41140.0</t>
+          <t>20403.0</t>
         </is>
       </c>
       <c r="BK10" t="n">
-        <v>11797.2</v>
+        <v>26063.2</v>
       </c>
       <c r="BL10" t="inlineStr">
         <is>
-          <t>8601.1</t>
+          <t>15063.2</t>
         </is>
       </c>
       <c r="BM10" t="n">
-        <v>6711.92</v>
+        <v>7895.76</v>
       </c>
       <c r="BN10" t="inlineStr">
         <is>
-          <t>3196</t>
+          <t>11000</t>
         </is>
       </c>
       <c r="BO10" t="inlineStr">
         <is>
-          <t>265.5803973787148</t>
+          <t>1650.002176524341</t>
         </is>
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>2574.473626155068</t>
+          <t>4795.441880062685</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>41140.0</t>
+          <t>20403.0</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -5174,7 +5174,7 @@
       </c>
       <c r="BU10" t="inlineStr">
         <is>
-          <t>-10.88</t>
+          <t>-9.54</t>
         </is>
       </c>
       <c r="BV10" t="inlineStr">
@@ -5199,7 +5199,7 @@
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -5219,22 +5219,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -5259,12 +5259,12 @@
       </c>
       <c r="CL10" t="inlineStr">
         <is>
-          <t>94.46</t>
+          <t>93.4</t>
         </is>
       </c>
       <c r="CM10" t="inlineStr">
         <is>
-          <t>2640</t>
+          <t>2816</t>
         </is>
       </c>
       <c r="CN10" t="inlineStr">
@@ -5284,22 +5284,22 @@
       </c>
       <c r="CQ10" t="inlineStr">
         <is>
-          <t>22.3</t>
+          <t>24.1</t>
         </is>
       </c>
       <c r="CR10" t="inlineStr">
         <is>
-          <t>23.5</t>
+          <t>24.3</t>
         </is>
       </c>
       <c r="CS10" t="inlineStr">
         <is>
-          <t>22.0</t>
+          <t>23.7</t>
         </is>
       </c>
       <c r="CT10" t="inlineStr">
         <is>
-          <t>23.35</t>
+          <t>23.7</t>
         </is>
       </c>
       <c r="CU10" t="inlineStr">
@@ -5331,12 +5331,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>4.13</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>327.0</t>
+          <t>2341.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -5346,7 +5346,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>21.85</t>
+          <t>24.35</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -5356,17 +5356,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>16.92</t>
+          <t>13.19</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.86</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-9.26</t>
+          <t>66.36</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -5376,7 +5376,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -5431,7 +5431,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-23.87</t>
+          <t>-15.16</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.11</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -5506,17 +5506,17 @@
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>8.83</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>2.14</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
@@ -5527,12 +5527,12 @@
       <c r="AP11" t="inlineStr"/>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>34</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>7091</t>
+          <t>3968</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -5542,51 +5542,51 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>89.74</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AU11" t="n">
-        <v>1.49</v>
+        <v>8.029999999999999</v>
       </c>
       <c r="AV11" t="n">
-        <v>1.93</v>
+        <v>5.77</v>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>-5.03</t>
+          <t>-4.13</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>-6.45</t>
+          <t>-5.98</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>21.53</t>
+          <t>22.54</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>21.12</v>
+        <v>21.31</v>
       </c>
       <c r="BA11" t="n">
-        <v>22.24</v>
+        <v>22.23</v>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>23.77</t>
+          <t>23.64</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>50.37</t>
+          <t>192.87</t>
         </is>
       </c>
       <c r="BD11" t="n">
-        <v>-0.19</v>
+        <v>0.19</v>
       </c>
       <c r="BE11" t="n">
-        <v>-0.38</v>
+        <v>-0.21</v>
       </c>
       <c r="BF11" t="inlineStr">
         <is>
@@ -5595,7 +5595,7 @@
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>-112.58</t>
+          <t>-106.88</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
@@ -5605,43 +5605,43 @@
       </c>
       <c r="BI11" t="inlineStr">
         <is>
-          <t>65071.44150417828</t>
+          <t>65233.4125</t>
         </is>
       </c>
       <c r="BJ11" t="inlineStr">
         <is>
-          <t>7068.0</t>
+          <t>56318.0</t>
         </is>
       </c>
       <c r="BK11" t="n">
-        <v>4528.4</v>
+        <v>22534.6</v>
       </c>
       <c r="BL11" t="inlineStr">
         <is>
-          <t>4990.3</t>
+          <t>13545.3</t>
         </is>
       </c>
       <c r="BM11" t="n">
-        <v>6136.7</v>
+        <v>7743.9</v>
       </c>
       <c r="BN11" t="inlineStr">
         <is>
-          <t>-461</t>
+          <t>8989</t>
         </is>
       </c>
       <c r="BO11" t="inlineStr">
         <is>
-          <t>-154.2183714897131</t>
+          <t>1078.104048608279</t>
         </is>
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>-137.7011522302064</t>
+          <t>5546.984130370882</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>7068.0</t>
+          <t>56318.0</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5661,7 +5661,7 @@
       </c>
       <c r="BU11" t="inlineStr">
         <is>
-          <t>-16.60</t>
+          <t>-7.06</t>
         </is>
       </c>
       <c r="BV11" t="inlineStr">
@@ -5686,7 +5686,7 @@
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5706,7 +5706,7 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
@@ -5716,12 +5716,12 @@
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>0.80</t>
+          <t>0.90</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5746,12 +5746,12 @@
       </c>
       <c r="CL11" t="inlineStr">
         <is>
-          <t>94.46</t>
+          <t>93.4</t>
         </is>
       </c>
       <c r="CM11" t="inlineStr">
         <is>
-          <t>2640</t>
+          <t>2816</t>
         </is>
       </c>
       <c r="CN11" t="inlineStr">
@@ -5771,22 +5771,22 @@
       </c>
       <c r="CQ11" t="inlineStr">
         <is>
-          <t>21.55</t>
+          <t>24.2</t>
         </is>
       </c>
       <c r="CR11" t="inlineStr">
         <is>
-          <t>22.0</t>
+          <t>24.7</t>
         </is>
       </c>
       <c r="CS11" t="inlineStr">
         <is>
-          <t>21.25</t>
+          <t>23.7</t>
         </is>
       </c>
       <c r="CT11" t="inlineStr">
         <is>
-          <t>21.85</t>
+          <t>24.35</t>
         </is>
       </c>
       <c r="CU11" t="inlineStr">
@@ -5808,22 +5808,22 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>【d1】</t>
+          <t>價_量;【d1】</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>6234</t>
+          <t>6125</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>-0.83</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>253.0</t>
+          <t>2854.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5833,7 +5833,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>21.7</t>
+          <t>71.8</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5843,17 +5843,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>17.49</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>-0.84</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-23.84</t>
+          <t>30.27</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5863,37 +5863,37 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2025-07-28 00:00:00</t>
+          <t>2025-09-17 00:00:00</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>2025-08-14 00:00:00</t>
+          <t>2025-09-22 00:00:00</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>2025-07-11 00:00:00</t>
+          <t>2025-07-25 00:00:00</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>2025-07-22 00:00:00</t>
+          <t>2025-08-22 00:00:00</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>25.6</t>
+          <t>80.4</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>28.7</t>
+          <t>77.7</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
@@ -5903,12 +5903,12 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>24.25</t>
+          <t>73.8</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>23.7</t>
+          <t>78.5</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
@@ -5918,22 +5918,22 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-24.39</t>
+          <t>-7.59</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>8.02</t>
+          <t>2.42</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025/07/04</t>
+          <t>2025/06/02</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>24.65</t>
+          <t>67.8</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -5943,67 +5943,67 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>-0.06</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>2025/09/15</t>
+          <t>2025/09/30</t>
         </is>
       </c>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>24.2</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>2025/07/02</t>
+          <t>2025/07/07</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>22.2</t>
+          <t>60.7</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>2025/11/18</t>
+          <t>2025/10/27</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>20.6</t>
+          <t>71.1</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>2025/11/04</t>
+          <t>2025/09/22</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>21.7</t>
+          <t>77.7</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>2025-12-23 00:00:00</t>
+          <t>2025-01-08 00:00:00</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>6.57</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>2.63</t>
+          <t>-2.08</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
@@ -6014,121 +6014,121 @@
       <c r="AP12" t="inlineStr"/>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>7091</t>
+          <t>2854</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>85.29</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>80.41</t>
+          <t>92.16</t>
         </is>
       </c>
       <c r="AU12" t="n">
-        <v>1.31</v>
+        <v>0.76</v>
       </c>
       <c r="AV12" t="n">
-        <v>1.24</v>
+        <v>8.17</v>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>-5.14</t>
+          <t>-1.47</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>-6.52</t>
+          <t>-4.89</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>21.42</t>
+          <t>71.25999999999999</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>21.16</v>
+        <v>65.88</v>
       </c>
       <c r="BA12" t="n">
-        <v>22.3</v>
+        <v>66.86</v>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>23.86</t>
+          <t>70.29</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>41.44</t>
+          <t>326.92</t>
         </is>
       </c>
       <c r="BD12" t="n">
-        <v>-0.25</v>
+        <v>1.48</v>
       </c>
       <c r="BE12" t="n">
-        <v>-0.43</v>
+        <v>0.35</v>
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>3.04</t>
+          <t>10.1</t>
         </is>
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>-114.17</t>
+          <t>-96.56</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2025/11/26</t>
+          <t>2025/11/27</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
         <is>
-          <t>65071.44150417828</t>
+          <t>1148861.497916667</t>
         </is>
       </c>
       <c r="BJ12" t="inlineStr">
         <is>
-          <t>5387.0</t>
+          <t>205765.0</t>
         </is>
       </c>
       <c r="BK12" t="n">
-        <v>4063.2</v>
+        <v>368941</v>
       </c>
       <c r="BL12" t="inlineStr">
         <is>
-          <t>5335.1</t>
+          <t>283217.3</t>
         </is>
       </c>
       <c r="BM12" t="n">
-        <v>6211.32</v>
+        <v>123456.28</v>
       </c>
       <c r="BN12" t="inlineStr">
         <is>
-          <t>-1271</t>
+          <t>85723</t>
         </is>
       </c>
       <c r="BO12" t="inlineStr">
         <is>
-          <t>-157.2215022641689</t>
+          <t>30762.1782190815</t>
         </is>
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>-356.7472230580906</t>
+          <t>42844.99990001565</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>5387.0</t>
+          <t>205765.0</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -6138,27 +6138,27 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>26.2</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>2025/12/22</t>
+          <t>2025/08/01</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
         <is>
-          <t>-17.18</t>
+          <t>-4.90</t>
         </is>
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>高僑</t>
+          <t>廣運</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
         <is>
-          <t>高僑</t>
+          <t>廣運</t>
         </is>
       </c>
       <c r="BX12" t="inlineStr">
@@ -6173,82 +6173,82 @@
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
         <is>
-          <t>-43.51524843961707</t>
+          <t>-9.276867348133008</t>
         </is>
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>-49.65752068733421</t>
+          <t>49.33864609225594</t>
         </is>
       </c>
       <c r="CC12" t="inlineStr">
         <is>
-          <t>-33.1741339459368</t>
+          <t>18.62961592762674</t>
         </is>
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>0.80</t>
+          <t>4.25</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>0.97</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>4.00</t>
         </is>
       </c>
       <c r="CI12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>552.31</t>
         </is>
       </c>
       <c r="CJ12" t="inlineStr">
         <is>
-          <t>0.94%</t>
+          <t>17.69%</t>
         </is>
       </c>
       <c r="CK12" t="inlineStr">
         <is>
-          <t>-10.38%</t>
+          <t>-6.67%</t>
         </is>
       </c>
       <c r="CL12" t="inlineStr">
         <is>
-          <t>94.46</t>
+          <t>93.4</t>
         </is>
       </c>
       <c r="CM12" t="inlineStr">
         <is>
-          <t>2640</t>
+          <t>18597</t>
         </is>
       </c>
       <c r="CN12" t="inlineStr">
         <is>
-          <t>自動化設備58.40%、微型鑽頭41.60% (2024年)</t>
+          <t>自動化設備74.11%、太陽能產品12.33%、電子零組件8.12%、建材營建4.02%、其他1.41% (2024年)</t>
         </is>
       </c>
       <c r="CO12" t="inlineStr">
         <is>
-          <t>高僑-光電業-上櫃</t>
+          <t>廣運-光電業-上櫃</t>
         </is>
       </c>
       <c r="CP12" t="inlineStr">
@@ -6258,32 +6258,32 @@
       </c>
       <c r="CQ12" t="inlineStr">
         <is>
-          <t>21.4</t>
+          <t>72.6</t>
         </is>
       </c>
       <c r="CR12" t="inlineStr">
         <is>
-          <t>21.8</t>
+          <t>73.8</t>
         </is>
       </c>
       <c r="CS12" t="inlineStr">
         <is>
-          <t>21.05</t>
+          <t>71.3</t>
         </is>
       </c>
       <c r="CT12" t="inlineStr">
         <is>
-          <t>21.7</t>
+          <t>71.8</t>
         </is>
       </c>
       <c r="CU12" t="inlineStr">
         <is>
-          <t>27.15</t>
+          <t>16.88</t>
         </is>
       </c>
       <c r="CV12" t="inlineStr">
         <is>
-          <t>** 自動化 - 自動化機台、整體解決方案** 平面顯示器 - 生產製程及檢測設備** 電機機械 - 輸送機械及零配件、機電系統工程** 太陽能產業 - 太陽能發電設備/系統及系統工程</t>
+          <t>** 自動化 - 整體解決方案** 平面顯示器 - 生產製程及檢測設備** 電機機械 - 輸送機械及零配件、機電系統工程** 太陽能產業 - 太陽能發電設備/系統及系統工程</t>
         </is>
       </c>
       <c r="CW12" t="inlineStr">
@@ -6295,7 +6295,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>價_量;【d1】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -6305,12 +6305,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>-1.23</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>11495.0</t>
+          <t>4590.0</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -6320,7 +6320,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>73.3</t>
+          <t>72.4</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -6330,17 +6330,17 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.84</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>4.36</t>
+          <t>-0.84</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>9.24</t>
+          <t>24.41</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -6405,7 +6405,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>-5.66</t>
+          <t>-6.82</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -6430,7 +6430,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>0.29</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
@@ -6480,17 +6480,17 @@
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2025-12-24</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>26.48</t>
+          <t>10.57</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>3.86</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
@@ -6501,66 +6501,66 @@
       <c r="AP13" t="inlineStr"/>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>11495</t>
+          <t>2854</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>91.18</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>82.54</t>
+          <t>97.06</t>
         </is>
       </c>
       <c r="AU13" t="n">
-        <v>8.140000000000001</v>
+        <v>3.99</v>
       </c>
       <c r="AV13" t="n">
-        <v>4.35</v>
+        <v>6.41</v>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>-2.84</t>
+          <t>-2.18</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>-5.16</t>
+          <t>-4.99</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>67.78</t>
+          <t>69.62</t>
         </is>
       </c>
       <c r="AZ13" t="n">
-        <v>64.95999999999999</v>
+        <v>65.42</v>
       </c>
       <c r="BA13" t="n">
-        <v>66.84999999999999</v>
+        <v>66.88</v>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>70.49</t>
+          <t>70.39</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>478.83</t>
+          <t>1881.60</t>
         </is>
       </c>
       <c r="BD13" t="n">
-        <v>0.89</v>
+        <v>1.26</v>
       </c>
       <c r="BE13" t="n">
-        <v>-0.23</v>
+        <v>0.06</v>
       </c>
       <c r="BF13" t="inlineStr">
         <is>
@@ -6569,7 +6569,7 @@
       </c>
       <c r="BG13" t="inlineStr">
         <is>
-          <t>-102.32</t>
+          <t>-99.37</t>
         </is>
       </c>
       <c r="BH13" t="inlineStr">
@@ -6579,43 +6579,43 @@
       </c>
       <c r="BI13" t="inlineStr">
         <is>
-          <t>1150940.540389972</t>
+          <t>1148861.497916667</t>
         </is>
       </c>
       <c r="BJ13" t="inlineStr">
         <is>
-          <t>828291.0</t>
+          <t>330882.0</t>
         </is>
       </c>
       <c r="BK13" t="n">
-        <v>288810</v>
+        <v>344617.8</v>
       </c>
       <c r="BL13" t="inlineStr">
         <is>
-          <t>264378.8</t>
+          <t>277012.5</t>
         </is>
       </c>
       <c r="BM13" t="n">
-        <v>116266.12</v>
+        <v>120544.5</v>
       </c>
       <c r="BN13" t="inlineStr">
         <is>
-          <t>24431</t>
+          <t>67605</t>
         </is>
       </c>
       <c r="BO13" t="inlineStr">
         <is>
-          <t>23134.04973820278</t>
+          <t>28565.30154982075</t>
         </is>
       </c>
       <c r="BP13" t="inlineStr">
         <is>
-          <t>65219.30358637802</t>
+          <t>58437.18651371956</t>
         </is>
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>828291.0</t>
+          <t>330882.0</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
@@ -6635,7 +6635,7 @@
       </c>
       <c r="BU13" t="inlineStr">
         <is>
-          <t>-2.91</t>
+          <t>-4.11</t>
         </is>
       </c>
       <c r="BV13" t="inlineStr">
@@ -6680,22 +6680,22 @@
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>4.34</t>
+          <t>4.29</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>0.97</t>
         </is>
       </c>
       <c r="CH13" t="inlineStr">
@@ -6705,7 +6705,7 @@
       </c>
       <c r="CI13" t="inlineStr">
         <is>
-          <t>563.85</t>
+          <t>552.31</t>
         </is>
       </c>
       <c r="CJ13" t="inlineStr">
@@ -6720,12 +6720,12 @@
       </c>
       <c r="CL13" t="inlineStr">
         <is>
-          <t>94.46</t>
+          <t>93.4</t>
         </is>
       </c>
       <c r="CM13" t="inlineStr">
         <is>
-          <t>18986</t>
+          <t>18597</t>
         </is>
       </c>
       <c r="CN13" t="inlineStr">
@@ -6745,22 +6745,22 @@
       </c>
       <c r="CQ13" t="inlineStr">
         <is>
-          <t>71.3</t>
+          <t>73.3</t>
         </is>
       </c>
       <c r="CR13" t="inlineStr">
         <is>
-          <t>73.6</t>
+          <t>73.8</t>
         </is>
       </c>
       <c r="CS13" t="inlineStr">
         <is>
-          <t>70.3</t>
+          <t>70.9</t>
         </is>
       </c>
       <c r="CT13" t="inlineStr">
         <is>
-          <t>73.3</t>
+          <t>72.4</t>
         </is>
       </c>
       <c r="CU13" t="inlineStr">
@@ -6792,12 +6792,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>9.12</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>4186.0</t>
+          <t>11495.0</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6807,7 +6807,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>72.7</t>
+          <t>73.3</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6817,17 +6817,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>-2.09</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>4.36</t>
+          <t>-0.84</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>-20.83</t>
+          <t>9.24</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6892,7 +6892,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>-6.44</t>
+          <t>-5.66</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6917,7 +6917,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>0.29</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
@@ -6967,17 +6967,17 @@
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-23</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>9.64</t>
+          <t>26.48</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>2.97</t>
+          <t>3.86</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
@@ -6988,12 +6988,12 @@
       <c r="AP14" t="inlineStr"/>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>11495</t>
+          <t>2854</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -7003,51 +7003,51 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>51.85</t>
+          <t>82.54</t>
         </is>
       </c>
       <c r="AU14" t="n">
-        <v>10.59</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="AV14" t="n">
-        <v>2.1</v>
+        <v>4.35</v>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>-3.69</t>
+          <t>-2.84</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>-5.29</t>
+          <t>-5.16</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>65.74</t>
+          <t>67.78</t>
         </is>
       </c>
       <c r="AZ14" t="n">
-        <v>64.39</v>
+        <v>64.95999999999999</v>
       </c>
       <c r="BA14" t="n">
         <v>66.84999999999999</v>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>70.58</t>
+          <t>70.49</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>161.44</t>
+          <t>478.83</t>
         </is>
       </c>
       <c r="BD14" t="n">
-        <v>0.32</v>
+        <v>0.89</v>
       </c>
       <c r="BE14" t="n">
-        <v>-0.52</v>
+        <v>-0.23</v>
       </c>
       <c r="BF14" t="inlineStr">
         <is>
@@ -7056,7 +7056,7 @@
       </c>
       <c r="BG14" t="inlineStr">
         <is>
-          <t>-105.11</t>
+          <t>-102.32</t>
         </is>
       </c>
       <c r="BH14" t="inlineStr">
@@ -7066,43 +7066,43 @@
       </c>
       <c r="BI14" t="inlineStr">
         <is>
-          <t>1150940.540389972</t>
+          <t>1148861.497916667</t>
         </is>
       </c>
       <c r="BJ14" t="inlineStr">
         <is>
-          <t>304096.0</t>
+          <t>828291.0</t>
         </is>
       </c>
       <c r="BK14" t="n">
-        <v>148810.2</v>
+        <v>288810</v>
       </c>
       <c r="BL14" t="inlineStr">
         <is>
-          <t>187961.6</t>
+          <t>264378.8</t>
         </is>
       </c>
       <c r="BM14" t="n">
-        <v>102169.54</v>
+        <v>116266.12</v>
       </c>
       <c r="BN14" t="inlineStr">
         <is>
-          <t>-39151</t>
+          <t>24431</t>
         </is>
       </c>
       <c r="BO14" t="inlineStr">
         <is>
-          <t>15482.18540217091</t>
+          <t>23134.04973820278</t>
         </is>
       </c>
       <c r="BP14" t="inlineStr">
         <is>
-          <t>19284.95999066232</t>
+          <t>65219.30358637802</t>
         </is>
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>304096.0</t>
+          <t>828291.0</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
@@ -7122,7 +7122,7 @@
       </c>
       <c r="BU14" t="inlineStr">
         <is>
-          <t>-3.71</t>
+          <t>-2.91</t>
         </is>
       </c>
       <c r="BV14" t="inlineStr">
@@ -7167,22 +7167,22 @@
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>4.31</t>
+          <t>4.34</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>0.97</t>
         </is>
       </c>
       <c r="CH14" t="inlineStr">
@@ -7192,7 +7192,7 @@
       </c>
       <c r="CI14" t="inlineStr">
         <is>
-          <t>563.85</t>
+          <t>552.31</t>
         </is>
       </c>
       <c r="CJ14" t="inlineStr">
@@ -7207,12 +7207,12 @@
       </c>
       <c r="CL14" t="inlineStr">
         <is>
-          <t>94.46</t>
+          <t>93.4</t>
         </is>
       </c>
       <c r="CM14" t="inlineStr">
         <is>
-          <t>18986</t>
+          <t>18597</t>
         </is>
       </c>
       <c r="CN14" t="inlineStr">
@@ -7232,22 +7232,22 @@
       </c>
       <c r="CQ14" t="inlineStr">
         <is>
-          <t>72.4</t>
+          <t>71.3</t>
         </is>
       </c>
       <c r="CR14" t="inlineStr">
         <is>
-          <t>72.7</t>
+          <t>73.6</t>
         </is>
       </c>
       <c r="CS14" t="inlineStr">
         <is>
-          <t>70.6</t>
+          <t>70.3</t>
         </is>
       </c>
       <c r="CT14" t="inlineStr">
         <is>
-          <t>72.7</t>
+          <t>73.3</t>
         </is>
       </c>
       <c r="CU14" t="inlineStr">
@@ -7279,12 +7279,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>3.85</t>
+          <t>9.12</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2647.0</t>
+          <t>4186.0</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -7294,7 +7294,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>66.1</t>
+          <t>72.7</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -7304,17 +7304,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>9.82</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>4.36</t>
+          <t>-0.84</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>-10.23</t>
+          <t>-20.83</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -7379,7 +7379,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>-14.93</t>
+          <t>-6.44</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -7404,7 +7404,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
@@ -7454,17 +7454,17 @@
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>2025-12-19</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>6.10</t>
+          <t>9.64</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>2.97</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
@@ -7475,66 +7475,66 @@
       <c r="AP15" t="inlineStr"/>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>11495</t>
+          <t>2854</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
         <is>
-          <t>47.62</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>19.05</t>
+          <t>51.85</t>
         </is>
       </c>
       <c r="AU15" t="n">
-        <v>2.83</v>
+        <v>10.59</v>
       </c>
       <c r="AV15" t="n">
-        <v>0.67</v>
+        <v>2.1</v>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>-4.47</t>
+          <t>-3.69</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>-5.43</t>
+          <t>-5.29</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>64.28</t>
+          <t>65.74</t>
         </is>
       </c>
       <c r="AZ15" t="n">
-        <v>63.86</v>
+        <v>64.39</v>
       </c>
       <c r="BA15" t="n">
-        <v>66.84</v>
+        <v>66.84999999999999</v>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>70.68</t>
+          <t>70.58</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>50.65</t>
+          <t>161.44</t>
         </is>
       </c>
       <c r="BD15" t="n">
-        <v>-0.36</v>
+        <v>0.32</v>
       </c>
       <c r="BE15" t="n">
-        <v>-0.72</v>
+        <v>-0.52</v>
       </c>
       <c r="BF15" t="inlineStr">
         <is>
@@ -7543,7 +7543,7 @@
       </c>
       <c r="BG15" t="inlineStr">
         <is>
-          <t>-107.17</t>
+          <t>-105.11</t>
         </is>
       </c>
       <c r="BH15" t="inlineStr">
@@ -7553,43 +7553,43 @@
       </c>
       <c r="BI15" t="inlineStr">
         <is>
-          <t>1150940.540389972</t>
+          <t>1148861.497916667</t>
         </is>
       </c>
       <c r="BJ15" t="inlineStr">
         <is>
-          <t>175671.0</t>
+          <t>304096.0</t>
         </is>
       </c>
       <c r="BK15" t="n">
-        <v>153609.6</v>
+        <v>148810.2</v>
       </c>
       <c r="BL15" t="inlineStr">
         <is>
-          <t>171121.6</t>
+          <t>187961.6</t>
         </is>
       </c>
       <c r="BM15" t="n">
-        <v>98092.44</v>
+        <v>102169.54</v>
       </c>
       <c r="BN15" t="inlineStr">
         <is>
-          <t>-17512</t>
+          <t>-39151</t>
         </is>
       </c>
       <c r="BO15" t="inlineStr">
         <is>
-          <t>14790.77184062702</t>
+          <t>15482.18540217091</t>
         </is>
       </c>
       <c r="BP15" t="inlineStr">
         <is>
-          <t>9139.470568544813</t>
+          <t>19284.95999066232</t>
         </is>
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>175671.0</t>
+          <t>304096.0</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
@@ -7609,7 +7609,7 @@
       </c>
       <c r="BU15" t="inlineStr">
         <is>
-          <t>-12.45</t>
+          <t>-3.71</t>
         </is>
       </c>
       <c r="BV15" t="inlineStr">
@@ -7654,22 +7654,22 @@
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>3.92</t>
+          <t>4.31</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>0.97</t>
         </is>
       </c>
       <c r="CH15" t="inlineStr">
@@ -7679,7 +7679,7 @@
       </c>
       <c r="CI15" t="inlineStr">
         <is>
-          <t>563.85</t>
+          <t>552.31</t>
         </is>
       </c>
       <c r="CJ15" t="inlineStr">
@@ -7694,12 +7694,12 @@
       </c>
       <c r="CL15" t="inlineStr">
         <is>
-          <t>94.46</t>
+          <t>93.4</t>
         </is>
       </c>
       <c r="CM15" t="inlineStr">
         <is>
-          <t>18986</t>
+          <t>18597</t>
         </is>
       </c>
       <c r="CN15" t="inlineStr">
@@ -7719,22 +7719,22 @@
       </c>
       <c r="CQ15" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>72.4</t>
         </is>
       </c>
       <c r="CR15" t="inlineStr">
         <is>
-          <t>67.8</t>
+          <t>72.7</t>
         </is>
       </c>
       <c r="CS15" t="inlineStr">
         <is>
-          <t>64.3</t>
+          <t>70.6</t>
         </is>
       </c>
       <c r="CT15" t="inlineStr">
         <is>
-          <t>66.1</t>
+          <t>72.7</t>
         </is>
       </c>
       <c r="CU15" t="inlineStr">
@@ -7766,12 +7766,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>3.85</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1318.0</t>
+          <t>2647.0</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -7781,7 +7781,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>63.6</t>
+          <t>66.1</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -7791,17 +7791,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>13.23</t>
+          <t>7.94</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>4.36</t>
+          <t>-0.84</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>12.28</t>
+          <t>-10.23</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -7866,7 +7866,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>-18.15</t>
+          <t>-14.93</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7891,7 +7891,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>0.09</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
@@ -7941,17 +7941,17 @@
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2025-12-19</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>3.04</t>
+          <t>6.10</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
@@ -7962,66 +7962,66 @@
       <c r="AP16" t="inlineStr"/>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>11495</t>
+          <t>2854</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
-          <t>7.94</t>
+          <t>47.62</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>3.17</t>
+          <t>19.05</t>
         </is>
       </c>
       <c r="AU16" t="n">
-        <v>-2.06</v>
+        <v>2.83</v>
       </c>
       <c r="AV16" t="n">
-        <v>2.16</v>
+        <v>0.67</v>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>-5.1</t>
+          <t>-4.47</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>-5.47</t>
+          <t>-5.43</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>64.94000000000001</t>
+          <t>64.28</t>
         </is>
       </c>
       <c r="AZ16" t="n">
-        <v>63.57</v>
+        <v>63.86</v>
       </c>
       <c r="BA16" t="n">
-        <v>66.98999999999999</v>
+        <v>66.84</v>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>70.86</t>
+          <t>70.68</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>33.70</t>
+          <t>50.65</t>
         </is>
       </c>
       <c r="BD16" t="n">
-        <v>-0.54</v>
+        <v>-0.36</v>
       </c>
       <c r="BE16" t="n">
-        <v>-0.82</v>
+        <v>-0.72</v>
       </c>
       <c r="BF16" t="inlineStr">
         <is>
@@ -8030,7 +8030,7 @@
       </c>
       <c r="BG16" t="inlineStr">
         <is>
-          <t>-108.08</t>
+          <t>-107.17</t>
         </is>
       </c>
       <c r="BH16" t="inlineStr">
@@ -8040,43 +8040,43 @@
       </c>
       <c r="BI16" t="inlineStr">
         <is>
-          <t>1150940.540389972</t>
+          <t>1148861.497916667</t>
         </is>
       </c>
       <c r="BJ16" t="inlineStr">
         <is>
-          <t>84149.0</t>
+          <t>175671.0</t>
         </is>
       </c>
       <c r="BK16" t="n">
-        <v>197493.6</v>
+        <v>153609.6</v>
       </c>
       <c r="BL16" t="inlineStr">
         <is>
-          <t>175888.9</t>
+          <t>171121.6</t>
         </is>
       </c>
       <c r="BM16" t="n">
-        <v>95849.82000000001</v>
+        <v>98092.44</v>
       </c>
       <c r="BN16" t="inlineStr">
         <is>
-          <t>21604</t>
+          <t>-17512</t>
         </is>
       </c>
       <c r="BO16" t="inlineStr">
         <is>
-          <t>15818.28116282379</t>
+          <t>14790.77184062702</t>
         </is>
       </c>
       <c r="BP16" t="inlineStr">
         <is>
-          <t>8079.326016643201</t>
+          <t>9139.470568544813</t>
         </is>
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>84149.0</t>
+          <t>175671.0</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
@@ -8096,7 +8096,7 @@
       </c>
       <c r="BU16" t="inlineStr">
         <is>
-          <t>-15.76</t>
+          <t>-12.45</t>
         </is>
       </c>
       <c r="BV16" t="inlineStr">
@@ -8141,7 +8141,7 @@
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
@@ -8151,12 +8151,12 @@
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>3.77</t>
+          <t>3.92</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>0.97</t>
         </is>
       </c>
       <c r="CH16" t="inlineStr">
@@ -8166,7 +8166,7 @@
       </c>
       <c r="CI16" t="inlineStr">
         <is>
-          <t>563.85</t>
+          <t>552.31</t>
         </is>
       </c>
       <c r="CJ16" t="inlineStr">
@@ -8181,12 +8181,12 @@
       </c>
       <c r="CL16" t="inlineStr">
         <is>
-          <t>94.46</t>
+          <t>93.4</t>
         </is>
       </c>
       <c r="CM16" t="inlineStr">
         <is>
-          <t>18986</t>
+          <t>18597</t>
         </is>
       </c>
       <c r="CN16" t="inlineStr">
@@ -8206,22 +8206,22 @@
       </c>
       <c r="CQ16" t="inlineStr">
         <is>
-          <t>63.2</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="CR16" t="inlineStr">
         <is>
-          <t>65.3</t>
+          <t>67.8</t>
         </is>
       </c>
       <c r="CS16" t="inlineStr">
         <is>
-          <t>62.4</t>
+          <t>64.3</t>
         </is>
       </c>
       <c r="CT16" t="inlineStr">
         <is>
-          <t>63.6</t>
+          <t>66.1</t>
         </is>
       </c>
       <c r="CU16" t="inlineStr">
@@ -8253,12 +8253,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>816.0</t>
+          <t>1318.0</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -8268,7 +8268,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>63.2</t>
+          <t>63.6</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -8278,17 +8278,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>13.78</t>
+          <t>11.42</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>4.36</t>
+          <t>-0.84</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>14.88</t>
+          <t>12.28</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -8353,7 +8353,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>-18.66</t>
+          <t>-18.15</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -8378,7 +8378,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>-0.1</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
@@ -8428,17 +8428,17 @@
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>1.88</t>
+          <t>3.04</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>-1.58</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
@@ -8449,66 +8449,66 @@
       <c r="AP17" t="inlineStr"/>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>11495</t>
+          <t>2854</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>7.94</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>11.64</t>
+          <t>3.17</t>
         </is>
       </c>
       <c r="AU17" t="n">
-        <v>-3.36</v>
+        <v>-2.06</v>
       </c>
       <c r="AV17" t="n">
-        <v>2.94</v>
+        <v>2.16</v>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>-5.46</t>
+          <t>-5.1</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>-5.41</t>
+          <t>-5.47</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>65.4</t>
+          <t>64.94000000000001</t>
         </is>
       </c>
       <c r="AZ17" t="n">
-        <v>63.53</v>
+        <v>63.57</v>
       </c>
       <c r="BA17" t="n">
-        <v>67.2</v>
+        <v>66.98999999999999</v>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>71.05</t>
+          <t>70.86</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>42.05</t>
+          <t>33.70</t>
         </is>
       </c>
       <c r="BD17" t="n">
-        <v>-0.51</v>
+        <v>-0.54</v>
       </c>
       <c r="BE17" t="n">
-        <v>-0.88</v>
+        <v>-0.82</v>
       </c>
       <c r="BF17" t="inlineStr">
         <is>
@@ -8517,7 +8517,7 @@
       </c>
       <c r="BG17" t="inlineStr">
         <is>
-          <t>-108.76</t>
+          <t>-108.08</t>
         </is>
       </c>
       <c r="BH17" t="inlineStr">
@@ -8527,43 +8527,43 @@
       </c>
       <c r="BI17" t="inlineStr">
         <is>
-          <t>1150940.540389972</t>
+          <t>1148861.497916667</t>
         </is>
       </c>
       <c r="BJ17" t="inlineStr">
         <is>
-          <t>51843.0</t>
+          <t>84149.0</t>
         </is>
       </c>
       <c r="BK17" t="n">
-        <v>209407.2</v>
+        <v>197493.6</v>
       </c>
       <c r="BL17" t="inlineStr">
         <is>
-          <t>182286.2</t>
+          <t>175888.9</t>
         </is>
       </c>
       <c r="BM17" t="n">
-        <v>96185.08</v>
+        <v>95849.82000000001</v>
       </c>
       <c r="BN17" t="inlineStr">
         <is>
-          <t>27121</t>
+          <t>21604</t>
         </is>
       </c>
       <c r="BO17" t="inlineStr">
         <is>
-          <t>17225.3639166748</t>
+          <t>15818.28116282379</t>
         </is>
       </c>
       <c r="BP17" t="inlineStr">
         <is>
-          <t>16082.21501333226</t>
+          <t>8079.326016643201</t>
         </is>
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>51843.0</t>
+          <t>84149.0</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
@@ -8583,7 +8583,7 @@
       </c>
       <c r="BU17" t="inlineStr">
         <is>
-          <t>-16.29</t>
+          <t>-15.76</t>
         </is>
       </c>
       <c r="BV17" t="inlineStr">
@@ -8628,22 +8628,22 @@
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>價跌量縮</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>3.74</t>
+          <t>3.77</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>0.97</t>
         </is>
       </c>
       <c r="CH17" t="inlineStr">
@@ -8653,7 +8653,7 @@
       </c>
       <c r="CI17" t="inlineStr">
         <is>
-          <t>563.85</t>
+          <t>552.31</t>
         </is>
       </c>
       <c r="CJ17" t="inlineStr">
@@ -8668,12 +8668,12 @@
       </c>
       <c r="CL17" t="inlineStr">
         <is>
-          <t>94.46</t>
+          <t>93.4</t>
         </is>
       </c>
       <c r="CM17" t="inlineStr">
         <is>
-          <t>18986</t>
+          <t>18597</t>
         </is>
       </c>
       <c r="CN17" t="inlineStr">
@@ -8693,22 +8693,22 @@
       </c>
       <c r="CQ17" t="inlineStr">
         <is>
-          <t>63.1</t>
+          <t>63.2</t>
         </is>
       </c>
       <c r="CR17" t="inlineStr">
         <is>
-          <t>64.3</t>
+          <t>65.3</t>
         </is>
       </c>
       <c r="CS17" t="inlineStr">
         <is>
-          <t>63.1</t>
+          <t>62.4</t>
         </is>
       </c>
       <c r="CT17" t="inlineStr">
         <is>
-          <t>63.2</t>
+          <t>63.6</t>
         </is>
       </c>
       <c r="CU17" t="inlineStr">
@@ -8740,12 +8740,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-3.54</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2009.0</t>
+          <t>816.0</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -8755,7 +8755,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>63.1</t>
+          <t>63.2</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -8765,17 +8765,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>13.92</t>
+          <t>11.98</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>4.36</t>
+          <t>-0.84</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>31.55</t>
+          <t>14.88</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -8840,7 +8840,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>-18.79</t>
+          <t>-18.66</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -8865,7 +8865,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>-0.26</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
@@ -8915,17 +8915,17 @@
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>4.63</t>
+          <t>1.88</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>-3.49</t>
+          <t>-1.58</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
@@ -8936,66 +8936,66 @@
       <c r="AP18" t="inlineStr"/>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>11495</t>
+          <t>2854</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>44.44</t>
+          <t>11.64</t>
         </is>
       </c>
       <c r="AU18" t="n">
-        <v>-3.72</v>
+        <v>-3.36</v>
       </c>
       <c r="AV18" t="n">
-        <v>3.25</v>
+        <v>2.94</v>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>-5.82</t>
+          <t>-5.46</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>-5.43</t>
+          <t>-5.41</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>65.54</t>
+          <t>65.4</t>
         </is>
       </c>
       <c r="AZ18" t="n">
-        <v>63.48</v>
+        <v>63.53</v>
       </c>
       <c r="BA18" t="n">
-        <v>67.40000000000001</v>
+        <v>67.2</v>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>71.27</t>
+          <t>71.05</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>56.17</t>
+          <t>42.05</t>
         </is>
       </c>
       <c r="BD18" t="n">
-        <v>-0.43</v>
+        <v>-0.51</v>
       </c>
       <c r="BE18" t="n">
-        <v>-0.98</v>
+        <v>-0.88</v>
       </c>
       <c r="BF18" t="inlineStr">
         <is>
@@ -9004,7 +9004,7 @@
       </c>
       <c r="BG18" t="inlineStr">
         <is>
-          <t>-109.68</t>
+          <t>-108.76</t>
         </is>
       </c>
       <c r="BH18" t="inlineStr">
@@ -9014,43 +9014,43 @@
       </c>
       <c r="BI18" t="inlineStr">
         <is>
-          <t>1150940.540389972</t>
+          <t>1148861.497916667</t>
         </is>
       </c>
       <c r="BJ18" t="inlineStr">
         <is>
-          <t>128292.0</t>
+          <t>51843.0</t>
         </is>
       </c>
       <c r="BK18" t="n">
-        <v>239947.6</v>
+        <v>209407.2</v>
       </c>
       <c r="BL18" t="inlineStr">
         <is>
-          <t>182405.5</t>
+          <t>182286.2</t>
         </is>
       </c>
       <c r="BM18" t="n">
-        <v>96387.88</v>
+        <v>96185.08</v>
       </c>
       <c r="BN18" t="inlineStr">
         <is>
-          <t>57542</t>
+          <t>27121</t>
         </is>
       </c>
       <c r="BO18" t="inlineStr">
         <is>
-          <t>17433.20917182799</t>
+          <t>17225.3639166748</t>
         </is>
       </c>
       <c r="BP18" t="inlineStr">
         <is>
-          <t>30401.90590098329</t>
+          <t>16082.21501333226</t>
         </is>
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>128292.0</t>
+          <t>51843.0</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
@@ -9070,7 +9070,7 @@
       </c>
       <c r="BU18" t="inlineStr">
         <is>
-          <t>-16.42</t>
+          <t>-16.29</t>
         </is>
       </c>
       <c r="BV18" t="inlineStr">
@@ -9115,12 +9115,12 @@
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價跌量縮</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
@@ -9130,7 +9130,7 @@
       </c>
       <c r="CG18" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>0.97</t>
         </is>
       </c>
       <c r="CH18" t="inlineStr">
@@ -9140,7 +9140,7 @@
       </c>
       <c r="CI18" t="inlineStr">
         <is>
-          <t>563.85</t>
+          <t>552.31</t>
         </is>
       </c>
       <c r="CJ18" t="inlineStr">
@@ -9155,12 +9155,12 @@
       </c>
       <c r="CL18" t="inlineStr">
         <is>
-          <t>94.46</t>
+          <t>93.4</t>
         </is>
       </c>
       <c r="CM18" t="inlineStr">
         <is>
-          <t>18986</t>
+          <t>18597</t>
         </is>
       </c>
       <c r="CN18" t="inlineStr">
@@ -9180,22 +9180,22 @@
       </c>
       <c r="CQ18" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>63.1</t>
         </is>
       </c>
       <c r="CR18" t="inlineStr">
         <is>
-          <t>65.4</t>
+          <t>64.3</t>
         </is>
       </c>
       <c r="CS18" t="inlineStr">
         <is>
-          <t>63.0</t>
+          <t>63.1</t>
         </is>
       </c>
       <c r="CT18" t="inlineStr">
         <is>
-          <t>63.1</t>
+          <t>63.2</t>
         </is>
       </c>
       <c r="CU18" t="inlineStr">
@@ -9227,12 +9227,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-5.77</t>
+          <t>-3.54</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>4874.0</t>
+          <t>2009.0</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -9242,7 +9242,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>65.4</t>
+          <t>63.1</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -9252,17 +9252,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>10.78</t>
+          <t>12.12</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>4.36</t>
+          <t>-0.84</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>31.50</t>
+          <t>31.55</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -9327,7 +9327,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>-15.83</t>
+          <t>-18.79</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -9352,7 +9352,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
@@ -9402,17 +9402,17 @@
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>11.23</t>
+          <t>4.63</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>-5.50</t>
+          <t>-3.49</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
@@ -9423,66 +9423,66 @@
       <c r="AP19" t="inlineStr"/>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>11495</t>
+          <t>2854</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>77.78</t>
+          <t>44.44</t>
         </is>
       </c>
       <c r="AU19" t="n">
-        <v>-0.61</v>
+        <v>-3.72</v>
       </c>
       <c r="AV19" t="n">
-        <v>3.75</v>
+        <v>3.25</v>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>-6.17</t>
+          <t>-5.82</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>-5.44</t>
+          <t>-5.43</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>65.8</t>
+          <t>65.54</t>
         </is>
       </c>
       <c r="AZ19" t="n">
-        <v>63.42</v>
+        <v>63.48</v>
       </c>
       <c r="BA19" t="n">
-        <v>67.59</v>
+        <v>67.40000000000001</v>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>71.48</t>
+          <t>71.27</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>72.68</t>
+          <t>56.17</t>
         </is>
       </c>
       <c r="BD19" t="n">
-        <v>-0.3</v>
+        <v>-0.43</v>
       </c>
       <c r="BE19" t="n">
-        <v>-1.11</v>
+        <v>-0.98</v>
       </c>
       <c r="BF19" t="inlineStr">
         <is>
@@ -9491,7 +9491,7 @@
       </c>
       <c r="BG19" t="inlineStr">
         <is>
-          <t>-111.04</t>
+          <t>-109.68</t>
         </is>
       </c>
       <c r="BH19" t="inlineStr">
@@ -9501,43 +9501,43 @@
       </c>
       <c r="BI19" t="inlineStr">
         <is>
-          <t>1150940.540389972</t>
+          <t>1148861.497916667</t>
         </is>
       </c>
       <c r="BJ19" t="inlineStr">
         <is>
-          <t>328093.0</t>
+          <t>128292.0</t>
         </is>
       </c>
       <c r="BK19" t="n">
-        <v>227113</v>
+        <v>239947.6</v>
       </c>
       <c r="BL19" t="inlineStr">
         <is>
-          <t>172709.3</t>
+          <t>182405.5</t>
         </is>
       </c>
       <c r="BM19" t="n">
-        <v>95147.94</v>
+        <v>96387.88</v>
       </c>
       <c r="BN19" t="inlineStr">
         <is>
-          <t>54403</t>
+          <t>57542</t>
         </is>
       </c>
       <c r="BO19" t="inlineStr">
         <is>
-          <t>15075.26431198157</t>
+          <t>17433.20917182799</t>
         </is>
       </c>
       <c r="BP19" t="inlineStr">
         <is>
-          <t>41581.86052973534</t>
+          <t>30401.90590098329</t>
         </is>
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>328093.0</t>
+          <t>128292.0</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
@@ -9557,7 +9557,7 @@
       </c>
       <c r="BU19" t="inlineStr">
         <is>
-          <t>-13.38</t>
+          <t>-16.42</t>
         </is>
       </c>
       <c r="BV19" t="inlineStr">
@@ -9602,7 +9602,7 @@
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
@@ -9612,12 +9612,12 @@
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>3.87</t>
+          <t>3.74</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>0.97</t>
         </is>
       </c>
       <c r="CH19" t="inlineStr">
@@ -9627,7 +9627,7 @@
       </c>
       <c r="CI19" t="inlineStr">
         <is>
-          <t>563.85</t>
+          <t>552.31</t>
         </is>
       </c>
       <c r="CJ19" t="inlineStr">
@@ -9642,12 +9642,12 @@
       </c>
       <c r="CL19" t="inlineStr">
         <is>
-          <t>94.46</t>
+          <t>93.4</t>
         </is>
       </c>
       <c r="CM19" t="inlineStr">
         <is>
-          <t>18986</t>
+          <t>18597</t>
         </is>
       </c>
       <c r="CN19" t="inlineStr">
@@ -9667,22 +9667,22 @@
       </c>
       <c r="CQ19" t="inlineStr">
         <is>
-          <t>69.3</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="CR19" t="inlineStr">
         <is>
-          <t>69.4</t>
+          <t>65.4</t>
         </is>
       </c>
       <c r="CS19" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>63.0</t>
         </is>
       </c>
       <c r="CT19" t="inlineStr">
         <is>
-          <t>65.4</t>
+          <t>63.1</t>
         </is>
       </c>
       <c r="CU19" t="inlineStr">
@@ -9714,12 +9714,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>5.29</t>
+          <t>-5.77</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>5732.0</t>
+          <t>4874.0</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -9729,7 +9729,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>69.4</t>
+          <t>65.4</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -9739,17 +9739,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>5.32</t>
+          <t>8.91</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>4.36</t>
+          <t>-0.84</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>31.33</t>
+          <t>31.50</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -9814,7 +9814,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>-10.68</t>
+          <t>-15.83</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -9839,7 +9839,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
@@ -9889,17 +9889,17 @@
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>13.20</t>
+          <t>11.23</t>
         </is>
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>3.13</t>
+          <t>-5.50</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
@@ -9910,66 +9910,66 @@
       <c r="AP20" t="inlineStr"/>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>11495</t>
+          <t>2854</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>88.57</t>
+          <t>77.78</t>
         </is>
       </c>
       <c r="AU20" t="n">
-        <v>5.92</v>
+        <v>-0.61</v>
       </c>
       <c r="AV20" t="n">
-        <v>3.44</v>
+        <v>3.75</v>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>-6.53</t>
+          <t>-6.17</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>-5.49</t>
+          <t>-5.44</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>65.52000000000001</t>
+          <t>65.8</t>
         </is>
       </c>
       <c r="AZ20" t="n">
-        <v>63.34</v>
+        <v>63.42</v>
       </c>
       <c r="BA20" t="n">
-        <v>67.76000000000001</v>
+        <v>67.59</v>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>71.7</t>
+          <t>71.48</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>71.45</t>
+          <t>72.68</t>
         </is>
       </c>
       <c r="BD20" t="n">
-        <v>-0.38</v>
+        <v>-0.3</v>
       </c>
       <c r="BE20" t="n">
-        <v>-1.32</v>
+        <v>-1.11</v>
       </c>
       <c r="BF20" t="inlineStr">
         <is>
@@ -9978,7 +9978,7 @@
       </c>
       <c r="BG20" t="inlineStr">
         <is>
-          <t>-113.04</t>
+          <t>-111.04</t>
         </is>
       </c>
       <c r="BH20" t="inlineStr">
@@ -9988,43 +9988,43 @@
       </c>
       <c r="BI20" t="inlineStr">
         <is>
-          <t>1150940.540389972</t>
+          <t>1148861.497916667</t>
         </is>
       </c>
       <c r="BJ20" t="inlineStr">
         <is>
-          <t>395091.0</t>
+          <t>328093.0</t>
         </is>
       </c>
       <c r="BK20" t="n">
-        <v>188633.6</v>
+        <v>227113</v>
       </c>
       <c r="BL20" t="inlineStr">
         <is>
-          <t>143638.2</t>
+          <t>172709.3</t>
         </is>
       </c>
       <c r="BM20" t="n">
-        <v>90036.16</v>
+        <v>95147.94</v>
       </c>
       <c r="BN20" t="inlineStr">
         <is>
-          <t>44995</t>
+          <t>54403</t>
         </is>
       </c>
       <c r="BO20" t="inlineStr">
         <is>
-          <t>10255.88318148088</t>
+          <t>15075.26431198157</t>
         </is>
       </c>
       <c r="BP20" t="inlineStr">
         <is>
-          <t>34660.90783760487</t>
+          <t>41581.86052973534</t>
         </is>
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>395091.0</t>
+          <t>328093.0</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
@@ -10044,7 +10044,7 @@
       </c>
       <c r="BU20" t="inlineStr">
         <is>
-          <t>-8.08</t>
+          <t>-13.38</t>
         </is>
       </c>
       <c r="BV20" t="inlineStr">
@@ -10089,22 +10089,22 @@
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>4.11</t>
+          <t>3.87</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>0.97</t>
         </is>
       </c>
       <c r="CH20" t="inlineStr">
@@ -10114,7 +10114,7 @@
       </c>
       <c r="CI20" t="inlineStr">
         <is>
-          <t>563.85</t>
+          <t>552.31</t>
         </is>
       </c>
       <c r="CJ20" t="inlineStr">
@@ -10129,12 +10129,12 @@
       </c>
       <c r="CL20" t="inlineStr">
         <is>
-          <t>94.46</t>
+          <t>93.4</t>
         </is>
       </c>
       <c r="CM20" t="inlineStr">
         <is>
-          <t>18986</t>
+          <t>18597</t>
         </is>
       </c>
       <c r="CN20" t="inlineStr">
@@ -10154,22 +10154,22 @@
       </c>
       <c r="CQ20" t="inlineStr">
         <is>
-          <t>66.2</t>
+          <t>69.3</t>
         </is>
       </c>
       <c r="CR20" t="inlineStr">
         <is>
-          <t>70.8</t>
+          <t>69.4</t>
         </is>
       </c>
       <c r="CS20" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="CT20" t="inlineStr">
         <is>
-          <t>69.4</t>
+          <t>65.4</t>
         </is>
       </c>
       <c r="CU20" t="inlineStr">
@@ -10201,12 +10201,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>3.12</t>
+          <t>5.29</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2198.0</t>
+          <t>5732.0</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -10216,7 +10216,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>65.9</t>
+          <t>69.4</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -10226,17 +10226,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>10.1</t>
+          <t>3.34</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>4.36</t>
+          <t>-0.84</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>43.29</t>
+          <t>31.33</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -10301,7 +10301,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>-15.19</t>
+          <t>-10.68</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -10326,7 +10326,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
@@ -10376,17 +10376,17 @@
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>5.06</t>
+          <t>13.20</t>
         </is>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>2.82</t>
+          <t>3.13</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
@@ -10397,12 +10397,12 @@
       <c r="AP21" t="inlineStr"/>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>11495</t>
+          <t>2854</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -10412,51 +10412,51 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>81.9</t>
+          <t>88.57</t>
         </is>
       </c>
       <c r="AU21" t="n">
-        <v>1.92</v>
+        <v>5.92</v>
       </c>
       <c r="AV21" t="n">
-        <v>2.5</v>
+        <v>3.44</v>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>-7.01</t>
+          <t>-6.53</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>-5.67</t>
+          <t>-5.49</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>64.66</t>
+          <t>65.52000000000001</t>
         </is>
       </c>
       <c r="AZ21" t="n">
-        <v>63.08</v>
+        <v>63.34</v>
       </c>
       <c r="BA21" t="n">
-        <v>67.84</v>
+        <v>67.76000000000001</v>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>71.91</t>
+          <t>71.7</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>44.01</t>
+          <t>71.45</t>
         </is>
       </c>
       <c r="BD21" t="n">
-        <v>-0.87</v>
+        <v>-0.38</v>
       </c>
       <c r="BE21" t="n">
-        <v>-1.55</v>
+        <v>-1.32</v>
       </c>
       <c r="BF21" t="inlineStr">
         <is>
@@ -10465,7 +10465,7 @@
       </c>
       <c r="BG21" t="inlineStr">
         <is>
-          <t>-115.37</t>
+          <t>-113.04</t>
         </is>
       </c>
       <c r="BH21" t="inlineStr">
@@ -10475,43 +10475,43 @@
       </c>
       <c r="BI21" t="inlineStr">
         <is>
-          <t>1150940.540389972</t>
+          <t>1148861.497916667</t>
         </is>
       </c>
       <c r="BJ21" t="inlineStr">
         <is>
-          <t>143717.0</t>
+          <t>395091.0</t>
         </is>
       </c>
       <c r="BK21" t="n">
-        <v>154284.2</v>
+        <v>188633.6</v>
       </c>
       <c r="BL21" t="inlineStr">
         <is>
-          <t>107669.5</t>
+          <t>143638.2</t>
         </is>
       </c>
       <c r="BM21" t="n">
-        <v>83336.67999999999</v>
+        <v>90036.16</v>
       </c>
       <c r="BN21" t="inlineStr">
         <is>
-          <t>46614</t>
+          <t>44995</t>
         </is>
       </c>
       <c r="BO21" t="inlineStr">
         <is>
-          <t>5818.605971276522</t>
+          <t>10255.88318148088</t>
         </is>
       </c>
       <c r="BP21" t="inlineStr">
         <is>
-          <t>16357.5858546469</t>
+          <t>34660.90783760487</t>
         </is>
       </c>
       <c r="BQ21" t="inlineStr">
         <is>
-          <t>143717.0</t>
+          <t>395091.0</t>
         </is>
       </c>
       <c r="BR21" t="inlineStr">
@@ -10531,7 +10531,7 @@
       </c>
       <c r="BU21" t="inlineStr">
         <is>
-          <t>-12.72</t>
+          <t>-8.08</t>
         </is>
       </c>
       <c r="BV21" t="inlineStr">
@@ -10576,22 +10576,22 @@
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>3.90</t>
+          <t>4.11</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>0.97</t>
         </is>
       </c>
       <c r="CH21" t="inlineStr">
@@ -10601,7 +10601,7 @@
       </c>
       <c r="CI21" t="inlineStr">
         <is>
-          <t>563.85</t>
+          <t>552.31</t>
         </is>
       </c>
       <c r="CJ21" t="inlineStr">
@@ -10616,12 +10616,12 @@
       </c>
       <c r="CL21" t="inlineStr">
         <is>
-          <t>94.46</t>
+          <t>93.4</t>
         </is>
       </c>
       <c r="CM21" t="inlineStr">
         <is>
-          <t>18986</t>
+          <t>18597</t>
         </is>
       </c>
       <c r="CN21" t="inlineStr">
@@ -10641,22 +10641,22 @@
       </c>
       <c r="CQ21" t="inlineStr">
         <is>
-          <t>64.1</t>
+          <t>66.2</t>
         </is>
       </c>
       <c r="CR21" t="inlineStr">
         <is>
+          <t>70.8</t>
+        </is>
+      </c>
+      <c r="CS21" t="inlineStr">
+        <is>
           <t>66.0</t>
         </is>
       </c>
-      <c r="CS21" t="inlineStr">
-        <is>
-          <t>64.0</t>
-        </is>
-      </c>
       <c r="CT21" t="inlineStr">
         <is>
-          <t>65.9</t>
+          <t>69.4</t>
         </is>
       </c>
       <c r="CU21" t="inlineStr">
@@ -10678,22 +10678,22 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>【d1】</t>
+          <t>【d2】</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>6125</t>
+          <t>5371</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-0.77</t>
+          <t>-0.89</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>3125.0</t>
+          <t>4861.0</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -10703,7 +10703,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>63.9</t>
+          <t>89.3</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -10713,17 +10713,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>12.82</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>4.36</t>
+          <t>-1.23</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>61.30</t>
+          <t>34.32</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -10733,37 +10733,37 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2025-09-17 00:00:00</t>
+          <t>2025-07-30 00:00:00</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>2025-09-22 00:00:00</t>
+          <t>2025-09-08 00:00:00</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>2025-07-25 00:00:00</t>
+          <t>2025-03-24 00:00:00</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>2025-08-22 00:00:00</t>
+          <t>2025-03-31 00:00:00</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>80.4</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>77.7</t>
+          <t>119.5</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
@@ -10773,12 +10773,12 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>73.8</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>78.5</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
@@ -10788,22 +10788,22 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>-17.76</t>
+          <t>-25.27</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>2.42</t>
+          <t>8.22</t>
         </is>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025/06/02</t>
+          <t>2024/12/10</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>67.8</t>
+          <t>77.2</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -10813,67 +10813,67 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>2025/09/30</t>
+          <t>2025/10/22</t>
         </is>
       </c>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>2025/07/07</t>
+          <t>2025/02/12</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>60.7</t>
+          <t>78.7</t>
         </is>
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>2025/10/27</t>
+          <t>2025/12/16</t>
         </is>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>71.1</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>2025/09/22</t>
+          <t>2025/11/18</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>77.7</t>
+          <t>84.6</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>2025-01-08 00:00:00</t>
+          <t>2025-11-27 00:00:00</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>7.20</t>
+          <t>4.32</t>
         </is>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>-4.54</t>
+          <t>-1.00</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
@@ -10884,121 +10884,121 @@
       <c r="AP22" t="inlineStr"/>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>65</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>11495</t>
+          <t>4861</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
         <is>
-          <t>65.71</t>
+          <t>73.44</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>71.43</t>
+          <t>86.46</t>
         </is>
       </c>
       <c r="AU22" t="n">
-        <v>-0.62</v>
+        <v>-0.18</v>
       </c>
       <c r="AV22" t="n">
-        <v>1.98</v>
+        <v>-0.58</v>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>-7.24</t>
+          <t>-2.13</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>-5.82</t>
+          <t>-9.03</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>64.3</t>
+          <t>89.46</t>
         </is>
       </c>
       <c r="AZ22" t="n">
-        <v>63.05</v>
+        <v>89.98</v>
       </c>
       <c r="BA22" t="n">
-        <v>67.97</v>
+        <v>91.95</v>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>72.17</t>
+          <t>101.07</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>34.44</t>
+          <t>24.82</t>
         </is>
       </c>
       <c r="BD22" t="n">
-        <v>-1.13</v>
+        <v>-1.08</v>
       </c>
       <c r="BE22" t="n">
-        <v>-1.72</v>
+        <v>-1.44</v>
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>10.1</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="BG22" t="inlineStr">
         <is>
-          <t>-117.06</t>
+          <t>-111.97</t>
         </is>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2025/11/27</t>
+          <t>2025/12/23</t>
         </is>
       </c>
       <c r="BI22" t="inlineStr">
         <is>
-          <t>1150940.540389972</t>
+          <t>1197568.970833333</t>
         </is>
       </c>
       <c r="BJ22" t="inlineStr">
         <is>
-          <t>204545.0</t>
+          <t>433980.0</t>
         </is>
       </c>
       <c r="BK22" t="n">
-        <v>155165.2</v>
+        <v>721245.6</v>
       </c>
       <c r="BL22" t="inlineStr">
         <is>
-          <t>96194.2</t>
+          <t>536973.1</t>
         </is>
       </c>
       <c r="BM22" t="n">
-        <v>85465.89999999999</v>
+        <v>1297321.12</v>
       </c>
       <c r="BN22" t="inlineStr">
         <is>
-          <t>58971</t>
+          <t>184272</t>
         </is>
       </c>
       <c r="BO22" t="inlineStr">
         <is>
-          <t>3902.427810663727</t>
+          <t>-121083.4994620072</t>
         </is>
       </c>
       <c r="BP22" t="inlineStr">
         <is>
-          <t>16558.71209846955</t>
+          <t>-57339.85806714394</t>
         </is>
       </c>
       <c r="BQ22" t="inlineStr">
         <is>
-          <t>204545.0</t>
+          <t>433980.0</t>
         </is>
       </c>
       <c r="BR22" t="inlineStr">
@@ -11008,27 +11008,27 @@
       </c>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>75.5</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="BT22" t="inlineStr">
         <is>
-          <t>2025/08/01</t>
+          <t>2025/07/28</t>
         </is>
       </c>
       <c r="BU22" t="inlineStr">
         <is>
-          <t>-15.36</t>
+          <t>31.32</t>
         </is>
       </c>
       <c r="BV22" t="inlineStr">
         <is>
-          <t>廣運</t>
+          <t>中光電</t>
         </is>
       </c>
       <c r="BW22" t="inlineStr">
         <is>
-          <t>廣運</t>
+          <t>中光電</t>
         </is>
       </c>
       <c r="BX22" t="inlineStr">
@@ -11048,22 +11048,22 @@
       </c>
       <c r="CA22" t="inlineStr">
         <is>
-          <t>-9.276867348133008</t>
+          <t>10.52226299517467</t>
         </is>
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>49.33864609225594</t>
+          <t>27.79118773626352</t>
         </is>
       </c>
       <c r="CC22" t="inlineStr">
         <is>
-          <t>18.62961592762674</t>
+          <t>-2.044940352257788</t>
         </is>
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
@@ -11073,87 +11073,87 @@
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>3.79</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="CH22" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>25.44</t>
         </is>
       </c>
       <c r="CI22" t="inlineStr">
         <is>
-          <t>563.85</t>
+          <t>96.02</t>
         </is>
       </c>
       <c r="CJ22" t="inlineStr">
         <is>
-          <t>17.69%</t>
+          <t>15.18%</t>
         </is>
       </c>
       <c r="CK22" t="inlineStr">
         <is>
-          <t>-6.67%</t>
+          <t>-2.36%</t>
         </is>
       </c>
       <c r="CL22" t="inlineStr">
         <is>
-          <t>94.46</t>
+          <t>93.4</t>
         </is>
       </c>
       <c r="CM22" t="inlineStr">
         <is>
-          <t>18986</t>
+          <t>34915</t>
         </is>
       </c>
       <c r="CN22" t="inlineStr">
         <is>
-          <t>自動化設備74.11%、太陽能產品12.33%、電子零組件8.12%、建材營建4.02%、其他1.41% (2024年)</t>
+          <t>節能產品47.49%、影像產品32.05%、其他20.47% (2024年)</t>
         </is>
       </c>
       <c r="CO22" t="inlineStr">
         <is>
-          <t>廣運-光電業-上櫃</t>
+          <t>中光電-光電業-上櫃</t>
         </is>
       </c>
       <c r="CP22" t="inlineStr">
         <is>
-          <t>光電業平上櫃</t>
+          <t>光電業右上上櫃</t>
         </is>
       </c>
       <c r="CQ22" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>90.3</t>
         </is>
       </c>
       <c r="CR22" t="inlineStr">
         <is>
-          <t>66.8</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="CS22" t="inlineStr">
         <is>
-          <t>63.9</t>
+          <t>88.5</t>
         </is>
       </c>
       <c r="CT22" t="inlineStr">
         <is>
-          <t>63.9</t>
+          <t>89.3</t>
         </is>
       </c>
       <c r="CU22" t="inlineStr">
         <is>
-          <t>16.88</t>
+          <t>56.54</t>
         </is>
       </c>
       <c r="CV22" t="inlineStr">
         <is>
-          <t>** 自動化 - 整體解決方案** 平面顯示器 - 生產製程及檢測設備** 電機機械 - 輸送機械及零配件、機電系統工程** 太陽能產業 - 太陽能發電設備/系統及系統工程</t>
+          <t>** 自動化 - 整體解決方案** 電腦及週邊設備 - 印表機、傳真機、掃瞄器、多功能事務機、投影機** 平面顯示器 - 背光模組** 人工智慧 - 系統整合、領域解決方案** 體驗科技 - 近眼顯示(Dear-Eye Display)、垂直應用方案、顯示技術、光學元件/模組、LCoS、OLED、Micro LED、微型顯示器/光機引擎(Light Engine)、ODM/OEM、製造、重工業、物流、安防、醫療、其他</t>
         </is>
       </c>
       <c r="CW22" t="inlineStr">
@@ -11165,22 +11165,22 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>【d1】</t>
+          <t>【d2】</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>6125</t>
+          <t>5371</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>-0.99</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1001.0</t>
+          <t>8620.0</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -11190,7 +11190,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>64.4</t>
+          <t>90.1</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -11200,17 +11200,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>12.14</t>
+          <t>-0.9</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>4.36</t>
+          <t>-1.23</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>51.99</t>
+          <t>27.91</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -11220,37 +11220,37 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2025-09-17 00:00:00</t>
+          <t>2025-07-30 00:00:00</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>2025-09-22 00:00:00</t>
+          <t>2025-09-08 00:00:00</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>2025-07-25 00:00:00</t>
+          <t>2025-03-24 00:00:00</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>2025-08-22 00:00:00</t>
+          <t>2025-03-31 00:00:00</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>80.4</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>77.7</t>
+          <t>119.5</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
@@ -11260,12 +11260,12 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>73.8</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>78.5</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
@@ -11275,22 +11275,22 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>-17.12</t>
+          <t>-24.60</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>2.42</t>
+          <t>8.22</t>
         </is>
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025/06/02</t>
+          <t>2024/12/10</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>67.8</t>
+          <t>77.2</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -11300,67 +11300,67 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.11</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>2025/09/30</t>
+          <t>2025/10/22</t>
         </is>
       </c>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>2025/07/07</t>
+          <t>2025/02/12</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>60.7</t>
+          <t>78.7</t>
         </is>
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>2025/10/27</t>
+          <t>2025/12/16</t>
         </is>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>71.1</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>2025/09/22</t>
+          <t>2025/11/18</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>77.7</t>
+          <t>84.6</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>2025-01-08 00:00:00</t>
+          <t>2025-11-27 00:00:00</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-12-24</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>2.31</t>
+          <t>7.66</t>
         </is>
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>-3.66</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
@@ -11371,121 +11371,121 @@
       <c r="AP23" t="inlineStr"/>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>65</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>11495</t>
+          <t>4861</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>85.94</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>82.86</t>
+          <t>93.31</t>
         </is>
       </c>
       <c r="AU23" t="n">
-        <v>0.31</v>
+        <v>1.78</v>
       </c>
       <c r="AV23" t="n">
-        <v>1.64</v>
+        <v>-1.93</v>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>-7.42</t>
+          <t>-2.12</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>-5.76</t>
+          <t>-9.14</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>64.2</t>
+          <t>88.52000000000001</t>
         </is>
       </c>
       <c r="AZ23" t="n">
-        <v>63.17</v>
+        <v>90.27</v>
       </c>
       <c r="BA23" t="n">
-        <v>68.22</v>
+        <v>92.22</v>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>72.39</t>
+          <t>101.49</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>33.64</t>
+          <t>22.40</t>
         </is>
       </c>
       <c r="BD23" t="n">
-        <v>-1.24</v>
+        <v>-1.18</v>
       </c>
       <c r="BE23" t="n">
-        <v>-1.87</v>
+        <v>-1.53</v>
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>10.1</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="BG23" t="inlineStr">
         <is>
-          <t>-118.53</t>
+          <t>-112.71</t>
         </is>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2025/11/27</t>
+          <t>2025/12/23</t>
         </is>
       </c>
       <c r="BI23" t="inlineStr">
         <is>
-          <t>1150940.540389972</t>
+          <t>1197568.970833333</t>
         </is>
       </c>
       <c r="BJ23" t="inlineStr">
         <is>
-          <t>64119.0</t>
+          <t>788803.0</t>
         </is>
       </c>
       <c r="BK23" t="n">
-        <v>124863.4</v>
+        <v>681655.6</v>
       </c>
       <c r="BL23" t="inlineStr">
         <is>
-          <t>82153.4</t>
+          <t>532930.9</t>
         </is>
       </c>
       <c r="BM23" t="n">
-        <v>83874.48</v>
+        <v>1334873.04</v>
       </c>
       <c r="BN23" t="inlineStr">
         <is>
-          <t>42710</t>
+          <t>148724</t>
         </is>
       </c>
       <c r="BO23" t="inlineStr">
         <is>
-          <t>1601.285212880849</t>
+          <t>-132673.2524428914</t>
         </is>
       </c>
       <c r="BP23" t="inlineStr">
         <is>
-          <t>9737.367014699441</t>
+          <t>-42904.42591940647</t>
         </is>
       </c>
       <c r="BQ23" t="inlineStr">
         <is>
-          <t>64119.0</t>
+          <t>788803.0</t>
         </is>
       </c>
       <c r="BR23" t="inlineStr">
@@ -11495,27 +11495,27 @@
       </c>
       <c r="BS23" t="inlineStr">
         <is>
-          <t>75.5</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="BT23" t="inlineStr">
         <is>
-          <t>2025/08/01</t>
+          <t>2025/07/28</t>
         </is>
       </c>
       <c r="BU23" t="inlineStr">
         <is>
-          <t>-14.70</t>
+          <t>32.50</t>
         </is>
       </c>
       <c r="BV23" t="inlineStr">
         <is>
-          <t>廣運</t>
+          <t>中光電</t>
         </is>
       </c>
       <c r="BW23" t="inlineStr">
         <is>
-          <t>廣運</t>
+          <t>中光電</t>
         </is>
       </c>
       <c r="BX23" t="inlineStr">
@@ -11535,112 +11535,112 @@
       </c>
       <c r="CA23" t="inlineStr">
         <is>
-          <t>-9.276867348133008</t>
+          <t>10.52226299517467</t>
         </is>
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>49.33864609225594</t>
+          <t>27.79118773626352</t>
         </is>
       </c>
       <c r="CC23" t="inlineStr">
         <is>
-          <t>18.62961592762674</t>
+          <t>-2.044940352257788</t>
         </is>
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>3.82</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="CH23" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>25.44</t>
         </is>
       </c>
       <c r="CI23" t="inlineStr">
         <is>
-          <t>563.85</t>
+          <t>96.02</t>
         </is>
       </c>
       <c r="CJ23" t="inlineStr">
         <is>
-          <t>17.69%</t>
+          <t>15.18%</t>
         </is>
       </c>
       <c r="CK23" t="inlineStr">
         <is>
-          <t>-6.67%</t>
+          <t>-2.36%</t>
         </is>
       </c>
       <c r="CL23" t="inlineStr">
         <is>
-          <t>94.46</t>
+          <t>93.4</t>
         </is>
       </c>
       <c r="CM23" t="inlineStr">
         <is>
-          <t>18986</t>
+          <t>34915</t>
         </is>
       </c>
       <c r="CN23" t="inlineStr">
         <is>
-          <t>自動化設備74.11%、太陽能產品12.33%、電子零組件8.12%、建材營建4.02%、其他1.41% (2024年)</t>
+          <t>節能產品47.49%、影像產品32.05%、其他20.47% (2024年)</t>
         </is>
       </c>
       <c r="CO23" t="inlineStr">
         <is>
-          <t>廣運-光電業-上櫃</t>
+          <t>中光電-光電業-上櫃</t>
         </is>
       </c>
       <c r="CP23" t="inlineStr">
         <is>
-          <t>光電業平上櫃</t>
+          <t>光電業右上上櫃</t>
         </is>
       </c>
       <c r="CQ23" t="inlineStr">
         <is>
-          <t>63.8</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="CR23" t="inlineStr">
         <is>
-          <t>64.7</t>
+          <t>93.5</t>
         </is>
       </c>
       <c r="CS23" t="inlineStr">
         <is>
-          <t>63.5</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="CT23" t="inlineStr">
         <is>
-          <t>64.4</t>
+          <t>90.1</t>
         </is>
       </c>
       <c r="CU23" t="inlineStr">
         <is>
-          <t>16.88</t>
+          <t>56.54</t>
         </is>
       </c>
       <c r="CV23" t="inlineStr">
         <is>
-          <t>** 自動化 - 整體解決方案** 平面顯示器 - 生產製程及檢測設備** 電機機械 - 輸送機械及零配件、機電系統工程** 太陽能產業 - 太陽能發電設備/系統及系統工程</t>
+          <t>** 自動化 - 整體解決方案** 電腦及週邊設備 - 印表機、傳真機、掃瞄器、多功能事務機、投影機** 平面顯示器 - 背光模組** 人工智慧 - 系統整合、領域解決方案** 體驗科技 - 近眼顯示(Dear-Eye Display)、垂直應用方案、顯示技術、光學元件/模組、LCoS、OLED、Micro LED、微型顯示器/光機引擎(Light Engine)、ODM/OEM、製造、重工業、物流、安防、醫療、其他</t>
         </is>
       </c>
       <c r="CW23" t="inlineStr">
@@ -11687,12 +11687,12 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-1.9</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>-1.46</t>
+          <t>-1.23</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -11858,12 +11858,12 @@
       <c r="AP24" t="inlineStr"/>
       <c r="AQ24" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>65</t>
         </is>
       </c>
       <c r="AR24" t="inlineStr">
         <is>
-          <t>16680</t>
+          <t>4861</t>
         </is>
       </c>
       <c r="AS24" t="inlineStr">
@@ -11936,7 +11936,7 @@
       </c>
       <c r="BI24" t="inlineStr">
         <is>
-          <t>1198350.256963788</t>
+          <t>1197568.970833333</t>
         </is>
       </c>
       <c r="BJ24" t="inlineStr">
@@ -12017,7 +12017,7 @@
       </c>
       <c r="BZ24" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="CA24" t="inlineStr">
@@ -12052,7 +12052,7 @@
       </c>
       <c r="CG24" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="CH24" t="inlineStr">
@@ -12062,7 +12062,7 @@
       </c>
       <c r="CI24" t="inlineStr">
         <is>
-          <t>97.85</t>
+          <t>96.02</t>
         </is>
       </c>
       <c r="CJ24" t="inlineStr">
@@ -12077,12 +12077,12 @@
       </c>
       <c r="CL24" t="inlineStr">
         <is>
-          <t>94.46</t>
+          <t>93.4</t>
         </is>
       </c>
       <c r="CM24" t="inlineStr">
         <is>
-          <t>35579</t>
+          <t>34915</t>
         </is>
       </c>
       <c r="CN24" t="inlineStr">
@@ -12174,12 +12174,12 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>1.87</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>-1.46</t>
+          <t>-1.23</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -12345,12 +12345,12 @@
       <c r="AP25" t="inlineStr"/>
       <c r="AQ25" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>65</t>
         </is>
       </c>
       <c r="AR25" t="inlineStr">
         <is>
-          <t>16680</t>
+          <t>4861</t>
         </is>
       </c>
       <c r="AS25" t="inlineStr">
@@ -12423,7 +12423,7 @@
       </c>
       <c r="BI25" t="inlineStr">
         <is>
-          <t>1198350.256963788</t>
+          <t>1197568.970833333</t>
         </is>
       </c>
       <c r="BJ25" t="inlineStr">
@@ -12504,7 +12504,7 @@
       </c>
       <c r="BZ25" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="CA25" t="inlineStr">
@@ -12539,7 +12539,7 @@
       </c>
       <c r="CG25" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="CH25" t="inlineStr">
@@ -12549,7 +12549,7 @@
       </c>
       <c r="CI25" t="inlineStr">
         <is>
-          <t>97.85</t>
+          <t>96.02</t>
         </is>
       </c>
       <c r="CJ25" t="inlineStr">
@@ -12564,12 +12564,12 @@
       </c>
       <c r="CL25" t="inlineStr">
         <is>
-          <t>94.46</t>
+          <t>93.4</t>
         </is>
       </c>
       <c r="CM25" t="inlineStr">
         <is>
-          <t>35579</t>
+          <t>34915</t>
         </is>
       </c>
       <c r="CN25" t="inlineStr">
@@ -12661,12 +12661,12 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>3.74</t>
+          <t>1.9</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>-1.46</t>
+          <t>-1.23</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -12832,12 +12832,12 @@
       <c r="AP26" t="inlineStr"/>
       <c r="AQ26" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>65</t>
         </is>
       </c>
       <c r="AR26" t="inlineStr">
         <is>
-          <t>16680</t>
+          <t>4861</t>
         </is>
       </c>
       <c r="AS26" t="inlineStr">
@@ -12910,7 +12910,7 @@
       </c>
       <c r="BI26" t="inlineStr">
         <is>
-          <t>1198350.256963788</t>
+          <t>1197568.970833333</t>
         </is>
       </c>
       <c r="BJ26" t="inlineStr">
@@ -12991,7 +12991,7 @@
       </c>
       <c r="BZ26" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="CA26" t="inlineStr">
@@ -13026,7 +13026,7 @@
       </c>
       <c r="CG26" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="CH26" t="inlineStr">
@@ -13036,7 +13036,7 @@
       </c>
       <c r="CI26" t="inlineStr">
         <is>
-          <t>97.85</t>
+          <t>96.02</t>
         </is>
       </c>
       <c r="CJ26" t="inlineStr">
@@ -13051,12 +13051,12 @@
       </c>
       <c r="CL26" t="inlineStr">
         <is>
-          <t>94.46</t>
+          <t>93.4</t>
         </is>
       </c>
       <c r="CM26" t="inlineStr">
         <is>
-          <t>35579</t>
+          <t>34915</t>
         </is>
       </c>
       <c r="CN26" t="inlineStr">
@@ -13148,12 +13148,12 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>7.03</t>
+          <t>5.26</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>-1.46</t>
+          <t>-1.23</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -13319,12 +13319,12 @@
       <c r="AP27" t="inlineStr"/>
       <c r="AQ27" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>65</t>
         </is>
       </c>
       <c r="AR27" t="inlineStr">
         <is>
-          <t>16680</t>
+          <t>4861</t>
         </is>
       </c>
       <c r="AS27" t="inlineStr">
@@ -13397,7 +13397,7 @@
       </c>
       <c r="BI27" t="inlineStr">
         <is>
-          <t>1198350.256963788</t>
+          <t>1197568.970833333</t>
         </is>
       </c>
       <c r="BJ27" t="inlineStr">
@@ -13478,7 +13478,7 @@
       </c>
       <c r="BZ27" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="CA27" t="inlineStr">
@@ -13513,7 +13513,7 @@
       </c>
       <c r="CG27" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="CH27" t="inlineStr">
@@ -13523,7 +13523,7 @@
       </c>
       <c r="CI27" t="inlineStr">
         <is>
-          <t>97.85</t>
+          <t>96.02</t>
         </is>
       </c>
       <c r="CJ27" t="inlineStr">
@@ -13538,12 +13538,12 @@
       </c>
       <c r="CL27" t="inlineStr">
         <is>
-          <t>94.46</t>
+          <t>93.4</t>
         </is>
       </c>
       <c r="CM27" t="inlineStr">
         <is>
-          <t>35579</t>
+          <t>34915</t>
         </is>
       </c>
       <c r="CN27" t="inlineStr">
@@ -13635,12 +13635,12 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>5.93</t>
+          <t>4.14</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>-1.46</t>
+          <t>-1.23</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -13806,12 +13806,12 @@
       <c r="AP28" t="inlineStr"/>
       <c r="AQ28" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>65</t>
         </is>
       </c>
       <c r="AR28" t="inlineStr">
         <is>
-          <t>16680</t>
+          <t>4861</t>
         </is>
       </c>
       <c r="AS28" t="inlineStr">
@@ -13884,7 +13884,7 @@
       </c>
       <c r="BI28" t="inlineStr">
         <is>
-          <t>1198350.256963788</t>
+          <t>1197568.970833333</t>
         </is>
       </c>
       <c r="BJ28" t="inlineStr">
@@ -13965,7 +13965,7 @@
       </c>
       <c r="BZ28" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="CA28" t="inlineStr">
@@ -14000,7 +14000,7 @@
       </c>
       <c r="CG28" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="CH28" t="inlineStr">
@@ -14010,7 +14010,7 @@
       </c>
       <c r="CI28" t="inlineStr">
         <is>
-          <t>97.85</t>
+          <t>96.02</t>
         </is>
       </c>
       <c r="CJ28" t="inlineStr">
@@ -14025,12 +14025,12 @@
       </c>
       <c r="CL28" t="inlineStr">
         <is>
-          <t>94.46</t>
+          <t>93.4</t>
         </is>
       </c>
       <c r="CM28" t="inlineStr">
         <is>
-          <t>35579</t>
+          <t>34915</t>
         </is>
       </c>
       <c r="CN28" t="inlineStr">
@@ -14122,12 +14122,12 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>4.95</t>
+          <t>3.14</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>-1.46</t>
+          <t>-1.23</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -14293,12 +14293,12 @@
       <c r="AP29" t="inlineStr"/>
       <c r="AQ29" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>65</t>
         </is>
       </c>
       <c r="AR29" t="inlineStr">
         <is>
-          <t>16680</t>
+          <t>4861</t>
         </is>
       </c>
       <c r="AS29" t="inlineStr">
@@ -14371,7 +14371,7 @@
       </c>
       <c r="BI29" t="inlineStr">
         <is>
-          <t>1198350.256963788</t>
+          <t>1197568.970833333</t>
         </is>
       </c>
       <c r="BJ29" t="inlineStr">
@@ -14452,7 +14452,7 @@
       </c>
       <c r="BZ29" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="CA29" t="inlineStr">
@@ -14477,7 +14477,7 @@
       </c>
       <c r="CE29" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CF29" t="inlineStr">
@@ -14487,7 +14487,7 @@
       </c>
       <c r="CG29" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="CH29" t="inlineStr">
@@ -14497,7 +14497,7 @@
       </c>
       <c r="CI29" t="inlineStr">
         <is>
-          <t>97.85</t>
+          <t>96.02</t>
         </is>
       </c>
       <c r="CJ29" t="inlineStr">
@@ -14512,12 +14512,12 @@
       </c>
       <c r="CL29" t="inlineStr">
         <is>
-          <t>94.46</t>
+          <t>93.4</t>
         </is>
       </c>
       <c r="CM29" t="inlineStr">
         <is>
-          <t>35579</t>
+          <t>34915</t>
         </is>
       </c>
       <c r="CN29" t="inlineStr">
@@ -14609,12 +14609,12 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>-1.46</t>
+          <t>-1.23</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -14780,12 +14780,12 @@
       <c r="AP30" t="inlineStr"/>
       <c r="AQ30" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>65</t>
         </is>
       </c>
       <c r="AR30" t="inlineStr">
         <is>
-          <t>16680</t>
+          <t>4861</t>
         </is>
       </c>
       <c r="AS30" t="inlineStr">
@@ -14858,7 +14858,7 @@
       </c>
       <c r="BI30" t="inlineStr">
         <is>
-          <t>1198350.256963788</t>
+          <t>1197568.970833333</t>
         </is>
       </c>
       <c r="BJ30" t="inlineStr">
@@ -14939,7 +14939,7 @@
       </c>
       <c r="BZ30" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="CA30" t="inlineStr">
@@ -14964,7 +14964,7 @@
       </c>
       <c r="CE30" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CF30" t="inlineStr">
@@ -14974,7 +14974,7 @@
       </c>
       <c r="CG30" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="CH30" t="inlineStr">
@@ -14984,7 +14984,7 @@
       </c>
       <c r="CI30" t="inlineStr">
         <is>
-          <t>97.85</t>
+          <t>96.02</t>
         </is>
       </c>
       <c r="CJ30" t="inlineStr">
@@ -14999,12 +14999,12 @@
       </c>
       <c r="CL30" t="inlineStr">
         <is>
-          <t>94.46</t>
+          <t>93.4</t>
         </is>
       </c>
       <c r="CM30" t="inlineStr">
         <is>
-          <t>35579</t>
+          <t>34915</t>
         </is>
       </c>
       <c r="CN30" t="inlineStr">
@@ -15096,12 +15096,12 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2.64</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>-1.46</t>
+          <t>-1.23</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -15267,12 +15267,12 @@
       <c r="AP31" t="inlineStr"/>
       <c r="AQ31" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>65</t>
         </is>
       </c>
       <c r="AR31" t="inlineStr">
         <is>
-          <t>16680</t>
+          <t>4861</t>
         </is>
       </c>
       <c r="AS31" t="inlineStr">
@@ -15345,7 +15345,7 @@
       </c>
       <c r="BI31" t="inlineStr">
         <is>
-          <t>1198350.256963788</t>
+          <t>1197568.970833333</t>
         </is>
       </c>
       <c r="BJ31" t="inlineStr">
@@ -15426,7 +15426,7 @@
       </c>
       <c r="BZ31" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="CA31" t="inlineStr">
@@ -15461,7 +15461,7 @@
       </c>
       <c r="CG31" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="CH31" t="inlineStr">
@@ -15471,7 +15471,7 @@
       </c>
       <c r="CI31" t="inlineStr">
         <is>
-          <t>97.85</t>
+          <t>96.02</t>
         </is>
       </c>
       <c r="CJ31" t="inlineStr">
@@ -15486,12 +15486,12 @@
       </c>
       <c r="CL31" t="inlineStr">
         <is>
-          <t>94.46</t>
+          <t>93.4</t>
         </is>
       </c>
       <c r="CM31" t="inlineStr">
         <is>
-          <t>35579</t>
+          <t>34915</t>
         </is>
       </c>
       <c r="CN31" t="inlineStr">
@@ -15540,1467 +15540,6 @@
         </is>
       </c>
       <c r="CW31" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>【d1】</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>5371</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>0.11</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>4395.0</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>88.9</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>2.31</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>-1.46</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>-41.45</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L32" t="inlineStr">
-        <is>
-          <t>65.0</t>
-        </is>
-      </c>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>2025-07-30 00:00:00</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr">
-        <is>
-          <t>2025-09-08 00:00:00</t>
-        </is>
-      </c>
-      <c r="O32" t="inlineStr">
-        <is>
-          <t>2025-03-24 00:00:00</t>
-        </is>
-      </c>
-      <c r="P32" t="inlineStr">
-        <is>
-          <t>2025-03-31 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q32" t="inlineStr">
-        <is>
-          <t>79.0</t>
-        </is>
-      </c>
-      <c r="R32" t="inlineStr">
-        <is>
-          <t>119.5</t>
-        </is>
-      </c>
-      <c r="S32" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T32" t="inlineStr">
-        <is>
-          <t>84.0</t>
-        </is>
-      </c>
-      <c r="U32" t="inlineStr">
-        <is>
-          <t>73.0</t>
-        </is>
-      </c>
-      <c r="V32" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W32" t="inlineStr">
-        <is>
-          <t>-25.61</t>
-        </is>
-      </c>
-      <c r="X32" t="inlineStr">
-        <is>
-          <t>8.22</t>
-        </is>
-      </c>
-      <c r="Y32" t="inlineStr">
-        <is>
-          <t>2024/12/10</t>
-        </is>
-      </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>77.2</t>
-        </is>
-      </c>
-      <c r="AA32" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>-0.2</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>2025/10/22</t>
-        </is>
-      </c>
-      <c r="AD32" t="inlineStr">
-        <is>
-          <t>100.0</t>
-        </is>
-      </c>
-      <c r="AE32" t="inlineStr">
-        <is>
-          <t>2025/02/12</t>
-        </is>
-      </c>
-      <c r="AF32" t="inlineStr">
-        <is>
-          <t>78.7</t>
-        </is>
-      </c>
-      <c r="AG32" t="inlineStr">
-        <is>
-          <t>2025/12/16</t>
-        </is>
-      </c>
-      <c r="AH32" t="inlineStr">
-        <is>
-          <t>86.5</t>
-        </is>
-      </c>
-      <c r="AI32" t="inlineStr">
-        <is>
-          <t>2025/11/18</t>
-        </is>
-      </c>
-      <c r="AJ32" t="inlineStr">
-        <is>
-          <t>84.6</t>
-        </is>
-      </c>
-      <c r="AK32" t="inlineStr">
-        <is>
-          <t>2025-11-27 00:00:00</t>
-        </is>
-      </c>
-      <c r="AL32" t="inlineStr">
-        <is>
-          <t>2025-12-11</t>
-        </is>
-      </c>
-      <c r="AM32" t="inlineStr">
-        <is>
-          <t>3.91</t>
-        </is>
-      </c>
-      <c r="AN32" t="inlineStr">
-        <is>
-          <t>-1.35</t>
-        </is>
-      </c>
-      <c r="AO32" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AP32" t="inlineStr"/>
-      <c r="AQ32" t="inlineStr">
-        <is>
-          <t>110</t>
-        </is>
-      </c>
-      <c r="AR32" t="inlineStr">
-        <is>
-          <t>16680</t>
-        </is>
-      </c>
-      <c r="AS32" t="inlineStr">
-        <is>
-          <t>2.33</t>
-        </is>
-      </c>
-      <c r="AT32" t="inlineStr">
-        <is>
-          <t>5.68</t>
-        </is>
-      </c>
-      <c r="AU32" t="n">
-        <v>-2.18</v>
-      </c>
-      <c r="AV32" t="n">
-        <v>0.88</v>
-      </c>
-      <c r="AW32" t="inlineStr">
-        <is>
-          <t>-6.91</t>
-        </is>
-      </c>
-      <c r="AX32" t="inlineStr">
-        <is>
-          <t>-6.96</t>
-        </is>
-      </c>
-      <c r="AY32" t="inlineStr">
-        <is>
-          <t>90.88000000000001</t>
-        </is>
-      </c>
-      <c r="AZ32" t="n">
-        <v>90.09</v>
-      </c>
-      <c r="BA32" t="n">
-        <v>96.78</v>
-      </c>
-      <c r="BB32" t="inlineStr">
-        <is>
-          <t>104.03</t>
-        </is>
-      </c>
-      <c r="BC32" t="inlineStr">
-        <is>
-          <t>19.57</t>
-        </is>
-      </c>
-      <c r="BD32" t="n">
-        <v>-1.19</v>
-      </c>
-      <c r="BE32" t="n">
-        <v>-1.48</v>
-      </c>
-      <c r="BF32" t="inlineStr">
-        <is>
-          <t>12.0</t>
-        </is>
-      </c>
-      <c r="BG32" t="inlineStr">
-        <is>
-          <t>-112.30</t>
-        </is>
-      </c>
-      <c r="BH32" t="inlineStr">
-        <is>
-          <t>2025/12/23</t>
-        </is>
-      </c>
-      <c r="BI32" t="inlineStr">
-        <is>
-          <t>1198350.256963788</t>
-        </is>
-      </c>
-      <c r="BJ32" t="inlineStr">
-        <is>
-          <t>393558.0</t>
-        </is>
-      </c>
-      <c r="BK32" t="n">
-        <v>447237.6</v>
-      </c>
-      <c r="BL32" t="inlineStr">
-        <is>
-          <t>763802.0</t>
-        </is>
-      </c>
-      <c r="BM32" t="n">
-        <v>1655061.18</v>
-      </c>
-      <c r="BN32" t="inlineStr">
-        <is>
-          <t>-316564</t>
-        </is>
-      </c>
-      <c r="BO32" t="inlineStr">
-        <is>
-          <t>-121401.5499121291</t>
-        </is>
-      </c>
-      <c r="BP32" t="inlineStr">
-        <is>
-          <t>-208940.5799852051</t>
-        </is>
-      </c>
-      <c r="BQ32" t="inlineStr">
-        <is>
-          <t>393558.0</t>
-        </is>
-      </c>
-      <c r="BR32" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BS32" t="inlineStr">
-        <is>
-          <t>68.0</t>
-        </is>
-      </c>
-      <c r="BT32" t="inlineStr">
-        <is>
-          <t>2025/07/28</t>
-        </is>
-      </c>
-      <c r="BU32" t="inlineStr">
-        <is>
-          <t>30.74</t>
-        </is>
-      </c>
-      <c r="BV32" t="inlineStr">
-        <is>
-          <t>中光電</t>
-        </is>
-      </c>
-      <c r="BW32" t="inlineStr">
-        <is>
-          <t>中光電</t>
-        </is>
-      </c>
-      <c r="BX32" t="inlineStr">
-        <is>
-          <t>光電業</t>
-        </is>
-      </c>
-      <c r="BY32" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BZ32" t="inlineStr">
-        <is>
-          <t>1.27</t>
-        </is>
-      </c>
-      <c r="CA32" t="inlineStr">
-        <is>
-          <t>10.52226299517467</t>
-        </is>
-      </c>
-      <c r="CB32" t="inlineStr">
-        <is>
-          <t>27.79118773626352</t>
-        </is>
-      </c>
-      <c r="CC32" t="inlineStr">
-        <is>
-          <t>-2.044940352257788</t>
-        </is>
-      </c>
-      <c r="CD32" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="CE32" t="inlineStr">
-        <is>
-          <t>價跌量增</t>
-        </is>
-      </c>
-      <c r="CF32" t="inlineStr">
-        <is>
-          <t>1.57</t>
-        </is>
-      </c>
-      <c r="CG32" t="inlineStr">
-        <is>
-          <t>1.65</t>
-        </is>
-      </c>
-      <c r="CH32" t="inlineStr">
-        <is>
-          <t>25.44</t>
-        </is>
-      </c>
-      <c r="CI32" t="inlineStr">
-        <is>
-          <t>97.85</t>
-        </is>
-      </c>
-      <c r="CJ32" t="inlineStr">
-        <is>
-          <t>15.18%</t>
-        </is>
-      </c>
-      <c r="CK32" t="inlineStr">
-        <is>
-          <t>-2.36%</t>
-        </is>
-      </c>
-      <c r="CL32" t="inlineStr">
-        <is>
-          <t>94.46</t>
-        </is>
-      </c>
-      <c r="CM32" t="inlineStr">
-        <is>
-          <t>35579</t>
-        </is>
-      </c>
-      <c r="CN32" t="inlineStr">
-        <is>
-          <t>節能產品47.49%、影像產品32.05%、其他20.47% (2024年)</t>
-        </is>
-      </c>
-      <c r="CO32" t="inlineStr">
-        <is>
-          <t>中光電-光電業-上櫃</t>
-        </is>
-      </c>
-      <c r="CP32" t="inlineStr">
-        <is>
-          <t>光電業右上上櫃</t>
-        </is>
-      </c>
-      <c r="CQ32" t="inlineStr">
-        <is>
-          <t>89.7</t>
-        </is>
-      </c>
-      <c r="CR32" t="inlineStr">
-        <is>
-          <t>90.6</t>
-        </is>
-      </c>
-      <c r="CS32" t="inlineStr">
-        <is>
-          <t>88.4</t>
-        </is>
-      </c>
-      <c r="CT32" t="inlineStr">
-        <is>
-          <t>88.9</t>
-        </is>
-      </c>
-      <c r="CU32" t="inlineStr">
-        <is>
-          <t>56.54</t>
-        </is>
-      </c>
-      <c r="CV32" t="inlineStr">
-        <is>
-          <t>** 自動化 - 整體解決方案** 電腦及週邊設備 - 印表機、傳真機、掃瞄器、多功能事務機、投影機** 平面顯示器 - 背光模組** 人工智慧 - 系統整合、領域解決方案** 體驗科技 - 近眼顯示(Dear-Eye Display)、垂直應用方案、顯示技術、光學元件/模組、LCoS、OLED、Micro LED、微型顯示器/光機引擎(Light Engine)、ODM/OEM、製造、重工業、物流、安防、醫療、其他</t>
-        </is>
-      </c>
-      <c r="CW32" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>【d1】</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>5371</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>-3.47</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>7102.0</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>88.8</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>2.42</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>-1.46</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>-49.46</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L33" t="inlineStr">
-        <is>
-          <t>65.0</t>
-        </is>
-      </c>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>2025-07-30 00:00:00</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t>2025-09-08 00:00:00</t>
-        </is>
-      </c>
-      <c r="O33" t="inlineStr">
-        <is>
-          <t>2025-03-24 00:00:00</t>
-        </is>
-      </c>
-      <c r="P33" t="inlineStr">
-        <is>
-          <t>2025-03-31 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q33" t="inlineStr">
-        <is>
-          <t>79.0</t>
-        </is>
-      </c>
-      <c r="R33" t="inlineStr">
-        <is>
-          <t>119.5</t>
-        </is>
-      </c>
-      <c r="S33" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T33" t="inlineStr">
-        <is>
-          <t>84.0</t>
-        </is>
-      </c>
-      <c r="U33" t="inlineStr">
-        <is>
-          <t>73.0</t>
-        </is>
-      </c>
-      <c r="V33" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W33" t="inlineStr">
-        <is>
-          <t>-25.69</t>
-        </is>
-      </c>
-      <c r="X33" t="inlineStr">
-        <is>
-          <t>8.22</t>
-        </is>
-      </c>
-      <c r="Y33" t="inlineStr">
-        <is>
-          <t>2024/12/10</t>
-        </is>
-      </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>77.2</t>
-        </is>
-      </c>
-      <c r="AA33" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>-0.31</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>2025/10/22</t>
-        </is>
-      </c>
-      <c r="AD33" t="inlineStr">
-        <is>
-          <t>100.0</t>
-        </is>
-      </c>
-      <c r="AE33" t="inlineStr">
-        <is>
-          <t>2025/02/12</t>
-        </is>
-      </c>
-      <c r="AF33" t="inlineStr">
-        <is>
-          <t>78.7</t>
-        </is>
-      </c>
-      <c r="AG33" t="inlineStr">
-        <is>
-          <t>2025/12/16</t>
-        </is>
-      </c>
-      <c r="AH33" t="inlineStr">
-        <is>
-          <t>86.5</t>
-        </is>
-      </c>
-      <c r="AI33" t="inlineStr">
-        <is>
-          <t>2025/11/18</t>
-        </is>
-      </c>
-      <c r="AJ33" t="inlineStr">
-        <is>
-          <t>84.6</t>
-        </is>
-      </c>
-      <c r="AK33" t="inlineStr">
-        <is>
-          <t>2025-11-27 00:00:00</t>
-        </is>
-      </c>
-      <c r="AL33" t="inlineStr">
-        <is>
-          <t>2025-12-10</t>
-        </is>
-      </c>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>6.31</t>
-        </is>
-      </c>
-      <c r="AN33" t="inlineStr">
-        <is>
-          <t>-4.05</t>
-        </is>
-      </c>
-      <c r="AO33" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AP33" t="inlineStr"/>
-      <c r="AQ33" t="inlineStr">
-        <is>
-          <t>110</t>
-        </is>
-      </c>
-      <c r="AR33" t="inlineStr">
-        <is>
-          <t>16680</t>
-        </is>
-      </c>
-      <c r="AS33" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AT33" t="inlineStr">
-        <is>
-          <t>9.61</t>
-        </is>
-      </c>
-      <c r="AU33" t="n">
-        <v>-3.18</v>
-      </c>
-      <c r="AV33" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AW33" t="inlineStr">
-        <is>
-          <t>-7.16</t>
-        </is>
-      </c>
-      <c r="AX33" t="inlineStr">
-        <is>
-          <t>-6.61</t>
-        </is>
-      </c>
-      <c r="AY33" t="inlineStr">
-        <is>
-          <t>91.72</t>
-        </is>
-      </c>
-      <c r="AZ33" t="n">
-        <v>90.22</v>
-      </c>
-      <c r="BA33" t="n">
-        <v>97.18000000000001</v>
-      </c>
-      <c r="BB33" t="inlineStr">
-        <is>
-          <t>104.06</t>
-        </is>
-      </c>
-      <c r="BC33" t="inlineStr">
-        <is>
-          <t>31.61</t>
-        </is>
-      </c>
-      <c r="BD33" t="n">
-        <v>-1.06</v>
-      </c>
-      <c r="BE33" t="n">
-        <v>-1.55</v>
-      </c>
-      <c r="BF33" t="inlineStr">
-        <is>
-          <t>12.0</t>
-        </is>
-      </c>
-      <c r="BG33" t="inlineStr">
-        <is>
-          <t>-112.90</t>
-        </is>
-      </c>
-      <c r="BH33" t="inlineStr">
-        <is>
-          <t>2025/12/23</t>
-        </is>
-      </c>
-      <c r="BI33" t="inlineStr">
-        <is>
-          <t>1198350.256963788</t>
-        </is>
-      </c>
-      <c r="BJ33" t="inlineStr">
-        <is>
-          <t>640841.0</t>
-        </is>
-      </c>
-      <c r="BK33" t="n">
-        <v>672584.4</v>
-      </c>
-      <c r="BL33" t="inlineStr">
-        <is>
-          <t>1330779.6</t>
-        </is>
-      </c>
-      <c r="BM33" t="n">
-        <v>1690946.96</v>
-      </c>
-      <c r="BN33" t="inlineStr">
-        <is>
-          <t>-658195</t>
-        </is>
-      </c>
-      <c r="BO33" t="inlineStr">
-        <is>
-          <t>-105485.3626261153</t>
-        </is>
-      </c>
-      <c r="BP33" t="inlineStr">
-        <is>
-          <t>-196085.1223125921</t>
-        </is>
-      </c>
-      <c r="BQ33" t="inlineStr">
-        <is>
-          <t>640841.0</t>
-        </is>
-      </c>
-      <c r="BR33" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BS33" t="inlineStr">
-        <is>
-          <t>68.0</t>
-        </is>
-      </c>
-      <c r="BT33" t="inlineStr">
-        <is>
-          <t>2025/07/28</t>
-        </is>
-      </c>
-      <c r="BU33" t="inlineStr">
-        <is>
-          <t>30.59</t>
-        </is>
-      </c>
-      <c r="BV33" t="inlineStr">
-        <is>
-          <t>中光電</t>
-        </is>
-      </c>
-      <c r="BW33" t="inlineStr">
-        <is>
-          <t>中光電</t>
-        </is>
-      </c>
-      <c r="BX33" t="inlineStr">
-        <is>
-          <t>光電業</t>
-        </is>
-      </c>
-      <c r="BY33" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BZ33" t="inlineStr">
-        <is>
-          <t>1.27</t>
-        </is>
-      </c>
-      <c r="CA33" t="inlineStr">
-        <is>
-          <t>10.52226299517467</t>
-        </is>
-      </c>
-      <c r="CB33" t="inlineStr">
-        <is>
-          <t>27.79118773626352</t>
-        </is>
-      </c>
-      <c r="CC33" t="inlineStr">
-        <is>
-          <t>-2.044940352257788</t>
-        </is>
-      </c>
-      <c r="CD33" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="CE33" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="CF33" t="inlineStr">
-        <is>
-          <t>1.57</t>
-        </is>
-      </c>
-      <c r="CG33" t="inlineStr">
-        <is>
-          <t>1.65</t>
-        </is>
-      </c>
-      <c r="CH33" t="inlineStr">
-        <is>
-          <t>25.44</t>
-        </is>
-      </c>
-      <c r="CI33" t="inlineStr">
-        <is>
-          <t>97.85</t>
-        </is>
-      </c>
-      <c r="CJ33" t="inlineStr">
-        <is>
-          <t>15.18%</t>
-        </is>
-      </c>
-      <c r="CK33" t="inlineStr">
-        <is>
-          <t>-2.36%</t>
-        </is>
-      </c>
-      <c r="CL33" t="inlineStr">
-        <is>
-          <t>94.46</t>
-        </is>
-      </c>
-      <c r="CM33" t="inlineStr">
-        <is>
-          <t>35579</t>
-        </is>
-      </c>
-      <c r="CN33" t="inlineStr">
-        <is>
-          <t>節能產品47.49%、影像產品32.05%、其他20.47% (2024年)</t>
-        </is>
-      </c>
-      <c r="CO33" t="inlineStr">
-        <is>
-          <t>中光電-光電業-上櫃</t>
-        </is>
-      </c>
-      <c r="CP33" t="inlineStr">
-        <is>
-          <t>光電業右上上櫃</t>
-        </is>
-      </c>
-      <c r="CQ33" t="inlineStr">
-        <is>
-          <t>92.2</t>
-        </is>
-      </c>
-      <c r="CR33" t="inlineStr">
-        <is>
-          <t>92.7</t>
-        </is>
-      </c>
-      <c r="CS33" t="inlineStr">
-        <is>
-          <t>88.5</t>
-        </is>
-      </c>
-      <c r="CT33" t="inlineStr">
-        <is>
-          <t>88.8</t>
-        </is>
-      </c>
-      <c r="CU33" t="inlineStr">
-        <is>
-          <t>56.54</t>
-        </is>
-      </c>
-      <c r="CV33" t="inlineStr">
-        <is>
-          <t>** 自動化 - 整體解決方案** 電腦及週邊設備 - 印表機、傳真機、掃瞄器、多功能事務機、投影機** 平面顯示器 - 背光模組** 人工智慧 - 系統整合、領域解決方案** 體驗科技 - 近眼顯示(Dear-Eye Display)、垂直應用方案、顯示技術、光學元件/模組、LCoS、OLED、Micro LED、微型顯示器/光機引擎(Light Engine)、ODM/OEM、製造、重工業、物流、安防、醫療、其他</t>
-        </is>
-      </c>
-      <c r="CW33" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>【d1】</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>5371</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>-0.75</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>6095.0</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>92.0</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>-1.1</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>-1.46</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>-48.65</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L34" t="inlineStr">
-        <is>
-          <t>65.0</t>
-        </is>
-      </c>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>2025-07-30 00:00:00</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr">
-        <is>
-          <t>2025-09-08 00:00:00</t>
-        </is>
-      </c>
-      <c r="O34" t="inlineStr">
-        <is>
-          <t>2025-03-24 00:00:00</t>
-        </is>
-      </c>
-      <c r="P34" t="inlineStr">
-        <is>
-          <t>2025-03-31 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q34" t="inlineStr">
-        <is>
-          <t>79.0</t>
-        </is>
-      </c>
-      <c r="R34" t="inlineStr">
-        <is>
-          <t>119.5</t>
-        </is>
-      </c>
-      <c r="S34" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T34" t="inlineStr">
-        <is>
-          <t>84.0</t>
-        </is>
-      </c>
-      <c r="U34" t="inlineStr">
-        <is>
-          <t>73.0</t>
-        </is>
-      </c>
-      <c r="V34" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W34" t="inlineStr">
-        <is>
-          <t>-23.01</t>
-        </is>
-      </c>
-      <c r="X34" t="inlineStr">
-        <is>
-          <t>8.22</t>
-        </is>
-      </c>
-      <c r="Y34" t="inlineStr">
-        <is>
-          <t>2024/12/10</t>
-        </is>
-      </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>77.2</t>
-        </is>
-      </c>
-      <c r="AA34" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>-0.13</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>2025/10/22</t>
-        </is>
-      </c>
-      <c r="AD34" t="inlineStr">
-        <is>
-          <t>100.0</t>
-        </is>
-      </c>
-      <c r="AE34" t="inlineStr">
-        <is>
-          <t>2025/02/12</t>
-        </is>
-      </c>
-      <c r="AF34" t="inlineStr">
-        <is>
-          <t>78.7</t>
-        </is>
-      </c>
-      <c r="AG34" t="inlineStr">
-        <is>
-          <t>2025/12/16</t>
-        </is>
-      </c>
-      <c r="AH34" t="inlineStr">
-        <is>
-          <t>86.5</t>
-        </is>
-      </c>
-      <c r="AI34" t="inlineStr">
-        <is>
-          <t>2025/11/18</t>
-        </is>
-      </c>
-      <c r="AJ34" t="inlineStr">
-        <is>
-          <t>84.6</t>
-        </is>
-      </c>
-      <c r="AK34" t="inlineStr">
-        <is>
-          <t>2025-11-27 00:00:00</t>
-        </is>
-      </c>
-      <c r="AL34" t="inlineStr">
-        <is>
-          <t>2025-12-09</t>
-        </is>
-      </c>
-      <c r="AM34" t="inlineStr">
-        <is>
-          <t>5.42</t>
-        </is>
-      </c>
-      <c r="AN34" t="inlineStr">
-        <is>
-          <t>-2.83</t>
-        </is>
-      </c>
-      <c r="AO34" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AP34" t="inlineStr"/>
-      <c r="AQ34" t="inlineStr">
-        <is>
-          <t>110</t>
-        </is>
-      </c>
-      <c r="AR34" t="inlineStr">
-        <is>
-          <t>16680</t>
-        </is>
-      </c>
-      <c r="AS34" t="inlineStr">
-        <is>
-          <t>14.71</t>
-        </is>
-      </c>
-      <c r="AT34" t="inlineStr">
-        <is>
-          <t>13.31</t>
-        </is>
-      </c>
-      <c r="AU34" t="n">
-        <v>-0.61</v>
-      </c>
-      <c r="AV34" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AW34" t="inlineStr">
-        <is>
-          <t>-7.46</t>
-        </is>
-      </c>
-      <c r="AX34" t="inlineStr">
-        <is>
-          <t>-6.15</t>
-        </is>
-      </c>
-      <c r="AY34" t="inlineStr">
-        <is>
-          <t>92.55999999999999</t>
-        </is>
-      </c>
-      <c r="AZ34" t="n">
-        <v>90.40000000000001</v>
-      </c>
-      <c r="BA34" t="n">
-        <v>97.69</v>
-      </c>
-      <c r="BB34" t="inlineStr">
-        <is>
-          <t>104.1</t>
-        </is>
-      </c>
-      <c r="BC34" t="inlineStr">
-        <is>
-          <t>47.95</t>
-        </is>
-      </c>
-      <c r="BD34" t="n">
-        <v>-0.87</v>
-      </c>
-      <c r="BE34" t="n">
-        <v>-1.67</v>
-      </c>
-      <c r="BF34" t="inlineStr">
-        <is>
-          <t>12.0</t>
-        </is>
-      </c>
-      <c r="BG34" t="inlineStr">
-        <is>
-          <t>-113.92</t>
-        </is>
-      </c>
-      <c r="BH34" t="inlineStr">
-        <is>
-          <t>2025/12/23</t>
-        </is>
-      </c>
-      <c r="BI34" t="inlineStr">
-        <is>
-          <t>1198350.256963788</t>
-        </is>
-      </c>
-      <c r="BJ34" t="inlineStr">
-        <is>
-          <t>567794.0</t>
-        </is>
-      </c>
-      <c r="BK34" t="n">
-        <v>727242.2</v>
-      </c>
-      <c r="BL34" t="inlineStr">
-        <is>
-          <t>1416371.6</t>
-        </is>
-      </c>
-      <c r="BM34" t="n">
-        <v>1708425.82</v>
-      </c>
-      <c r="BN34" t="inlineStr">
-        <is>
-          <t>-689129</t>
-        </is>
-      </c>
-      <c r="BO34" t="inlineStr">
-        <is>
-          <t>-89012.67904675592</t>
-        </is>
-      </c>
-      <c r="BP34" t="inlineStr">
-        <is>
-          <t>-197211.7498405522</t>
-        </is>
-      </c>
-      <c r="BQ34" t="inlineStr">
-        <is>
-          <t>567794.0</t>
-        </is>
-      </c>
-      <c r="BR34" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BS34" t="inlineStr">
-        <is>
-          <t>68.0</t>
-        </is>
-      </c>
-      <c r="BT34" t="inlineStr">
-        <is>
-          <t>2025/07/28</t>
-        </is>
-      </c>
-      <c r="BU34" t="inlineStr">
-        <is>
-          <t>35.29</t>
-        </is>
-      </c>
-      <c r="BV34" t="inlineStr">
-        <is>
-          <t>中光電</t>
-        </is>
-      </c>
-      <c r="BW34" t="inlineStr">
-        <is>
-          <t>中光電</t>
-        </is>
-      </c>
-      <c r="BX34" t="inlineStr">
-        <is>
-          <t>光電業</t>
-        </is>
-      </c>
-      <c r="BY34" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BZ34" t="inlineStr">
-        <is>
-          <t>1.27</t>
-        </is>
-      </c>
-      <c r="CA34" t="inlineStr">
-        <is>
-          <t>10.52226299517467</t>
-        </is>
-      </c>
-      <c r="CB34" t="inlineStr">
-        <is>
-          <t>27.79118773626352</t>
-        </is>
-      </c>
-      <c r="CC34" t="inlineStr">
-        <is>
-          <t>-2.044940352257788</t>
-        </is>
-      </c>
-      <c r="CD34" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="CE34" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="CF34" t="inlineStr">
-        <is>
-          <t>1.63</t>
-        </is>
-      </c>
-      <c r="CG34" t="inlineStr">
-        <is>
-          <t>1.65</t>
-        </is>
-      </c>
-      <c r="CH34" t="inlineStr">
-        <is>
-          <t>25.44</t>
-        </is>
-      </c>
-      <c r="CI34" t="inlineStr">
-        <is>
-          <t>97.85</t>
-        </is>
-      </c>
-      <c r="CJ34" t="inlineStr">
-        <is>
-          <t>15.18%</t>
-        </is>
-      </c>
-      <c r="CK34" t="inlineStr">
-        <is>
-          <t>-2.36%</t>
-        </is>
-      </c>
-      <c r="CL34" t="inlineStr">
-        <is>
-          <t>94.46</t>
-        </is>
-      </c>
-      <c r="CM34" t="inlineStr">
-        <is>
-          <t>35579</t>
-        </is>
-      </c>
-      <c r="CN34" t="inlineStr">
-        <is>
-          <t>節能產品47.49%、影像產品32.05%、其他20.47% (2024年)</t>
-        </is>
-      </c>
-      <c r="CO34" t="inlineStr">
-        <is>
-          <t>中光電-光電業-上櫃</t>
-        </is>
-      </c>
-      <c r="CP34" t="inlineStr">
-        <is>
-          <t>光電業右上上櫃</t>
-        </is>
-      </c>
-      <c r="CQ34" t="inlineStr">
-        <is>
-          <t>93.1</t>
-        </is>
-      </c>
-      <c r="CR34" t="inlineStr">
-        <is>
-          <t>94.6</t>
-        </is>
-      </c>
-      <c r="CS34" t="inlineStr">
-        <is>
-          <t>92.0</t>
-        </is>
-      </c>
-      <c r="CT34" t="inlineStr">
-        <is>
-          <t>92.0</t>
-        </is>
-      </c>
-      <c r="CU34" t="inlineStr">
-        <is>
-          <t>56.54</t>
-        </is>
-      </c>
-      <c r="CV34" t="inlineStr">
-        <is>
-          <t>** 自動化 - 整體解決方案** 電腦及週邊設備 - 印表機、傳真機、掃瞄器、多功能事務機、投影機** 平面顯示器 - 背光模組** 人工智慧 - 系統整合、領域解決方案** 體驗科技 - 近眼顯示(Dear-Eye Display)、垂直應用方案、顯示技術、光學元件/模組、LCoS、OLED、Micro LED、微型顯示器/光機引擎(Light Engine)、ODM/OEM、製造、重工業、物流、安防、醫療、其他</t>
-        </is>
-      </c>
-      <c r="CW34" t="inlineStr">
         <is>
           <t>False</t>
         </is>

--- a/Result/checksun_type/整體解決方案.xlsx
+++ b/Result/checksun_type/整體解決方案.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CW31"/>
+  <dimension ref="A1:CW28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -938,7 +938,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>價_量;【b1】</t>
+          <t>【b1】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -948,12 +948,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-0.97</t>
+          <t>-1.83</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>12182.0</t>
+          <t>3877.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -963,7 +963,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>30.55</t>
+          <t>29.5</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -978,12 +978,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>60.09</t>
+          <t>52.64</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -993,7 +993,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -1003,7 +1003,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>2025-12-31 00:00:00</t>
+          <t>2026-01-04 00:00:00</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -1043,7 +1043,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>-0.97</t>
+          <t>-4.38</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
@@ -1073,7 +1073,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -1118,22 +1118,22 @@
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>2025-12-23 00:00:00</t>
+          <t>2025-12-22 00:00:00</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2026-01-02</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>45.93</t>
+          <t>14.62</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>2.97</t>
+          <t>-4.24</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
@@ -1144,75 +1144,75 @@
       <c r="AP2" t="inlineStr"/>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>32</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>12182</t>
+          <t>3877</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>95.74</t>
+          <t>80.71</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>98.58</t>
+          <t>88.37</t>
         </is>
       </c>
       <c r="AU2" t="n">
-        <v>8.140000000000001</v>
+        <v>-1.01</v>
       </c>
       <c r="AV2" t="n">
-        <v>16.53</v>
+        <v>18.7</v>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>6.33</t>
+          <t>8.81</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>-2.87</t>
+          <t>-2.09</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>28.25</t>
+          <t>29.8</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>24.24</v>
+        <v>25.1</v>
       </c>
       <c r="BA2" t="n">
-        <v>22.8</v>
+        <v>23.07</v>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>23.47</t>
+          <t>23.56</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>71.73</t>
+          <t>43.99</t>
         </is>
       </c>
       <c r="BD2" t="n">
-        <v>1.87</v>
+        <v>2.06</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.09</v>
+        <v>1.43</v>
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>3.04</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>-64.19</t>
+          <t>-14.36</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -1222,48 +1222,48 @@
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>66670.20914127423</t>
+          <t>43637.08144329896</t>
         </is>
       </c>
       <c r="BJ2" t="inlineStr">
         <is>
-          <t>367884.0</t>
+          <t>116293.0</t>
         </is>
       </c>
       <c r="BK2" t="n">
-        <v>226272.4</v>
+        <v>262896.2</v>
       </c>
       <c r="BL2" t="inlineStr">
         <is>
-          <t>141340.3</t>
+          <t>172236.8</t>
         </is>
       </c>
       <c r="BM2" t="n">
-        <v>34625.74</v>
+        <v>42873.58</v>
       </c>
       <c r="BN2" t="inlineStr">
         <is>
-          <t>84932</t>
+          <t>90659</t>
         </is>
       </c>
       <c r="BO2" t="inlineStr">
         <is>
-          <t>20188.8974861608</t>
+          <t>27610.27668396823</t>
         </is>
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>51327.71450249714</t>
+          <t>39860.31382102531</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>367884.0</t>
+          <t>116293.0</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2026-01-04</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
@@ -1278,7 +1278,7 @@
       </c>
       <c r="BU2" t="inlineStr">
         <is>
-          <t>16.60</t>
+          <t>12.60</t>
         </is>
       </c>
       <c r="BV2" t="inlineStr">
@@ -1323,22 +1323,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價跌量縮</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1363,12 +1363,12 @@
       </c>
       <c r="CL2" t="inlineStr">
         <is>
-          <t>95.01</t>
+          <t>95.21</t>
         </is>
       </c>
       <c r="CM2" t="inlineStr">
         <is>
-          <t>3067</t>
+          <t>2961</t>
         </is>
       </c>
       <c r="CN2" t="inlineStr">
@@ -1388,22 +1388,22 @@
       </c>
       <c r="CQ2" t="inlineStr">
         <is>
-          <t>30.85</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="CR2" t="inlineStr">
         <is>
-          <t>31.0</t>
+          <t>30.75</t>
         </is>
       </c>
       <c r="CS2" t="inlineStr">
         <is>
-          <t>29.25</t>
+          <t>29.5</t>
         </is>
       </c>
       <c r="CT2" t="inlineStr">
         <is>
-          <t>30.55</t>
+          <t>29.5</t>
         </is>
       </c>
       <c r="CU2" t="inlineStr">
@@ -1435,12 +1435,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>9.49</t>
+          <t>-1.63</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>13687.0</t>
+          <t>10117.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1450,74 +1450,74 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
+          <t>30.05</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>-1.86</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>0.13</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>51.98</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>2025-12-29</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>2025-12-29 00:00:00</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>2026-01-04 00:00:00</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>2025-07-28 00:00:00</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>2025-08-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
           <t>30.85</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>-0.98</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>2.05</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>67.00</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>2025-12-29</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>65.0</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>2025-12-29 00:00:00</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>2025-12-31 00:00:00</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>2025-07-28 00:00:00</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>2025-08-14 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
         <is>
           <t>30.85</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>30.85</t>
-        </is>
-      </c>
       <c r="T3" t="inlineStr">
         <is>
           <t>25.6</t>
@@ -1530,7 +1530,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-2.59</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -1560,7 +1560,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -1605,22 +1605,22 @@
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>2025-12-23 00:00:00</t>
+          <t>2025-12-22 00:00:00</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>51.61</t>
+          <t>38.15</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>8.06</t>
+          <t>-3.79</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
@@ -1631,75 +1631,75 @@
       <c r="AP3" t="inlineStr"/>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>32</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>12182</t>
+          <t>3877</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>88.65</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>89.74</t>
+          <t>94.8</t>
         </is>
       </c>
       <c r="AU3" t="n">
-        <v>12.67</v>
+        <v>3.62</v>
       </c>
       <c r="AV3" t="n">
-        <v>15.21</v>
+        <v>17.43</v>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>4.96</t>
+          <t>7.61</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>-3.29</t>
+          <t>-2.44</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>27.38</t>
+          <t>29.0</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>23.76</v>
+        <v>24.7</v>
       </c>
       <c r="BA3" t="n">
-        <v>22.64</v>
+        <v>22.95</v>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>23.41</t>
+          <t>23.52</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>79.85</t>
+          <t>58.13</t>
         </is>
       </c>
       <c r="BD3" t="n">
-        <v>1.61</v>
+        <v>2.02</v>
       </c>
       <c r="BE3" t="n">
-        <v>0.89</v>
+        <v>1.28</v>
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>3.04</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>-70.62</t>
+          <t>-23.77</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -1709,48 +1709,48 @@
       </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>66670.20914127423</t>
+          <t>43637.08144329896</t>
         </is>
       </c>
       <c r="BJ3" t="inlineStr">
         <is>
-          <t>410672.0</t>
+          <t>310659.0</t>
         </is>
       </c>
       <c r="BK3" t="n">
-        <v>178004</v>
+        <v>250744.6</v>
       </c>
       <c r="BL3" t="inlineStr">
         <is>
-          <t>106592.2</t>
+          <t>164984.5</t>
         </is>
       </c>
       <c r="BM3" t="n">
-        <v>27334.72</v>
+        <v>40749.4</v>
       </c>
       <c r="BN3" t="inlineStr">
         <is>
-          <t>71411</t>
+          <t>85760</t>
         </is>
       </c>
       <c r="BO3" t="inlineStr">
         <is>
-          <t>14527.29439228146</t>
+          <t>25382.9972045033</t>
         </is>
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>39616.43019470811</t>
+          <t>53950.54565538705</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>410672.0</t>
+          <t>310659.0</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2026-01-04</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
@@ -1765,7 +1765,7 @@
       </c>
       <c r="BU3" t="inlineStr">
         <is>
-          <t>17.75</t>
+          <t>14.69</t>
         </is>
       </c>
       <c r="BV3" t="inlineStr">
@@ -1810,22 +1810,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1850,12 +1850,12 @@
       </c>
       <c r="CL3" t="inlineStr">
         <is>
-          <t>95.01</t>
+          <t>95.21</t>
         </is>
       </c>
       <c r="CM3" t="inlineStr">
         <is>
-          <t>3067</t>
+          <t>2961</t>
         </is>
       </c>
       <c r="CN3" t="inlineStr">
@@ -1875,22 +1875,22 @@
       </c>
       <c r="CQ3" t="inlineStr">
         <is>
-          <t>29.5</t>
+          <t>30.75</t>
         </is>
       </c>
       <c r="CR3" t="inlineStr">
         <is>
-          <t>30.85</t>
+          <t>31.8</t>
         </is>
       </c>
       <c r="CS3" t="inlineStr">
         <is>
-          <t>28.55</t>
+          <t>29.45</t>
         </is>
       </c>
       <c r="CT3" t="inlineStr">
         <is>
-          <t>30.85</t>
+          <t>30.05</t>
         </is>
       </c>
       <c r="CU3" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>9.85</t>
+          <t>-0.97</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>3968.0</t>
+          <t>12182.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1937,7 +1937,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>28.05</t>
+          <t>30.55</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1947,27 +1947,27 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>8.18</t>
+          <t>-3.56</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>40.41</t>
+          <t>60.09</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -1977,7 +1977,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>2025-12-31 00:00:00</t>
+          <t>2026-01-04 00:00:00</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -2002,7 +2002,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>30.85</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -2017,7 +2017,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-0.97</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -2047,7 +2047,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -2092,22 +2092,22 @@
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>2025-12-23 00:00:00</t>
+          <t>2025-12-22 00:00:00</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>14.96</t>
+          <t>45.93</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>11.09</t>
+          <t>2.97</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
@@ -2118,75 +2118,75 @@
       <c r="AP4" t="inlineStr"/>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>32</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>12182</t>
+          <t>3877</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>95.74</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>89.74</t>
+          <t>98.58</t>
         </is>
       </c>
       <c r="AU4" t="n">
-        <v>7.97</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="AV4" t="n">
-        <v>11.48</v>
+        <v>16.53</v>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>3.68</t>
+          <t>6.33</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>-3.74</t>
+          <t>-2.87</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>25.98</t>
+          <t>28.25</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>23.3</v>
+        <v>24.24</v>
       </c>
       <c r="BA4" t="n">
-        <v>22.48</v>
+        <v>22.8</v>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>23.35</t>
+          <t>23.47</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>70.30</t>
+          <t>71.73</t>
         </is>
       </c>
       <c r="BD4" t="n">
-        <v>1.22</v>
+        <v>1.87</v>
       </c>
       <c r="BE4" t="n">
-        <v>0.72</v>
+        <v>1.09</v>
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>3.04</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>-76.48</t>
+          <t>-34.85</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -2196,48 +2196,48 @@
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>66670.20914127423</t>
+          <t>43637.08144329896</t>
         </is>
       </c>
       <c r="BJ4" t="inlineStr">
         <is>
-          <t>108973.0</t>
+          <t>367884.0</t>
         </is>
       </c>
       <c r="BK4" t="n">
-        <v>99912.8</v>
+        <v>226272.4</v>
       </c>
       <c r="BL4" t="inlineStr">
         <is>
-          <t>71156.8</t>
+          <t>141340.3</t>
         </is>
       </c>
       <c r="BM4" t="n">
-        <v>19249.48</v>
+        <v>34625.74</v>
       </c>
       <c r="BN4" t="inlineStr">
         <is>
-          <t>28756</t>
+          <t>84932</t>
         </is>
       </c>
       <c r="BO4" t="inlineStr">
         <is>
-          <t>9965.6333372948</t>
+          <t>20188.8974861608</t>
         </is>
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>16886.72296234135</t>
+          <t>51327.71450249714</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>108973.0</t>
+          <t>367884.0</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2026-01-04</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
@@ -2252,7 +2252,7 @@
       </c>
       <c r="BU4" t="inlineStr">
         <is>
-          <t>7.06</t>
+          <t>16.60</t>
         </is>
       </c>
       <c r="BV4" t="inlineStr">
@@ -2297,22 +2297,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議關注買點&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;2&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="CL4" t="inlineStr">
         <is>
-          <t>95.01</t>
+          <t>95.21</t>
         </is>
       </c>
       <c r="CM4" t="inlineStr">
         <is>
-          <t>3067</t>
+          <t>2961</t>
         </is>
       </c>
       <c r="CN4" t="inlineStr">
@@ -2362,22 +2362,22 @@
       </c>
       <c r="CQ4" t="inlineStr">
         <is>
-          <t>25.9</t>
+          <t>30.85</t>
         </is>
       </c>
       <c r="CR4" t="inlineStr">
         <is>
-          <t>28.05</t>
+          <t>31.0</t>
         </is>
       </c>
       <c r="CS4" t="inlineStr">
         <is>
-          <t>25.25</t>
+          <t>29.25</t>
         </is>
       </c>
       <c r="CT4" t="inlineStr">
         <is>
-          <t>28.05</t>
+          <t>30.55</t>
         </is>
       </c>
       <c r="CU4" t="inlineStr">
@@ -2409,12 +2409,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-3.09</t>
+          <t>9.49</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2162.0</t>
+          <t>13687.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2424,7 +2424,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>25.5</t>
+          <t>30.85</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2434,27 +2434,27 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>16.53</t>
+          <t>-4.58</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>26.73</t>
+          <t>67.00</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>2025-12-31 00:00:00</t>
+          <t>2026-01-04 00:00:00</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -2489,7 +2489,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>30.85</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -2534,7 +2534,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -2579,43 +2579,43 @@
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>2025-12-23 00:00:00</t>
+          <t>2025-12-22 00:00:00</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>2025-12-24</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>51.61</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>-2.35</t>
+          <t>8.06</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr"/>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>32</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>12182</t>
+          <t>3877</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>69.23</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
@@ -2624,56 +2624,56 @@
         </is>
       </c>
       <c r="AU5" t="n">
-        <v>1.47</v>
+        <v>12.67</v>
       </c>
       <c r="AV5" t="n">
-        <v>9.42</v>
+        <v>15.21</v>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>2.68</t>
+          <t>4.96</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>-4.17</t>
+          <t>-3.29</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>25.13</t>
+          <t>27.38</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>22.97</v>
+        <v>23.76</v>
       </c>
       <c r="BA5" t="n">
-        <v>22.37</v>
+        <v>22.64</v>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>23.34</t>
+          <t>23.41</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>67.67</t>
+          <t>79.85</t>
         </is>
       </c>
       <c r="BD5" t="n">
-        <v>0.99</v>
+        <v>1.61</v>
       </c>
       <c r="BE5" t="n">
-        <v>0.59</v>
+        <v>0.89</v>
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>3.04</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>-80.61</t>
+          <t>-46.53</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
@@ -2683,48 +2683,48 @@
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>66670.20914127423</t>
+          <t>43637.08144329896</t>
         </is>
       </c>
       <c r="BJ5" t="inlineStr">
         <is>
-          <t>55535.0</t>
+          <t>410672.0</t>
         </is>
       </c>
       <c r="BK5" t="n">
-        <v>81577.39999999999</v>
+        <v>178004</v>
       </c>
       <c r="BL5" t="inlineStr">
         <is>
-          <t>64373.5</t>
+          <t>106592.2</t>
         </is>
       </c>
       <c r="BM5" t="n">
-        <v>17193.38</v>
+        <v>27334.72</v>
       </c>
       <c r="BN5" t="inlineStr">
         <is>
-          <t>17203</t>
+          <t>71411</t>
         </is>
       </c>
       <c r="BO5" t="inlineStr">
         <is>
-          <t>8707.253405468153</t>
+          <t>14527.29439228146</t>
         </is>
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>16137.50823887664</t>
+          <t>39616.43019470811</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>55535.0</t>
+          <t>410672.0</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2026-01-04</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
@@ -2739,7 +2739,7 @@
       </c>
       <c r="BU5" t="inlineStr">
         <is>
-          <t>-2.67</t>
+          <t>17.75</t>
         </is>
       </c>
       <c r="BV5" t="inlineStr">
@@ -2784,22 +2784,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2824,12 +2824,12 @@
       </c>
       <c r="CL5" t="inlineStr">
         <is>
-          <t>95.01</t>
+          <t>95.21</t>
         </is>
       </c>
       <c r="CM5" t="inlineStr">
         <is>
-          <t>3067</t>
+          <t>2961</t>
         </is>
       </c>
       <c r="CN5" t="inlineStr">
@@ -2849,22 +2849,22 @@
       </c>
       <c r="CQ5" t="inlineStr">
         <is>
-          <t>25.85</t>
+          <t>29.5</t>
         </is>
       </c>
       <c r="CR5" t="inlineStr">
         <is>
-          <t>26.2</t>
+          <t>30.85</t>
         </is>
       </c>
       <c r="CS5" t="inlineStr">
         <is>
-          <t>25.4</t>
+          <t>28.55</t>
         </is>
       </c>
       <c r="CT5" t="inlineStr">
         <is>
-          <t>25.5</t>
+          <t>30.85</t>
         </is>
       </c>
       <c r="CU5" t="inlineStr">
@@ -2896,12 +2896,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>9.85</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>7091.0</t>
+          <t>3968.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>26.3</t>
+          <t>28.05</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2921,17 +2921,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>13.91</t>
+          <t>4.92</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>33.09</t>
+          <t>40.41</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2941,7 +2941,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -2951,7 +2951,7 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>2025-12-31 00:00:00</t>
+          <t>2026-01-04 00:00:00</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -3021,7 +3021,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -3066,38 +3066,38 @@
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>2025-12-23 00:00:00</t>
+          <t>2025-12-22 00:00:00</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>26.74</t>
+          <t>14.96</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>-2.65</t>
+          <t>11.09</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr"/>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>32</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>12182</t>
+          <t>3877</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -3107,60 +3107,60 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>93.21</t>
+          <t>89.74</t>
         </is>
       </c>
       <c r="AU6" t="n">
-        <v>5.92</v>
+        <v>7.97</v>
       </c>
       <c r="AV6" t="n">
-        <v>9.119999999999999</v>
+        <v>11.48</v>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>1.99</t>
+          <t>3.68</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>-4.57</t>
+          <t>-3.74</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>24.83</t>
+          <t>25.98</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>22.76</v>
+        <v>23.3</v>
       </c>
       <c r="BA6" t="n">
-        <v>22.31</v>
+        <v>22.48</v>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>23.38</t>
+          <t>23.35</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>92.01</t>
+          <t>70.30</t>
         </is>
       </c>
       <c r="BD6" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.22</v>
       </c>
       <c r="BE6" t="n">
-        <v>0.49</v>
+        <v>0.72</v>
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>3.04</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>-83.89</t>
+          <t>-57.21</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
@@ -3170,43 +3170,43 @@
       </c>
       <c r="BI6" t="inlineStr">
         <is>
-          <t>66670.20914127423</t>
+          <t>43637.08144329896</t>
         </is>
       </c>
       <c r="BJ6" t="inlineStr">
         <is>
-          <t>188298.0</t>
+          <t>108973.0</t>
         </is>
       </c>
       <c r="BK6" t="n">
-        <v>79224.39999999999</v>
+        <v>99912.8</v>
       </c>
       <c r="BL6" t="inlineStr">
         <is>
-          <t>59526.8</t>
+          <t>71156.8</t>
         </is>
       </c>
       <c r="BM6" t="n">
-        <v>16223.06</v>
+        <v>19249.48</v>
       </c>
       <c r="BN6" t="inlineStr">
         <is>
-          <t>19697</t>
+          <t>28756</t>
         </is>
       </c>
       <c r="BO6" t="inlineStr">
         <is>
-          <t>7356.297981212065</t>
+          <t>9965.6333372948</t>
         </is>
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>20216.36191111003</t>
+          <t>16886.72296234135</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>188298.0</t>
+          <t>108973.0</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="BU6" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>7.06</t>
         </is>
       </c>
       <c r="BV6" t="inlineStr">
@@ -3271,22 +3271,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議關注買點&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;2&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3311,12 +3311,12 @@
       </c>
       <c r="CL6" t="inlineStr">
         <is>
-          <t>95.01</t>
+          <t>95.21</t>
         </is>
       </c>
       <c r="CM6" t="inlineStr">
         <is>
-          <t>3067</t>
+          <t>2961</t>
         </is>
       </c>
       <c r="CN6" t="inlineStr">
@@ -3336,22 +3336,22 @@
       </c>
       <c r="CQ6" t="inlineStr">
         <is>
-          <t>26.45</t>
+          <t>25.9</t>
         </is>
       </c>
       <c r="CR6" t="inlineStr">
         <is>
-          <t>27.3</t>
+          <t>28.05</t>
         </is>
       </c>
       <c r="CS6" t="inlineStr">
         <is>
-          <t>26.0</t>
+          <t>25.25</t>
         </is>
       </c>
       <c r="CT6" t="inlineStr">
         <is>
-          <t>26.3</t>
+          <t>28.05</t>
         </is>
       </c>
       <c r="CU6" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>9.4</t>
+          <t>-3.09</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>4853.0</t>
+          <t>2162.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3398,7 +3398,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>26.2</t>
+          <t>25.5</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3408,17 +3408,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>14.24</t>
+          <t>13.56</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>36.79</t>
+          <t>26.73</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3428,7 +3428,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -3438,7 +3438,7 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>2025-12-31 00:00:00</t>
+          <t>2026-01-04 00:00:00</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -3508,7 +3508,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -3553,22 +3553,22 @@
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>2025-12-23 00:00:00</t>
+          <t>2025-12-22 00:00:00</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-24</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>18.30</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>4.80</t>
+          <t>-2.35</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
@@ -3579,75 +3579,75 @@
       <c r="AP7" t="inlineStr"/>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>32</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>12182</t>
+          <t>3877</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>69.23</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>86.43</t>
+          <t>89.74</t>
         </is>
       </c>
       <c r="AU7" t="n">
-        <v>7.16</v>
+        <v>1.47</v>
       </c>
       <c r="AV7" t="n">
-        <v>8.859999999999999</v>
+        <v>9.42</v>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>2.68</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>-4.90</t>
+          <t>-4.17</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>24.45</t>
+          <t>25.13</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>22.46</v>
+        <v>22.97</v>
       </c>
       <c r="BA7" t="n">
-        <v>22.25</v>
+        <v>22.37</v>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>23.39</t>
+          <t>23.34</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>107.93</t>
+          <t>67.67</t>
         </is>
       </c>
       <c r="BD7" t="n">
-        <v>0.78</v>
+        <v>0.99</v>
       </c>
       <c r="BE7" t="n">
-        <v>0.38</v>
+        <v>0.59</v>
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>3.04</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>-87.60</t>
+          <t>-64.73</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -3657,43 +3657,43 @@
       </c>
       <c r="BI7" t="inlineStr">
         <is>
-          <t>66670.20914127423</t>
+          <t>43637.08144329896</t>
         </is>
       </c>
       <c r="BJ7" t="inlineStr">
         <is>
-          <t>126542.0</t>
+          <t>55535.0</t>
         </is>
       </c>
       <c r="BK7" t="n">
-        <v>56408.2</v>
+        <v>81577.39999999999</v>
       </c>
       <c r="BL7" t="inlineStr">
         <is>
-          <t>41235.7</t>
+          <t>64373.5</t>
         </is>
       </c>
       <c r="BM7" t="n">
-        <v>12661.38</v>
+        <v>17193.38</v>
       </c>
       <c r="BN7" t="inlineStr">
         <is>
-          <t>15172</t>
+          <t>17203</t>
         </is>
       </c>
       <c r="BO7" t="inlineStr">
         <is>
-          <t>5018.104539412434</t>
+          <t>8707.253405468153</t>
         </is>
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>11096.67566033239</t>
+          <t>16137.50823887664</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>126542.0</t>
+          <t>55535.0</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -3713,7 +3713,7 @@
       </c>
       <c r="BU7" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-2.67</t>
         </is>
       </c>
       <c r="BV7" t="inlineStr">
@@ -3758,22 +3758,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議關注買點&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;2&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3798,12 +3798,12 @@
       </c>
       <c r="CL7" t="inlineStr">
         <is>
-          <t>95.01</t>
+          <t>95.21</t>
         </is>
       </c>
       <c r="CM7" t="inlineStr">
         <is>
-          <t>3067</t>
+          <t>2961</t>
         </is>
       </c>
       <c r="CN7" t="inlineStr">
@@ -3823,7 +3823,7 @@
       </c>
       <c r="CQ7" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>25.85</t>
         </is>
       </c>
       <c r="CR7" t="inlineStr">
@@ -3833,12 +3833,12 @@
       </c>
       <c r="CS7" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>25.4</t>
         </is>
       </c>
       <c r="CT7" t="inlineStr">
         <is>
-          <t>26.2</t>
+          <t>25.5</t>
         </is>
       </c>
       <c r="CU7" t="inlineStr">
@@ -3860,7 +3860,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>【d1】</t>
+          <t>【b1】</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3870,12 +3870,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>843.0</t>
+          <t>7091.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3885,7 +3885,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>23.85</t>
+          <t>26.3</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3895,17 +3895,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>21.93</t>
+          <t>10.85</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>21.91</t>
+          <t>33.09</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3915,7 +3915,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -3925,7 +3925,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>2025-12-31 00:00:00</t>
+          <t>2026-01-04 00:00:00</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -3995,7 +3995,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -4040,101 +4040,101 @@
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>2025-12-23 00:00:00</t>
+          <t>2025-12-22 00:00:00</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>2025-12-19</t>
+          <t>2025-12-23</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>3.18</t>
+          <t>26.74</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>-1.24</t>
+          <t>-2.65</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr"/>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>32</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>12182</t>
+          <t>3877</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>79.63</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>82.13</t>
+          <t>93.21</t>
         </is>
       </c>
       <c r="AU8" t="n">
-        <v>-0.42</v>
+        <v>5.92</v>
       </c>
       <c r="AV8" t="n">
-        <v>8.02</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>1.99</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>-5.17</t>
+          <t>-4.57</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>23.95</t>
+          <t>24.83</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>22.17</v>
+        <v>22.76</v>
       </c>
       <c r="BA8" t="n">
-        <v>22.2</v>
+        <v>22.31</v>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>23.41</t>
+          <t>23.38</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>111.88</t>
+          <t>92.01</t>
         </is>
       </c>
       <c r="BD8" t="n">
-        <v>0.58</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="BE8" t="n">
-        <v>0.28</v>
+        <v>0.49</v>
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>3.04</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>-90.95</t>
+          <t>-70.69</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -4144,43 +4144,43 @@
       </c>
       <c r="BI8" t="inlineStr">
         <is>
-          <t>66670.20914127423</t>
+          <t>43637.08144329896</t>
         </is>
       </c>
       <c r="BJ8" t="inlineStr">
         <is>
-          <t>20216.0</t>
+          <t>188298.0</t>
         </is>
       </c>
       <c r="BK8" t="n">
-        <v>35180.4</v>
+        <v>79224.39999999999</v>
       </c>
       <c r="BL8" t="inlineStr">
         <is>
-          <t>28857.5</t>
+          <t>59526.8</t>
         </is>
       </c>
       <c r="BM8" t="n">
-        <v>10271.14</v>
+        <v>16223.06</v>
       </c>
       <c r="BN8" t="inlineStr">
         <is>
-          <t>6322</t>
+          <t>19697</t>
         </is>
       </c>
       <c r="BO8" t="inlineStr">
         <is>
-          <t>3912.909790154261</t>
+          <t>7356.297981212065</t>
         </is>
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>4288.956885638152</t>
+          <t>20216.36191111003</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>20216.0</t>
+          <t>188298.0</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
@@ -4200,7 +4200,7 @@
       </c>
       <c r="BU8" t="inlineStr">
         <is>
-          <t>-8.97</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="BV8" t="inlineStr">
@@ -4245,22 +4245,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>0.97</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -4285,12 +4285,12 @@
       </c>
       <c r="CL8" t="inlineStr">
         <is>
-          <t>95.01</t>
+          <t>95.21</t>
         </is>
       </c>
       <c r="CM8" t="inlineStr">
         <is>
-          <t>3067</t>
+          <t>2961</t>
         </is>
       </c>
       <c r="CN8" t="inlineStr">
@@ -4310,22 +4310,22 @@
       </c>
       <c r="CQ8" t="inlineStr">
         <is>
-          <t>24.05</t>
+          <t>26.45</t>
         </is>
       </c>
       <c r="CR8" t="inlineStr">
         <is>
-          <t>24.45</t>
+          <t>27.3</t>
         </is>
       </c>
       <c r="CS8" t="inlineStr">
         <is>
-          <t>23.55</t>
+          <t>26.0</t>
         </is>
       </c>
       <c r="CT8" t="inlineStr">
         <is>
-          <t>23.85</t>
+          <t>26.3</t>
         </is>
       </c>
       <c r="CU8" t="inlineStr">
@@ -4347,7 +4347,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>【d1】</t>
+          <t>【b1】</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -4357,12 +4357,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-0.84</t>
+          <t>9.4</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>732.0</t>
+          <t>4853.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -4372,7 +4372,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>23.8</t>
+          <t>26.2</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -4382,17 +4382,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>22.09</t>
+          <t>11.19</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>56.47</t>
+          <t>36.79</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -4402,7 +4402,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -4412,7 +4412,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>2025-12-31 00:00:00</t>
+          <t>2026-01-04 00:00:00</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -4482,7 +4482,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -4527,101 +4527,101 @@
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>2025-12-23 00:00:00</t>
+          <t>2025-12-22 00:00:00</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>2.76</t>
+          <t>18.30</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>2.38</t>
+          <t>4.80</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr"/>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>32</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>12182</t>
+          <t>3877</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>79.66</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>88.92</t>
+          <t>86.43</t>
         </is>
       </c>
       <c r="AU9" t="n">
-        <v>-1.04</v>
+        <v>7.16</v>
       </c>
       <c r="AV9" t="n">
-        <v>9.44</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>-1.01</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>-5.36</t>
+          <t>-4.90</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>24.05</t>
+          <t>24.45</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>21.98</v>
+        <v>22.46</v>
       </c>
       <c r="BA9" t="n">
-        <v>22.2</v>
+        <v>22.25</v>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>23.46</t>
+          <t>23.39</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>181.23</t>
+          <t>107.93</t>
         </is>
       </c>
       <c r="BD9" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.78</v>
       </c>
       <c r="BE9" t="n">
-        <v>0.2</v>
+        <v>0.38</v>
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>3.04</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>-93.48</t>
+          <t>-77.44</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -4631,43 +4631,43 @@
       </c>
       <c r="BI9" t="inlineStr">
         <is>
-          <t>66670.20914127423</t>
+          <t>43637.08144329896</t>
         </is>
       </c>
       <c r="BJ9" t="inlineStr">
         <is>
-          <t>17296.0</t>
+          <t>126542.0</t>
         </is>
       </c>
       <c r="BK9" t="n">
-        <v>42400.8</v>
+        <v>56408.2</v>
       </c>
       <c r="BL9" t="inlineStr">
         <is>
-          <t>27099.0</t>
+          <t>41235.7</t>
         </is>
       </c>
       <c r="BM9" t="n">
-        <v>10048.64</v>
+        <v>12661.38</v>
       </c>
       <c r="BN9" t="inlineStr">
         <is>
-          <t>15301</t>
+          <t>15172</t>
         </is>
       </c>
       <c r="BO9" t="inlineStr">
         <is>
-          <t>3844.537590975371</t>
+          <t>5018.104539412434</t>
         </is>
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>5802.538747302169</t>
+          <t>11096.67566033239</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>17296.0</t>
+          <t>126542.0</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
@@ -4687,7 +4687,7 @@
       </c>
       <c r="BU9" t="inlineStr">
         <is>
-          <t>-9.16</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="BV9" t="inlineStr">
@@ -4732,22 +4732,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議關注買點&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;2&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>0.97</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4772,12 +4772,12 @@
       </c>
       <c r="CL9" t="inlineStr">
         <is>
-          <t>95.01</t>
+          <t>95.21</t>
         </is>
       </c>
       <c r="CM9" t="inlineStr">
         <is>
-          <t>3067</t>
+          <t>2961</t>
         </is>
       </c>
       <c r="CN9" t="inlineStr">
@@ -4797,22 +4797,22 @@
       </c>
       <c r="CQ9" t="inlineStr">
         <is>
-          <t>23.75</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="CR9" t="inlineStr">
         <is>
-          <t>23.85</t>
+          <t>26.2</t>
         </is>
       </c>
       <c r="CS9" t="inlineStr">
         <is>
-          <t>23.2</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="CT9" t="inlineStr">
         <is>
-          <t>23.8</t>
+          <t>26.2</t>
         </is>
       </c>
       <c r="CU9" t="inlineStr">
@@ -4844,12 +4844,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-1.63</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1808.0</t>
+          <t>843.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4859,7 +4859,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>24.0</t>
+          <t>23.85</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4869,17 +4869,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>21.44</t>
+          <t>19.15</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>82.48</t>
+          <t>21.91</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4889,7 +4889,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -4899,7 +4899,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>2025-12-31 00:00:00</t>
+          <t>2026-01-04 00:00:00</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -4969,7 +4969,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -5014,22 +5014,22 @@
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>2025-12-23 00:00:00</t>
+          <t>2025-12-22 00:00:00</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2025-12-19</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>6.82</t>
+          <t>3.18</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>-1.41</t>
+          <t>-1.24</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
@@ -5040,75 +5040,75 @@
       <c r="AP10" t="inlineStr"/>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>32</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>12182</t>
+          <t>3877</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>87.1</t>
+          <t>79.63</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>88.6</t>
+          <t>82.13</t>
         </is>
       </c>
       <c r="AU10" t="n">
-        <v>0.17</v>
+        <v>-0.42</v>
       </c>
       <c r="AV10" t="n">
-        <v>9.85</v>
+        <v>8.02</v>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>-1.79</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>-5.50</t>
+          <t>-5.17</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>23.96</t>
+          <t>23.95</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>21.81</v>
+        <v>22.17</v>
       </c>
       <c r="BA10" t="n">
-        <v>22.21</v>
+        <v>22.2</v>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>23.5</t>
+          <t>23.41</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>381.30</t>
+          <t>111.88</t>
         </is>
       </c>
       <c r="BD10" t="n">
-        <v>0.52</v>
+        <v>0.58</v>
       </c>
       <c r="BE10" t="n">
-        <v>0.11</v>
+        <v>0.28</v>
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>3.04</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>-96.43</t>
+          <t>-83.52</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -5118,43 +5118,43 @@
       </c>
       <c r="BI10" t="inlineStr">
         <is>
-          <t>66670.20914127423</t>
+          <t>43637.08144329896</t>
         </is>
       </c>
       <c r="BJ10" t="inlineStr">
         <is>
-          <t>43770.0</t>
+          <t>20216.0</t>
         </is>
       </c>
       <c r="BK10" t="n">
-        <v>47169.6</v>
+        <v>35180.4</v>
       </c>
       <c r="BL10" t="inlineStr">
         <is>
-          <t>25849.0</t>
+          <t>28857.5</t>
         </is>
       </c>
       <c r="BM10" t="n">
-        <v>9818.92</v>
+        <v>10271.14</v>
       </c>
       <c r="BN10" t="inlineStr">
         <is>
-          <t>21320</t>
+          <t>6322</t>
         </is>
       </c>
       <c r="BO10" t="inlineStr">
         <is>
-          <t>3488.537380734135</t>
+          <t>3912.909790154261</t>
         </is>
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>8070.422165847122</t>
+          <t>4288.956885638152</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>43770.0</t>
+          <t>20216.0</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -5174,7 +5174,7 @@
       </c>
       <c r="BU10" t="inlineStr">
         <is>
-          <t>-8.40</t>
+          <t>-8.97</t>
         </is>
       </c>
       <c r="BV10" t="inlineStr">
@@ -5219,7 +5219,7 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
@@ -5234,7 +5234,7 @@
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -5259,12 +5259,12 @@
       </c>
       <c r="CL10" t="inlineStr">
         <is>
-          <t>95.01</t>
+          <t>95.21</t>
         </is>
       </c>
       <c r="CM10" t="inlineStr">
         <is>
-          <t>3067</t>
+          <t>2961</t>
         </is>
       </c>
       <c r="CN10" t="inlineStr">
@@ -5284,22 +5284,22 @@
       </c>
       <c r="CQ10" t="inlineStr">
         <is>
-          <t>24.55</t>
+          <t>24.05</t>
         </is>
       </c>
       <c r="CR10" t="inlineStr">
         <is>
-          <t>24.85</t>
+          <t>24.45</t>
         </is>
       </c>
       <c r="CS10" t="inlineStr">
         <is>
-          <t>23.5</t>
+          <t>23.55</t>
         </is>
       </c>
       <c r="CT10" t="inlineStr">
         <is>
-          <t>24.0</t>
+          <t>23.85</t>
         </is>
       </c>
       <c r="CU10" t="inlineStr">
@@ -5321,22 +5321,22 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>【d1】</t>
+          <t>【b1】</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>6234</t>
+          <t>6125</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2.79</t>
+          <t>-1.11</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>3021.0</t>
+          <t>1512.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -5346,7 +5346,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>24.4</t>
+          <t>71.3</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -5356,17 +5356,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>20.13</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>81.49</t>
+          <t>-17.80</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -5376,37 +5376,37 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2025-12-29 00:00:00</t>
+          <t>2025-09-17 00:00:00</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>2025-12-31 00:00:00</t>
+          <t>2025-09-22 00:00:00</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>2025-07-28 00:00:00</t>
+          <t>2025-07-25 00:00:00</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>2025-08-14 00:00:00</t>
+          <t>2025-08-22 00:00:00</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>30.85</t>
+          <t>80.4</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>77.7</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -5416,12 +5416,12 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>25.6</t>
+          <t>73.8</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>28.7</t>
+          <t>78.5</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
@@ -5431,22 +5431,22 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-8.24</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>7.49</t>
+          <t>2.42</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025/07/04</t>
+          <t>2025/08/01</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>24.65</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -5456,67 +5456,67 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>-0.2</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>2025/09/15</t>
+          <t>2025/09/30</t>
         </is>
       </c>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>24.2</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>2025/07/02</t>
+          <t>2025/07/07</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>22.2</t>
+          <t>60.7</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>2025/11/18</t>
+          <t>2025/10/27</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>20.6</t>
+          <t>71.1</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>2025/11/04</t>
+          <t>2025/09/22</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>21.7</t>
+          <t>77.7</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>2025-12-23 00:00:00</t>
+          <t>2025-01-08 00:00:00</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2026-01-02</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>11.39</t>
+          <t>3.48</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>-2.42</t>
+          <t>-1.40</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
@@ -5527,121 +5527,121 @@
       <c r="AP11" t="inlineStr"/>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>12182</t>
+          <t>1512</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>72.22</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>92.9</t>
+          <t>85.63</t>
         </is>
       </c>
       <c r="AU11" t="n">
-        <v>3.7</v>
+        <v>-1.08</v>
       </c>
       <c r="AV11" t="n">
-        <v>8.779999999999999</v>
+        <v>6.23</v>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>-2.62</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>-5.66</t>
+          <t>-4.72</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>23.53</t>
+          <t>72.08000000000001</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>21.63</v>
+        <v>67.84999999999999</v>
       </c>
       <c r="BA11" t="n">
-        <v>22.21</v>
+        <v>66.76000000000001</v>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>23.54</t>
+          <t>70.07</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>8743.35</t>
+          <t>52.45</t>
         </is>
       </c>
       <c r="BD11" t="n">
-        <v>0.45</v>
+        <v>1.89</v>
       </c>
       <c r="BE11" t="n">
-        <v>0.01</v>
+        <v>1.24</v>
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>3.04</t>
+          <t>8.38</t>
         </is>
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>-99.83</t>
+          <t>-85.23</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2025/11/26</t>
+          <t>2025/11/27</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
         <is>
-          <t>66670.20914127423</t>
+          <t>1281159.541237113</t>
         </is>
       </c>
       <c r="BJ11" t="inlineStr">
         <is>
-          <t>74217.0</t>
+          <t>108597.0</t>
         </is>
       </c>
       <c r="BK11" t="n">
-        <v>39829.2</v>
+        <v>240458.2</v>
       </c>
       <c r="BL11" t="inlineStr">
         <is>
-          <t>21946.2</t>
+          <t>292538.0</t>
         </is>
       </c>
       <c r="BM11" t="n">
-        <v>9166.76</v>
+        <v>136053.42</v>
       </c>
       <c r="BN11" t="inlineStr">
         <is>
-          <t>17883</t>
+          <t>-52079</t>
         </is>
       </c>
       <c r="BO11" t="inlineStr">
         <is>
-          <t>2655.4674198045</t>
+          <t>28607.15703432796</t>
         </is>
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>8185.526257845377</t>
+          <t>11096.73365911728</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>74217.0</t>
+          <t>108597.0</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5651,27 +5651,27 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>26.2</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>2025/12/22</t>
+          <t>2025/12/30</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
         <is>
-          <t>-6.87</t>
+          <t>-2.33</t>
         </is>
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>高僑</t>
+          <t>廣運</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
         <is>
-          <t>高僑</t>
+          <t>廣運</t>
         </is>
       </c>
       <c r="BX11" t="inlineStr">
@@ -5686,27 +5686,27 @@
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
         <is>
-          <t>-43.51524843961707</t>
+          <t>-9.276867348133008</t>
         </is>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>-49.65752068733421</t>
+          <t>49.33864609225594</t>
         </is>
       </c>
       <c r="CC11" t="inlineStr">
         <is>
-          <t>-33.1741339459368</t>
+          <t>18.62961592762674</t>
         </is>
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
@@ -5716,87 +5716,87 @@
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>0.90</t>
+          <t>4.22</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>4.00</t>
         </is>
       </c>
       <c r="CI11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>548.46</t>
         </is>
       </c>
       <c r="CJ11" t="inlineStr">
         <is>
-          <t>0.94%</t>
+          <t>17.69%</t>
         </is>
       </c>
       <c r="CK11" t="inlineStr">
         <is>
-          <t>-10.38%</t>
+          <t>-6.67%</t>
         </is>
       </c>
       <c r="CL11" t="inlineStr">
         <is>
-          <t>95.01</t>
+          <t>95.21</t>
         </is>
       </c>
       <c r="CM11" t="inlineStr">
         <is>
-          <t>3067</t>
+          <t>18467</t>
         </is>
       </c>
       <c r="CN11" t="inlineStr">
         <is>
-          <t>自動化設備58.40%、微型鑽頭41.60% (2024年)</t>
+          <t>自動化設備74.11%、太陽能產品12.33%、電子零組件8.12%、建材營建4.02%、其他1.41% (2024年)</t>
         </is>
       </c>
       <c r="CO11" t="inlineStr">
         <is>
-          <t>高僑-光電業-上櫃</t>
+          <t>廣運-光電業-上櫃</t>
         </is>
       </c>
       <c r="CP11" t="inlineStr">
         <is>
-          <t>光電業右上上櫃</t>
+          <t>光電業右下上櫃</t>
         </is>
       </c>
       <c r="CQ11" t="inlineStr">
         <is>
-          <t>25.05</t>
+          <t>71.8</t>
         </is>
       </c>
       <c r="CR11" t="inlineStr">
         <is>
-          <t>25.45</t>
+          <t>72.3</t>
         </is>
       </c>
       <c r="CS11" t="inlineStr">
         <is>
-          <t>23.95</t>
+          <t>71.3</t>
         </is>
       </c>
       <c r="CT11" t="inlineStr">
         <is>
-          <t>24.4</t>
+          <t>71.3</t>
         </is>
       </c>
       <c r="CU11" t="inlineStr">
         <is>
-          <t>27.15</t>
+          <t>16.88</t>
         </is>
       </c>
       <c r="CV11" t="inlineStr">
         <is>
-          <t>** 自動化 - 自動化機台、整體解決方案** 平面顯示器 - 生產製程及檢測設備** 電機機械 - 輸送機械及零配件、機電系統工程** 太陽能產業 - 太陽能發電設備/系統及系統工程</t>
+          <t>** 自動化 - 整體解決方案** 平面顯示器 - 生產製程及檢測設備** 電機機械 - 輸送機械及零配件、機電系統工程** 太陽能產業 - 太陽能發電設備/系統及系統工程</t>
         </is>
       </c>
       <c r="CW11" t="inlineStr">
@@ -5808,7 +5808,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>價_量;【b1】</t>
+          <t>【b1】</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5818,12 +5818,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>6029.0</t>
+          <t>3170.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5833,7 +5833,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>72.1</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5843,17 +5843,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-1.12</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>46.27</t>
+          <t>-0.68</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5863,7 +5863,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -5918,7 +5918,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-6.05</t>
+          <t>-7.21</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5943,7 +5943,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -5993,17 +5993,17 @@
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>13.89</t>
+          <t>7.30</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>1.86</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
@@ -6014,75 +6014,75 @@
       <c r="AP12" t="inlineStr"/>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>6029</t>
+          <t>1512</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>97.03</t>
+          <t>87.63</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>90.51</t>
+          <t>91.29</t>
         </is>
       </c>
       <c r="AU12" t="n">
-        <v>0.63</v>
+        <v>-0.28</v>
       </c>
       <c r="AV12" t="n">
-        <v>8.380000000000001</v>
+        <v>7.18</v>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>-4.81</t>
+          <t>-4.74</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>72.54</t>
+          <t>72.3</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>66.93000000000001</v>
+        <v>67.45999999999999</v>
       </c>
       <c r="BA12" t="n">
         <v>66.81</v>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>70.19</t>
+          <t>70.14</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>116.34</t>
+          <t>79.09</t>
         </is>
       </c>
       <c r="BD12" t="n">
-        <v>1.87</v>
+        <v>1.93</v>
       </c>
       <c r="BE12" t="n">
-        <v>0.86</v>
+        <v>1.08</v>
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>10.1</t>
+          <t>8.38</t>
         </is>
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>-91.45</t>
+          <t>-87.17</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
@@ -6092,43 +6092,43 @@
       </c>
       <c r="BI12" t="inlineStr">
         <is>
-          <t>1147051.08033241</t>
+          <t>1281159.541237113</t>
         </is>
       </c>
       <c r="BJ12" t="inlineStr">
         <is>
-          <t>435553.0</t>
+          <t>227528.0</t>
         </is>
       </c>
       <c r="BK12" t="n">
-        <v>405067.8</v>
+        <v>284915.2</v>
       </c>
       <c r="BL12" t="inlineStr">
         <is>
-          <t>276939.0</t>
+          <t>286862.6</t>
         </is>
       </c>
       <c r="BM12" t="n">
-        <v>133176.84</v>
+        <v>136315.58</v>
       </c>
       <c r="BN12" t="inlineStr">
         <is>
-          <t>128128</t>
+          <t>-1947</t>
         </is>
       </c>
       <c r="BO12" t="inlineStr">
         <is>
-          <t>32366.66350395649</t>
+          <t>31790.87037527536</t>
         </is>
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>39898.07860213425</t>
+          <t>28624.00816752913</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>435553.0</t>
+          <t>227528.0</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -6148,7 +6148,7 @@
       </c>
       <c r="BU12" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-1.23</t>
         </is>
       </c>
       <c r="BV12" t="inlineStr">
@@ -6173,7 +6173,7 @@
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -6193,22 +6193,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>4.32</t>
+          <t>4.27</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
@@ -6218,7 +6218,7 @@
       </c>
       <c r="CI12" t="inlineStr">
         <is>
-          <t>561.54</t>
+          <t>548.46</t>
         </is>
       </c>
       <c r="CJ12" t="inlineStr">
@@ -6233,12 +6233,12 @@
       </c>
       <c r="CL12" t="inlineStr">
         <is>
-          <t>95.01</t>
+          <t>95.21</t>
         </is>
       </c>
       <c r="CM12" t="inlineStr">
         <is>
-          <t>18908</t>
+          <t>18467</t>
         </is>
       </c>
       <c r="CN12" t="inlineStr">
@@ -6253,17 +6253,17 @@
       </c>
       <c r="CP12" t="inlineStr">
         <is>
-          <t>光電業平上櫃</t>
+          <t>光電業右下上櫃</t>
         </is>
       </c>
       <c r="CQ12" t="inlineStr">
         <is>
-          <t>73.6</t>
+          <t>72.2</t>
         </is>
       </c>
       <c r="CR12" t="inlineStr">
         <is>
-          <t>73.7</t>
+          <t>72.7</t>
         </is>
       </c>
       <c r="CS12" t="inlineStr">
@@ -6273,7 +6273,7 @@
       </c>
       <c r="CT12" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>72.1</t>
         </is>
       </c>
       <c r="CU12" t="inlineStr">
@@ -6295,7 +6295,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>【d1】</t>
+          <t>【b1】</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -6305,12 +6305,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>3110.0</t>
+          <t>6029.0</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -6320,7 +6320,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>72.2</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -6330,17 +6330,17 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>-2.38</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>42.29</t>
+          <t>46.27</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -6350,7 +6350,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -6405,7 +6405,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>-7.08</t>
+          <t>-6.05</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -6430,7 +6430,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>-0.06</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
@@ -6480,17 +6480,17 @@
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>7.16</t>
+          <t>13.89</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>1.86</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
@@ -6501,75 +6501,75 @@
       <c r="AP13" t="inlineStr"/>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>6029</t>
+          <t>1512</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
         <is>
-          <t>89.22</t>
+          <t>97.03</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>88.56</t>
+          <t>90.51</t>
         </is>
       </c>
       <c r="AU13" t="n">
-        <v>-0.39</v>
+        <v>0.63</v>
       </c>
       <c r="AV13" t="n">
-        <v>9.199999999999999</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>-4.87</t>
+          <t>-4.81</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>72.47999999999999</t>
+          <t>72.54</t>
         </is>
       </c>
       <c r="AZ13" t="n">
-        <v>66.38</v>
+        <v>66.93000000000001</v>
       </c>
       <c r="BA13" t="n">
-        <v>66.81999999999999</v>
+        <v>66.81</v>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>70.24</t>
+          <t>70.19</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>173.26</t>
+          <t>116.34</t>
         </is>
       </c>
       <c r="BD13" t="n">
-        <v>1.67</v>
+        <v>1.87</v>
       </c>
       <c r="BE13" t="n">
-        <v>0.61</v>
+        <v>0.86</v>
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>10.1</t>
+          <t>8.38</t>
         </is>
       </c>
       <c r="BG13" t="inlineStr">
         <is>
-          <t>-93.94</t>
+          <t>-89.70</t>
         </is>
       </c>
       <c r="BH13" t="inlineStr">
@@ -6579,43 +6579,43 @@
       </c>
       <c r="BI13" t="inlineStr">
         <is>
-          <t>1147051.08033241</t>
+          <t>1281159.541237113</t>
         </is>
       </c>
       <c r="BJ13" t="inlineStr">
         <is>
-          <t>224848.0</t>
+          <t>435553.0</t>
         </is>
       </c>
       <c r="BK13" t="n">
-        <v>378776.4</v>
+        <v>405067.8</v>
       </c>
       <c r="BL13" t="inlineStr">
         <is>
-          <t>266193.0</t>
+          <t>276939.0</t>
         </is>
       </c>
       <c r="BM13" t="n">
-        <v>125841.48</v>
+        <v>133176.84</v>
       </c>
       <c r="BN13" t="inlineStr">
         <is>
-          <t>112583</t>
+          <t>128128</t>
         </is>
       </c>
       <c r="BO13" t="inlineStr">
         <is>
-          <t>30997.31530428781</t>
+          <t>32366.66350395649</t>
         </is>
       </c>
       <c r="BP13" t="inlineStr">
         <is>
-          <t>32290.56927292253</t>
+          <t>39898.07860213425</t>
         </is>
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>224848.0</t>
+          <t>435553.0</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
@@ -6635,7 +6635,7 @@
       </c>
       <c r="BU13" t="inlineStr">
         <is>
-          <t>-1.10</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="BV13" t="inlineStr">
@@ -6660,7 +6660,7 @@
       </c>
       <c r="BZ13" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="CA13" t="inlineStr">
@@ -6680,22 +6680,22 @@
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>4.28</t>
+          <t>4.32</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="CH13" t="inlineStr">
@@ -6705,7 +6705,7 @@
       </c>
       <c r="CI13" t="inlineStr">
         <is>
-          <t>561.54</t>
+          <t>548.46</t>
         </is>
       </c>
       <c r="CJ13" t="inlineStr">
@@ -6720,12 +6720,12 @@
       </c>
       <c r="CL13" t="inlineStr">
         <is>
-          <t>95.01</t>
+          <t>95.21</t>
         </is>
       </c>
       <c r="CM13" t="inlineStr">
         <is>
-          <t>18908</t>
+          <t>18467</t>
         </is>
       </c>
       <c r="CN13" t="inlineStr">
@@ -6740,27 +6740,27 @@
       </c>
       <c r="CP13" t="inlineStr">
         <is>
-          <t>光電業平上櫃</t>
+          <t>光電業右下上櫃</t>
         </is>
       </c>
       <c r="CQ13" t="inlineStr">
         <is>
-          <t>71.5</t>
+          <t>73.6</t>
         </is>
       </c>
       <c r="CR13" t="inlineStr">
         <is>
-          <t>73.4</t>
+          <t>73.7</t>
         </is>
       </c>
       <c r="CS13" t="inlineStr">
         <is>
-          <t>70.7</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="CT13" t="inlineStr">
         <is>
-          <t>72.2</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="CU13" t="inlineStr">
@@ -6792,12 +6792,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-0.83</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2854.0</t>
+          <t>3110.0</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6807,7 +6807,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>71.8</t>
+          <t>72.2</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6817,17 +6817,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>-1.26</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>30.27</t>
+          <t>42.29</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6837,7 +6837,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -6892,7 +6892,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>-7.59</t>
+          <t>-7.08</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6917,7 +6917,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
@@ -6967,17 +6967,17 @@
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>6.57</t>
+          <t>7.16</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>-2.08</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
@@ -6988,75 +6988,75 @@
       <c r="AP14" t="inlineStr"/>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>6029</t>
+          <t>1512</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
         <is>
-          <t>85.29</t>
+          <t>89.22</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>92.16</t>
+          <t>88.56</t>
         </is>
       </c>
       <c r="AU14" t="n">
-        <v>0.76</v>
+        <v>-0.39</v>
       </c>
       <c r="AV14" t="n">
-        <v>8.17</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>-1.47</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>-4.89</t>
+          <t>-4.87</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>71.25999999999999</t>
+          <t>72.47999999999999</t>
         </is>
       </c>
       <c r="AZ14" t="n">
-        <v>65.88</v>
+        <v>66.38</v>
       </c>
       <c r="BA14" t="n">
-        <v>66.86</v>
+        <v>66.81999999999999</v>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>70.29</t>
+          <t>70.24</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>326.92</t>
+          <t>173.26</t>
         </is>
       </c>
       <c r="BD14" t="n">
-        <v>1.48</v>
+        <v>1.67</v>
       </c>
       <c r="BE14" t="n">
-        <v>0.35</v>
+        <v>0.61</v>
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>10.1</t>
+          <t>8.38</t>
         </is>
       </c>
       <c r="BG14" t="inlineStr">
         <is>
-          <t>-96.56</t>
+          <t>-92.70</t>
         </is>
       </c>
       <c r="BH14" t="inlineStr">
@@ -7066,43 +7066,43 @@
       </c>
       <c r="BI14" t="inlineStr">
         <is>
-          <t>1147051.08033241</t>
+          <t>1281159.541237113</t>
         </is>
       </c>
       <c r="BJ14" t="inlineStr">
         <is>
-          <t>205765.0</t>
+          <t>224848.0</t>
         </is>
       </c>
       <c r="BK14" t="n">
-        <v>368941</v>
+        <v>378776.4</v>
       </c>
       <c r="BL14" t="inlineStr">
         <is>
-          <t>283217.3</t>
+          <t>266193.0</t>
         </is>
       </c>
       <c r="BM14" t="n">
-        <v>123456.28</v>
+        <v>125841.48</v>
       </c>
       <c r="BN14" t="inlineStr">
         <is>
-          <t>85723</t>
+          <t>112583</t>
         </is>
       </c>
       <c r="BO14" t="inlineStr">
         <is>
-          <t>30762.1782190815</t>
+          <t>30997.31530428781</t>
         </is>
       </c>
       <c r="BP14" t="inlineStr">
         <is>
-          <t>42844.99990001565</t>
+          <t>32290.56927292253</t>
         </is>
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>205765.0</t>
+          <t>224848.0</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
@@ -7122,7 +7122,7 @@
       </c>
       <c r="BU14" t="inlineStr">
         <is>
-          <t>-1.64</t>
+          <t>-1.10</t>
         </is>
       </c>
       <c r="BV14" t="inlineStr">
@@ -7147,7 +7147,7 @@
       </c>
       <c r="BZ14" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="CA14" t="inlineStr">
@@ -7172,17 +7172,17 @@
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>4.25</t>
+          <t>4.28</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="CH14" t="inlineStr">
@@ -7192,7 +7192,7 @@
       </c>
       <c r="CI14" t="inlineStr">
         <is>
-          <t>561.54</t>
+          <t>548.46</t>
         </is>
       </c>
       <c r="CJ14" t="inlineStr">
@@ -7207,12 +7207,12 @@
       </c>
       <c r="CL14" t="inlineStr">
         <is>
-          <t>95.01</t>
+          <t>95.21</t>
         </is>
       </c>
       <c r="CM14" t="inlineStr">
         <is>
-          <t>18908</t>
+          <t>18467</t>
         </is>
       </c>
       <c r="CN14" t="inlineStr">
@@ -7227,27 +7227,27 @@
       </c>
       <c r="CP14" t="inlineStr">
         <is>
-          <t>光電業平上櫃</t>
+          <t>光電業右下上櫃</t>
         </is>
       </c>
       <c r="CQ14" t="inlineStr">
         <is>
-          <t>72.6</t>
+          <t>71.5</t>
         </is>
       </c>
       <c r="CR14" t="inlineStr">
         <is>
-          <t>73.8</t>
+          <t>73.4</t>
         </is>
       </c>
       <c r="CS14" t="inlineStr">
         <is>
-          <t>71.3</t>
+          <t>70.7</t>
         </is>
       </c>
       <c r="CT14" t="inlineStr">
         <is>
-          <t>71.8</t>
+          <t>72.2</t>
         </is>
       </c>
       <c r="CU14" t="inlineStr">
@@ -7279,12 +7279,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-1.23</t>
+          <t>-0.83</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>4590.0</t>
+          <t>2854.0</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -7294,7 +7294,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>72.4</t>
+          <t>71.8</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -7304,17 +7304,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>-0.7</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>24.41</t>
+          <t>30.27</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -7324,7 +7324,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -7379,7 +7379,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>-6.82</t>
+          <t>-7.59</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -7404,7 +7404,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>-0.06</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
@@ -7454,17 +7454,17 @@
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>2025-12-24</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>10.57</t>
+          <t>6.57</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>-2.08</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
@@ -7475,75 +7475,75 @@
       <c r="AP15" t="inlineStr"/>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>6029</t>
+          <t>1512</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
         <is>
-          <t>91.18</t>
+          <t>85.29</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>97.06</t>
+          <t>92.16</t>
         </is>
       </c>
       <c r="AU15" t="n">
-        <v>3.99</v>
+        <v>0.76</v>
       </c>
       <c r="AV15" t="n">
-        <v>6.41</v>
+        <v>8.17</v>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>-2.18</t>
+          <t>-1.47</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>-4.99</t>
+          <t>-4.89</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>69.62</t>
+          <t>71.25999999999999</t>
         </is>
       </c>
       <c r="AZ15" t="n">
-        <v>65.42</v>
+        <v>65.88</v>
       </c>
       <c r="BA15" t="n">
-        <v>66.88</v>
+        <v>66.86</v>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>70.39</t>
+          <t>70.3</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>1881.60</t>
+          <t>326.92</t>
         </is>
       </c>
       <c r="BD15" t="n">
-        <v>1.26</v>
+        <v>1.48</v>
       </c>
       <c r="BE15" t="n">
-        <v>0.06</v>
+        <v>0.35</v>
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>10.1</t>
+          <t>8.38</t>
         </is>
       </c>
       <c r="BG15" t="inlineStr">
         <is>
-          <t>-99.37</t>
+          <t>-95.86</t>
         </is>
       </c>
       <c r="BH15" t="inlineStr">
@@ -7553,43 +7553,43 @@
       </c>
       <c r="BI15" t="inlineStr">
         <is>
-          <t>1147051.08033241</t>
+          <t>1281159.541237113</t>
         </is>
       </c>
       <c r="BJ15" t="inlineStr">
         <is>
-          <t>330882.0</t>
+          <t>205765.0</t>
         </is>
       </c>
       <c r="BK15" t="n">
-        <v>344617.8</v>
+        <v>368941</v>
       </c>
       <c r="BL15" t="inlineStr">
         <is>
-          <t>277012.5</t>
+          <t>283217.3</t>
         </is>
       </c>
       <c r="BM15" t="n">
-        <v>120544.5</v>
+        <v>123456.28</v>
       </c>
       <c r="BN15" t="inlineStr">
         <is>
-          <t>67605</t>
+          <t>85723</t>
         </is>
       </c>
       <c r="BO15" t="inlineStr">
         <is>
-          <t>28565.30154982075</t>
+          <t>30762.1782190815</t>
         </is>
       </c>
       <c r="BP15" t="inlineStr">
         <is>
-          <t>58437.18651371956</t>
+          <t>42844.99990001565</t>
         </is>
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>330882.0</t>
+          <t>205765.0</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
@@ -7609,7 +7609,7 @@
       </c>
       <c r="BU15" t="inlineStr">
         <is>
-          <t>-0.82</t>
+          <t>-1.64</t>
         </is>
       </c>
       <c r="BV15" t="inlineStr">
@@ -7634,7 +7634,7 @@
       </c>
       <c r="BZ15" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="CA15" t="inlineStr">
@@ -7654,22 +7654,22 @@
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>4.29</t>
+          <t>4.25</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="CH15" t="inlineStr">
@@ -7679,7 +7679,7 @@
       </c>
       <c r="CI15" t="inlineStr">
         <is>
-          <t>561.54</t>
+          <t>548.46</t>
         </is>
       </c>
       <c r="CJ15" t="inlineStr">
@@ -7694,12 +7694,12 @@
       </c>
       <c r="CL15" t="inlineStr">
         <is>
-          <t>95.01</t>
+          <t>95.21</t>
         </is>
       </c>
       <c r="CM15" t="inlineStr">
         <is>
-          <t>18908</t>
+          <t>18467</t>
         </is>
       </c>
       <c r="CN15" t="inlineStr">
@@ -7714,12 +7714,12 @@
       </c>
       <c r="CP15" t="inlineStr">
         <is>
-          <t>光電業平上櫃</t>
+          <t>光電業右下上櫃</t>
         </is>
       </c>
       <c r="CQ15" t="inlineStr">
         <is>
-          <t>73.3</t>
+          <t>72.6</t>
         </is>
       </c>
       <c r="CR15" t="inlineStr">
@@ -7729,12 +7729,12 @@
       </c>
       <c r="CS15" t="inlineStr">
         <is>
-          <t>70.9</t>
+          <t>71.3</t>
         </is>
       </c>
       <c r="CT15" t="inlineStr">
         <is>
-          <t>72.4</t>
+          <t>71.8</t>
         </is>
       </c>
       <c r="CU15" t="inlineStr">
@@ -7766,12 +7766,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>-1.23</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>11495.0</t>
+          <t>4590.0</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -7781,7 +7781,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>73.3</t>
+          <t>72.4</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -7791,17 +7791,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>-1.54</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>9.24</t>
+          <t>24.41</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -7811,7 +7811,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -7866,7 +7866,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>-5.66</t>
+          <t>-6.82</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7891,7 +7891,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>0.29</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
@@ -7941,17 +7941,17 @@
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2025-12-24</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>26.48</t>
+          <t>10.57</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>3.86</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
@@ -7962,75 +7962,75 @@
       <c r="AP16" t="inlineStr"/>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>6029</t>
+          <t>1512</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>91.18</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>82.54</t>
+          <t>97.06</t>
         </is>
       </c>
       <c r="AU16" t="n">
-        <v>8.140000000000001</v>
+        <v>3.99</v>
       </c>
       <c r="AV16" t="n">
-        <v>4.35</v>
+        <v>6.41</v>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>-2.84</t>
+          <t>-2.18</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>-5.16</t>
+          <t>-4.99</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>67.78</t>
+          <t>69.62</t>
         </is>
       </c>
       <c r="AZ16" t="n">
-        <v>64.95999999999999</v>
+        <v>65.42</v>
       </c>
       <c r="BA16" t="n">
-        <v>66.84999999999999</v>
+        <v>66.88</v>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>70.49</t>
+          <t>70.39</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>478.83</t>
+          <t>1881.60</t>
         </is>
       </c>
       <c r="BD16" t="n">
-        <v>0.89</v>
+        <v>1.26</v>
       </c>
       <c r="BE16" t="n">
-        <v>-0.23</v>
+        <v>0.06</v>
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>10.1</t>
+          <t>8.38</t>
         </is>
       </c>
       <c r="BG16" t="inlineStr">
         <is>
-          <t>-102.32</t>
+          <t>-99.24</t>
         </is>
       </c>
       <c r="BH16" t="inlineStr">
@@ -8040,43 +8040,43 @@
       </c>
       <c r="BI16" t="inlineStr">
         <is>
-          <t>1147051.08033241</t>
+          <t>1281159.541237113</t>
         </is>
       </c>
       <c r="BJ16" t="inlineStr">
         <is>
-          <t>828291.0</t>
+          <t>330882.0</t>
         </is>
       </c>
       <c r="BK16" t="n">
-        <v>288810</v>
+        <v>344617.8</v>
       </c>
       <c r="BL16" t="inlineStr">
         <is>
-          <t>264378.8</t>
+          <t>277012.5</t>
         </is>
       </c>
       <c r="BM16" t="n">
-        <v>116266.12</v>
+        <v>120544.5</v>
       </c>
       <c r="BN16" t="inlineStr">
         <is>
-          <t>24431</t>
+          <t>67605</t>
         </is>
       </c>
       <c r="BO16" t="inlineStr">
         <is>
-          <t>23134.04973820278</t>
+          <t>28565.30154982075</t>
         </is>
       </c>
       <c r="BP16" t="inlineStr">
         <is>
-          <t>65219.30358637802</t>
+          <t>58437.18651371956</t>
         </is>
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>828291.0</t>
+          <t>330882.0</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
@@ -8096,7 +8096,7 @@
       </c>
       <c r="BU16" t="inlineStr">
         <is>
-          <t>0.41</t>
+          <t>-0.82</t>
         </is>
       </c>
       <c r="BV16" t="inlineStr">
@@ -8121,7 +8121,7 @@
       </c>
       <c r="BZ16" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="CA16" t="inlineStr">
@@ -8141,22 +8141,22 @@
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>4.34</t>
+          <t>4.29</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="CH16" t="inlineStr">
@@ -8166,7 +8166,7 @@
       </c>
       <c r="CI16" t="inlineStr">
         <is>
-          <t>561.54</t>
+          <t>548.46</t>
         </is>
       </c>
       <c r="CJ16" t="inlineStr">
@@ -8181,12 +8181,12 @@
       </c>
       <c r="CL16" t="inlineStr">
         <is>
-          <t>95.01</t>
+          <t>95.21</t>
         </is>
       </c>
       <c r="CM16" t="inlineStr">
         <is>
-          <t>18908</t>
+          <t>18467</t>
         </is>
       </c>
       <c r="CN16" t="inlineStr">
@@ -8201,27 +8201,27 @@
       </c>
       <c r="CP16" t="inlineStr">
         <is>
-          <t>光電業平上櫃</t>
+          <t>光電業右下上櫃</t>
         </is>
       </c>
       <c r="CQ16" t="inlineStr">
         <is>
-          <t>71.3</t>
+          <t>73.3</t>
         </is>
       </c>
       <c r="CR16" t="inlineStr">
         <is>
-          <t>73.6</t>
+          <t>73.8</t>
         </is>
       </c>
       <c r="CS16" t="inlineStr">
         <is>
-          <t>70.3</t>
+          <t>70.9</t>
         </is>
       </c>
       <c r="CT16" t="inlineStr">
         <is>
-          <t>73.3</t>
+          <t>72.4</t>
         </is>
       </c>
       <c r="CU16" t="inlineStr">
@@ -8253,12 +8253,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>9.12</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>4186.0</t>
+          <t>11495.0</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -8268,7 +8268,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>72.7</t>
+          <t>73.3</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -8278,17 +8278,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>0.41</t>
+          <t>-2.81</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>-20.83</t>
+          <t>9.24</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -8298,7 +8298,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -8353,7 +8353,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>-6.44</t>
+          <t>-5.66</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -8378,7 +8378,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>0.29</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
@@ -8428,17 +8428,17 @@
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-23</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>9.64</t>
+          <t>26.48</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>2.97</t>
+          <t>3.86</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
@@ -8449,12 +8449,12 @@
       <c r="AP17" t="inlineStr"/>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>6029</t>
+          <t>1512</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -8464,60 +8464,60 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>51.85</t>
+          <t>82.54</t>
         </is>
       </c>
       <c r="AU17" t="n">
-        <v>10.59</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="AV17" t="n">
-        <v>2.1</v>
+        <v>4.35</v>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>-3.69</t>
+          <t>-2.84</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>-5.29</t>
+          <t>-5.16</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>65.74</t>
+          <t>67.78</t>
         </is>
       </c>
       <c r="AZ17" t="n">
-        <v>64.39</v>
+        <v>64.95999999999999</v>
       </c>
       <c r="BA17" t="n">
         <v>66.84999999999999</v>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>70.58</t>
+          <t>70.5</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>161.44</t>
+          <t>478.83</t>
         </is>
       </c>
       <c r="BD17" t="n">
-        <v>0.32</v>
+        <v>0.89</v>
       </c>
       <c r="BE17" t="n">
-        <v>-0.52</v>
+        <v>-0.23</v>
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>10.1</t>
+          <t>8.38</t>
         </is>
       </c>
       <c r="BG17" t="inlineStr">
         <is>
-          <t>-105.11</t>
+          <t>-102.80</t>
         </is>
       </c>
       <c r="BH17" t="inlineStr">
@@ -8527,43 +8527,43 @@
       </c>
       <c r="BI17" t="inlineStr">
         <is>
-          <t>1147051.08033241</t>
+          <t>1281159.541237113</t>
         </is>
       </c>
       <c r="BJ17" t="inlineStr">
         <is>
-          <t>304096.0</t>
+          <t>828291.0</t>
         </is>
       </c>
       <c r="BK17" t="n">
-        <v>148810.2</v>
+        <v>288810</v>
       </c>
       <c r="BL17" t="inlineStr">
         <is>
-          <t>187961.6</t>
+          <t>264378.8</t>
         </is>
       </c>
       <c r="BM17" t="n">
-        <v>102169.54</v>
+        <v>116266.12</v>
       </c>
       <c r="BN17" t="inlineStr">
         <is>
-          <t>-39151</t>
+          <t>24431</t>
         </is>
       </c>
       <c r="BO17" t="inlineStr">
         <is>
-          <t>15482.18540217091</t>
+          <t>23134.04973820278</t>
         </is>
       </c>
       <c r="BP17" t="inlineStr">
         <is>
-          <t>19284.95999066232</t>
+          <t>65219.30358637802</t>
         </is>
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>304096.0</t>
+          <t>828291.0</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
@@ -8583,7 +8583,7 @@
       </c>
       <c r="BU17" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>0.41</t>
         </is>
       </c>
       <c r="BV17" t="inlineStr">
@@ -8608,7 +8608,7 @@
       </c>
       <c r="BZ17" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="CA17" t="inlineStr">
@@ -8628,7 +8628,7 @@
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
@@ -8638,12 +8638,12 @@
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>4.31</t>
+          <t>4.34</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="CH17" t="inlineStr">
@@ -8653,7 +8653,7 @@
       </c>
       <c r="CI17" t="inlineStr">
         <is>
-          <t>561.54</t>
+          <t>548.46</t>
         </is>
       </c>
       <c r="CJ17" t="inlineStr">
@@ -8668,12 +8668,12 @@
       </c>
       <c r="CL17" t="inlineStr">
         <is>
-          <t>95.01</t>
+          <t>95.21</t>
         </is>
       </c>
       <c r="CM17" t="inlineStr">
         <is>
-          <t>18908</t>
+          <t>18467</t>
         </is>
       </c>
       <c r="CN17" t="inlineStr">
@@ -8688,27 +8688,27 @@
       </c>
       <c r="CP17" t="inlineStr">
         <is>
-          <t>光電業平上櫃</t>
+          <t>光電業右下上櫃</t>
         </is>
       </c>
       <c r="CQ17" t="inlineStr">
         <is>
-          <t>72.4</t>
+          <t>71.3</t>
         </is>
       </c>
       <c r="CR17" t="inlineStr">
         <is>
-          <t>72.7</t>
+          <t>73.6</t>
         </is>
       </c>
       <c r="CS17" t="inlineStr">
         <is>
-          <t>70.6</t>
+          <t>70.3</t>
         </is>
       </c>
       <c r="CT17" t="inlineStr">
         <is>
-          <t>72.7</t>
+          <t>73.3</t>
         </is>
       </c>
       <c r="CU17" t="inlineStr">
@@ -8740,12 +8740,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>3.85</t>
+          <t>9.12</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2647.0</t>
+          <t>4186.0</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -8755,7 +8755,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>66.1</t>
+          <t>72.7</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -8765,17 +8765,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>9.45</t>
+          <t>-1.96</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>-10.23</t>
+          <t>-20.83</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -8785,7 +8785,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -8840,7 +8840,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>-14.93</t>
+          <t>-6.44</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -8865,7 +8865,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
@@ -8915,17 +8915,17 @@
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>2025-12-19</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>6.10</t>
+          <t>9.64</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>2.97</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
@@ -8936,75 +8936,75 @@
       <c r="AP18" t="inlineStr"/>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>6029</t>
+          <t>1512</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
         <is>
-          <t>47.62</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>19.05</t>
+          <t>51.85</t>
         </is>
       </c>
       <c r="AU18" t="n">
-        <v>2.83</v>
+        <v>10.59</v>
       </c>
       <c r="AV18" t="n">
-        <v>0.67</v>
+        <v>2.1</v>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>-4.47</t>
+          <t>-3.69</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>-5.43</t>
+          <t>-5.29</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>64.28</t>
+          <t>65.74</t>
         </is>
       </c>
       <c r="AZ18" t="n">
-        <v>63.86</v>
+        <v>64.39</v>
       </c>
       <c r="BA18" t="n">
-        <v>66.84</v>
+        <v>66.84999999999999</v>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>70.68</t>
+          <t>70.58</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>50.65</t>
+          <t>161.44</t>
         </is>
       </c>
       <c r="BD18" t="n">
-        <v>-0.36</v>
+        <v>0.32</v>
       </c>
       <c r="BE18" t="n">
-        <v>-0.72</v>
+        <v>-0.52</v>
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>10.1</t>
+          <t>8.38</t>
         </is>
       </c>
       <c r="BG18" t="inlineStr">
         <is>
-          <t>-107.17</t>
+          <t>-106.15</t>
         </is>
       </c>
       <c r="BH18" t="inlineStr">
@@ -9014,43 +9014,43 @@
       </c>
       <c r="BI18" t="inlineStr">
         <is>
-          <t>1147051.08033241</t>
+          <t>1281159.541237113</t>
         </is>
       </c>
       <c r="BJ18" t="inlineStr">
         <is>
-          <t>175671.0</t>
+          <t>304096.0</t>
         </is>
       </c>
       <c r="BK18" t="n">
-        <v>153609.6</v>
+        <v>148810.2</v>
       </c>
       <c r="BL18" t="inlineStr">
         <is>
-          <t>171121.6</t>
+          <t>187961.6</t>
         </is>
       </c>
       <c r="BM18" t="n">
-        <v>98092.44</v>
+        <v>102169.54</v>
       </c>
       <c r="BN18" t="inlineStr">
         <is>
-          <t>-17512</t>
+          <t>-39151</t>
         </is>
       </c>
       <c r="BO18" t="inlineStr">
         <is>
-          <t>14790.77184062702</t>
+          <t>15482.18540217091</t>
         </is>
       </c>
       <c r="BP18" t="inlineStr">
         <is>
-          <t>9139.470568544813</t>
+          <t>19284.95999066232</t>
         </is>
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>175671.0</t>
+          <t>304096.0</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
@@ -9070,7 +9070,7 @@
       </c>
       <c r="BU18" t="inlineStr">
         <is>
-          <t>-9.45</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="BV18" t="inlineStr">
@@ -9095,7 +9095,7 @@
       </c>
       <c r="BZ18" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="CA18" t="inlineStr">
@@ -9115,22 +9115,22 @@
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>3.92</t>
+          <t>4.31</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="CH18" t="inlineStr">
@@ -9140,7 +9140,7 @@
       </c>
       <c r="CI18" t="inlineStr">
         <is>
-          <t>561.54</t>
+          <t>548.46</t>
         </is>
       </c>
       <c r="CJ18" t="inlineStr">
@@ -9155,12 +9155,12 @@
       </c>
       <c r="CL18" t="inlineStr">
         <is>
-          <t>95.01</t>
+          <t>95.21</t>
         </is>
       </c>
       <c r="CM18" t="inlineStr">
         <is>
-          <t>18908</t>
+          <t>18467</t>
         </is>
       </c>
       <c r="CN18" t="inlineStr">
@@ -9175,27 +9175,27 @@
       </c>
       <c r="CP18" t="inlineStr">
         <is>
-          <t>光電業平上櫃</t>
+          <t>光電業右下上櫃</t>
         </is>
       </c>
       <c r="CQ18" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>72.4</t>
         </is>
       </c>
       <c r="CR18" t="inlineStr">
         <is>
-          <t>67.8</t>
+          <t>72.7</t>
         </is>
       </c>
       <c r="CS18" t="inlineStr">
         <is>
-          <t>64.3</t>
+          <t>70.6</t>
         </is>
       </c>
       <c r="CT18" t="inlineStr">
         <is>
-          <t>66.1</t>
+          <t>72.7</t>
         </is>
       </c>
       <c r="CU18" t="inlineStr">
@@ -9227,12 +9227,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>3.85</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1318.0</t>
+          <t>2647.0</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -9242,7 +9242,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>63.6</t>
+          <t>66.1</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -9252,17 +9252,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>12.88</t>
+          <t>7.29</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>12.28</t>
+          <t>-10.23</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -9272,7 +9272,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -9327,7 +9327,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>-18.15</t>
+          <t>-14.93</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -9352,7 +9352,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>0.09</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
@@ -9402,17 +9402,17 @@
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2025-12-19</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>3.04</t>
+          <t>6.10</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
@@ -9423,75 +9423,75 @@
       <c r="AP19" t="inlineStr"/>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>6029</t>
+          <t>1512</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
         <is>
-          <t>7.94</t>
+          <t>47.62</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>3.17</t>
+          <t>19.05</t>
         </is>
       </c>
       <c r="AU19" t="n">
-        <v>-2.06</v>
+        <v>2.83</v>
       </c>
       <c r="AV19" t="n">
-        <v>2.16</v>
+        <v>0.67</v>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>-5.1</t>
+          <t>-4.47</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>-5.47</t>
+          <t>-5.43</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>64.94000000000001</t>
+          <t>64.28</t>
         </is>
       </c>
       <c r="AZ19" t="n">
-        <v>63.57</v>
+        <v>63.86</v>
       </c>
       <c r="BA19" t="n">
-        <v>66.98999999999999</v>
+        <v>66.84</v>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>70.86</t>
+          <t>70.68</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>33.70</t>
+          <t>50.65</t>
         </is>
       </c>
       <c r="BD19" t="n">
-        <v>-0.54</v>
+        <v>-0.36</v>
       </c>
       <c r="BE19" t="n">
-        <v>-0.82</v>
+        <v>-0.72</v>
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>10.1</t>
+          <t>8.38</t>
         </is>
       </c>
       <c r="BG19" t="inlineStr">
         <is>
-          <t>-108.08</t>
+          <t>-108.64</t>
         </is>
       </c>
       <c r="BH19" t="inlineStr">
@@ -9501,43 +9501,43 @@
       </c>
       <c r="BI19" t="inlineStr">
         <is>
-          <t>1147051.08033241</t>
+          <t>1281159.541237113</t>
         </is>
       </c>
       <c r="BJ19" t="inlineStr">
         <is>
-          <t>84149.0</t>
+          <t>175671.0</t>
         </is>
       </c>
       <c r="BK19" t="n">
-        <v>197493.6</v>
+        <v>153609.6</v>
       </c>
       <c r="BL19" t="inlineStr">
         <is>
-          <t>175888.9</t>
+          <t>171121.6</t>
         </is>
       </c>
       <c r="BM19" t="n">
-        <v>95849.82000000001</v>
+        <v>98092.44</v>
       </c>
       <c r="BN19" t="inlineStr">
         <is>
-          <t>21604</t>
+          <t>-17512</t>
         </is>
       </c>
       <c r="BO19" t="inlineStr">
         <is>
-          <t>15818.28116282379</t>
+          <t>14790.77184062702</t>
         </is>
       </c>
       <c r="BP19" t="inlineStr">
         <is>
-          <t>8079.326016643201</t>
+          <t>9139.470568544813</t>
         </is>
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>84149.0</t>
+          <t>175671.0</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
@@ -9557,7 +9557,7 @@
       </c>
       <c r="BU19" t="inlineStr">
         <is>
-          <t>-12.88</t>
+          <t>-9.45</t>
         </is>
       </c>
       <c r="BV19" t="inlineStr">
@@ -9582,7 +9582,7 @@
       </c>
       <c r="BZ19" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="CA19" t="inlineStr">
@@ -9602,22 +9602,22 @@
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>3.77</t>
+          <t>3.92</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="CH19" t="inlineStr">
@@ -9627,7 +9627,7 @@
       </c>
       <c r="CI19" t="inlineStr">
         <is>
-          <t>561.54</t>
+          <t>548.46</t>
         </is>
       </c>
       <c r="CJ19" t="inlineStr">
@@ -9642,12 +9642,12 @@
       </c>
       <c r="CL19" t="inlineStr">
         <is>
-          <t>95.01</t>
+          <t>95.21</t>
         </is>
       </c>
       <c r="CM19" t="inlineStr">
         <is>
-          <t>18908</t>
+          <t>18467</t>
         </is>
       </c>
       <c r="CN19" t="inlineStr">
@@ -9662,27 +9662,27 @@
       </c>
       <c r="CP19" t="inlineStr">
         <is>
-          <t>光電業平上櫃</t>
+          <t>光電業右下上櫃</t>
         </is>
       </c>
       <c r="CQ19" t="inlineStr">
         <is>
-          <t>63.2</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="CR19" t="inlineStr">
         <is>
-          <t>65.3</t>
+          <t>67.8</t>
         </is>
       </c>
       <c r="CS19" t="inlineStr">
         <is>
-          <t>62.4</t>
+          <t>64.3</t>
         </is>
       </c>
       <c r="CT19" t="inlineStr">
         <is>
-          <t>63.6</t>
+          <t>66.1</t>
         </is>
       </c>
       <c r="CU19" t="inlineStr">
@@ -9704,22 +9704,22 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>【d1】</t>
+          <t>【d2】</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>6125</t>
+          <t>5371</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>816.0</t>
+          <t>4517.0</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -9729,7 +9729,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>63.2</t>
+          <t>86.6</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -9739,17 +9739,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>13.42</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>14.88</t>
+          <t>19.31</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -9764,32 +9764,32 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2025-09-17 00:00:00</t>
+          <t>2025-07-30 00:00:00</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>2025-09-22 00:00:00</t>
+          <t>2025-09-08 00:00:00</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>2025-07-25 00:00:00</t>
+          <t>2025-03-24 00:00:00</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>2025-08-22 00:00:00</t>
+          <t>2025-03-31 00:00:00</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>80.4</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>77.7</t>
+          <t>119.5</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
@@ -9799,12 +9799,12 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>73.8</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>78.5</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
@@ -9814,22 +9814,22 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>-18.66</t>
+          <t>-27.53</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>2.42</t>
+          <t>8.22</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025/08/01</t>
+          <t>2024/12/10</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>75.5</t>
+          <t>77.2</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -9839,67 +9839,67 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>-0.1</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>2025/09/30</t>
+          <t>2025/10/22</t>
         </is>
       </c>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>2025/07/07</t>
+          <t>2025/02/12</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>60.7</t>
+          <t>78.7</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>2025/10/27</t>
+          <t>2025/12/16</t>
         </is>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>71.1</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>2025/09/22</t>
+          <t>2025/11/18</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>77.7</t>
+          <t>84.6</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>2025-01-08 00:00:00</t>
+          <t>2025-11-27 00:00:00</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2026-01-02</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>1.88</t>
+          <t>4.01</t>
         </is>
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>-1.58</t>
+          <t>-1.27</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
@@ -9910,121 +9910,121 @@
       <c r="AP20" t="inlineStr"/>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>69</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>6029</t>
+          <t>4517</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>9.84</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>11.64</t>
+          <t>23.28</t>
         </is>
       </c>
       <c r="AU20" t="n">
-        <v>-3.36</v>
+        <v>-1.97</v>
       </c>
       <c r="AV20" t="n">
-        <v>2.94</v>
+        <v>-0.86</v>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>-5.46</t>
+          <t>-1.65</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>-5.41</t>
+          <t>-8.74</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>65.4</t>
+          <t>88.34</t>
         </is>
       </c>
       <c r="AZ20" t="n">
-        <v>63.53</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="BA20" t="n">
-        <v>67.2</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>71.05</t>
+          <t>99.28</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>42.05</t>
+          <t>1.98</t>
         </is>
       </c>
       <c r="BD20" t="n">
-        <v>-0.51</v>
+        <v>-1.15</v>
       </c>
       <c r="BE20" t="n">
-        <v>-0.88</v>
+        <v>-1.18</v>
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>10.1</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="BG20" t="inlineStr">
         <is>
-          <t>-108.76</t>
+          <t>-109.79</t>
         </is>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2025/11/27</t>
+          <t>2025/12/23</t>
         </is>
       </c>
       <c r="BI20" t="inlineStr">
         <is>
-          <t>1147051.08033241</t>
+          <t>1620700.515463918</t>
         </is>
       </c>
       <c r="BJ20" t="inlineStr">
         <is>
-          <t>51843.0</t>
+          <t>393125.0</t>
         </is>
       </c>
       <c r="BK20" t="n">
-        <v>209407.2</v>
+        <v>1007832.8</v>
       </c>
       <c r="BL20" t="inlineStr">
         <is>
-          <t>182286.2</t>
+          <t>844744.2</t>
         </is>
       </c>
       <c r="BM20" t="n">
-        <v>96185.08</v>
+        <v>1254190.86</v>
       </c>
       <c r="BN20" t="inlineStr">
         <is>
-          <t>27121</t>
+          <t>163088</t>
         </is>
       </c>
       <c r="BO20" t="inlineStr">
         <is>
-          <t>17225.3639166748</t>
+          <t>-39604.96234035039</t>
         </is>
       </c>
       <c r="BP20" t="inlineStr">
         <is>
-          <t>16082.21501333226</t>
+          <t>8933.593054521945</t>
         </is>
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>51843.0</t>
+          <t>393125.0</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
@@ -10034,27 +10034,27 @@
       </c>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
         <is>
-          <t>2025/12/30</t>
+          <t>2025/07/28</t>
         </is>
       </c>
       <c r="BU20" t="inlineStr">
         <is>
-          <t>-13.42</t>
+          <t>27.35</t>
         </is>
       </c>
       <c r="BV20" t="inlineStr">
         <is>
-          <t>廣運</t>
+          <t>中光電</t>
         </is>
       </c>
       <c r="BW20" t="inlineStr">
         <is>
-          <t>廣運</t>
+          <t>中光電</t>
         </is>
       </c>
       <c r="BX20" t="inlineStr">
@@ -10074,22 +10074,22 @@
       </c>
       <c r="CA20" t="inlineStr">
         <is>
-          <t>-9.276867348133008</t>
+          <t>10.52226299517467</t>
         </is>
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>49.33864609225594</t>
+          <t>27.79118773626352</t>
         </is>
       </c>
       <c r="CC20" t="inlineStr">
         <is>
-          <t>18.62961592762674</t>
+          <t>-2.044940352257788</t>
         </is>
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
@@ -10099,52 +10099,52 @@
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>3.74</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="CH20" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>25.44</t>
         </is>
       </c>
       <c r="CI20" t="inlineStr">
         <is>
-          <t>561.54</t>
+          <t>93.12</t>
         </is>
       </c>
       <c r="CJ20" t="inlineStr">
         <is>
-          <t>17.69%</t>
+          <t>15.18%</t>
         </is>
       </c>
       <c r="CK20" t="inlineStr">
         <is>
-          <t>-6.67%</t>
+          <t>-2.36%</t>
         </is>
       </c>
       <c r="CL20" t="inlineStr">
         <is>
-          <t>95.01</t>
+          <t>95.21</t>
         </is>
       </c>
       <c r="CM20" t="inlineStr">
         <is>
-          <t>18908</t>
+          <t>33859</t>
         </is>
       </c>
       <c r="CN20" t="inlineStr">
         <is>
-          <t>自動化設備74.11%、太陽能產品12.33%、電子零組件8.12%、建材營建4.02%、其他1.41% (2024年)</t>
+          <t>節能產品47.49%、影像產品32.05%、其他20.47% (2024年)</t>
         </is>
       </c>
       <c r="CO20" t="inlineStr">
         <is>
-          <t>廣運-光電業-上櫃</t>
+          <t>中光電-光電業-上櫃</t>
         </is>
       </c>
       <c r="CP20" t="inlineStr">
@@ -10154,32 +10154,32 @@
       </c>
       <c r="CQ20" t="inlineStr">
         <is>
-          <t>63.1</t>
+          <t>86.8</t>
         </is>
       </c>
       <c r="CR20" t="inlineStr">
         <is>
-          <t>64.3</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="CS20" t="inlineStr">
         <is>
-          <t>63.1</t>
+          <t>86.3</t>
         </is>
       </c>
       <c r="CT20" t="inlineStr">
         <is>
-          <t>63.2</t>
+          <t>86.6</t>
         </is>
       </c>
       <c r="CU20" t="inlineStr">
         <is>
-          <t>16.88</t>
+          <t>56.54</t>
         </is>
       </c>
       <c r="CV20" t="inlineStr">
         <is>
-          <t>** 自動化 - 整體解決方案** 平面顯示器 - 生產製程及檢測設備** 電機機械 - 輸送機械及零配件、機電系統工程** 太陽能產業 - 太陽能發電設備/系統及系統工程</t>
+          <t>** 自動化 - 整體解決方案** 電腦及週邊設備 - 印表機、傳真機、掃瞄器、多功能事務機、投影機** 平面顯示器 - 背光模組** 人工智慧 - 系統整合、領域解決方案** 體驗科技 - 近眼顯示(Dear-Eye Display)、垂直應用方案、顯示技術、光學元件/模組、LCoS、OLED、Micro LED、微型顯示器/光機引擎(Light Engine)、ODM/OEM、製造、重工業、物流、安防、醫療、其他</t>
         </is>
       </c>
       <c r="CW20" t="inlineStr">
@@ -10191,22 +10191,22 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>【d1】</t>
+          <t>【d2】</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>6125</t>
+          <t>5371</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-3.54</t>
+          <t>-1.93</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2009.0</t>
+          <t>7033.0</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -10216,7 +10216,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>63.1</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -10226,17 +10226,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>13.56</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>31.55</t>
+          <t>30.41</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -10251,32 +10251,32 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2025-09-17 00:00:00</t>
+          <t>2025-07-30 00:00:00</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>2025-09-22 00:00:00</t>
+          <t>2025-09-08 00:00:00</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>2025-07-25 00:00:00</t>
+          <t>2025-03-24 00:00:00</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>2025-08-22 00:00:00</t>
+          <t>2025-03-31 00:00:00</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>80.4</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>77.7</t>
+          <t>119.5</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
@@ -10286,12 +10286,12 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>73.8</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>78.5</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
@@ -10301,22 +10301,22 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>-18.79</t>
+          <t>-28.03</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>2.42</t>
+          <t>8.22</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025/08/01</t>
+          <t>2024/12/10</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>75.5</t>
+          <t>77.2</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -10326,67 +10326,67 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>-0.26</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>2025/09/30</t>
+          <t>2025/10/22</t>
         </is>
       </c>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>2025/07/07</t>
+          <t>2025/02/12</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>60.7</t>
+          <t>78.7</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>2025/10/27</t>
+          <t>2025/12/16</t>
         </is>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>71.1</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>2025/09/22</t>
+          <t>2025/11/18</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>77.7</t>
+          <t>84.6</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>2025-01-08 00:00:00</t>
+          <t>2025-11-27 00:00:00</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>4.63</t>
+          <t>6.25</t>
         </is>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>-3.49</t>
+          <t>-2.09</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
@@ -10397,121 +10397,121 @@
       <c r="AP21" t="inlineStr"/>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>69</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>6029</t>
+          <t>4517</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>18.67</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>44.44</t>
+          <t>53.33</t>
         </is>
       </c>
       <c r="AU21" t="n">
-        <v>-3.72</v>
+        <v>-3.41</v>
       </c>
       <c r="AV21" t="n">
-        <v>3.25</v>
+        <v>-0.43</v>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>-5.82</t>
+          <t>-1.68</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>-5.43</t>
+          <t>-8.86</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>65.54</t>
+          <t>89.03999999999999</t>
         </is>
       </c>
       <c r="AZ21" t="n">
-        <v>63.48</v>
+        <v>89.42</v>
       </c>
       <c r="BA21" t="n">
-        <v>67.40000000000001</v>
+        <v>90.95</v>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>71.27</t>
+          <t>99.8</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>56.17</t>
+          <t>10.62</t>
         </is>
       </c>
       <c r="BD21" t="n">
-        <v>-0.43</v>
+        <v>-1.06</v>
       </c>
       <c r="BE21" t="n">
-        <v>-0.98</v>
+        <v>-1.18</v>
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>10.1</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="BG21" t="inlineStr">
         <is>
-          <t>-109.68</t>
+          <t>-109.84</t>
         </is>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2025/11/27</t>
+          <t>2025/12/23</t>
         </is>
       </c>
       <c r="BI21" t="inlineStr">
         <is>
-          <t>1147051.08033241</t>
+          <t>1620700.515463918</t>
         </is>
       </c>
       <c r="BJ21" t="inlineStr">
         <is>
-          <t>128292.0</t>
+          <t>608192.0</t>
         </is>
       </c>
       <c r="BK21" t="n">
-        <v>239947.6</v>
+        <v>1086968.4</v>
       </c>
       <c r="BL21" t="inlineStr">
         <is>
-          <t>182405.5</t>
+          <t>833474.0</t>
         </is>
       </c>
       <c r="BM21" t="n">
-        <v>96387.88</v>
+        <v>1262665.78</v>
       </c>
       <c r="BN21" t="inlineStr">
         <is>
-          <t>57542</t>
+          <t>253494</t>
         </is>
       </c>
       <c r="BO21" t="inlineStr">
         <is>
-          <t>17433.20917182799</t>
+          <t>-48430.15423032719</t>
         </is>
       </c>
       <c r="BP21" t="inlineStr">
         <is>
-          <t>30401.90590098329</t>
+          <t>60614.92030778143</t>
         </is>
       </c>
       <c r="BQ21" t="inlineStr">
         <is>
-          <t>128292.0</t>
+          <t>608192.0</t>
         </is>
       </c>
       <c r="BR21" t="inlineStr">
@@ -10521,27 +10521,27 @@
       </c>
       <c r="BS21" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="BT21" t="inlineStr">
         <is>
-          <t>2025/12/30</t>
+          <t>2025/07/28</t>
         </is>
       </c>
       <c r="BU21" t="inlineStr">
         <is>
-          <t>-13.56</t>
+          <t>26.47</t>
         </is>
       </c>
       <c r="BV21" t="inlineStr">
         <is>
-          <t>廣運</t>
+          <t>中光電</t>
         </is>
       </c>
       <c r="BW21" t="inlineStr">
         <is>
-          <t>廣運</t>
+          <t>中光電</t>
         </is>
       </c>
       <c r="BX21" t="inlineStr">
@@ -10561,22 +10561,22 @@
       </c>
       <c r="CA21" t="inlineStr">
         <is>
-          <t>-9.276867348133008</t>
+          <t>10.52226299517467</t>
         </is>
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>49.33864609225594</t>
+          <t>27.79118773626352</t>
         </is>
       </c>
       <c r="CC21" t="inlineStr">
         <is>
-          <t>18.62961592762674</t>
+          <t>-2.044940352257788</t>
         </is>
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
@@ -10586,52 +10586,52 @@
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>3.74</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="CH21" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>25.44</t>
         </is>
       </c>
       <c r="CI21" t="inlineStr">
         <is>
-          <t>561.54</t>
+          <t>93.12</t>
         </is>
       </c>
       <c r="CJ21" t="inlineStr">
         <is>
-          <t>17.69%</t>
+          <t>15.18%</t>
         </is>
       </c>
       <c r="CK21" t="inlineStr">
         <is>
-          <t>-6.67%</t>
+          <t>-2.36%</t>
         </is>
       </c>
       <c r="CL21" t="inlineStr">
         <is>
-          <t>95.01</t>
+          <t>95.21</t>
         </is>
       </c>
       <c r="CM21" t="inlineStr">
         <is>
-          <t>18908</t>
+          <t>33859</t>
         </is>
       </c>
       <c r="CN21" t="inlineStr">
         <is>
-          <t>自動化設備74.11%、太陽能產品12.33%、電子零組件8.12%、建材營建4.02%、其他1.41% (2024年)</t>
+          <t>節能產品47.49%、影像產品32.05%、其他20.47% (2024年)</t>
         </is>
       </c>
       <c r="CO21" t="inlineStr">
         <is>
-          <t>廣運-光電業-上櫃</t>
+          <t>中光電-光電業-上櫃</t>
         </is>
       </c>
       <c r="CP21" t="inlineStr">
@@ -10641,32 +10641,32 @@
       </c>
       <c r="CQ21" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="CR21" t="inlineStr">
         <is>
-          <t>65.4</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="CS21" t="inlineStr">
         <is>
-          <t>63.0</t>
+          <t>85.8</t>
         </is>
       </c>
       <c r="CT21" t="inlineStr">
         <is>
-          <t>63.1</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="CU21" t="inlineStr">
         <is>
-          <t>16.88</t>
+          <t>56.54</t>
         </is>
       </c>
       <c r="CV21" t="inlineStr">
         <is>
-          <t>** 自動化 - 整體解決方案** 平面顯示器 - 生產製程及檢測設備** 電機機械 - 輸送機械及零配件、機電系統工程** 太陽能產業 - 太陽能發電設備/系統及系統工程</t>
+          <t>** 自動化 - 整體解決方案** 電腦及週邊設備 - 印表機、傳真機、掃瞄器、多功能事務機、投影機** 平面顯示器 - 背光模組** 人工智慧 - 系統整合、領域解決方案** 體驗科技 - 近眼顯示(Dear-Eye Display)、垂直應用方案、顯示技術、光學元件/模組、LCoS、OLED、Micro LED、微型顯示器/光機引擎(Light Engine)、ODM/OEM、製造、重工業、物流、安防、醫療、其他</t>
         </is>
       </c>
       <c r="CW21" t="inlineStr">
@@ -10713,12 +10713,12 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-1.27</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-1.01</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -10733,7 +10733,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -10858,7 +10858,7 @@
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>2025-12-30 00:00:00</t>
+          <t>2025-11-27 00:00:00</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
@@ -10884,12 +10884,12 @@
       <c r="AP22" t="inlineStr"/>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>249</t>
+          <t>69</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>23549</t>
+          <t>4517</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -10962,7 +10962,7 @@
       </c>
       <c r="BI22" t="inlineStr">
         <is>
-          <t>1201738.863573407</t>
+          <t>1620700.515463918</t>
         </is>
       </c>
       <c r="BJ22" t="inlineStr">
@@ -11043,7 +11043,7 @@
       </c>
       <c r="BZ22" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="CA22" t="inlineStr">
@@ -11078,7 +11078,7 @@
       </c>
       <c r="CG22" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="CH22" t="inlineStr">
@@ -11088,7 +11088,7 @@
       </c>
       <c r="CI22" t="inlineStr">
         <is>
-          <t>94.3</t>
+          <t>93.12</t>
         </is>
       </c>
       <c r="CJ22" t="inlineStr">
@@ -11103,12 +11103,12 @@
       </c>
       <c r="CL22" t="inlineStr">
         <is>
-          <t>95.01</t>
+          <t>95.21</t>
         </is>
       </c>
       <c r="CM22" t="inlineStr">
         <is>
-          <t>34289</t>
+          <t>33859</t>
         </is>
       </c>
       <c r="CN22" t="inlineStr">
@@ -11123,7 +11123,7 @@
       </c>
       <c r="CP22" t="inlineStr">
         <is>
-          <t>光電業右上上櫃</t>
+          <t>光電業平上櫃</t>
         </is>
       </c>
       <c r="CQ22" t="inlineStr">
@@ -11200,12 +11200,12 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-5.02</t>
+          <t>-6.35</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-1.01</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -11220,7 +11220,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -11345,7 +11345,7 @@
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>2025-12-30 00:00:00</t>
+          <t>2025-11-27 00:00:00</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
@@ -11371,12 +11371,12 @@
       <c r="AP23" t="inlineStr"/>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>249</t>
+          <t>69</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>23549</t>
+          <t>4517</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -11411,7 +11411,7 @@
         </is>
       </c>
       <c r="AZ23" t="n">
-        <v>89.94</v>
+        <v>89.93000000000001</v>
       </c>
       <c r="BA23" t="n">
         <v>91.61</v>
@@ -11449,7 +11449,7 @@
       </c>
       <c r="BI23" t="inlineStr">
         <is>
-          <t>1201738.863573407</t>
+          <t>1620700.515463918</t>
         </is>
       </c>
       <c r="BJ23" t="inlineStr">
@@ -11530,7 +11530,7 @@
       </c>
       <c r="BZ23" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="CA23" t="inlineStr">
@@ -11565,7 +11565,7 @@
       </c>
       <c r="CG23" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="CH23" t="inlineStr">
@@ -11575,7 +11575,7 @@
       </c>
       <c r="CI23" t="inlineStr">
         <is>
-          <t>94.3</t>
+          <t>93.12</t>
         </is>
       </c>
       <c r="CJ23" t="inlineStr">
@@ -11590,12 +11590,12 @@
       </c>
       <c r="CL23" t="inlineStr">
         <is>
-          <t>95.01</t>
+          <t>95.21</t>
         </is>
       </c>
       <c r="CM23" t="inlineStr">
         <is>
-          <t>34289</t>
+          <t>33859</t>
         </is>
       </c>
       <c r="CN23" t="inlineStr">
@@ -11610,7 +11610,7 @@
       </c>
       <c r="CP23" t="inlineStr">
         <is>
-          <t>光電業右上上櫃</t>
+          <t>光電業平上櫃</t>
         </is>
       </c>
       <c r="CQ23" t="inlineStr">
@@ -11687,12 +11687,12 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>-1.82</t>
+          <t>-3.12</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>-1.01</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -11707,7 +11707,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -11832,7 +11832,7 @@
       </c>
       <c r="AK24" t="inlineStr">
         <is>
-          <t>2025-12-30 00:00:00</t>
+          <t>2025-11-27 00:00:00</t>
         </is>
       </c>
       <c r="AL24" t="inlineStr">
@@ -11858,12 +11858,12 @@
       <c r="AP24" t="inlineStr"/>
       <c r="AQ24" t="inlineStr">
         <is>
-          <t>249</t>
+          <t>69</t>
         </is>
       </c>
       <c r="AR24" t="inlineStr">
         <is>
-          <t>23549</t>
+          <t>4517</t>
         </is>
       </c>
       <c r="AS24" t="inlineStr">
@@ -11936,7 +11936,7 @@
       </c>
       <c r="BI24" t="inlineStr">
         <is>
-          <t>1201738.863573407</t>
+          <t>1620700.515463918</t>
         </is>
       </c>
       <c r="BJ24" t="inlineStr">
@@ -12017,7 +12017,7 @@
       </c>
       <c r="BZ24" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="CA24" t="inlineStr">
@@ -12052,7 +12052,7 @@
       </c>
       <c r="CG24" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="CH24" t="inlineStr">
@@ -12062,7 +12062,7 @@
       </c>
       <c r="CI24" t="inlineStr">
         <is>
-          <t>94.3</t>
+          <t>93.12</t>
         </is>
       </c>
       <c r="CJ24" t="inlineStr">
@@ -12077,12 +12077,12 @@
       </c>
       <c r="CL24" t="inlineStr">
         <is>
-          <t>95.01</t>
+          <t>95.21</t>
         </is>
       </c>
       <c r="CM24" t="inlineStr">
         <is>
-          <t>34289</t>
+          <t>33859</t>
         </is>
       </c>
       <c r="CN24" t="inlineStr">
@@ -12097,7 +12097,7 @@
       </c>
       <c r="CP24" t="inlineStr">
         <is>
-          <t>光電業右上上櫃</t>
+          <t>光電業平上櫃</t>
         </is>
       </c>
       <c r="CQ24" t="inlineStr">
@@ -12174,12 +12174,12 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>-2.74</t>
+          <t>-4.04</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>-1.01</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -12194,7 +12194,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -12319,7 +12319,7 @@
       </c>
       <c r="AK25" t="inlineStr">
         <is>
-          <t>2025-12-30 00:00:00</t>
+          <t>2025-11-27 00:00:00</t>
         </is>
       </c>
       <c r="AL25" t="inlineStr">
@@ -12345,12 +12345,12 @@
       <c r="AP25" t="inlineStr"/>
       <c r="AQ25" t="inlineStr">
         <is>
-          <t>249</t>
+          <t>69</t>
         </is>
       </c>
       <c r="AR25" t="inlineStr">
         <is>
-          <t>23549</t>
+          <t>4517</t>
         </is>
       </c>
       <c r="AS25" t="inlineStr">
@@ -12385,7 +12385,7 @@
         </is>
       </c>
       <c r="AZ25" t="n">
-        <v>90.27</v>
+        <v>90.26000000000001</v>
       </c>
       <c r="BA25" t="n">
         <v>92.22</v>
@@ -12423,7 +12423,7 @@
       </c>
       <c r="BI25" t="inlineStr">
         <is>
-          <t>1201738.863573407</t>
+          <t>1620700.515463918</t>
         </is>
       </c>
       <c r="BJ25" t="inlineStr">
@@ -12504,7 +12504,7 @@
       </c>
       <c r="BZ25" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="CA25" t="inlineStr">
@@ -12539,7 +12539,7 @@
       </c>
       <c r="CG25" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="CH25" t="inlineStr">
@@ -12549,7 +12549,7 @@
       </c>
       <c r="CI25" t="inlineStr">
         <is>
-          <t>94.3</t>
+          <t>93.12</t>
         </is>
       </c>
       <c r="CJ25" t="inlineStr">
@@ -12564,12 +12564,12 @@
       </c>
       <c r="CL25" t="inlineStr">
         <is>
-          <t>95.01</t>
+          <t>95.21</t>
         </is>
       </c>
       <c r="CM25" t="inlineStr">
         <is>
-          <t>34289</t>
+          <t>33859</t>
         </is>
       </c>
       <c r="CN25" t="inlineStr">
@@ -12584,7 +12584,7 @@
       </c>
       <c r="CP25" t="inlineStr">
         <is>
-          <t>光電業右上上櫃</t>
+          <t>光電業平上櫃</t>
         </is>
       </c>
       <c r="CQ25" t="inlineStr">
@@ -12661,12 +12661,12 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>-3.76</t>
+          <t>-5.08</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>-1.01</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -12681,7 +12681,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -12806,7 +12806,7 @@
       </c>
       <c r="AK26" t="inlineStr">
         <is>
-          <t>2025-12-30 00:00:00</t>
+          <t>2025-11-27 00:00:00</t>
         </is>
       </c>
       <c r="AL26" t="inlineStr">
@@ -12832,12 +12832,12 @@
       <c r="AP26" t="inlineStr"/>
       <c r="AQ26" t="inlineStr">
         <is>
-          <t>249</t>
+          <t>69</t>
         </is>
       </c>
       <c r="AR26" t="inlineStr">
         <is>
-          <t>23549</t>
+          <t>4517</t>
         </is>
       </c>
       <c r="AS26" t="inlineStr">
@@ -12910,7 +12910,7 @@
       </c>
       <c r="BI26" t="inlineStr">
         <is>
-          <t>1201738.863573407</t>
+          <t>1620700.515463918</t>
         </is>
       </c>
       <c r="BJ26" t="inlineStr">
@@ -12991,7 +12991,7 @@
       </c>
       <c r="BZ26" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="CA26" t="inlineStr">
@@ -13026,7 +13026,7 @@
       </c>
       <c r="CG26" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="CH26" t="inlineStr">
@@ -13036,7 +13036,7 @@
       </c>
       <c r="CI26" t="inlineStr">
         <is>
-          <t>94.3</t>
+          <t>93.12</t>
         </is>
       </c>
       <c r="CJ26" t="inlineStr">
@@ -13051,12 +13051,12 @@
       </c>
       <c r="CL26" t="inlineStr">
         <is>
-          <t>95.01</t>
+          <t>95.21</t>
         </is>
       </c>
       <c r="CM26" t="inlineStr">
         <is>
-          <t>34289</t>
+          <t>33859</t>
         </is>
       </c>
       <c r="CN26" t="inlineStr">
@@ -13071,7 +13071,7 @@
       </c>
       <c r="CP26" t="inlineStr">
         <is>
-          <t>光電業右上上櫃</t>
+          <t>光電業平上櫃</t>
         </is>
       </c>
       <c r="CQ26" t="inlineStr">
@@ -13148,12 +13148,12 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>-1.82</t>
+          <t>-3.12</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>-1.01</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -13168,7 +13168,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -13293,7 +13293,7 @@
       </c>
       <c r="AK27" t="inlineStr">
         <is>
-          <t>2025-12-30 00:00:00</t>
+          <t>2025-11-27 00:00:00</t>
         </is>
       </c>
       <c r="AL27" t="inlineStr">
@@ -13319,12 +13319,12 @@
       <c r="AP27" t="inlineStr"/>
       <c r="AQ27" t="inlineStr">
         <is>
-          <t>249</t>
+          <t>69</t>
         </is>
       </c>
       <c r="AR27" t="inlineStr">
         <is>
-          <t>23549</t>
+          <t>4517</t>
         </is>
       </c>
       <c r="AS27" t="inlineStr">
@@ -13397,7 +13397,7 @@
       </c>
       <c r="BI27" t="inlineStr">
         <is>
-          <t>1201738.863573407</t>
+          <t>1620700.515463918</t>
         </is>
       </c>
       <c r="BJ27" t="inlineStr">
@@ -13478,7 +13478,7 @@
       </c>
       <c r="BZ27" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="CA27" t="inlineStr">
@@ -13503,7 +13503,7 @@
       </c>
       <c r="CE27" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CF27" t="inlineStr">
@@ -13513,7 +13513,7 @@
       </c>
       <c r="CG27" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="CH27" t="inlineStr">
@@ -13523,7 +13523,7 @@
       </c>
       <c r="CI27" t="inlineStr">
         <is>
-          <t>94.3</t>
+          <t>93.12</t>
         </is>
       </c>
       <c r="CJ27" t="inlineStr">
@@ -13538,12 +13538,12 @@
       </c>
       <c r="CL27" t="inlineStr">
         <is>
-          <t>95.01</t>
+          <t>95.21</t>
         </is>
       </c>
       <c r="CM27" t="inlineStr">
         <is>
-          <t>34289</t>
+          <t>33859</t>
         </is>
       </c>
       <c r="CN27" t="inlineStr">
@@ -13558,7 +13558,7 @@
       </c>
       <c r="CP27" t="inlineStr">
         <is>
-          <t>光電業右上上櫃</t>
+          <t>光電業平上櫃</t>
         </is>
       </c>
       <c r="CQ27" t="inlineStr">
@@ -13635,12 +13635,12 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>-1.15</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>-1.01</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -13655,7 +13655,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -13780,7 +13780,7 @@
       </c>
       <c r="AK28" t="inlineStr">
         <is>
-          <t>2025-12-30 00:00:00</t>
+          <t>2025-11-27 00:00:00</t>
         </is>
       </c>
       <c r="AL28" t="inlineStr">
@@ -13806,12 +13806,12 @@
       <c r="AP28" t="inlineStr"/>
       <c r="AQ28" t="inlineStr">
         <is>
-          <t>249</t>
+          <t>69</t>
         </is>
       </c>
       <c r="AR28" t="inlineStr">
         <is>
-          <t>23549</t>
+          <t>4517</t>
         </is>
       </c>
       <c r="AS28" t="inlineStr">
@@ -13884,7 +13884,7 @@
       </c>
       <c r="BI28" t="inlineStr">
         <is>
-          <t>1201738.863573407</t>
+          <t>1620700.515463918</t>
         </is>
       </c>
       <c r="BJ28" t="inlineStr">
@@ -13965,7 +13965,7 @@
       </c>
       <c r="BZ28" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="CA28" t="inlineStr">
@@ -13990,7 +13990,7 @@
       </c>
       <c r="CE28" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CF28" t="inlineStr">
@@ -14000,7 +14000,7 @@
       </c>
       <c r="CG28" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="CH28" t="inlineStr">
@@ -14010,7 +14010,7 @@
       </c>
       <c r="CI28" t="inlineStr">
         <is>
-          <t>94.3</t>
+          <t>93.12</t>
         </is>
       </c>
       <c r="CJ28" t="inlineStr">
@@ -14025,12 +14025,12 @@
       </c>
       <c r="CL28" t="inlineStr">
         <is>
-          <t>95.01</t>
+          <t>95.21</t>
         </is>
       </c>
       <c r="CM28" t="inlineStr">
         <is>
-          <t>34289</t>
+          <t>33859</t>
         </is>
       </c>
       <c r="CN28" t="inlineStr">
@@ -14045,7 +14045,7 @@
       </c>
       <c r="CP28" t="inlineStr">
         <is>
-          <t>光電業右上上櫃</t>
+          <t>光電業平上櫃</t>
         </is>
       </c>
       <c r="CQ28" t="inlineStr">
@@ -14079,1467 +14079,6 @@
         </is>
       </c>
       <c r="CW28" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>【e】</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>5371</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>-1.17</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>2769.0</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>84.6</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>3.53</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>-1.01</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>-11.82</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L29" t="inlineStr">
-        <is>
-          <t>50.0</t>
-        </is>
-      </c>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>2025-07-30 00:00:00</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>2025-09-08 00:00:00</t>
-        </is>
-      </c>
-      <c r="O29" t="inlineStr">
-        <is>
-          <t>2025-03-24 00:00:00</t>
-        </is>
-      </c>
-      <c r="P29" t="inlineStr">
-        <is>
-          <t>2025-03-31 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q29" t="inlineStr">
-        <is>
-          <t>79.0</t>
-        </is>
-      </c>
-      <c r="R29" t="inlineStr">
-        <is>
-          <t>119.5</t>
-        </is>
-      </c>
-      <c r="S29" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T29" t="inlineStr">
-        <is>
-          <t>84.0</t>
-        </is>
-      </c>
-      <c r="U29" t="inlineStr">
-        <is>
-          <t>73.0</t>
-        </is>
-      </c>
-      <c r="V29" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W29" t="inlineStr">
-        <is>
-          <t>-29.21</t>
-        </is>
-      </c>
-      <c r="X29" t="inlineStr">
-        <is>
-          <t>8.22</t>
-        </is>
-      </c>
-      <c r="Y29" t="inlineStr">
-        <is>
-          <t>2024/12/10</t>
-        </is>
-      </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>77.2</t>
-        </is>
-      </c>
-      <c r="AA29" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>-0.14</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>2025/10/22</t>
-        </is>
-      </c>
-      <c r="AD29" t="inlineStr">
-        <is>
-          <t>100.0</t>
-        </is>
-      </c>
-      <c r="AE29" t="inlineStr">
-        <is>
-          <t>2025/02/12</t>
-        </is>
-      </c>
-      <c r="AF29" t="inlineStr">
-        <is>
-          <t>78.7</t>
-        </is>
-      </c>
-      <c r="AG29" t="inlineStr">
-        <is>
-          <t>2025/12/16</t>
-        </is>
-      </c>
-      <c r="AH29" t="inlineStr">
-        <is>
-          <t>86.5</t>
-        </is>
-      </c>
-      <c r="AI29" t="inlineStr">
-        <is>
-          <t>2025/11/18</t>
-        </is>
-      </c>
-      <c r="AJ29" t="inlineStr">
-        <is>
-          <t>84.6</t>
-        </is>
-      </c>
-      <c r="AK29" t="inlineStr">
-        <is>
-          <t>2025-12-30 00:00:00</t>
-        </is>
-      </c>
-      <c r="AL29" t="inlineStr">
-        <is>
-          <t>2025-12-18</t>
-        </is>
-      </c>
-      <c r="AM29" t="inlineStr">
-        <is>
-          <t>2.46</t>
-        </is>
-      </c>
-      <c r="AN29" t="inlineStr">
-        <is>
-          <t>-2.01</t>
-        </is>
-      </c>
-      <c r="AO29" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AP29" t="inlineStr"/>
-      <c r="AQ29" t="inlineStr">
-        <is>
-          <t>249</t>
-        </is>
-      </c>
-      <c r="AR29" t="inlineStr">
-        <is>
-          <t>23549</t>
-        </is>
-      </c>
-      <c r="AS29" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AT29" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AU29" t="n">
-        <v>-2.74</v>
-      </c>
-      <c r="AV29" t="n">
-        <v>-3.67</v>
-      </c>
-      <c r="AW29" t="inlineStr">
-        <is>
-          <t>-4.1</t>
-        </is>
-      </c>
-      <c r="AX29" t="inlineStr">
-        <is>
-          <t>-8.59</t>
-        </is>
-      </c>
-      <c r="AY29" t="inlineStr">
-        <is>
-          <t>86.97999999999999</t>
-        </is>
-      </c>
-      <c r="AZ29" t="n">
-        <v>90.29000000000001</v>
-      </c>
-      <c r="BA29" t="n">
-        <v>94.15000000000001</v>
-      </c>
-      <c r="BB29" t="inlineStr">
-        <is>
-          <t>102.99</t>
-        </is>
-      </c>
-      <c r="BC29" t="inlineStr">
-        <is>
-          <t>-24.86</t>
-        </is>
-      </c>
-      <c r="BD29" t="n">
-        <v>-1.99</v>
-      </c>
-      <c r="BE29" t="n">
-        <v>-1.59</v>
-      </c>
-      <c r="BF29" t="inlineStr">
-        <is>
-          <t>12.0</t>
-        </is>
-      </c>
-      <c r="BG29" t="inlineStr">
-        <is>
-          <t>-113.29</t>
-        </is>
-      </c>
-      <c r="BH29" t="inlineStr">
-        <is>
-          <t>2025/12/23</t>
-        </is>
-      </c>
-      <c r="BI29" t="inlineStr">
-        <is>
-          <t>1201738.863573407</t>
-        </is>
-      </c>
-      <c r="BJ29" t="inlineStr">
-        <is>
-          <t>236030.0</t>
-        </is>
-      </c>
-      <c r="BK29" t="n">
-        <v>352700.6</v>
-      </c>
-      <c r="BL29" t="inlineStr">
-        <is>
-          <t>399969.1</t>
-        </is>
-      </c>
-      <c r="BM29" t="n">
-        <v>1446860.1</v>
-      </c>
-      <c r="BN29" t="inlineStr">
-        <is>
-          <t>-47268</t>
-        </is>
-      </c>
-      <c r="BO29" t="inlineStr">
-        <is>
-          <t>-166597.4333998408</t>
-        </is>
-      </c>
-      <c r="BP29" t="inlineStr">
-        <is>
-          <t>-194070.4931036173</t>
-        </is>
-      </c>
-      <c r="BQ29" t="inlineStr">
-        <is>
-          <t>236030.0</t>
-        </is>
-      </c>
-      <c r="BR29" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BS29" t="inlineStr">
-        <is>
-          <t>68.0</t>
-        </is>
-      </c>
-      <c r="BT29" t="inlineStr">
-        <is>
-          <t>2025/07/28</t>
-        </is>
-      </c>
-      <c r="BU29" t="inlineStr">
-        <is>
-          <t>24.41</t>
-        </is>
-      </c>
-      <c r="BV29" t="inlineStr">
-        <is>
-          <t>中光電</t>
-        </is>
-      </c>
-      <c r="BW29" t="inlineStr">
-        <is>
-          <t>中光電</t>
-        </is>
-      </c>
-      <c r="BX29" t="inlineStr">
-        <is>
-          <t>光電業</t>
-        </is>
-      </c>
-      <c r="BY29" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BZ29" t="inlineStr">
-        <is>
-          <t>1.27</t>
-        </is>
-      </c>
-      <c r="CA29" t="inlineStr">
-        <is>
-          <t>10.52226299517467</t>
-        </is>
-      </c>
-      <c r="CB29" t="inlineStr">
-        <is>
-          <t>27.79118773626352</t>
-        </is>
-      </c>
-      <c r="CC29" t="inlineStr">
-        <is>
-          <t>-2.044940352257788</t>
-        </is>
-      </c>
-      <c r="CD29" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
-        </is>
-      </c>
-      <c r="CE29" t="inlineStr">
-        <is>
-          <t>價跌量增</t>
-        </is>
-      </c>
-      <c r="CF29" t="inlineStr">
-        <is>
-          <t>1.50</t>
-        </is>
-      </c>
-      <c r="CG29" t="inlineStr">
-        <is>
-          <t>1.71</t>
-        </is>
-      </c>
-      <c r="CH29" t="inlineStr">
-        <is>
-          <t>25.44</t>
-        </is>
-      </c>
-      <c r="CI29" t="inlineStr">
-        <is>
-          <t>94.3</t>
-        </is>
-      </c>
-      <c r="CJ29" t="inlineStr">
-        <is>
-          <t>15.18%</t>
-        </is>
-      </c>
-      <c r="CK29" t="inlineStr">
-        <is>
-          <t>-2.36%</t>
-        </is>
-      </c>
-      <c r="CL29" t="inlineStr">
-        <is>
-          <t>95.01</t>
-        </is>
-      </c>
-      <c r="CM29" t="inlineStr">
-        <is>
-          <t>34289</t>
-        </is>
-      </c>
-      <c r="CN29" t="inlineStr">
-        <is>
-          <t>節能產品47.49%、影像產品32.05%、其他20.47% (2024年)</t>
-        </is>
-      </c>
-      <c r="CO29" t="inlineStr">
-        <is>
-          <t>中光電-光電業-上櫃</t>
-        </is>
-      </c>
-      <c r="CP29" t="inlineStr">
-        <is>
-          <t>光電業右上上櫃</t>
-        </is>
-      </c>
-      <c r="CQ29" t="inlineStr">
-        <is>
-          <t>85.7</t>
-        </is>
-      </c>
-      <c r="CR29" t="inlineStr">
-        <is>
-          <t>86.3</t>
-        </is>
-      </c>
-      <c r="CS29" t="inlineStr">
-        <is>
-          <t>84.6</t>
-        </is>
-      </c>
-      <c r="CT29" t="inlineStr">
-        <is>
-          <t>84.6</t>
-        </is>
-      </c>
-      <c r="CU29" t="inlineStr">
-        <is>
-          <t>56.54</t>
-        </is>
-      </c>
-      <c r="CV29" t="inlineStr">
-        <is>
-          <t>** 自動化 - 整體解決方案** 電腦及週邊設備 - 印表機、傳真機、掃瞄器、多功能事務機、投影機** 平面顯示器 - 背光模組** 人工智慧 - 系統整合、領域解決方案** 體驗科技 - 近眼顯示(Dear-Eye Display)、垂直應用方案、顯示技術、光學元件/模組、LCoS、OLED、Micro LED、微型顯示器/光機引擎(Light Engine)、ODM/OEM、製造、重工業、物流、安防、醫療、其他</t>
-        </is>
-      </c>
-      <c r="CW29" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>【e】</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>5371</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>-1.03</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>3248.0</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>85.6</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>2.39</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>-1.01</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>-27.29</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L30" t="inlineStr">
-        <is>
-          <t>50.0</t>
-        </is>
-      </c>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>2025-07-30 00:00:00</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr">
-        <is>
-          <t>2025-09-08 00:00:00</t>
-        </is>
-      </c>
-      <c r="O30" t="inlineStr">
-        <is>
-          <t>2025-03-24 00:00:00</t>
-        </is>
-      </c>
-      <c r="P30" t="inlineStr">
-        <is>
-          <t>2025-03-31 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q30" t="inlineStr">
-        <is>
-          <t>79.0</t>
-        </is>
-      </c>
-      <c r="R30" t="inlineStr">
-        <is>
-          <t>119.5</t>
-        </is>
-      </c>
-      <c r="S30" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T30" t="inlineStr">
-        <is>
-          <t>84.0</t>
-        </is>
-      </c>
-      <c r="U30" t="inlineStr">
-        <is>
-          <t>73.0</t>
-        </is>
-      </c>
-      <c r="V30" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W30" t="inlineStr">
-        <is>
-          <t>-28.37</t>
-        </is>
-      </c>
-      <c r="X30" t="inlineStr">
-        <is>
-          <t>8.22</t>
-        </is>
-      </c>
-      <c r="Y30" t="inlineStr">
-        <is>
-          <t>2024/12/10</t>
-        </is>
-      </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>77.2</t>
-        </is>
-      </c>
-      <c r="AA30" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>-0.17</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>2025/10/22</t>
-        </is>
-      </c>
-      <c r="AD30" t="inlineStr">
-        <is>
-          <t>100.0</t>
-        </is>
-      </c>
-      <c r="AE30" t="inlineStr">
-        <is>
-          <t>2025/02/12</t>
-        </is>
-      </c>
-      <c r="AF30" t="inlineStr">
-        <is>
-          <t>78.7</t>
-        </is>
-      </c>
-      <c r="AG30" t="inlineStr">
-        <is>
-          <t>2025/12/16</t>
-        </is>
-      </c>
-      <c r="AH30" t="inlineStr">
-        <is>
-          <t>86.5</t>
-        </is>
-      </c>
-      <c r="AI30" t="inlineStr">
-        <is>
-          <t>2025/11/18</t>
-        </is>
-      </c>
-      <c r="AJ30" t="inlineStr">
-        <is>
-          <t>84.6</t>
-        </is>
-      </c>
-      <c r="AK30" t="inlineStr">
-        <is>
-          <t>2025-12-30 00:00:00</t>
-        </is>
-      </c>
-      <c r="AL30" t="inlineStr">
-        <is>
-          <t>2025-12-17</t>
-        </is>
-      </c>
-      <c r="AM30" t="inlineStr">
-        <is>
-          <t>2.89</t>
-        </is>
-      </c>
-      <c r="AN30" t="inlineStr">
-        <is>
-          <t>-1.87</t>
-        </is>
-      </c>
-      <c r="AO30" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AP30" t="inlineStr"/>
-      <c r="AQ30" t="inlineStr">
-        <is>
-          <t>249</t>
-        </is>
-      </c>
-      <c r="AR30" t="inlineStr">
-        <is>
-          <t>23549</t>
-        </is>
-      </c>
-      <c r="AS30" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AT30" t="inlineStr">
-        <is>
-          <t>7.41</t>
-        </is>
-      </c>
-      <c r="AU30" t="n">
-        <v>-2.55</v>
-      </c>
-      <c r="AV30" t="n">
-        <v>-2.77</v>
-      </c>
-      <c r="AW30" t="inlineStr">
-        <is>
-          <t>-4.74</t>
-        </is>
-      </c>
-      <c r="AX30" t="inlineStr">
-        <is>
-          <t>-8.12</t>
-        </is>
-      </c>
-      <c r="AY30" t="inlineStr">
-        <is>
-          <t>87.84</t>
-        </is>
-      </c>
-      <c r="AZ30" t="n">
-        <v>90.34</v>
-      </c>
-      <c r="BA30" t="n">
-        <v>94.84</v>
-      </c>
-      <c r="BB30" t="inlineStr">
-        <is>
-          <t>103.22</t>
-        </is>
-      </c>
-      <c r="BC30" t="inlineStr">
-        <is>
-          <t>-16.97</t>
-        </is>
-      </c>
-      <c r="BD30" t="n">
-        <v>-1.75</v>
-      </c>
-      <c r="BE30" t="n">
-        <v>-1.5</v>
-      </c>
-      <c r="BF30" t="inlineStr">
-        <is>
-          <t>12.0</t>
-        </is>
-      </c>
-      <c r="BG30" t="inlineStr">
-        <is>
-          <t>-112.46</t>
-        </is>
-      </c>
-      <c r="BH30" t="inlineStr">
-        <is>
-          <t>2025/12/23</t>
-        </is>
-      </c>
-      <c r="BI30" t="inlineStr">
-        <is>
-          <t>1201738.863573407</t>
-        </is>
-      </c>
-      <c r="BJ30" t="inlineStr">
-        <is>
-          <t>280423.0</t>
-        </is>
-      </c>
-      <c r="BK30" t="n">
-        <v>384206.2</v>
-      </c>
-      <c r="BL30" t="inlineStr">
-        <is>
-          <t>528395.3</t>
-        </is>
-      </c>
-      <c r="BM30" t="n">
-        <v>1510744.88</v>
-      </c>
-      <c r="BN30" t="inlineStr">
-        <is>
-          <t>-144189</t>
-        </is>
-      </c>
-      <c r="BO30" t="inlineStr">
-        <is>
-          <t>-161602.3316355178</t>
-        </is>
-      </c>
-      <c r="BP30" t="inlineStr">
-        <is>
-          <t>-194841.1553868933</t>
-        </is>
-      </c>
-      <c r="BQ30" t="inlineStr">
-        <is>
-          <t>280423.0</t>
-        </is>
-      </c>
-      <c r="BR30" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BS30" t="inlineStr">
-        <is>
-          <t>68.0</t>
-        </is>
-      </c>
-      <c r="BT30" t="inlineStr">
-        <is>
-          <t>2025/07/28</t>
-        </is>
-      </c>
-      <c r="BU30" t="inlineStr">
-        <is>
-          <t>25.88</t>
-        </is>
-      </c>
-      <c r="BV30" t="inlineStr">
-        <is>
-          <t>中光電</t>
-        </is>
-      </c>
-      <c r="BW30" t="inlineStr">
-        <is>
-          <t>中光電</t>
-        </is>
-      </c>
-      <c r="BX30" t="inlineStr">
-        <is>
-          <t>光電業</t>
-        </is>
-      </c>
-      <c r="BY30" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BZ30" t="inlineStr">
-        <is>
-          <t>1.27</t>
-        </is>
-      </c>
-      <c r="CA30" t="inlineStr">
-        <is>
-          <t>10.52226299517467</t>
-        </is>
-      </c>
-      <c r="CB30" t="inlineStr">
-        <is>
-          <t>27.79118773626352</t>
-        </is>
-      </c>
-      <c r="CC30" t="inlineStr">
-        <is>
-          <t>-2.044940352257788</t>
-        </is>
-      </c>
-      <c r="CD30" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="CE30" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="CF30" t="inlineStr">
-        <is>
-          <t>1.51</t>
-        </is>
-      </c>
-      <c r="CG30" t="inlineStr">
-        <is>
-          <t>1.71</t>
-        </is>
-      </c>
-      <c r="CH30" t="inlineStr">
-        <is>
-          <t>25.44</t>
-        </is>
-      </c>
-      <c r="CI30" t="inlineStr">
-        <is>
-          <t>94.3</t>
-        </is>
-      </c>
-      <c r="CJ30" t="inlineStr">
-        <is>
-          <t>15.18%</t>
-        </is>
-      </c>
-      <c r="CK30" t="inlineStr">
-        <is>
-          <t>-2.36%</t>
-        </is>
-      </c>
-      <c r="CL30" t="inlineStr">
-        <is>
-          <t>95.01</t>
-        </is>
-      </c>
-      <c r="CM30" t="inlineStr">
-        <is>
-          <t>34289</t>
-        </is>
-      </c>
-      <c r="CN30" t="inlineStr">
-        <is>
-          <t>節能產品47.49%、影像產品32.05%、其他20.47% (2024年)</t>
-        </is>
-      </c>
-      <c r="CO30" t="inlineStr">
-        <is>
-          <t>中光電-光電業-上櫃</t>
-        </is>
-      </c>
-      <c r="CP30" t="inlineStr">
-        <is>
-          <t>光電業右上上櫃</t>
-        </is>
-      </c>
-      <c r="CQ30" t="inlineStr">
-        <is>
-          <t>87.0</t>
-        </is>
-      </c>
-      <c r="CR30" t="inlineStr">
-        <is>
-          <t>87.4</t>
-        </is>
-      </c>
-      <c r="CS30" t="inlineStr">
-        <is>
-          <t>85.4</t>
-        </is>
-      </c>
-      <c r="CT30" t="inlineStr">
-        <is>
-          <t>85.6</t>
-        </is>
-      </c>
-      <c r="CU30" t="inlineStr">
-        <is>
-          <t>56.54</t>
-        </is>
-      </c>
-      <c r="CV30" t="inlineStr">
-        <is>
-          <t>** 自動化 - 整體解決方案** 電腦及週邊設備 - 印表機、傳真機、掃瞄器、多功能事務機、投影機** 平面顯示器 - 背光模組** 人工智慧 - 系統整合、領域解決方案** 體驗科技 - 近眼顯示(Dear-Eye Display)、垂直應用方案、顯示技術、光學元件/模組、LCoS、OLED、Micro LED、微型顯示器/光機引擎(Light Engine)、ODM/OEM、製造、重工業、物流、安防、醫療、其他</t>
-        </is>
-      </c>
-      <c r="CW30" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>【e】</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>5371</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>-3.44</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>6318.0</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>86.5</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>1.37</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>-1.01</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>-22.89</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L31" t="inlineStr">
-        <is>
-          <t>50.0</t>
-        </is>
-      </c>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>2025-07-30 00:00:00</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr">
-        <is>
-          <t>2025-09-08 00:00:00</t>
-        </is>
-      </c>
-      <c r="O31" t="inlineStr">
-        <is>
-          <t>2025-03-24 00:00:00</t>
-        </is>
-      </c>
-      <c r="P31" t="inlineStr">
-        <is>
-          <t>2025-03-31 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q31" t="inlineStr">
-        <is>
-          <t>79.0</t>
-        </is>
-      </c>
-      <c r="R31" t="inlineStr">
-        <is>
-          <t>119.5</t>
-        </is>
-      </c>
-      <c r="S31" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T31" t="inlineStr">
-        <is>
-          <t>84.0</t>
-        </is>
-      </c>
-      <c r="U31" t="inlineStr">
-        <is>
-          <t>73.0</t>
-        </is>
-      </c>
-      <c r="V31" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W31" t="inlineStr">
-        <is>
-          <t>-27.62</t>
-        </is>
-      </c>
-      <c r="X31" t="inlineStr">
-        <is>
-          <t>8.22</t>
-        </is>
-      </c>
-      <c r="Y31" t="inlineStr">
-        <is>
-          <t>2024/12/10</t>
-        </is>
-      </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>77.2</t>
-        </is>
-      </c>
-      <c r="AA31" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>-0.21</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>2025/10/22</t>
-        </is>
-      </c>
-      <c r="AD31" t="inlineStr">
-        <is>
-          <t>100.0</t>
-        </is>
-      </c>
-      <c r="AE31" t="inlineStr">
-        <is>
-          <t>2025/02/12</t>
-        </is>
-      </c>
-      <c r="AF31" t="inlineStr">
-        <is>
-          <t>78.7</t>
-        </is>
-      </c>
-      <c r="AG31" t="inlineStr">
-        <is>
-          <t>2025/12/16</t>
-        </is>
-      </c>
-      <c r="AH31" t="inlineStr">
-        <is>
-          <t>86.5</t>
-        </is>
-      </c>
-      <c r="AI31" t="inlineStr">
-        <is>
-          <t>2025/11/18</t>
-        </is>
-      </c>
-      <c r="AJ31" t="inlineStr">
-        <is>
-          <t>84.6</t>
-        </is>
-      </c>
-      <c r="AK31" t="inlineStr">
-        <is>
-          <t>2025-12-30 00:00:00</t>
-        </is>
-      </c>
-      <c r="AL31" t="inlineStr">
-        <is>
-          <t>2025-12-16</t>
-        </is>
-      </c>
-      <c r="AM31" t="inlineStr">
-        <is>
-          <t>5.61</t>
-        </is>
-      </c>
-      <c r="AN31" t="inlineStr">
-        <is>
-          <t>-2.63</t>
-        </is>
-      </c>
-      <c r="AO31" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AP31" t="inlineStr"/>
-      <c r="AQ31" t="inlineStr">
-        <is>
-          <t>249</t>
-        </is>
-      </c>
-      <c r="AR31" t="inlineStr">
-        <is>
-          <t>23549</t>
-        </is>
-      </c>
-      <c r="AS31" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AT31" t="inlineStr">
-        <is>
-          <t>7.41</t>
-        </is>
-      </c>
-      <c r="AU31" t="n">
-        <v>-2.24</v>
-      </c>
-      <c r="AV31" t="n">
-        <v>-1.96</v>
-      </c>
-      <c r="AW31" t="inlineStr">
-        <is>
-          <t>-5.45</t>
-        </is>
-      </c>
-      <c r="AX31" t="inlineStr">
-        <is>
-          <t>-7.76</t>
-        </is>
-      </c>
-      <c r="AY31" t="inlineStr">
-        <is>
-          <t>88.47999999999999</t>
-        </is>
-      </c>
-      <c r="AZ31" t="n">
-        <v>90.23999999999999</v>
-      </c>
-      <c r="BA31" t="n">
-        <v>95.45</v>
-      </c>
-      <c r="BB31" t="inlineStr">
-        <is>
-          <t>103.47</t>
-        </is>
-      </c>
-      <c r="BC31" t="inlineStr">
-        <is>
-          <t>-5.95</t>
-        </is>
-      </c>
-      <c r="BD31" t="n">
-        <v>-1.52</v>
-      </c>
-      <c r="BE31" t="n">
-        <v>-1.43</v>
-      </c>
-      <c r="BF31" t="inlineStr">
-        <is>
-          <t>12.0</t>
-        </is>
-      </c>
-      <c r="BG31" t="inlineStr">
-        <is>
-          <t>-111.93</t>
-        </is>
-      </c>
-      <c r="BH31" t="inlineStr">
-        <is>
-          <t>2025/12/23</t>
-        </is>
-      </c>
-      <c r="BI31" t="inlineStr">
-        <is>
-          <t>1201738.863573407</t>
-        </is>
-      </c>
-      <c r="BJ31" t="inlineStr">
-        <is>
-          <t>548561.0</t>
-        </is>
-      </c>
-      <c r="BK31" t="n">
-        <v>456289.8</v>
-      </c>
-      <c r="BL31" t="inlineStr">
-        <is>
-          <t>591766.0</t>
-        </is>
-      </c>
-      <c r="BM31" t="n">
-        <v>1597364</v>
-      </c>
-      <c r="BN31" t="inlineStr">
-        <is>
-          <t>-135476</t>
-        </is>
-      </c>
-      <c r="BO31" t="inlineStr">
-        <is>
-          <t>-155558.9091352677</t>
-        </is>
-      </c>
-      <c r="BP31" t="inlineStr">
-        <is>
-          <t>-193739.8816706128</t>
-        </is>
-      </c>
-      <c r="BQ31" t="inlineStr">
-        <is>
-          <t>548561.0</t>
-        </is>
-      </c>
-      <c r="BR31" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BS31" t="inlineStr">
-        <is>
-          <t>68.0</t>
-        </is>
-      </c>
-      <c r="BT31" t="inlineStr">
-        <is>
-          <t>2025/07/28</t>
-        </is>
-      </c>
-      <c r="BU31" t="inlineStr">
-        <is>
-          <t>27.21</t>
-        </is>
-      </c>
-      <c r="BV31" t="inlineStr">
-        <is>
-          <t>中光電</t>
-        </is>
-      </c>
-      <c r="BW31" t="inlineStr">
-        <is>
-          <t>中光電</t>
-        </is>
-      </c>
-      <c r="BX31" t="inlineStr">
-        <is>
-          <t>光電業</t>
-        </is>
-      </c>
-      <c r="BY31" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BZ31" t="inlineStr">
-        <is>
-          <t>1.27</t>
-        </is>
-      </c>
-      <c r="CA31" t="inlineStr">
-        <is>
-          <t>10.52226299517467</t>
-        </is>
-      </c>
-      <c r="CB31" t="inlineStr">
-        <is>
-          <t>27.79118773626352</t>
-        </is>
-      </c>
-      <c r="CC31" t="inlineStr">
-        <is>
-          <t>-2.044940352257788</t>
-        </is>
-      </c>
-      <c r="CD31" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="CE31" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="CF31" t="inlineStr">
-        <is>
-          <t>1.53</t>
-        </is>
-      </c>
-      <c r="CG31" t="inlineStr">
-        <is>
-          <t>1.71</t>
-        </is>
-      </c>
-      <c r="CH31" t="inlineStr">
-        <is>
-          <t>25.44</t>
-        </is>
-      </c>
-      <c r="CI31" t="inlineStr">
-        <is>
-          <t>94.3</t>
-        </is>
-      </c>
-      <c r="CJ31" t="inlineStr">
-        <is>
-          <t>15.18%</t>
-        </is>
-      </c>
-      <c r="CK31" t="inlineStr">
-        <is>
-          <t>-2.36%</t>
-        </is>
-      </c>
-      <c r="CL31" t="inlineStr">
-        <is>
-          <t>95.01</t>
-        </is>
-      </c>
-      <c r="CM31" t="inlineStr">
-        <is>
-          <t>34289</t>
-        </is>
-      </c>
-      <c r="CN31" t="inlineStr">
-        <is>
-          <t>節能產品47.49%、影像產品32.05%、其他20.47% (2024年)</t>
-        </is>
-      </c>
-      <c r="CO31" t="inlineStr">
-        <is>
-          <t>中光電-光電業-上櫃</t>
-        </is>
-      </c>
-      <c r="CP31" t="inlineStr">
-        <is>
-          <t>光電業右上上櫃</t>
-        </is>
-      </c>
-      <c r="CQ31" t="inlineStr">
-        <is>
-          <t>90.2</t>
-        </is>
-      </c>
-      <c r="CR31" t="inlineStr">
-        <is>
-          <t>90.3</t>
-        </is>
-      </c>
-      <c r="CS31" t="inlineStr">
-        <is>
-          <t>85.0</t>
-        </is>
-      </c>
-      <c r="CT31" t="inlineStr">
-        <is>
-          <t>86.5</t>
-        </is>
-      </c>
-      <c r="CU31" t="inlineStr">
-        <is>
-          <t>56.54</t>
-        </is>
-      </c>
-      <c r="CV31" t="inlineStr">
-        <is>
-          <t>** 自動化 - 整體解決方案** 電腦及週邊設備 - 印表機、傳真機、掃瞄器、多功能事務機、投影機** 平面顯示器 - 背光模組** 人工智慧 - 系統整合、領域解決方案** 體驗科技 - 近眼顯示(Dear-Eye Display)、垂直應用方案、顯示技術、光學元件/模組、LCoS、OLED、Micro LED、微型顯示器/光機引擎(Light Engine)、ODM/OEM、製造、重工業、物流、安防、醫療、其他</t>
-        </is>
-      </c>
-      <c r="CW31" t="inlineStr">
         <is>
           <t>False</t>
         </is>

--- a/Result/checksun_type/整體解決方案.xlsx
+++ b/Result/checksun_type/整體解決方案.xlsx
@@ -948,12 +948,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-1.83</t>
+          <t>-6.42</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>3877.0</t>
+          <t>3771.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -963,7 +963,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>29.5</t>
+          <t>27.6</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -978,12 +978,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>2.09</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>52.64</t>
+          <t>44.84</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -993,7 +993,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -1003,7 +1003,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>2026-01-04 00:00:00</t>
+          <t>2026-01-06 00:00:00</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -1043,7 +1043,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>-4.38</t>
+          <t>-10.53</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
@@ -1073,7 +1073,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -1118,22 +1118,22 @@
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>2025-12-22 00:00:00</t>
+          <t>2025-12-23 00:00:00</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>2026-01-02</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>14.62</t>
+          <t>14.22</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>-4.24</t>
+          <t>-6.87</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
@@ -1144,75 +1144,75 @@
       <c r="AP2" t="inlineStr"/>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>3877</t>
+          <t>3771</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>80.71</t>
+          <t>39.25</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>88.37</t>
+          <t>69.54</t>
         </is>
       </c>
       <c r="AU2" t="n">
-        <v>-1.01</v>
+        <v>-7.1</v>
       </c>
       <c r="AV2" t="n">
-        <v>18.7</v>
+        <v>16.89</v>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>8.81</t>
+          <t>9.77</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>-2.09</t>
+          <t>-1.84</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>29.8</t>
+          <t>29.71</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>25.1</v>
+        <v>25.42</v>
       </c>
       <c r="BA2" t="n">
-        <v>23.07</v>
+        <v>23.16</v>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>23.56</t>
+          <t>23.59</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>43.99</t>
+          <t>25.69</t>
         </is>
       </c>
       <c r="BD2" t="n">
-        <v>2.06</v>
+        <v>1.92</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>3.04</t>
         </is>
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>-14.36</t>
+          <t>-49.70</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -1222,48 +1222,48 @@
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>43637.08144329896</t>
+          <t>67497.18206896551</t>
         </is>
       </c>
       <c r="BJ2" t="inlineStr">
         <is>
-          <t>116293.0</t>
+          <t>106092.0</t>
         </is>
       </c>
       <c r="BK2" t="n">
-        <v>262896.2</v>
+        <v>262320</v>
       </c>
       <c r="BL2" t="inlineStr">
         <is>
-          <t>172236.8</t>
+          <t>181116.4</t>
         </is>
       </c>
       <c r="BM2" t="n">
-        <v>42873.58</v>
+        <v>44883.2</v>
       </c>
       <c r="BN2" t="inlineStr">
         <is>
-          <t>90659</t>
+          <t>81203</t>
         </is>
       </c>
       <c r="BO2" t="inlineStr">
         <is>
-          <t>27610.27668396823</t>
+          <t>27706.47545434949</t>
         </is>
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>39860.31382102531</t>
+          <t>28235.56869144645</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>116293.0</t>
+          <t>106092.0</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>2026-01-04</t>
+          <t>2026-01-06</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
@@ -1278,7 +1278,7 @@
       </c>
       <c r="BU2" t="inlineStr">
         <is>
-          <t>12.60</t>
+          <t>5.34</t>
         </is>
       </c>
       <c r="BV2" t="inlineStr">
@@ -1308,17 +1308,17 @@
       </c>
       <c r="CA2" t="inlineStr">
         <is>
-          <t>-43.51524843961707</t>
+          <t>106.1934722768384</t>
         </is>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>-49.65752068733421</t>
+          <t>16.51186561194561</t>
         </is>
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>-33.1741339459368</t>
+          <t>-29.52438315737241</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
@@ -1333,12 +1333,12 @@
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1363,12 +1363,12 @@
       </c>
       <c r="CL2" t="inlineStr">
         <is>
-          <t>95.21</t>
+          <t>93.1</t>
         </is>
       </c>
       <c r="CM2" t="inlineStr">
         <is>
-          <t>2961</t>
+          <t>2771</t>
         </is>
       </c>
       <c r="CN2" t="inlineStr">
@@ -1383,27 +1383,27 @@
       </c>
       <c r="CP2" t="inlineStr">
         <is>
-          <t>光電業右上上櫃</t>
+          <t>光電業平上櫃</t>
         </is>
       </c>
       <c r="CQ2" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>29.6</t>
         </is>
       </c>
       <c r="CR2" t="inlineStr">
         <is>
-          <t>30.75</t>
+          <t>29.85</t>
         </is>
       </c>
       <c r="CS2" t="inlineStr">
         <is>
-          <t>29.5</t>
+          <t>27.25</t>
         </is>
       </c>
       <c r="CT2" t="inlineStr">
         <is>
-          <t>29.5</t>
+          <t>27.6</t>
         </is>
       </c>
       <c r="CU2" t="inlineStr">
@@ -1435,12 +1435,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-1.63</t>
+          <t>-1.83</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>10117.0</t>
+          <t>3877.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1450,7 +1450,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>30.05</t>
+          <t>29.5</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1460,17 +1460,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-1.86</t>
+          <t>-6.88</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>2.09</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>51.98</t>
+          <t>52.64</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1480,7 +1480,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -1490,7 +1490,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>2026-01-04 00:00:00</t>
+          <t>2026-01-06 00:00:00</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>-2.59</t>
+          <t>-4.38</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -1560,7 +1560,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -1605,22 +1605,22 @@
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>2025-12-22 00:00:00</t>
+          <t>2025-12-23 00:00:00</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2026-01-02</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>38.15</t>
+          <t>14.62</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>-3.79</t>
+          <t>-4.24</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
@@ -1631,75 +1631,75 @@
       <c r="AP3" t="inlineStr"/>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>3877</t>
+          <t>3771</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>88.65</t>
+          <t>80.71</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>94.8</t>
+          <t>88.37</t>
         </is>
       </c>
       <c r="AU3" t="n">
-        <v>3.62</v>
+        <v>-1.01</v>
       </c>
       <c r="AV3" t="n">
-        <v>17.43</v>
+        <v>18.7</v>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>7.61</t>
+          <t>8.81</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>-2.44</t>
+          <t>-2.09</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>29.0</t>
+          <t>29.8</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>24.7</v>
+        <v>25.1</v>
       </c>
       <c r="BA3" t="n">
-        <v>22.95</v>
+        <v>23.07</v>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>23.52</t>
+          <t>23.56</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>58.13</t>
+          <t>43.99</t>
         </is>
       </c>
       <c r="BD3" t="n">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.28</v>
+        <v>1.43</v>
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>3.04</t>
         </is>
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>-23.77</t>
+          <t>-52.93</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -1709,48 +1709,48 @@
       </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>43637.08144329896</t>
+          <t>67497.18206896551</t>
         </is>
       </c>
       <c r="BJ3" t="inlineStr">
         <is>
-          <t>310659.0</t>
+          <t>116293.0</t>
         </is>
       </c>
       <c r="BK3" t="n">
-        <v>250744.6</v>
+        <v>262896.2</v>
       </c>
       <c r="BL3" t="inlineStr">
         <is>
-          <t>164984.5</t>
+          <t>172236.8</t>
         </is>
       </c>
       <c r="BM3" t="n">
-        <v>40749.4</v>
+        <v>42873.58</v>
       </c>
       <c r="BN3" t="inlineStr">
         <is>
-          <t>85760</t>
+          <t>90659</t>
         </is>
       </c>
       <c r="BO3" t="inlineStr">
         <is>
-          <t>25382.9972045033</t>
+          <t>27610.27668396823</t>
         </is>
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>53950.54565538705</t>
+          <t>39860.31382102531</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>310659.0</t>
+          <t>116293.0</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>2026-01-04</t>
+          <t>2026-01-06</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
@@ -1765,7 +1765,7 @@
       </c>
       <c r="BU3" t="inlineStr">
         <is>
-          <t>14.69</t>
+          <t>12.60</t>
         </is>
       </c>
       <c r="BV3" t="inlineStr">
@@ -1795,37 +1795,37 @@
       </c>
       <c r="CA3" t="inlineStr">
         <is>
-          <t>-43.51524843961707</t>
+          <t>106.1934722768384</t>
         </is>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>-49.65752068733421</t>
+          <t>16.51186561194561</t>
         </is>
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>-33.1741339459368</t>
+          <t>-29.52438315737241</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價跌量縮</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1850,12 +1850,12 @@
       </c>
       <c r="CL3" t="inlineStr">
         <is>
-          <t>95.21</t>
+          <t>93.1</t>
         </is>
       </c>
       <c r="CM3" t="inlineStr">
         <is>
-          <t>2961</t>
+          <t>2771</t>
         </is>
       </c>
       <c r="CN3" t="inlineStr">
@@ -1870,27 +1870,27 @@
       </c>
       <c r="CP3" t="inlineStr">
         <is>
-          <t>光電業右上上櫃</t>
+          <t>光電業平上櫃</t>
         </is>
       </c>
       <c r="CQ3" t="inlineStr">
         <is>
+          <t>30.0</t>
+        </is>
+      </c>
+      <c r="CR3" t="inlineStr">
+        <is>
           <t>30.75</t>
         </is>
       </c>
-      <c r="CR3" t="inlineStr">
-        <is>
-          <t>31.8</t>
-        </is>
-      </c>
       <c r="CS3" t="inlineStr">
         <is>
-          <t>29.45</t>
+          <t>29.5</t>
         </is>
       </c>
       <c r="CT3" t="inlineStr">
         <is>
-          <t>30.05</t>
+          <t>29.5</t>
         </is>
       </c>
       <c r="CU3" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-0.97</t>
+          <t>-1.63</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>12182.0</t>
+          <t>10117.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1937,7 +1937,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>30.55</t>
+          <t>30.05</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1947,17 +1947,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-3.56</t>
+          <t>-8.88</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>2.09</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>60.09</t>
+          <t>51.98</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1967,7 +1967,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -1977,7 +1977,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>2026-01-04 00:00:00</t>
+          <t>2026-01-06 00:00:00</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -2017,7 +2017,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>-0.97</t>
+          <t>-2.59</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -2047,7 +2047,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -2092,22 +2092,22 @@
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>2025-12-22 00:00:00</t>
+          <t>2025-12-23 00:00:00</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>45.93</t>
+          <t>38.15</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>2.97</t>
+          <t>-3.79</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
@@ -2118,75 +2118,75 @@
       <c r="AP4" t="inlineStr"/>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>3877</t>
+          <t>3771</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>95.74</t>
+          <t>88.65</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>98.58</t>
+          <t>94.8</t>
         </is>
       </c>
       <c r="AU4" t="n">
-        <v>8.140000000000001</v>
+        <v>3.62</v>
       </c>
       <c r="AV4" t="n">
-        <v>16.53</v>
+        <v>17.43</v>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>6.33</t>
+          <t>7.61</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>-2.87</t>
+          <t>-2.44</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>28.25</t>
+          <t>29.0</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>24.24</v>
+        <v>24.7</v>
       </c>
       <c r="BA4" t="n">
-        <v>22.8</v>
+        <v>22.95</v>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>23.47</t>
+          <t>23.52</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>71.73</t>
+          <t>58.13</t>
         </is>
       </c>
       <c r="BD4" t="n">
-        <v>1.87</v>
+        <v>2.02</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.09</v>
+        <v>1.28</v>
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>3.04</t>
         </is>
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>-34.85</t>
+          <t>-58.11</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -2196,48 +2196,48 @@
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>43637.08144329896</t>
+          <t>67497.18206896551</t>
         </is>
       </c>
       <c r="BJ4" t="inlineStr">
         <is>
-          <t>367884.0</t>
+          <t>310659.0</t>
         </is>
       </c>
       <c r="BK4" t="n">
-        <v>226272.4</v>
+        <v>250744.6</v>
       </c>
       <c r="BL4" t="inlineStr">
         <is>
-          <t>141340.3</t>
+          <t>164984.5</t>
         </is>
       </c>
       <c r="BM4" t="n">
-        <v>34625.74</v>
+        <v>40749.4</v>
       </c>
       <c r="BN4" t="inlineStr">
         <is>
-          <t>84932</t>
+          <t>85760</t>
         </is>
       </c>
       <c r="BO4" t="inlineStr">
         <is>
-          <t>20188.8974861608</t>
+          <t>25382.9972045033</t>
         </is>
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>51327.71450249714</t>
+          <t>53950.54565538705</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>367884.0</t>
+          <t>310659.0</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>2026-01-04</t>
+          <t>2026-01-06</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
@@ -2252,7 +2252,7 @@
       </c>
       <c r="BU4" t="inlineStr">
         <is>
-          <t>16.60</t>
+          <t>14.69</t>
         </is>
       </c>
       <c r="BV4" t="inlineStr">
@@ -2282,37 +2282,37 @@
       </c>
       <c r="CA4" t="inlineStr">
         <is>
-          <t>-43.51524843961707</t>
+          <t>106.1934722768384</t>
         </is>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>-49.65752068733421</t>
+          <t>16.51186561194561</t>
         </is>
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>-33.1741339459368</t>
+          <t>-29.52438315737241</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="CL4" t="inlineStr">
         <is>
-          <t>95.21</t>
+          <t>93.1</t>
         </is>
       </c>
       <c r="CM4" t="inlineStr">
         <is>
-          <t>2961</t>
+          <t>2771</t>
         </is>
       </c>
       <c r="CN4" t="inlineStr">
@@ -2357,27 +2357,27 @@
       </c>
       <c r="CP4" t="inlineStr">
         <is>
-          <t>光電業右上上櫃</t>
+          <t>光電業平上櫃</t>
         </is>
       </c>
       <c r="CQ4" t="inlineStr">
         <is>
-          <t>30.85</t>
+          <t>30.75</t>
         </is>
       </c>
       <c r="CR4" t="inlineStr">
         <is>
-          <t>31.0</t>
+          <t>31.8</t>
         </is>
       </c>
       <c r="CS4" t="inlineStr">
         <is>
-          <t>29.25</t>
+          <t>29.45</t>
         </is>
       </c>
       <c r="CT4" t="inlineStr">
         <is>
-          <t>30.55</t>
+          <t>30.05</t>
         </is>
       </c>
       <c r="CU4" t="inlineStr">
@@ -2409,12 +2409,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>9.49</t>
+          <t>-0.97</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>13687.0</t>
+          <t>12182.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2424,74 +2424,74 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
+          <t>30.55</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>-10.69</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2.09</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>60.09</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>2025-12-29</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>2025-12-29 00:00:00</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>2026-01-06 00:00:00</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>2025-07-28 00:00:00</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>2025-08-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
           <t>30.85</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>-4.58</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>0.13</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>67.00</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>2025-12-29</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>90.0</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>2025-12-29 00:00:00</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>2026-01-04 00:00:00</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>2025-07-28 00:00:00</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>2025-08-14 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
         <is>
           <t>30.85</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>30.85</t>
-        </is>
-      </c>
       <c r="T5" t="inlineStr">
         <is>
           <t>25.6</t>
@@ -2504,7 +2504,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.97</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -2534,7 +2534,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -2579,22 +2579,22 @@
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>2025-12-22 00:00:00</t>
+          <t>2025-12-23 00:00:00</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>51.61</t>
+          <t>45.93</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>8.06</t>
+          <t>2.97</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
@@ -2605,75 +2605,75 @@
       <c r="AP5" t="inlineStr"/>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>3877</t>
+          <t>3771</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>95.74</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>89.74</t>
+          <t>98.58</t>
         </is>
       </c>
       <c r="AU5" t="n">
-        <v>12.67</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="AV5" t="n">
-        <v>15.21</v>
+        <v>16.53</v>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>4.96</t>
+          <t>6.33</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>-3.29</t>
+          <t>-2.87</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>27.38</t>
+          <t>28.25</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>23.76</v>
+        <v>24.24</v>
       </c>
       <c r="BA5" t="n">
-        <v>22.64</v>
+        <v>22.8</v>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>23.41</t>
+          <t>23.47</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>79.85</t>
+          <t>71.73</t>
         </is>
       </c>
       <c r="BD5" t="n">
-        <v>1.61</v>
+        <v>1.87</v>
       </c>
       <c r="BE5" t="n">
-        <v>0.89</v>
+        <v>1.09</v>
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>3.04</t>
         </is>
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>-46.53</t>
+          <t>-64.19</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
@@ -2683,48 +2683,48 @@
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>43637.08144329896</t>
+          <t>67497.18206896551</t>
         </is>
       </c>
       <c r="BJ5" t="inlineStr">
         <is>
-          <t>410672.0</t>
+          <t>367884.0</t>
         </is>
       </c>
       <c r="BK5" t="n">
-        <v>178004</v>
+        <v>226272.4</v>
       </c>
       <c r="BL5" t="inlineStr">
         <is>
-          <t>106592.2</t>
+          <t>141340.3</t>
         </is>
       </c>
       <c r="BM5" t="n">
-        <v>27334.72</v>
+        <v>34625.74</v>
       </c>
       <c r="BN5" t="inlineStr">
         <is>
-          <t>71411</t>
+          <t>84932</t>
         </is>
       </c>
       <c r="BO5" t="inlineStr">
         <is>
-          <t>14527.29439228146</t>
+          <t>20188.8974861608</t>
         </is>
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>39616.43019470811</t>
+          <t>51327.71450249714</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>410672.0</t>
+          <t>367884.0</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>2026-01-04</t>
+          <t>2026-01-06</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
@@ -2739,7 +2739,7 @@
       </c>
       <c r="BU5" t="inlineStr">
         <is>
-          <t>17.75</t>
+          <t>16.60</t>
         </is>
       </c>
       <c r="BV5" t="inlineStr">
@@ -2769,37 +2769,37 @@
       </c>
       <c r="CA5" t="inlineStr">
         <is>
-          <t>-43.51524843961707</t>
+          <t>106.1934722768384</t>
         </is>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>-49.65752068733421</t>
+          <t>16.51186561194561</t>
         </is>
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>-33.1741339459368</t>
+          <t>-29.52438315737241</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2824,12 +2824,12 @@
       </c>
       <c r="CL5" t="inlineStr">
         <is>
-          <t>95.21</t>
+          <t>93.1</t>
         </is>
       </c>
       <c r="CM5" t="inlineStr">
         <is>
-          <t>2961</t>
+          <t>2771</t>
         </is>
       </c>
       <c r="CN5" t="inlineStr">
@@ -2844,27 +2844,27 @@
       </c>
       <c r="CP5" t="inlineStr">
         <is>
-          <t>光電業右上上櫃</t>
+          <t>光電業平上櫃</t>
         </is>
       </c>
       <c r="CQ5" t="inlineStr">
         <is>
-          <t>29.5</t>
+          <t>30.85</t>
         </is>
       </c>
       <c r="CR5" t="inlineStr">
         <is>
-          <t>30.85</t>
+          <t>31.0</t>
         </is>
       </c>
       <c r="CS5" t="inlineStr">
         <is>
-          <t>28.55</t>
+          <t>29.25</t>
         </is>
       </c>
       <c r="CT5" t="inlineStr">
         <is>
-          <t>30.85</t>
+          <t>30.55</t>
         </is>
       </c>
       <c r="CU5" t="inlineStr">
@@ -2896,12 +2896,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>9.85</t>
+          <t>9.49</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>3968.0</t>
+          <t>13687.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>28.05</t>
+          <t>30.85</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2921,27 +2921,27 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>4.92</t>
+          <t>-11.78</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>2.09</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>40.41</t>
+          <t>67.00</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -2951,7 +2951,7 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>2026-01-04 00:00:00</t>
+          <t>2026-01-06 00:00:00</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -2976,7 +2976,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>30.85</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -2991,7 +2991,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -3021,7 +3021,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -3066,22 +3066,22 @@
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>2025-12-22 00:00:00</t>
+          <t>2025-12-23 00:00:00</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>14.96</t>
+          <t>51.61</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>11.09</t>
+          <t>8.06</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
@@ -3092,12 +3092,12 @@
       <c r="AP6" t="inlineStr"/>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>3877</t>
+          <t>3771</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -3111,56 +3111,56 @@
         </is>
       </c>
       <c r="AU6" t="n">
-        <v>7.97</v>
+        <v>12.67</v>
       </c>
       <c r="AV6" t="n">
-        <v>11.48</v>
+        <v>15.21</v>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>3.68</t>
+          <t>4.96</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>-3.74</t>
+          <t>-3.29</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>25.98</t>
+          <t>27.38</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>23.3</v>
+        <v>23.76</v>
       </c>
       <c r="BA6" t="n">
-        <v>22.48</v>
+        <v>22.64</v>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>23.35</t>
+          <t>23.41</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>70.30</t>
+          <t>79.85</t>
         </is>
       </c>
       <c r="BD6" t="n">
-        <v>1.22</v>
+        <v>1.61</v>
       </c>
       <c r="BE6" t="n">
-        <v>0.72</v>
+        <v>0.89</v>
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>3.04</t>
         </is>
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>-57.21</t>
+          <t>-70.62</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
@@ -3170,48 +3170,48 @@
       </c>
       <c r="BI6" t="inlineStr">
         <is>
-          <t>43637.08144329896</t>
+          <t>67497.18206896551</t>
         </is>
       </c>
       <c r="BJ6" t="inlineStr">
         <is>
-          <t>108973.0</t>
+          <t>410672.0</t>
         </is>
       </c>
       <c r="BK6" t="n">
-        <v>99912.8</v>
+        <v>178004</v>
       </c>
       <c r="BL6" t="inlineStr">
         <is>
-          <t>71156.8</t>
+          <t>106592.2</t>
         </is>
       </c>
       <c r="BM6" t="n">
-        <v>19249.48</v>
+        <v>27334.72</v>
       </c>
       <c r="BN6" t="inlineStr">
         <is>
-          <t>28756</t>
+          <t>71411</t>
         </is>
       </c>
       <c r="BO6" t="inlineStr">
         <is>
-          <t>9965.6333372948</t>
+          <t>14527.29439228146</t>
         </is>
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>16886.72296234135</t>
+          <t>39616.43019470811</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>108973.0</t>
+          <t>410672.0</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2026-01-06</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="BU6" t="inlineStr">
         <is>
-          <t>7.06</t>
+          <t>17.75</t>
         </is>
       </c>
       <c r="BV6" t="inlineStr">
@@ -3256,37 +3256,37 @@
       </c>
       <c r="CA6" t="inlineStr">
         <is>
-          <t>-43.51524843961707</t>
+          <t>106.1934722768384</t>
         </is>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>-49.65752068733421</t>
+          <t>16.51186561194561</t>
         </is>
       </c>
       <c r="CC6" t="inlineStr">
         <is>
-          <t>-33.1741339459368</t>
+          <t>-29.52438315737241</t>
         </is>
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議關注買點&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;2&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3311,12 +3311,12 @@
       </c>
       <c r="CL6" t="inlineStr">
         <is>
-          <t>95.21</t>
+          <t>93.1</t>
         </is>
       </c>
       <c r="CM6" t="inlineStr">
         <is>
-          <t>2961</t>
+          <t>2771</t>
         </is>
       </c>
       <c r="CN6" t="inlineStr">
@@ -3331,27 +3331,27 @@
       </c>
       <c r="CP6" t="inlineStr">
         <is>
-          <t>光電業右上上櫃</t>
+          <t>光電業平上櫃</t>
         </is>
       </c>
       <c r="CQ6" t="inlineStr">
         <is>
-          <t>25.9</t>
+          <t>29.5</t>
         </is>
       </c>
       <c r="CR6" t="inlineStr">
         <is>
-          <t>28.05</t>
+          <t>30.85</t>
         </is>
       </c>
       <c r="CS6" t="inlineStr">
         <is>
-          <t>25.25</t>
+          <t>28.55</t>
         </is>
       </c>
       <c r="CT6" t="inlineStr">
         <is>
-          <t>28.05</t>
+          <t>30.85</t>
         </is>
       </c>
       <c r="CU6" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-3.09</t>
+          <t>9.85</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2162.0</t>
+          <t>3968.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3398,7 +3398,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>25.5</t>
+          <t>28.05</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3408,17 +3408,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>13.56</t>
+          <t>-1.63</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>2.09</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>26.73</t>
+          <t>40.41</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3428,7 +3428,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -3438,7 +3438,7 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>2026-01-04 00:00:00</t>
+          <t>2026-01-06 00:00:00</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -3508,7 +3508,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -3553,43 +3553,43 @@
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>2025-12-22 00:00:00</t>
+          <t>2025-12-23 00:00:00</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>2025-12-24</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>14.96</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>-2.35</t>
+          <t>11.09</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr"/>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>3877</t>
+          <t>3771</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>69.23</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
@@ -3598,56 +3598,56 @@
         </is>
       </c>
       <c r="AU7" t="n">
-        <v>1.47</v>
+        <v>7.97</v>
       </c>
       <c r="AV7" t="n">
-        <v>9.42</v>
+        <v>11.48</v>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>2.68</t>
+          <t>3.68</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>-4.17</t>
+          <t>-3.74</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>25.13</t>
+          <t>25.98</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>22.97</v>
+        <v>23.3</v>
       </c>
       <c r="BA7" t="n">
-        <v>22.37</v>
+        <v>22.48</v>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>23.34</t>
+          <t>23.35</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>67.67</t>
+          <t>70.30</t>
         </is>
       </c>
       <c r="BD7" t="n">
-        <v>0.99</v>
+        <v>1.22</v>
       </c>
       <c r="BE7" t="n">
-        <v>0.59</v>
+        <v>0.72</v>
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>3.04</t>
         </is>
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>-64.73</t>
+          <t>-76.48</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -3657,43 +3657,43 @@
       </c>
       <c r="BI7" t="inlineStr">
         <is>
-          <t>43637.08144329896</t>
+          <t>67497.18206896551</t>
         </is>
       </c>
       <c r="BJ7" t="inlineStr">
         <is>
-          <t>55535.0</t>
+          <t>108973.0</t>
         </is>
       </c>
       <c r="BK7" t="n">
-        <v>81577.39999999999</v>
+        <v>99912.8</v>
       </c>
       <c r="BL7" t="inlineStr">
         <is>
-          <t>64373.5</t>
+          <t>71156.8</t>
         </is>
       </c>
       <c r="BM7" t="n">
-        <v>17193.38</v>
+        <v>19249.48</v>
       </c>
       <c r="BN7" t="inlineStr">
         <is>
-          <t>17203</t>
+          <t>28756</t>
         </is>
       </c>
       <c r="BO7" t="inlineStr">
         <is>
-          <t>8707.253405468153</t>
+          <t>9965.6333372948</t>
         </is>
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>16137.50823887664</t>
+          <t>16886.72296234135</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>55535.0</t>
+          <t>108973.0</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -3713,7 +3713,7 @@
       </c>
       <c r="BU7" t="inlineStr">
         <is>
-          <t>-2.67</t>
+          <t>7.06</t>
         </is>
       </c>
       <c r="BV7" t="inlineStr">
@@ -3743,37 +3743,37 @@
       </c>
       <c r="CA7" t="inlineStr">
         <is>
-          <t>-43.51524843961707</t>
+          <t>106.1934722768384</t>
         </is>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>-49.65752068733421</t>
+          <t>16.51186561194561</t>
         </is>
       </c>
       <c r="CC7" t="inlineStr">
         <is>
-          <t>-33.1741339459368</t>
+          <t>-29.52438315737241</t>
         </is>
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議關注買點&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;2&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3798,12 +3798,12 @@
       </c>
       <c r="CL7" t="inlineStr">
         <is>
-          <t>95.21</t>
+          <t>93.1</t>
         </is>
       </c>
       <c r="CM7" t="inlineStr">
         <is>
-          <t>2961</t>
+          <t>2771</t>
         </is>
       </c>
       <c r="CN7" t="inlineStr">
@@ -3818,27 +3818,27 @@
       </c>
       <c r="CP7" t="inlineStr">
         <is>
-          <t>光電業右上上櫃</t>
+          <t>光電業平上櫃</t>
         </is>
       </c>
       <c r="CQ7" t="inlineStr">
         <is>
-          <t>25.85</t>
+          <t>25.9</t>
         </is>
       </c>
       <c r="CR7" t="inlineStr">
         <is>
-          <t>26.2</t>
+          <t>28.05</t>
         </is>
       </c>
       <c r="CS7" t="inlineStr">
         <is>
-          <t>25.4</t>
+          <t>25.25</t>
         </is>
       </c>
       <c r="CT7" t="inlineStr">
         <is>
-          <t>25.5</t>
+          <t>28.05</t>
         </is>
       </c>
       <c r="CU7" t="inlineStr">
@@ -3870,12 +3870,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>-3.09</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>7091.0</t>
+          <t>2162.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3885,7 +3885,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>26.3</t>
+          <t>25.5</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3895,17 +3895,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>10.85</t>
+          <t>7.61</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>2.09</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>33.09</t>
+          <t>26.73</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3915,7 +3915,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -3925,7 +3925,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>2026-01-04 00:00:00</t>
+          <t>2026-01-06 00:00:00</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -3995,7 +3995,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -4040,22 +4040,22 @@
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>2025-12-22 00:00:00</t>
+          <t>2025-12-23 00:00:00</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2025-12-24</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>26.74</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>-2.65</t>
+          <t>-2.35</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
@@ -4066,75 +4066,75 @@
       <c r="AP8" t="inlineStr"/>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>3877</t>
+          <t>3771</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>69.23</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>93.21</t>
+          <t>89.74</t>
         </is>
       </c>
       <c r="AU8" t="n">
-        <v>5.92</v>
+        <v>1.47</v>
       </c>
       <c r="AV8" t="n">
-        <v>9.119999999999999</v>
+        <v>9.42</v>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>1.99</t>
+          <t>2.68</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>-4.57</t>
+          <t>-4.17</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>24.83</t>
+          <t>25.13</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>22.76</v>
+        <v>22.97</v>
       </c>
       <c r="BA8" t="n">
-        <v>22.31</v>
+        <v>22.37</v>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>23.38</t>
+          <t>23.34</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>92.01</t>
+          <t>67.67</t>
         </is>
       </c>
       <c r="BD8" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.99</v>
       </c>
       <c r="BE8" t="n">
-        <v>0.49</v>
+        <v>0.59</v>
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>3.04</t>
         </is>
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>-70.69</t>
+          <t>-80.61</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -4144,43 +4144,43 @@
       </c>
       <c r="BI8" t="inlineStr">
         <is>
-          <t>43637.08144329896</t>
+          <t>67497.18206896551</t>
         </is>
       </c>
       <c r="BJ8" t="inlineStr">
         <is>
-          <t>188298.0</t>
+          <t>55535.0</t>
         </is>
       </c>
       <c r="BK8" t="n">
-        <v>79224.39999999999</v>
+        <v>81577.39999999999</v>
       </c>
       <c r="BL8" t="inlineStr">
         <is>
-          <t>59526.8</t>
+          <t>64373.5</t>
         </is>
       </c>
       <c r="BM8" t="n">
-        <v>16223.06</v>
+        <v>17193.38</v>
       </c>
       <c r="BN8" t="inlineStr">
         <is>
-          <t>19697</t>
+          <t>17203</t>
         </is>
       </c>
       <c r="BO8" t="inlineStr">
         <is>
-          <t>7356.297981212065</t>
+          <t>8707.253405468153</t>
         </is>
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>20216.36191111003</t>
+          <t>16137.50823887664</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>188298.0</t>
+          <t>55535.0</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
@@ -4200,7 +4200,7 @@
       </c>
       <c r="BU8" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>-2.67</t>
         </is>
       </c>
       <c r="BV8" t="inlineStr">
@@ -4230,22 +4230,22 @@
       </c>
       <c r="CA8" t="inlineStr">
         <is>
-          <t>-43.51524843961707</t>
+          <t>106.1934722768384</t>
         </is>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>-49.65752068733421</t>
+          <t>16.51186561194561</t>
         </is>
       </c>
       <c r="CC8" t="inlineStr">
         <is>
-          <t>-33.1741339459368</t>
+          <t>-29.52438315737241</t>
         </is>
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -4285,12 +4285,12 @@
       </c>
       <c r="CL8" t="inlineStr">
         <is>
-          <t>95.21</t>
+          <t>93.1</t>
         </is>
       </c>
       <c r="CM8" t="inlineStr">
         <is>
-          <t>2961</t>
+          <t>2771</t>
         </is>
       </c>
       <c r="CN8" t="inlineStr">
@@ -4305,27 +4305,27 @@
       </c>
       <c r="CP8" t="inlineStr">
         <is>
-          <t>光電業右上上櫃</t>
+          <t>光電業平上櫃</t>
         </is>
       </c>
       <c r="CQ8" t="inlineStr">
         <is>
-          <t>26.45</t>
+          <t>25.85</t>
         </is>
       </c>
       <c r="CR8" t="inlineStr">
         <is>
-          <t>27.3</t>
+          <t>26.2</t>
         </is>
       </c>
       <c r="CS8" t="inlineStr">
         <is>
-          <t>26.0</t>
+          <t>25.4</t>
         </is>
       </c>
       <c r="CT8" t="inlineStr">
         <is>
-          <t>26.3</t>
+          <t>25.5</t>
         </is>
       </c>
       <c r="CU8" t="inlineStr">
@@ -4357,12 +4357,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>9.4</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>4853.0</t>
+          <t>7091.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -4372,7 +4372,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>26.2</t>
+          <t>26.3</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -4382,17 +4382,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>11.19</t>
+          <t>4.71</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>2.09</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>36.79</t>
+          <t>33.09</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -4402,7 +4402,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -4412,7 +4412,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>2026-01-04 00:00:00</t>
+          <t>2026-01-06 00:00:00</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -4482,7 +4482,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -4527,22 +4527,22 @@
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>2025-12-22 00:00:00</t>
+          <t>2025-12-23 00:00:00</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-23</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>18.30</t>
+          <t>26.74</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>4.80</t>
+          <t>-2.65</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
@@ -4553,12 +4553,12 @@
       <c r="AP9" t="inlineStr"/>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>3877</t>
+          <t>3771</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4568,60 +4568,60 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>86.43</t>
+          <t>93.21</t>
         </is>
       </c>
       <c r="AU9" t="n">
-        <v>7.16</v>
+        <v>5.92</v>
       </c>
       <c r="AV9" t="n">
-        <v>8.859999999999999</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>1.99</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>-4.90</t>
+          <t>-4.57</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>24.45</t>
+          <t>24.83</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>22.46</v>
+        <v>22.76</v>
       </c>
       <c r="BA9" t="n">
-        <v>22.25</v>
+        <v>22.31</v>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>23.39</t>
+          <t>23.38</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>107.93</t>
+          <t>92.01</t>
         </is>
       </c>
       <c r="BD9" t="n">
-        <v>0.78</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="BE9" t="n">
-        <v>0.38</v>
+        <v>0.49</v>
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>3.04</t>
         </is>
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>-77.44</t>
+          <t>-83.89</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -4631,43 +4631,43 @@
       </c>
       <c r="BI9" t="inlineStr">
         <is>
-          <t>43637.08144329896</t>
+          <t>67497.18206896551</t>
         </is>
       </c>
       <c r="BJ9" t="inlineStr">
         <is>
-          <t>126542.0</t>
+          <t>188298.0</t>
         </is>
       </c>
       <c r="BK9" t="n">
-        <v>56408.2</v>
+        <v>79224.39999999999</v>
       </c>
       <c r="BL9" t="inlineStr">
         <is>
-          <t>41235.7</t>
+          <t>59526.8</t>
         </is>
       </c>
       <c r="BM9" t="n">
-        <v>12661.38</v>
+        <v>16223.06</v>
       </c>
       <c r="BN9" t="inlineStr">
         <is>
-          <t>15172</t>
+          <t>19697</t>
         </is>
       </c>
       <c r="BO9" t="inlineStr">
         <is>
-          <t>5018.104539412434</t>
+          <t>7356.297981212065</t>
         </is>
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>11096.67566033239</t>
+          <t>20216.36191111003</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>126542.0</t>
+          <t>188298.0</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
@@ -4687,7 +4687,7 @@
       </c>
       <c r="BU9" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="BV9" t="inlineStr">
@@ -4717,22 +4717,22 @@
       </c>
       <c r="CA9" t="inlineStr">
         <is>
-          <t>-43.51524843961707</t>
+          <t>106.1934722768384</t>
         </is>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>-49.65752068733421</t>
+          <t>16.51186561194561</t>
         </is>
       </c>
       <c r="CC9" t="inlineStr">
         <is>
-          <t>-33.1741339459368</t>
+          <t>-29.52438315737241</t>
         </is>
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議關注買點&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;2&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
@@ -4747,7 +4747,7 @@
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4772,12 +4772,12 @@
       </c>
       <c r="CL9" t="inlineStr">
         <is>
-          <t>95.21</t>
+          <t>93.1</t>
         </is>
       </c>
       <c r="CM9" t="inlineStr">
         <is>
-          <t>2961</t>
+          <t>2771</t>
         </is>
       </c>
       <c r="CN9" t="inlineStr">
@@ -4792,27 +4792,27 @@
       </c>
       <c r="CP9" t="inlineStr">
         <is>
-          <t>光電業右上上櫃</t>
+          <t>光電業平上櫃</t>
         </is>
       </c>
       <c r="CQ9" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>26.45</t>
         </is>
       </c>
       <c r="CR9" t="inlineStr">
         <is>
-          <t>26.2</t>
+          <t>27.3</t>
         </is>
       </c>
       <c r="CS9" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>26.0</t>
         </is>
       </c>
       <c r="CT9" t="inlineStr">
         <is>
-          <t>26.2</t>
+          <t>26.3</t>
         </is>
       </c>
       <c r="CU9" t="inlineStr">
@@ -4834,7 +4834,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>【d1】</t>
+          <t>【b1】</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4844,12 +4844,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>9.4</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>843.0</t>
+          <t>4853.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4859,7 +4859,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>23.85</t>
+          <t>26.2</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4869,17 +4869,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>19.15</t>
+          <t>5.07</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>2.09</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>21.91</t>
+          <t>36.79</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4889,7 +4889,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -4899,7 +4899,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>2026-01-04 00:00:00</t>
+          <t>2026-01-06 00:00:00</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -4969,7 +4969,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -5014,101 +5014,101 @@
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>2025-12-22 00:00:00</t>
+          <t>2025-12-23 00:00:00</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>2025-12-19</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>3.18</t>
+          <t>18.30</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>-1.24</t>
+          <t>4.80</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr"/>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>3877</t>
+          <t>3771</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>79.63</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>82.13</t>
+          <t>86.43</t>
         </is>
       </c>
       <c r="AU10" t="n">
-        <v>-0.42</v>
+        <v>7.16</v>
       </c>
       <c r="AV10" t="n">
-        <v>8.02</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>-5.17</t>
+          <t>-4.90</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>23.95</t>
+          <t>24.45</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>22.17</v>
+        <v>22.46</v>
       </c>
       <c r="BA10" t="n">
-        <v>22.2</v>
+        <v>22.25</v>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>23.41</t>
+          <t>23.39</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>111.88</t>
+          <t>107.93</t>
         </is>
       </c>
       <c r="BD10" t="n">
-        <v>0.58</v>
+        <v>0.78</v>
       </c>
       <c r="BE10" t="n">
-        <v>0.28</v>
+        <v>0.38</v>
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>3.04</t>
         </is>
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>-83.52</t>
+          <t>-87.60</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -5118,43 +5118,43 @@
       </c>
       <c r="BI10" t="inlineStr">
         <is>
-          <t>43637.08144329896</t>
+          <t>67497.18206896551</t>
         </is>
       </c>
       <c r="BJ10" t="inlineStr">
         <is>
-          <t>20216.0</t>
+          <t>126542.0</t>
         </is>
       </c>
       <c r="BK10" t="n">
-        <v>35180.4</v>
+        <v>56408.2</v>
       </c>
       <c r="BL10" t="inlineStr">
         <is>
-          <t>28857.5</t>
+          <t>41235.7</t>
         </is>
       </c>
       <c r="BM10" t="n">
-        <v>10271.14</v>
+        <v>12661.38</v>
       </c>
       <c r="BN10" t="inlineStr">
         <is>
-          <t>6322</t>
+          <t>15172</t>
         </is>
       </c>
       <c r="BO10" t="inlineStr">
         <is>
-          <t>3912.909790154261</t>
+          <t>5018.104539412434</t>
         </is>
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>4288.956885638152</t>
+          <t>11096.67566033239</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>20216.0</t>
+          <t>126542.0</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -5174,7 +5174,7 @@
       </c>
       <c r="BU10" t="inlineStr">
         <is>
-          <t>-8.97</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="BV10" t="inlineStr">
@@ -5204,22 +5204,22 @@
       </c>
       <c r="CA10" t="inlineStr">
         <is>
-          <t>-43.51524843961707</t>
+          <t>106.1934722768384</t>
         </is>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>-49.65752068733421</t>
+          <t>16.51186561194561</t>
         </is>
       </c>
       <c r="CC10" t="inlineStr">
         <is>
-          <t>-33.1741339459368</t>
+          <t>-29.52438315737241</t>
         </is>
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議關注買點&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;2&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
@@ -5229,12 +5229,12 @@
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>0.97</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -5259,12 +5259,12 @@
       </c>
       <c r="CL10" t="inlineStr">
         <is>
-          <t>95.21</t>
+          <t>93.1</t>
         </is>
       </c>
       <c r="CM10" t="inlineStr">
         <is>
-          <t>2961</t>
+          <t>2771</t>
         </is>
       </c>
       <c r="CN10" t="inlineStr">
@@ -5279,27 +5279,27 @@
       </c>
       <c r="CP10" t="inlineStr">
         <is>
-          <t>光電業右上上櫃</t>
+          <t>光電業平上櫃</t>
         </is>
       </c>
       <c r="CQ10" t="inlineStr">
         <is>
-          <t>24.05</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="CR10" t="inlineStr">
         <is>
-          <t>24.45</t>
+          <t>26.2</t>
         </is>
       </c>
       <c r="CS10" t="inlineStr">
         <is>
-          <t>23.55</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="CT10" t="inlineStr">
         <is>
-          <t>23.85</t>
+          <t>26.2</t>
         </is>
       </c>
       <c r="CU10" t="inlineStr">
@@ -5331,12 +5331,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-1.11</t>
+          <t>-0.42</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1512.0</t>
+          <t>3194.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -5346,7 +5346,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>71.3</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -5361,12 +5361,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-17.80</t>
+          <t>-20.34</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -5376,7 +5376,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -5431,7 +5431,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-8.24</t>
+          <t>-8.62</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -5506,17 +5506,17 @@
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>2026-01-02</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>3.48</t>
+          <t>7.36</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>-1.40</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
@@ -5527,75 +5527,75 @@
       <c r="AP11" t="inlineStr"/>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>36</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>1512</t>
+          <t>3194</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>72.22</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>85.63</t>
+          <t>53.28</t>
         </is>
       </c>
       <c r="AU11" t="n">
-        <v>-1.08</v>
+        <v>-1.28</v>
       </c>
       <c r="AV11" t="n">
-        <v>6.23</v>
+        <v>5.46</v>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>-4.72</t>
+          <t>-4.74</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>72.08000000000001</t>
+          <t>71.92</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>67.84999999999999</v>
+        <v>68.19</v>
       </c>
       <c r="BA11" t="n">
-        <v>66.76000000000001</v>
+        <v>66.69</v>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>70.07</t>
+          <t>70.01</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>52.45</t>
+          <t>33.90</t>
         </is>
       </c>
       <c r="BD11" t="n">
-        <v>1.89</v>
+        <v>1.81</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.24</v>
+        <v>1.35</v>
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>8.38</t>
+          <t>10.1</t>
         </is>
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>-85.23</t>
+          <t>-86.60</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
@@ -5605,43 +5605,43 @@
       </c>
       <c r="BI11" t="inlineStr">
         <is>
-          <t>1281159.541237113</t>
+          <t>1143464.882068966</t>
         </is>
       </c>
       <c r="BJ11" t="inlineStr">
         <is>
-          <t>108597.0</t>
+          <t>224648.0</t>
         </is>
       </c>
       <c r="BK11" t="n">
-        <v>240458.2</v>
+        <v>244234.8</v>
       </c>
       <c r="BL11" t="inlineStr">
         <is>
-          <t>292538.0</t>
+          <t>306587.9</t>
         </is>
       </c>
       <c r="BM11" t="n">
-        <v>136053.42</v>
+        <v>138785.12</v>
       </c>
       <c r="BN11" t="inlineStr">
         <is>
-          <t>-52079</t>
+          <t>-62353</t>
         </is>
       </c>
       <c r="BO11" t="inlineStr">
         <is>
-          <t>28607.15703432796</t>
+          <t>25322.06336162383</t>
         </is>
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>11096.73365911728</t>
+          <t>7254.048161751067</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>108597.0</t>
+          <t>224648.0</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5661,7 +5661,7 @@
       </c>
       <c r="BU11" t="inlineStr">
         <is>
-          <t>-2.33</t>
+          <t>-2.74</t>
         </is>
       </c>
       <c r="BV11" t="inlineStr">
@@ -5691,22 +5691,22 @@
       </c>
       <c r="CA11" t="inlineStr">
         <is>
-          <t>-9.276867348133008</t>
+          <t>8.126510269834878</t>
         </is>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>49.33864609225594</t>
+          <t>71.54723574191938</t>
         </is>
       </c>
       <c r="CC11" t="inlineStr">
         <is>
-          <t>18.62961592762674</t>
+          <t>22.92929018430961</t>
         </is>
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
@@ -5716,12 +5716,12 @@
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>4.22</t>
+          <t>4.21</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5731,7 +5731,7 @@
       </c>
       <c r="CI11" t="inlineStr">
         <is>
-          <t>548.46</t>
+          <t>546.15</t>
         </is>
       </c>
       <c r="CJ11" t="inlineStr">
@@ -5746,12 +5746,12 @@
       </c>
       <c r="CL11" t="inlineStr">
         <is>
-          <t>95.21</t>
+          <t>93.1</t>
         </is>
       </c>
       <c r="CM11" t="inlineStr">
         <is>
-          <t>18467</t>
+          <t>18390</t>
         </is>
       </c>
       <c r="CN11" t="inlineStr">
@@ -5766,27 +5766,27 @@
       </c>
       <c r="CP11" t="inlineStr">
         <is>
-          <t>光電業右下上櫃</t>
+          <t>光電業平上櫃</t>
         </is>
       </c>
       <c r="CQ11" t="inlineStr">
         <is>
-          <t>71.8</t>
+          <t>71.3</t>
         </is>
       </c>
       <c r="CR11" t="inlineStr">
         <is>
-          <t>72.3</t>
+          <t>71.5</t>
         </is>
       </c>
       <c r="CS11" t="inlineStr">
         <is>
-          <t>71.3</t>
+          <t>69.4</t>
         </is>
       </c>
       <c r="CT11" t="inlineStr">
         <is>
-          <t>71.3</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="CU11" t="inlineStr">
@@ -5818,12 +5818,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>-1.11</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>3170.0</t>
+          <t>1512.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5833,7 +5833,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>72.1</t>
+          <t>71.3</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5843,17 +5843,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-1.12</t>
+          <t>-0.42</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-0.68</t>
+          <t>-17.80</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5863,7 +5863,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -5918,7 +5918,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-7.21</t>
+          <t>-8.24</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5943,7 +5943,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>-0.2</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -5993,17 +5993,17 @@
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2026-01-02</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>7.30</t>
+          <t>3.48</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>-1.40</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
@@ -6014,266 +6014,266 @@
       <c r="AP12" t="inlineStr"/>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>36</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>1512</t>
+          <t>3194</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>87.63</t>
+          <t>72.22</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>91.29</t>
+          <t>85.63</t>
         </is>
       </c>
       <c r="AU12" t="n">
-        <v>-0.28</v>
+        <v>-1.08</v>
       </c>
       <c r="AV12" t="n">
-        <v>7.18</v>
+        <v>6.23</v>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>-4.74</t>
+          <t>-4.72</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
+          <t>72.08000000000001</t>
+        </is>
+      </c>
+      <c r="AZ12" t="n">
+        <v>67.84999999999999</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>66.76000000000001</v>
+      </c>
+      <c r="BB12" t="inlineStr">
+        <is>
+          <t>70.07</t>
+        </is>
+      </c>
+      <c r="BC12" t="inlineStr">
+        <is>
+          <t>52.45</t>
+        </is>
+      </c>
+      <c r="BD12" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="BF12" t="inlineStr">
+        <is>
+          <t>10.1</t>
+        </is>
+      </c>
+      <c r="BG12" t="inlineStr">
+        <is>
+          <t>-87.74</t>
+        </is>
+      </c>
+      <c r="BH12" t="inlineStr">
+        <is>
+          <t>2025/11/27</t>
+        </is>
+      </c>
+      <c r="BI12" t="inlineStr">
+        <is>
+          <t>1143464.882068966</t>
+        </is>
+      </c>
+      <c r="BJ12" t="inlineStr">
+        <is>
+          <t>108597.0</t>
+        </is>
+      </c>
+      <c r="BK12" t="n">
+        <v>240458.2</v>
+      </c>
+      <c r="BL12" t="inlineStr">
+        <is>
+          <t>292538.0</t>
+        </is>
+      </c>
+      <c r="BM12" t="n">
+        <v>136053.42</v>
+      </c>
+      <c r="BN12" t="inlineStr">
+        <is>
+          <t>-52079</t>
+        </is>
+      </c>
+      <c r="BO12" t="inlineStr">
+        <is>
+          <t>28607.15703432796</t>
+        </is>
+      </c>
+      <c r="BP12" t="inlineStr">
+        <is>
+          <t>11096.73365911728</t>
+        </is>
+      </c>
+      <c r="BQ12" t="inlineStr">
+        <is>
+          <t>108597.0</t>
+        </is>
+      </c>
+      <c r="BR12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BS12" t="inlineStr">
+        <is>
+          <t>73.0</t>
+        </is>
+      </c>
+      <c r="BT12" t="inlineStr">
+        <is>
+          <t>2025/12/30</t>
+        </is>
+      </c>
+      <c r="BU12" t="inlineStr">
+        <is>
+          <t>-2.33</t>
+        </is>
+      </c>
+      <c r="BV12" t="inlineStr">
+        <is>
+          <t>廣運</t>
+        </is>
+      </c>
+      <c r="BW12" t="inlineStr">
+        <is>
+          <t>廣運</t>
+        </is>
+      </c>
+      <c r="BX12" t="inlineStr">
+        <is>
+          <t>光電業</t>
+        </is>
+      </c>
+      <c r="BY12" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BZ12" t="inlineStr">
+        <is>
+          <t>1.25</t>
+        </is>
+      </c>
+      <c r="CA12" t="inlineStr">
+        <is>
+          <t>8.126510269834878</t>
+        </is>
+      </c>
+      <c r="CB12" t="inlineStr">
+        <is>
+          <t>71.54723574191938</t>
+        </is>
+      </c>
+      <c r="CC12" t="inlineStr">
+        <is>
+          <t>22.92929018430961</t>
+        </is>
+      </c>
+      <c r="CD12" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+        </is>
+      </c>
+      <c r="CE12" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="CF12" t="inlineStr">
+        <is>
+          <t>4.22</t>
+        </is>
+      </c>
+      <c r="CG12" t="inlineStr">
+        <is>
+          <t>0.99</t>
+        </is>
+      </c>
+      <c r="CH12" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="CI12" t="inlineStr">
+        <is>
+          <t>546.15</t>
+        </is>
+      </c>
+      <c r="CJ12" t="inlineStr">
+        <is>
+          <t>17.69%</t>
+        </is>
+      </c>
+      <c r="CK12" t="inlineStr">
+        <is>
+          <t>-6.67%</t>
+        </is>
+      </c>
+      <c r="CL12" t="inlineStr">
+        <is>
+          <t>93.1</t>
+        </is>
+      </c>
+      <c r="CM12" t="inlineStr">
+        <is>
+          <t>18390</t>
+        </is>
+      </c>
+      <c r="CN12" t="inlineStr">
+        <is>
+          <t>自動化設備74.11%、太陽能產品12.33%、電子零組件8.12%、建材營建4.02%、其他1.41% (2024年)</t>
+        </is>
+      </c>
+      <c r="CO12" t="inlineStr">
+        <is>
+          <t>廣運-光電業-上櫃</t>
+        </is>
+      </c>
+      <c r="CP12" t="inlineStr">
+        <is>
+          <t>光電業平上櫃</t>
+        </is>
+      </c>
+      <c r="CQ12" t="inlineStr">
+        <is>
+          <t>71.8</t>
+        </is>
+      </c>
+      <c r="CR12" t="inlineStr">
+        <is>
           <t>72.3</t>
         </is>
       </c>
-      <c r="AZ12" t="n">
-        <v>67.45999999999999</v>
-      </c>
-      <c r="BA12" t="n">
-        <v>66.81</v>
-      </c>
-      <c r="BB12" t="inlineStr">
-        <is>
-          <t>70.14</t>
-        </is>
-      </c>
-      <c r="BC12" t="inlineStr">
-        <is>
-          <t>79.09</t>
-        </is>
-      </c>
-      <c r="BD12" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="BE12" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="BF12" t="inlineStr">
-        <is>
-          <t>8.38</t>
-        </is>
-      </c>
-      <c r="BG12" t="inlineStr">
-        <is>
-          <t>-87.17</t>
-        </is>
-      </c>
-      <c r="BH12" t="inlineStr">
-        <is>
-          <t>2025/11/27</t>
-        </is>
-      </c>
-      <c r="BI12" t="inlineStr">
-        <is>
-          <t>1281159.541237113</t>
-        </is>
-      </c>
-      <c r="BJ12" t="inlineStr">
-        <is>
-          <t>227528.0</t>
-        </is>
-      </c>
-      <c r="BK12" t="n">
-        <v>284915.2</v>
-      </c>
-      <c r="BL12" t="inlineStr">
-        <is>
-          <t>286862.6</t>
-        </is>
-      </c>
-      <c r="BM12" t="n">
-        <v>136315.58</v>
-      </c>
-      <c r="BN12" t="inlineStr">
-        <is>
-          <t>-1947</t>
-        </is>
-      </c>
-      <c r="BO12" t="inlineStr">
-        <is>
-          <t>31790.87037527536</t>
-        </is>
-      </c>
-      <c r="BP12" t="inlineStr">
-        <is>
-          <t>28624.00816752913</t>
-        </is>
-      </c>
-      <c r="BQ12" t="inlineStr">
-        <is>
-          <t>227528.0</t>
-        </is>
-      </c>
-      <c r="BR12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BS12" t="inlineStr">
-        <is>
-          <t>73.0</t>
-        </is>
-      </c>
-      <c r="BT12" t="inlineStr">
-        <is>
-          <t>2025/12/30</t>
-        </is>
-      </c>
-      <c r="BU12" t="inlineStr">
-        <is>
-          <t>-1.23</t>
-        </is>
-      </c>
-      <c r="BV12" t="inlineStr">
-        <is>
-          <t>廣運</t>
-        </is>
-      </c>
-      <c r="BW12" t="inlineStr">
-        <is>
-          <t>廣運</t>
-        </is>
-      </c>
-      <c r="BX12" t="inlineStr">
-        <is>
-          <t>光電業</t>
-        </is>
-      </c>
-      <c r="BY12" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BZ12" t="inlineStr">
-        <is>
-          <t>1.25</t>
-        </is>
-      </c>
-      <c r="CA12" t="inlineStr">
-        <is>
-          <t>-9.276867348133008</t>
-        </is>
-      </c>
-      <c r="CB12" t="inlineStr">
-        <is>
-          <t>49.33864609225594</t>
-        </is>
-      </c>
-      <c r="CC12" t="inlineStr">
-        <is>
-          <t>18.62961592762674</t>
-        </is>
-      </c>
-      <c r="CD12" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="CE12" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="CF12" t="inlineStr">
-        <is>
-          <t>4.27</t>
-        </is>
-      </c>
-      <c r="CG12" t="inlineStr">
-        <is>
-          <t>0.98</t>
-        </is>
-      </c>
-      <c r="CH12" t="inlineStr">
-        <is>
-          <t>4.00</t>
-        </is>
-      </c>
-      <c r="CI12" t="inlineStr">
-        <is>
-          <t>548.46</t>
-        </is>
-      </c>
-      <c r="CJ12" t="inlineStr">
-        <is>
-          <t>17.69%</t>
-        </is>
-      </c>
-      <c r="CK12" t="inlineStr">
-        <is>
-          <t>-6.67%</t>
-        </is>
-      </c>
-      <c r="CL12" t="inlineStr">
-        <is>
-          <t>95.21</t>
-        </is>
-      </c>
-      <c r="CM12" t="inlineStr">
-        <is>
-          <t>18467</t>
-        </is>
-      </c>
-      <c r="CN12" t="inlineStr">
-        <is>
-          <t>自動化設備74.11%、太陽能產品12.33%、電子零組件8.12%、建材營建4.02%、其他1.41% (2024年)</t>
-        </is>
-      </c>
-      <c r="CO12" t="inlineStr">
-        <is>
-          <t>廣運-光電業-上櫃</t>
-        </is>
-      </c>
-      <c r="CP12" t="inlineStr">
-        <is>
-          <t>光電業右下上櫃</t>
-        </is>
-      </c>
-      <c r="CQ12" t="inlineStr">
-        <is>
-          <t>72.2</t>
-        </is>
-      </c>
-      <c r="CR12" t="inlineStr">
-        <is>
-          <t>72.7</t>
-        </is>
-      </c>
       <c r="CS12" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>71.3</t>
         </is>
       </c>
       <c r="CT12" t="inlineStr">
         <is>
-          <t>72.1</t>
+          <t>71.3</t>
         </is>
       </c>
       <c r="CU12" t="inlineStr">
@@ -6305,12 +6305,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>6029.0</t>
+          <t>3170.0</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -6320,7 +6320,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>72.1</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -6330,17 +6330,17 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>-2.38</t>
+          <t>-1.55</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>46.27</t>
+          <t>-0.68</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -6350,7 +6350,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -6405,7 +6405,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>-6.05</t>
+          <t>-7.21</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -6430,7 +6430,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
@@ -6480,17 +6480,17 @@
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>13.89</t>
+          <t>7.30</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>1.86</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
@@ -6501,75 +6501,75 @@
       <c r="AP13" t="inlineStr"/>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>36</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>1512</t>
+          <t>3194</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
         <is>
-          <t>97.03</t>
+          <t>87.63</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>90.51</t>
+          <t>91.29</t>
         </is>
       </c>
       <c r="AU13" t="n">
-        <v>0.63</v>
+        <v>-0.28</v>
       </c>
       <c r="AV13" t="n">
-        <v>8.380000000000001</v>
+        <v>7.18</v>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>-4.81</t>
+          <t>-4.74</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>72.54</t>
+          <t>72.3</t>
         </is>
       </c>
       <c r="AZ13" t="n">
-        <v>66.93000000000001</v>
+        <v>67.45999999999999</v>
       </c>
       <c r="BA13" t="n">
         <v>66.81</v>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>70.19</t>
+          <t>70.14</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>116.34</t>
+          <t>79.09</t>
         </is>
       </c>
       <c r="BD13" t="n">
-        <v>1.87</v>
+        <v>1.93</v>
       </c>
       <c r="BE13" t="n">
-        <v>0.86</v>
+        <v>1.08</v>
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>8.38</t>
+          <t>10.1</t>
         </is>
       </c>
       <c r="BG13" t="inlineStr">
         <is>
-          <t>-89.70</t>
+          <t>-89.35</t>
         </is>
       </c>
       <c r="BH13" t="inlineStr">
@@ -6579,43 +6579,43 @@
       </c>
       <c r="BI13" t="inlineStr">
         <is>
-          <t>1281159.541237113</t>
+          <t>1143464.882068966</t>
         </is>
       </c>
       <c r="BJ13" t="inlineStr">
         <is>
-          <t>435553.0</t>
+          <t>227528.0</t>
         </is>
       </c>
       <c r="BK13" t="n">
-        <v>405067.8</v>
+        <v>284915.2</v>
       </c>
       <c r="BL13" t="inlineStr">
         <is>
-          <t>276939.0</t>
+          <t>286862.6</t>
         </is>
       </c>
       <c r="BM13" t="n">
-        <v>133176.84</v>
+        <v>136315.58</v>
       </c>
       <c r="BN13" t="inlineStr">
         <is>
-          <t>128128</t>
+          <t>-1947</t>
         </is>
       </c>
       <c r="BO13" t="inlineStr">
         <is>
-          <t>32366.66350395649</t>
+          <t>31790.87037527536</t>
         </is>
       </c>
       <c r="BP13" t="inlineStr">
         <is>
-          <t>39898.07860213425</t>
+          <t>28624.00816752913</t>
         </is>
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>435553.0</t>
+          <t>227528.0</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
@@ -6635,7 +6635,7 @@
       </c>
       <c r="BU13" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-1.23</t>
         </is>
       </c>
       <c r="BV13" t="inlineStr">
@@ -6665,37 +6665,37 @@
       </c>
       <c r="CA13" t="inlineStr">
         <is>
-          <t>-9.276867348133008</t>
+          <t>8.126510269834878</t>
         </is>
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>49.33864609225594</t>
+          <t>71.54723574191938</t>
         </is>
       </c>
       <c r="CC13" t="inlineStr">
         <is>
-          <t>18.62961592762674</t>
+          <t>22.92929018430961</t>
         </is>
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>4.32</t>
+          <t>4.27</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="CH13" t="inlineStr">
@@ -6705,7 +6705,7 @@
       </c>
       <c r="CI13" t="inlineStr">
         <is>
-          <t>548.46</t>
+          <t>546.15</t>
         </is>
       </c>
       <c r="CJ13" t="inlineStr">
@@ -6720,12 +6720,12 @@
       </c>
       <c r="CL13" t="inlineStr">
         <is>
-          <t>95.21</t>
+          <t>93.1</t>
         </is>
       </c>
       <c r="CM13" t="inlineStr">
         <is>
-          <t>18467</t>
+          <t>18390</t>
         </is>
       </c>
       <c r="CN13" t="inlineStr">
@@ -6740,17 +6740,17 @@
       </c>
       <c r="CP13" t="inlineStr">
         <is>
-          <t>光電業右下上櫃</t>
+          <t>光電業平上櫃</t>
         </is>
       </c>
       <c r="CQ13" t="inlineStr">
         <is>
-          <t>73.6</t>
+          <t>72.2</t>
         </is>
       </c>
       <c r="CR13" t="inlineStr">
         <is>
-          <t>73.7</t>
+          <t>72.7</t>
         </is>
       </c>
       <c r="CS13" t="inlineStr">
@@ -6760,7 +6760,7 @@
       </c>
       <c r="CT13" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>72.1</t>
         </is>
       </c>
       <c r="CU13" t="inlineStr">
@@ -6782,7 +6782,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>【d1】</t>
+          <t>【b1】</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -6792,12 +6792,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>3110.0</t>
+          <t>6029.0</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6807,7 +6807,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>72.2</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6817,17 +6817,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-1.26</t>
+          <t>-2.82</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>42.29</t>
+          <t>46.27</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6837,7 +6837,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -6892,7 +6892,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>-7.08</t>
+          <t>-6.05</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6917,7 +6917,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>-0.06</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
@@ -6967,17 +6967,17 @@
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>7.16</t>
+          <t>13.89</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>1.86</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
@@ -6988,75 +6988,75 @@
       <c r="AP14" t="inlineStr"/>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>36</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>1512</t>
+          <t>3194</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
         <is>
-          <t>89.22</t>
+          <t>97.03</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>88.56</t>
+          <t>90.51</t>
         </is>
       </c>
       <c r="AU14" t="n">
-        <v>-0.39</v>
+        <v>0.63</v>
       </c>
       <c r="AV14" t="n">
-        <v>9.199999999999999</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>-4.87</t>
+          <t>-4.81</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>72.47999999999999</t>
+          <t>72.54</t>
         </is>
       </c>
       <c r="AZ14" t="n">
-        <v>66.38</v>
+        <v>66.93000000000001</v>
       </c>
       <c r="BA14" t="n">
-        <v>66.81999999999999</v>
+        <v>66.81</v>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>70.24</t>
+          <t>70.19</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>173.26</t>
+          <t>116.34</t>
         </is>
       </c>
       <c r="BD14" t="n">
-        <v>1.67</v>
+        <v>1.87</v>
       </c>
       <c r="BE14" t="n">
-        <v>0.61</v>
+        <v>0.86</v>
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>8.38</t>
+          <t>10.1</t>
         </is>
       </c>
       <c r="BG14" t="inlineStr">
         <is>
-          <t>-92.70</t>
+          <t>-91.45</t>
         </is>
       </c>
       <c r="BH14" t="inlineStr">
@@ -7066,43 +7066,43 @@
       </c>
       <c r="BI14" t="inlineStr">
         <is>
-          <t>1281159.541237113</t>
+          <t>1143464.882068966</t>
         </is>
       </c>
       <c r="BJ14" t="inlineStr">
         <is>
-          <t>224848.0</t>
+          <t>435553.0</t>
         </is>
       </c>
       <c r="BK14" t="n">
-        <v>378776.4</v>
+        <v>405067.8</v>
       </c>
       <c r="BL14" t="inlineStr">
         <is>
-          <t>266193.0</t>
+          <t>276939.0</t>
         </is>
       </c>
       <c r="BM14" t="n">
-        <v>125841.48</v>
+        <v>133176.84</v>
       </c>
       <c r="BN14" t="inlineStr">
         <is>
-          <t>112583</t>
+          <t>128128</t>
         </is>
       </c>
       <c r="BO14" t="inlineStr">
         <is>
-          <t>30997.31530428781</t>
+          <t>32366.66350395649</t>
         </is>
       </c>
       <c r="BP14" t="inlineStr">
         <is>
-          <t>32290.56927292253</t>
+          <t>39898.07860213425</t>
         </is>
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>224848.0</t>
+          <t>435553.0</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
@@ -7122,7 +7122,7 @@
       </c>
       <c r="BU14" t="inlineStr">
         <is>
-          <t>-1.10</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="BV14" t="inlineStr">
@@ -7152,37 +7152,37 @@
       </c>
       <c r="CA14" t="inlineStr">
         <is>
-          <t>-9.276867348133008</t>
+          <t>8.126510269834878</t>
         </is>
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>49.33864609225594</t>
+          <t>71.54723574191938</t>
         </is>
       </c>
       <c r="CC14" t="inlineStr">
         <is>
-          <t>18.62961592762674</t>
+          <t>22.92929018430961</t>
         </is>
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>4.28</t>
+          <t>4.32</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="CH14" t="inlineStr">
@@ -7192,7 +7192,7 @@
       </c>
       <c r="CI14" t="inlineStr">
         <is>
-          <t>548.46</t>
+          <t>546.15</t>
         </is>
       </c>
       <c r="CJ14" t="inlineStr">
@@ -7207,12 +7207,12 @@
       </c>
       <c r="CL14" t="inlineStr">
         <is>
-          <t>95.21</t>
+          <t>93.1</t>
         </is>
       </c>
       <c r="CM14" t="inlineStr">
         <is>
-          <t>18467</t>
+          <t>18390</t>
         </is>
       </c>
       <c r="CN14" t="inlineStr">
@@ -7227,27 +7227,27 @@
       </c>
       <c r="CP14" t="inlineStr">
         <is>
-          <t>光電業右下上櫃</t>
+          <t>光電業平上櫃</t>
         </is>
       </c>
       <c r="CQ14" t="inlineStr">
         <is>
-          <t>71.5</t>
+          <t>73.6</t>
         </is>
       </c>
       <c r="CR14" t="inlineStr">
         <is>
-          <t>73.4</t>
+          <t>73.7</t>
         </is>
       </c>
       <c r="CS14" t="inlineStr">
         <is>
-          <t>70.7</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="CT14" t="inlineStr">
         <is>
-          <t>72.2</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="CU14" t="inlineStr">
@@ -7279,12 +7279,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-0.83</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2854.0</t>
+          <t>3110.0</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -7294,7 +7294,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>71.8</t>
+          <t>72.2</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -7304,17 +7304,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-0.7</t>
+          <t>-1.69</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>30.27</t>
+          <t>42.29</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -7324,7 +7324,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -7379,7 +7379,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>-7.59</t>
+          <t>-7.08</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -7404,7 +7404,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
@@ -7454,17 +7454,17 @@
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>6.57</t>
+          <t>7.16</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>-2.08</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
@@ -7475,75 +7475,75 @@
       <c r="AP15" t="inlineStr"/>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>36</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>1512</t>
+          <t>3194</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
         <is>
-          <t>85.29</t>
+          <t>89.22</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>92.16</t>
+          <t>88.56</t>
         </is>
       </c>
       <c r="AU15" t="n">
-        <v>0.76</v>
+        <v>-0.39</v>
       </c>
       <c r="AV15" t="n">
-        <v>8.17</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>-1.47</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>-4.89</t>
+          <t>-4.87</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>71.25999999999999</t>
+          <t>72.47999999999999</t>
         </is>
       </c>
       <c r="AZ15" t="n">
-        <v>65.88</v>
+        <v>66.38</v>
       </c>
       <c r="BA15" t="n">
-        <v>66.86</v>
+        <v>66.81999999999999</v>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>70.3</t>
+          <t>70.24</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>326.92</t>
+          <t>173.26</t>
         </is>
       </c>
       <c r="BD15" t="n">
-        <v>1.48</v>
+        <v>1.67</v>
       </c>
       <c r="BE15" t="n">
-        <v>0.35</v>
+        <v>0.61</v>
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>8.38</t>
+          <t>10.1</t>
         </is>
       </c>
       <c r="BG15" t="inlineStr">
         <is>
-          <t>-95.86</t>
+          <t>-93.94</t>
         </is>
       </c>
       <c r="BH15" t="inlineStr">
@@ -7553,43 +7553,43 @@
       </c>
       <c r="BI15" t="inlineStr">
         <is>
-          <t>1281159.541237113</t>
+          <t>1143464.882068966</t>
         </is>
       </c>
       <c r="BJ15" t="inlineStr">
         <is>
-          <t>205765.0</t>
+          <t>224848.0</t>
         </is>
       </c>
       <c r="BK15" t="n">
-        <v>368941</v>
+        <v>378776.4</v>
       </c>
       <c r="BL15" t="inlineStr">
         <is>
-          <t>283217.3</t>
+          <t>266193.0</t>
         </is>
       </c>
       <c r="BM15" t="n">
-        <v>123456.28</v>
+        <v>125841.48</v>
       </c>
       <c r="BN15" t="inlineStr">
         <is>
-          <t>85723</t>
+          <t>112583</t>
         </is>
       </c>
       <c r="BO15" t="inlineStr">
         <is>
-          <t>30762.1782190815</t>
+          <t>30997.31530428781</t>
         </is>
       </c>
       <c r="BP15" t="inlineStr">
         <is>
-          <t>42844.99990001565</t>
+          <t>32290.56927292253</t>
         </is>
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>205765.0</t>
+          <t>224848.0</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
@@ -7609,7 +7609,7 @@
       </c>
       <c r="BU15" t="inlineStr">
         <is>
-          <t>-1.64</t>
+          <t>-1.10</t>
         </is>
       </c>
       <c r="BV15" t="inlineStr">
@@ -7639,17 +7639,17 @@
       </c>
       <c r="CA15" t="inlineStr">
         <is>
-          <t>-9.276867348133008</t>
+          <t>8.126510269834878</t>
         </is>
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>49.33864609225594</t>
+          <t>71.54723574191938</t>
         </is>
       </c>
       <c r="CC15" t="inlineStr">
         <is>
-          <t>18.62961592762674</t>
+          <t>22.92929018430961</t>
         </is>
       </c>
       <c r="CD15" t="inlineStr">
@@ -7659,17 +7659,17 @@
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>4.25</t>
+          <t>4.28</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="CH15" t="inlineStr">
@@ -7679,7 +7679,7 @@
       </c>
       <c r="CI15" t="inlineStr">
         <is>
-          <t>548.46</t>
+          <t>546.15</t>
         </is>
       </c>
       <c r="CJ15" t="inlineStr">
@@ -7694,12 +7694,12 @@
       </c>
       <c r="CL15" t="inlineStr">
         <is>
-          <t>95.21</t>
+          <t>93.1</t>
         </is>
       </c>
       <c r="CM15" t="inlineStr">
         <is>
-          <t>18467</t>
+          <t>18390</t>
         </is>
       </c>
       <c r="CN15" t="inlineStr">
@@ -7714,27 +7714,27 @@
       </c>
       <c r="CP15" t="inlineStr">
         <is>
-          <t>光電業右下上櫃</t>
+          <t>光電業平上櫃</t>
         </is>
       </c>
       <c r="CQ15" t="inlineStr">
         <is>
-          <t>72.6</t>
+          <t>71.5</t>
         </is>
       </c>
       <c r="CR15" t="inlineStr">
         <is>
-          <t>73.8</t>
+          <t>73.4</t>
         </is>
       </c>
       <c r="CS15" t="inlineStr">
         <is>
-          <t>71.3</t>
+          <t>70.7</t>
         </is>
       </c>
       <c r="CT15" t="inlineStr">
         <is>
-          <t>71.8</t>
+          <t>72.2</t>
         </is>
       </c>
       <c r="CU15" t="inlineStr">
@@ -7766,12 +7766,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-1.23</t>
+          <t>-0.83</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>4590.0</t>
+          <t>2854.0</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -7781,7 +7781,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>72.4</t>
+          <t>71.8</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -7791,17 +7791,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-1.54</t>
+          <t>-1.13</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>24.41</t>
+          <t>30.27</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -7811,7 +7811,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -7866,7 +7866,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>-6.82</t>
+          <t>-7.59</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7891,7 +7891,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>-0.06</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
@@ -7941,17 +7941,17 @@
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>2025-12-24</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>10.57</t>
+          <t>6.57</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>-2.08</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
@@ -7962,75 +7962,75 @@
       <c r="AP16" t="inlineStr"/>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>36</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>1512</t>
+          <t>3194</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
-          <t>91.18</t>
+          <t>85.29</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>97.06</t>
+          <t>92.16</t>
         </is>
       </c>
       <c r="AU16" t="n">
-        <v>3.99</v>
+        <v>0.76</v>
       </c>
       <c r="AV16" t="n">
-        <v>6.41</v>
+        <v>8.17</v>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>-2.18</t>
+          <t>-1.47</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>-4.99</t>
+          <t>-4.89</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>69.62</t>
+          <t>71.25999999999999</t>
         </is>
       </c>
       <c r="AZ16" t="n">
-        <v>65.42</v>
+        <v>65.88</v>
       </c>
       <c r="BA16" t="n">
-        <v>66.88</v>
+        <v>66.86</v>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>70.39</t>
+          <t>70.29</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>1881.60</t>
+          <t>326.92</t>
         </is>
       </c>
       <c r="BD16" t="n">
-        <v>1.26</v>
+        <v>1.48</v>
       </c>
       <c r="BE16" t="n">
-        <v>0.06</v>
+        <v>0.35</v>
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>8.38</t>
+          <t>10.1</t>
         </is>
       </c>
       <c r="BG16" t="inlineStr">
         <is>
-          <t>-99.24</t>
+          <t>-96.56</t>
         </is>
       </c>
       <c r="BH16" t="inlineStr">
@@ -8040,43 +8040,43 @@
       </c>
       <c r="BI16" t="inlineStr">
         <is>
-          <t>1281159.541237113</t>
+          <t>1143464.882068966</t>
         </is>
       </c>
       <c r="BJ16" t="inlineStr">
         <is>
-          <t>330882.0</t>
+          <t>205765.0</t>
         </is>
       </c>
       <c r="BK16" t="n">
-        <v>344617.8</v>
+        <v>368941</v>
       </c>
       <c r="BL16" t="inlineStr">
         <is>
-          <t>277012.5</t>
+          <t>283217.3</t>
         </is>
       </c>
       <c r="BM16" t="n">
-        <v>120544.5</v>
+        <v>123456.28</v>
       </c>
       <c r="BN16" t="inlineStr">
         <is>
-          <t>67605</t>
+          <t>85723</t>
         </is>
       </c>
       <c r="BO16" t="inlineStr">
         <is>
-          <t>28565.30154982075</t>
+          <t>30762.1782190815</t>
         </is>
       </c>
       <c r="BP16" t="inlineStr">
         <is>
-          <t>58437.18651371956</t>
+          <t>42844.99990001565</t>
         </is>
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>330882.0</t>
+          <t>205765.0</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
@@ -8096,7 +8096,7 @@
       </c>
       <c r="BU16" t="inlineStr">
         <is>
-          <t>-0.82</t>
+          <t>-1.64</t>
         </is>
       </c>
       <c r="BV16" t="inlineStr">
@@ -8126,37 +8126,37 @@
       </c>
       <c r="CA16" t="inlineStr">
         <is>
-          <t>-9.276867348133008</t>
+          <t>8.126510269834878</t>
         </is>
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>49.33864609225594</t>
+          <t>71.54723574191938</t>
         </is>
       </c>
       <c r="CC16" t="inlineStr">
         <is>
-          <t>18.62961592762674</t>
+          <t>22.92929018430961</t>
         </is>
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>4.29</t>
+          <t>4.25</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="CH16" t="inlineStr">
@@ -8166,7 +8166,7 @@
       </c>
       <c r="CI16" t="inlineStr">
         <is>
-          <t>548.46</t>
+          <t>546.15</t>
         </is>
       </c>
       <c r="CJ16" t="inlineStr">
@@ -8181,12 +8181,12 @@
       </c>
       <c r="CL16" t="inlineStr">
         <is>
-          <t>95.21</t>
+          <t>93.1</t>
         </is>
       </c>
       <c r="CM16" t="inlineStr">
         <is>
-          <t>18467</t>
+          <t>18390</t>
         </is>
       </c>
       <c r="CN16" t="inlineStr">
@@ -8201,12 +8201,12 @@
       </c>
       <c r="CP16" t="inlineStr">
         <is>
-          <t>光電業右下上櫃</t>
+          <t>光電業平上櫃</t>
         </is>
       </c>
       <c r="CQ16" t="inlineStr">
         <is>
-          <t>73.3</t>
+          <t>72.6</t>
         </is>
       </c>
       <c r="CR16" t="inlineStr">
@@ -8216,12 +8216,12 @@
       </c>
       <c r="CS16" t="inlineStr">
         <is>
-          <t>70.9</t>
+          <t>71.3</t>
         </is>
       </c>
       <c r="CT16" t="inlineStr">
         <is>
-          <t>72.4</t>
+          <t>71.8</t>
         </is>
       </c>
       <c r="CU16" t="inlineStr">
@@ -8253,12 +8253,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>-1.23</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>11495.0</t>
+          <t>4590.0</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -8268,7 +8268,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>73.3</t>
+          <t>72.4</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -8278,17 +8278,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-2.81</t>
+          <t>-1.97</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>9.24</t>
+          <t>24.41</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -8298,7 +8298,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -8353,7 +8353,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>-5.66</t>
+          <t>-6.82</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -8378,7 +8378,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>0.29</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
@@ -8428,17 +8428,17 @@
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2025-12-24</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>26.48</t>
+          <t>10.57</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>3.86</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
@@ -8449,75 +8449,75 @@
       <c r="AP17" t="inlineStr"/>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>36</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>1512</t>
+          <t>3194</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>91.18</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>82.54</t>
+          <t>97.06</t>
         </is>
       </c>
       <c r="AU17" t="n">
-        <v>8.140000000000001</v>
+        <v>3.99</v>
       </c>
       <c r="AV17" t="n">
-        <v>4.35</v>
+        <v>6.41</v>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>-2.84</t>
+          <t>-2.18</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>-5.16</t>
+          <t>-4.99</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>67.78</t>
+          <t>69.62</t>
         </is>
       </c>
       <c r="AZ17" t="n">
-        <v>64.95999999999999</v>
+        <v>65.42</v>
       </c>
       <c r="BA17" t="n">
-        <v>66.84999999999999</v>
+        <v>66.88</v>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>70.5</t>
+          <t>70.39</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>478.83</t>
+          <t>1881.60</t>
         </is>
       </c>
       <c r="BD17" t="n">
-        <v>0.89</v>
+        <v>1.26</v>
       </c>
       <c r="BE17" t="n">
-        <v>-0.23</v>
+        <v>0.06</v>
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>8.38</t>
+          <t>10.1</t>
         </is>
       </c>
       <c r="BG17" t="inlineStr">
         <is>
-          <t>-102.80</t>
+          <t>-99.37</t>
         </is>
       </c>
       <c r="BH17" t="inlineStr">
@@ -8527,43 +8527,43 @@
       </c>
       <c r="BI17" t="inlineStr">
         <is>
-          <t>1281159.541237113</t>
+          <t>1143464.882068966</t>
         </is>
       </c>
       <c r="BJ17" t="inlineStr">
         <is>
-          <t>828291.0</t>
+          <t>330882.0</t>
         </is>
       </c>
       <c r="BK17" t="n">
-        <v>288810</v>
+        <v>344617.8</v>
       </c>
       <c r="BL17" t="inlineStr">
         <is>
-          <t>264378.8</t>
+          <t>277012.5</t>
         </is>
       </c>
       <c r="BM17" t="n">
-        <v>116266.12</v>
+        <v>120544.5</v>
       </c>
       <c r="BN17" t="inlineStr">
         <is>
-          <t>24431</t>
+          <t>67605</t>
         </is>
       </c>
       <c r="BO17" t="inlineStr">
         <is>
-          <t>23134.04973820278</t>
+          <t>28565.30154982075</t>
         </is>
       </c>
       <c r="BP17" t="inlineStr">
         <is>
-          <t>65219.30358637802</t>
+          <t>58437.18651371956</t>
         </is>
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>828291.0</t>
+          <t>330882.0</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
@@ -8583,7 +8583,7 @@
       </c>
       <c r="BU17" t="inlineStr">
         <is>
-          <t>0.41</t>
+          <t>-0.82</t>
         </is>
       </c>
       <c r="BV17" t="inlineStr">
@@ -8613,22 +8613,22 @@
       </c>
       <c r="CA17" t="inlineStr">
         <is>
-          <t>-9.276867348133008</t>
+          <t>8.126510269834878</t>
         </is>
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>49.33864609225594</t>
+          <t>71.54723574191938</t>
         </is>
       </c>
       <c r="CC17" t="inlineStr">
         <is>
-          <t>18.62961592762674</t>
+          <t>22.92929018430961</t>
         </is>
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
@@ -8638,12 +8638,12 @@
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>4.34</t>
+          <t>4.29</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="CH17" t="inlineStr">
@@ -8653,7 +8653,7 @@
       </c>
       <c r="CI17" t="inlineStr">
         <is>
-          <t>548.46</t>
+          <t>546.15</t>
         </is>
       </c>
       <c r="CJ17" t="inlineStr">
@@ -8668,12 +8668,12 @@
       </c>
       <c r="CL17" t="inlineStr">
         <is>
-          <t>95.21</t>
+          <t>93.1</t>
         </is>
       </c>
       <c r="CM17" t="inlineStr">
         <is>
-          <t>18467</t>
+          <t>18390</t>
         </is>
       </c>
       <c r="CN17" t="inlineStr">
@@ -8688,27 +8688,27 @@
       </c>
       <c r="CP17" t="inlineStr">
         <is>
-          <t>光電業右下上櫃</t>
+          <t>光電業平上櫃</t>
         </is>
       </c>
       <c r="CQ17" t="inlineStr">
         <is>
-          <t>71.3</t>
+          <t>73.3</t>
         </is>
       </c>
       <c r="CR17" t="inlineStr">
         <is>
-          <t>73.6</t>
+          <t>73.8</t>
         </is>
       </c>
       <c r="CS17" t="inlineStr">
         <is>
-          <t>70.3</t>
+          <t>70.9</t>
         </is>
       </c>
       <c r="CT17" t="inlineStr">
         <is>
-          <t>73.3</t>
+          <t>72.4</t>
         </is>
       </c>
       <c r="CU17" t="inlineStr">
@@ -8740,12 +8740,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>9.12</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>4186.0</t>
+          <t>11495.0</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -8755,7 +8755,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>72.7</t>
+          <t>73.3</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -8765,17 +8765,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-1.96</t>
+          <t>-3.24</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>-20.83</t>
+          <t>9.24</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -8785,7 +8785,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -8840,7 +8840,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>-6.44</t>
+          <t>-5.66</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -8865,7 +8865,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>0.29</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
@@ -8915,17 +8915,17 @@
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-23</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>9.64</t>
+          <t>26.48</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>2.97</t>
+          <t>3.86</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
@@ -8936,12 +8936,12 @@
       <c r="AP18" t="inlineStr"/>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>36</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>1512</t>
+          <t>3194</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -8951,60 +8951,60 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>51.85</t>
+          <t>82.54</t>
         </is>
       </c>
       <c r="AU18" t="n">
-        <v>10.59</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="AV18" t="n">
-        <v>2.1</v>
+        <v>4.35</v>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>-3.69</t>
+          <t>-2.84</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>-5.29</t>
+          <t>-5.16</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>65.74</t>
+          <t>67.78</t>
         </is>
       </c>
       <c r="AZ18" t="n">
-        <v>64.39</v>
+        <v>64.95999999999999</v>
       </c>
       <c r="BA18" t="n">
         <v>66.84999999999999</v>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>70.58</t>
+          <t>70.49</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>161.44</t>
+          <t>478.83</t>
         </is>
       </c>
       <c r="BD18" t="n">
-        <v>0.32</v>
+        <v>0.89</v>
       </c>
       <c r="BE18" t="n">
-        <v>-0.52</v>
+        <v>-0.23</v>
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>8.38</t>
+          <t>10.1</t>
         </is>
       </c>
       <c r="BG18" t="inlineStr">
         <is>
-          <t>-106.15</t>
+          <t>-102.32</t>
         </is>
       </c>
       <c r="BH18" t="inlineStr">
@@ -9014,43 +9014,43 @@
       </c>
       <c r="BI18" t="inlineStr">
         <is>
-          <t>1281159.541237113</t>
+          <t>1143464.882068966</t>
         </is>
       </c>
       <c r="BJ18" t="inlineStr">
         <is>
-          <t>304096.0</t>
+          <t>828291.0</t>
         </is>
       </c>
       <c r="BK18" t="n">
-        <v>148810.2</v>
+        <v>288810</v>
       </c>
       <c r="BL18" t="inlineStr">
         <is>
-          <t>187961.6</t>
+          <t>264378.8</t>
         </is>
       </c>
       <c r="BM18" t="n">
-        <v>102169.54</v>
+        <v>116266.12</v>
       </c>
       <c r="BN18" t="inlineStr">
         <is>
-          <t>-39151</t>
+          <t>24431</t>
         </is>
       </c>
       <c r="BO18" t="inlineStr">
         <is>
-          <t>15482.18540217091</t>
+          <t>23134.04973820278</t>
         </is>
       </c>
       <c r="BP18" t="inlineStr">
         <is>
-          <t>19284.95999066232</t>
+          <t>65219.30358637802</t>
         </is>
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>304096.0</t>
+          <t>828291.0</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
@@ -9070,7 +9070,7 @@
       </c>
       <c r="BU18" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>0.41</t>
         </is>
       </c>
       <c r="BV18" t="inlineStr">
@@ -9100,22 +9100,22 @@
       </c>
       <c r="CA18" t="inlineStr">
         <is>
-          <t>-9.276867348133008</t>
+          <t>8.126510269834878</t>
         </is>
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>49.33864609225594</t>
+          <t>71.54723574191938</t>
         </is>
       </c>
       <c r="CC18" t="inlineStr">
         <is>
-          <t>18.62961592762674</t>
+          <t>22.92929018430961</t>
         </is>
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
@@ -9125,12 +9125,12 @@
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>4.31</t>
+          <t>4.34</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="CH18" t="inlineStr">
@@ -9140,7 +9140,7 @@
       </c>
       <c r="CI18" t="inlineStr">
         <is>
-          <t>548.46</t>
+          <t>546.15</t>
         </is>
       </c>
       <c r="CJ18" t="inlineStr">
@@ -9155,12 +9155,12 @@
       </c>
       <c r="CL18" t="inlineStr">
         <is>
-          <t>95.21</t>
+          <t>93.1</t>
         </is>
       </c>
       <c r="CM18" t="inlineStr">
         <is>
-          <t>18467</t>
+          <t>18390</t>
         </is>
       </c>
       <c r="CN18" t="inlineStr">
@@ -9175,27 +9175,27 @@
       </c>
       <c r="CP18" t="inlineStr">
         <is>
-          <t>光電業右下上櫃</t>
+          <t>光電業平上櫃</t>
         </is>
       </c>
       <c r="CQ18" t="inlineStr">
         <is>
-          <t>72.4</t>
+          <t>71.3</t>
         </is>
       </c>
       <c r="CR18" t="inlineStr">
         <is>
-          <t>72.7</t>
+          <t>73.6</t>
         </is>
       </c>
       <c r="CS18" t="inlineStr">
         <is>
-          <t>70.6</t>
+          <t>70.3</t>
         </is>
       </c>
       <c r="CT18" t="inlineStr">
         <is>
-          <t>72.7</t>
+          <t>73.3</t>
         </is>
       </c>
       <c r="CU18" t="inlineStr">
@@ -9227,12 +9227,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>3.85</t>
+          <t>9.12</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2647.0</t>
+          <t>4186.0</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -9242,7 +9242,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>66.1</t>
+          <t>72.7</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -9252,17 +9252,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>7.29</t>
+          <t>-2.39</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>-10.23</t>
+          <t>-20.83</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -9272,7 +9272,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -9327,7 +9327,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>-14.93</t>
+          <t>-6.44</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -9352,7 +9352,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
@@ -9402,17 +9402,17 @@
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>2025-12-19</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>6.10</t>
+          <t>9.64</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>2.97</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
@@ -9423,75 +9423,75 @@
       <c r="AP19" t="inlineStr"/>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>36</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>1512</t>
+          <t>3194</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
         <is>
-          <t>47.62</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>19.05</t>
+          <t>51.85</t>
         </is>
       </c>
       <c r="AU19" t="n">
-        <v>2.83</v>
+        <v>10.59</v>
       </c>
       <c r="AV19" t="n">
-        <v>0.67</v>
+        <v>2.1</v>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>-4.47</t>
+          <t>-3.69</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>-5.43</t>
+          <t>-5.29</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>64.28</t>
+          <t>65.74</t>
         </is>
       </c>
       <c r="AZ19" t="n">
-        <v>63.86</v>
+        <v>64.39</v>
       </c>
       <c r="BA19" t="n">
-        <v>66.84</v>
+        <v>66.84999999999999</v>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>70.68</t>
+          <t>70.58</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>50.65</t>
+          <t>161.44</t>
         </is>
       </c>
       <c r="BD19" t="n">
-        <v>-0.36</v>
+        <v>0.32</v>
       </c>
       <c r="BE19" t="n">
-        <v>-0.72</v>
+        <v>-0.52</v>
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>8.38</t>
+          <t>10.1</t>
         </is>
       </c>
       <c r="BG19" t="inlineStr">
         <is>
-          <t>-108.64</t>
+          <t>-105.11</t>
         </is>
       </c>
       <c r="BH19" t="inlineStr">
@@ -9501,43 +9501,43 @@
       </c>
       <c r="BI19" t="inlineStr">
         <is>
-          <t>1281159.541237113</t>
+          <t>1143464.882068966</t>
         </is>
       </c>
       <c r="BJ19" t="inlineStr">
         <is>
-          <t>175671.0</t>
+          <t>304096.0</t>
         </is>
       </c>
       <c r="BK19" t="n">
-        <v>153609.6</v>
+        <v>148810.2</v>
       </c>
       <c r="BL19" t="inlineStr">
         <is>
-          <t>171121.6</t>
+          <t>187961.6</t>
         </is>
       </c>
       <c r="BM19" t="n">
-        <v>98092.44</v>
+        <v>102169.54</v>
       </c>
       <c r="BN19" t="inlineStr">
         <is>
-          <t>-17512</t>
+          <t>-39151</t>
         </is>
       </c>
       <c r="BO19" t="inlineStr">
         <is>
-          <t>14790.77184062702</t>
+          <t>15482.18540217091</t>
         </is>
       </c>
       <c r="BP19" t="inlineStr">
         <is>
-          <t>9139.470568544813</t>
+          <t>19284.95999066232</t>
         </is>
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>175671.0</t>
+          <t>304096.0</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
@@ -9557,7 +9557,7 @@
       </c>
       <c r="BU19" t="inlineStr">
         <is>
-          <t>-9.45</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="BV19" t="inlineStr">
@@ -9587,22 +9587,22 @@
       </c>
       <c r="CA19" t="inlineStr">
         <is>
-          <t>-9.276867348133008</t>
+          <t>8.126510269834878</t>
         </is>
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>49.33864609225594</t>
+          <t>71.54723574191938</t>
         </is>
       </c>
       <c r="CC19" t="inlineStr">
         <is>
-          <t>18.62961592762674</t>
+          <t>22.92929018430961</t>
         </is>
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
@@ -9612,12 +9612,12 @@
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>3.92</t>
+          <t>4.31</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="CH19" t="inlineStr">
@@ -9627,7 +9627,7 @@
       </c>
       <c r="CI19" t="inlineStr">
         <is>
-          <t>548.46</t>
+          <t>546.15</t>
         </is>
       </c>
       <c r="CJ19" t="inlineStr">
@@ -9642,12 +9642,12 @@
       </c>
       <c r="CL19" t="inlineStr">
         <is>
-          <t>95.21</t>
+          <t>93.1</t>
         </is>
       </c>
       <c r="CM19" t="inlineStr">
         <is>
-          <t>18467</t>
+          <t>18390</t>
         </is>
       </c>
       <c r="CN19" t="inlineStr">
@@ -9662,27 +9662,27 @@
       </c>
       <c r="CP19" t="inlineStr">
         <is>
-          <t>光電業右下上櫃</t>
+          <t>光電業平上櫃</t>
         </is>
       </c>
       <c r="CQ19" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>72.4</t>
         </is>
       </c>
       <c r="CR19" t="inlineStr">
         <is>
-          <t>67.8</t>
+          <t>72.7</t>
         </is>
       </c>
       <c r="CS19" t="inlineStr">
         <is>
-          <t>64.3</t>
+          <t>70.6</t>
         </is>
       </c>
       <c r="CT19" t="inlineStr">
         <is>
-          <t>66.1</t>
+          <t>72.7</t>
         </is>
       </c>
       <c r="CU19" t="inlineStr">
@@ -9704,7 +9704,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>【d2】</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -9714,12 +9714,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>-1.95</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>4517.0</t>
+          <t>5699.0</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -9729,7 +9729,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>86.6</t>
+          <t>84.9</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -9744,12 +9744,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>19.31</t>
+          <t>17.09</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -9814,7 +9814,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>-27.53</t>
+          <t>-28.95</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -9839,7 +9839,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
@@ -9864,42 +9864,42 @@
       </c>
       <c r="AG20" t="inlineStr">
         <is>
+          <t>2026/01/05</t>
+        </is>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>84.9</t>
+        </is>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
           <t>2025/12/16</t>
         </is>
       </c>
-      <c r="AH20" t="inlineStr">
+      <c r="AJ20" t="inlineStr">
         <is>
           <t>86.5</t>
         </is>
       </c>
-      <c r="AI20" t="inlineStr">
-        <is>
-          <t>2025/11/18</t>
-        </is>
-      </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>84.6</t>
-        </is>
-      </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>2025-11-27 00:00:00</t>
+          <t>2025-12-30 00:00:00</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>2026-01-02</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>4.01</t>
+          <t>5.06</t>
         </is>
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>-1.27</t>
+          <t>-3.30</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
@@ -9910,66 +9910,66 @@
       <c r="AP20" t="inlineStr"/>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>125</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>4517</t>
+          <t>5699</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
         <is>
-          <t>9.84</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>23.28</t>
+          <t>9.5</t>
         </is>
       </c>
       <c r="AU20" t="n">
-        <v>-1.97</v>
+        <v>-2.93</v>
       </c>
       <c r="AV20" t="n">
-        <v>-0.86</v>
+        <v>-1.39</v>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>-1.65</t>
+          <t>-1.78</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>-8.74</t>
+          <t>-8.57</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>88.34</t>
+          <t>87.46000000000001</t>
         </is>
       </c>
       <c r="AZ20" t="n">
-        <v>89.09999999999999</v>
+        <v>88.7</v>
       </c>
       <c r="BA20" t="n">
-        <v>90.59999999999999</v>
+        <v>90.3</v>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>99.28</t>
+          <t>98.77</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>1.98</t>
+          <t>-11.55</t>
         </is>
       </c>
       <c r="BD20" t="n">
-        <v>-1.15</v>
+        <v>-1.35</v>
       </c>
       <c r="BE20" t="n">
-        <v>-1.18</v>
+        <v>-1.21</v>
       </c>
       <c r="BF20" t="inlineStr">
         <is>
@@ -9978,7 +9978,7 @@
       </c>
       <c r="BG20" t="inlineStr">
         <is>
-          <t>-109.79</t>
+          <t>-110.08</t>
         </is>
       </c>
       <c r="BH20" t="inlineStr">
@@ -9988,43 +9988,43 @@
       </c>
       <c r="BI20" t="inlineStr">
         <is>
-          <t>1620700.515463918</t>
+          <t>1199847.889655172</t>
         </is>
       </c>
       <c r="BJ20" t="inlineStr">
         <is>
-          <t>393125.0</t>
+          <t>488190.0</t>
         </is>
       </c>
       <c r="BK20" t="n">
-        <v>1007832.8</v>
+        <v>1018674.8</v>
       </c>
       <c r="BL20" t="inlineStr">
         <is>
-          <t>844744.2</t>
+          <t>869960.2</t>
         </is>
       </c>
       <c r="BM20" t="n">
-        <v>1254190.86</v>
+        <v>1235131.72</v>
       </c>
       <c r="BN20" t="inlineStr">
         <is>
-          <t>163088</t>
+          <t>148714</t>
         </is>
       </c>
       <c r="BO20" t="inlineStr">
         <is>
-          <t>-39604.96234035039</t>
+          <t>-36640.62980323846</t>
         </is>
       </c>
       <c r="BP20" t="inlineStr">
         <is>
-          <t>8933.593054521945</t>
+          <t>-20336.80084912281</t>
         </is>
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>393125.0</t>
+          <t>488190.0</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
@@ -10044,7 +10044,7 @@
       </c>
       <c r="BU20" t="inlineStr">
         <is>
-          <t>27.35</t>
+          <t>24.85</t>
         </is>
       </c>
       <c r="BV20" t="inlineStr">
@@ -10074,37 +10074,37 @@
       </c>
       <c r="CA20" t="inlineStr">
         <is>
-          <t>10.52226299517467</t>
+          <t>-10.72295503475104</t>
         </is>
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>27.79118773626352</t>
+          <t>6.089521543140648</t>
         </is>
       </c>
       <c r="CC20" t="inlineStr">
         <is>
-          <t>-2.044940352257788</t>
+          <t>-1.317487052973139</t>
         </is>
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>1.77</t>
         </is>
       </c>
       <c r="CH20" t="inlineStr">
@@ -10114,7 +10114,7 @@
       </c>
       <c r="CI20" t="inlineStr">
         <is>
-          <t>93.12</t>
+          <t>91.29</t>
         </is>
       </c>
       <c r="CJ20" t="inlineStr">
@@ -10129,12 +10129,12 @@
       </c>
       <c r="CL20" t="inlineStr">
         <is>
-          <t>95.21</t>
+          <t>93.1</t>
         </is>
       </c>
       <c r="CM20" t="inlineStr">
         <is>
-          <t>33859</t>
+          <t>33194</t>
         </is>
       </c>
       <c r="CN20" t="inlineStr">
@@ -10154,22 +10154,22 @@
       </c>
       <c r="CQ20" t="inlineStr">
         <is>
-          <t>86.8</t>
+          <t>87.1</t>
         </is>
       </c>
       <c r="CR20" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>87.7</t>
         </is>
       </c>
       <c r="CS20" t="inlineStr">
         <is>
-          <t>86.3</t>
+          <t>84.9</t>
         </is>
       </c>
       <c r="CT20" t="inlineStr">
         <is>
-          <t>86.6</t>
+          <t>84.9</t>
         </is>
       </c>
       <c r="CU20" t="inlineStr">
@@ -10201,12 +10201,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-1.93</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>7033.0</t>
+          <t>4517.0</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -10216,7 +10216,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>86.6</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -10226,17 +10226,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>-2.0</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>30.41</t>
+          <t>19.31</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -10301,7 +10301,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>-28.03</t>
+          <t>-27.53</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -10326,7 +10326,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.1</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
@@ -10351,42 +10351,42 @@
       </c>
       <c r="AG21" t="inlineStr">
         <is>
+          <t>2026/01/05</t>
+        </is>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>84.9</t>
+        </is>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
           <t>2025/12/16</t>
         </is>
       </c>
-      <c r="AH21" t="inlineStr">
+      <c r="AJ21" t="inlineStr">
         <is>
           <t>86.5</t>
         </is>
       </c>
-      <c r="AI21" t="inlineStr">
-        <is>
-          <t>2025/11/18</t>
-        </is>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>84.6</t>
-        </is>
-      </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>2025-11-27 00:00:00</t>
+          <t>2025-12-30 00:00:00</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2026-01-02</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>6.25</t>
+          <t>4.01</t>
         </is>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>-2.09</t>
+          <t>-1.27</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
@@ -10397,63 +10397,63 @@
       <c r="AP21" t="inlineStr"/>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>125</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>4517</t>
+          <t>5699</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
         <is>
-          <t>18.67</t>
+          <t>9.84</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>53.33</t>
+          <t>23.28</t>
         </is>
       </c>
       <c r="AU21" t="n">
-        <v>-3.41</v>
+        <v>-1.97</v>
       </c>
       <c r="AV21" t="n">
-        <v>-0.43</v>
+        <v>-0.86</v>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>-1.68</t>
+          <t>-1.65</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>-8.86</t>
+          <t>-8.74</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>89.03999999999999</t>
+          <t>88.34</t>
         </is>
       </c>
       <c r="AZ21" t="n">
-        <v>89.42</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="BA21" t="n">
-        <v>90.95</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>99.8</t>
+          <t>99.28</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>10.62</t>
+          <t>1.98</t>
         </is>
       </c>
       <c r="BD21" t="n">
-        <v>-1.06</v>
+        <v>-1.15</v>
       </c>
       <c r="BE21" t="n">
         <v>-1.18</v>
@@ -10465,7 +10465,7 @@
       </c>
       <c r="BG21" t="inlineStr">
         <is>
-          <t>-109.84</t>
+          <t>-109.79</t>
         </is>
       </c>
       <c r="BH21" t="inlineStr">
@@ -10475,43 +10475,43 @@
       </c>
       <c r="BI21" t="inlineStr">
         <is>
-          <t>1620700.515463918</t>
+          <t>1199847.889655172</t>
         </is>
       </c>
       <c r="BJ21" t="inlineStr">
         <is>
-          <t>608192.0</t>
+          <t>393125.0</t>
         </is>
       </c>
       <c r="BK21" t="n">
-        <v>1086968.4</v>
+        <v>1007832.8</v>
       </c>
       <c r="BL21" t="inlineStr">
         <is>
-          <t>833474.0</t>
+          <t>844744.2</t>
         </is>
       </c>
       <c r="BM21" t="n">
-        <v>1262665.78</v>
+        <v>1254190.86</v>
       </c>
       <c r="BN21" t="inlineStr">
         <is>
-          <t>253494</t>
+          <t>163088</t>
         </is>
       </c>
       <c r="BO21" t="inlineStr">
         <is>
-          <t>-48430.15423032719</t>
+          <t>-39604.96234035039</t>
         </is>
       </c>
       <c r="BP21" t="inlineStr">
         <is>
-          <t>60614.92030778143</t>
+          <t>8933.593054521945</t>
         </is>
       </c>
       <c r="BQ21" t="inlineStr">
         <is>
-          <t>608192.0</t>
+          <t>393125.0</t>
         </is>
       </c>
       <c r="BR21" t="inlineStr">
@@ -10531,7 +10531,7 @@
       </c>
       <c r="BU21" t="inlineStr">
         <is>
-          <t>26.47</t>
+          <t>27.35</t>
         </is>
       </c>
       <c r="BV21" t="inlineStr">
@@ -10561,17 +10561,17 @@
       </c>
       <c r="CA21" t="inlineStr">
         <is>
-          <t>10.52226299517467</t>
+          <t>-10.72295503475104</t>
         </is>
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>27.79118773626352</t>
+          <t>6.089521543140648</t>
         </is>
       </c>
       <c r="CC21" t="inlineStr">
         <is>
-          <t>-2.044940352257788</t>
+          <t>-1.317487052973139</t>
         </is>
       </c>
       <c r="CD21" t="inlineStr">
@@ -10586,12 +10586,12 @@
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>1.77</t>
         </is>
       </c>
       <c r="CH21" t="inlineStr">
@@ -10601,7 +10601,7 @@
       </c>
       <c r="CI21" t="inlineStr">
         <is>
-          <t>93.12</t>
+          <t>91.29</t>
         </is>
       </c>
       <c r="CJ21" t="inlineStr">
@@ -10616,12 +10616,12 @@
       </c>
       <c r="CL21" t="inlineStr">
         <is>
-          <t>95.21</t>
+          <t>93.1</t>
         </is>
       </c>
       <c r="CM21" t="inlineStr">
         <is>
-          <t>33859</t>
+          <t>33194</t>
         </is>
       </c>
       <c r="CN21" t="inlineStr">
@@ -10641,22 +10641,22 @@
       </c>
       <c r="CQ21" t="inlineStr">
         <is>
+          <t>86.8</t>
+        </is>
+      </c>
+      <c r="CR21" t="inlineStr">
+        <is>
           <t>88.0</t>
         </is>
       </c>
-      <c r="CR21" t="inlineStr">
-        <is>
-          <t>88.0</t>
-        </is>
-      </c>
       <c r="CS21" t="inlineStr">
         <is>
-          <t>85.8</t>
+          <t>86.3</t>
         </is>
       </c>
       <c r="CT21" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>86.6</t>
         </is>
       </c>
       <c r="CU21" t="inlineStr">
@@ -10678,7 +10678,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>【d1】</t>
+          <t>【d2】</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -10688,12 +10688,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-4.68</t>
+          <t>-1.93</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>23549.0</t>
+          <t>7033.0</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -10703,7 +10703,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>87.7</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -10713,17 +10713,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-1.27</t>
+          <t>-1.3</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>53.66</t>
+          <t>30.41</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -10788,7 +10788,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>-26.61</t>
+          <t>-28.03</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -10813,7 +10813,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
@@ -10838,42 +10838,42 @@
       </c>
       <c r="AG22" t="inlineStr">
         <is>
+          <t>2026/01/05</t>
+        </is>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>84.9</t>
+        </is>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
           <t>2025/12/16</t>
         </is>
       </c>
-      <c r="AH22" t="inlineStr">
+      <c r="AJ22" t="inlineStr">
         <is>
           <t>86.5</t>
         </is>
       </c>
-      <c r="AI22" t="inlineStr">
-        <is>
-          <t>2025/11/18</t>
-        </is>
-      </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>84.6</t>
-        </is>
-      </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>2025-11-27 00:00:00</t>
+          <t>2025-12-30 00:00:00</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>20.92</t>
+          <t>6.25</t>
         </is>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>-7.98</t>
+          <t>-2.09</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
@@ -10884,66 +10884,66 @@
       <c r="AP22" t="inlineStr"/>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>125</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>4517</t>
+          <t>5699</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
         <is>
-          <t>41.33</t>
+          <t>18.67</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>71.59</t>
+          <t>53.33</t>
         </is>
       </c>
       <c r="AU22" t="n">
-        <v>-2.6</v>
+        <v>-3.41</v>
       </c>
       <c r="AV22" t="n">
-        <v>0.38</v>
+        <v>-0.43</v>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>-1.73</t>
+          <t>-1.68</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>-9.04</t>
+          <t>-8.86</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>90.03999999999999</t>
+          <t>89.03999999999999</t>
         </is>
       </c>
       <c r="AZ22" t="n">
-        <v>89.7</v>
+        <v>89.42</v>
       </c>
       <c r="BA22" t="n">
-        <v>91.28</v>
+        <v>90.95</v>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>100.36</t>
+          <t>99.8</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>29.37</t>
+          <t>10.62</t>
         </is>
       </c>
       <c r="BD22" t="n">
-        <v>-0.86</v>
+        <v>-1.06</v>
       </c>
       <c r="BE22" t="n">
-        <v>-1.21</v>
+        <v>-1.18</v>
       </c>
       <c r="BF22" t="inlineStr">
         <is>
@@ -10952,7 +10952,7 @@
       </c>
       <c r="BG22" t="inlineStr">
         <is>
-          <t>-110.10</t>
+          <t>-109.84</t>
         </is>
       </c>
       <c r="BH22" t="inlineStr">
@@ -10962,43 +10962,43 @@
       </c>
       <c r="BI22" t="inlineStr">
         <is>
-          <t>1620700.515463918</t>
+          <t>1199847.889655172</t>
         </is>
       </c>
       <c r="BJ22" t="inlineStr">
         <is>
-          <t>2122726.0</t>
+          <t>608192.0</t>
         </is>
       </c>
       <c r="BK22" t="n">
-        <v>1271524.8</v>
+        <v>1086968.4</v>
       </c>
       <c r="BL22" t="inlineStr">
         <is>
-          <t>827510.9</t>
+          <t>833474.0</t>
         </is>
       </c>
       <c r="BM22" t="n">
-        <v>1267007.76</v>
+        <v>1262665.78</v>
       </c>
       <c r="BN22" t="inlineStr">
         <is>
-          <t>444013</t>
+          <t>253494</t>
         </is>
       </c>
       <c r="BO22" t="inlineStr">
         <is>
-          <t>-68256.5314190742</t>
+          <t>-48430.15423032719</t>
         </is>
       </c>
       <c r="BP22" t="inlineStr">
         <is>
-          <t>109237.6763728742</t>
+          <t>60614.92030778143</t>
         </is>
       </c>
       <c r="BQ22" t="inlineStr">
         <is>
-          <t>2122726.0</t>
+          <t>608192.0</t>
         </is>
       </c>
       <c r="BR22" t="inlineStr">
@@ -11018,7 +11018,7 @@
       </c>
       <c r="BU22" t="inlineStr">
         <is>
-          <t>28.97</t>
+          <t>26.47</t>
         </is>
       </c>
       <c r="BV22" t="inlineStr">
@@ -11048,37 +11048,37 @@
       </c>
       <c r="CA22" t="inlineStr">
         <is>
-          <t>10.52226299517467</t>
+          <t>-10.72295503475104</t>
         </is>
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>27.79118773626352</t>
+          <t>6.089521543140648</t>
         </is>
       </c>
       <c r="CC22" t="inlineStr">
         <is>
-          <t>-2.044940352257788</t>
+          <t>-1.317487052973139</t>
         </is>
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>1.77</t>
         </is>
       </c>
       <c r="CH22" t="inlineStr">
@@ -11088,7 +11088,7 @@
       </c>
       <c r="CI22" t="inlineStr">
         <is>
-          <t>93.12</t>
+          <t>91.29</t>
         </is>
       </c>
       <c r="CJ22" t="inlineStr">
@@ -11103,12 +11103,12 @@
       </c>
       <c r="CL22" t="inlineStr">
         <is>
-          <t>95.21</t>
+          <t>93.1</t>
         </is>
       </c>
       <c r="CM22" t="inlineStr">
         <is>
-          <t>33859</t>
+          <t>33194</t>
         </is>
       </c>
       <c r="CN22" t="inlineStr">
@@ -11128,22 +11128,22 @@
       </c>
       <c r="CQ22" t="inlineStr">
         <is>
-          <t>94.0</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="CR22" t="inlineStr">
         <is>
-          <t>95.1</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="CS22" t="inlineStr">
         <is>
-          <t>87.3</t>
+          <t>85.8</t>
         </is>
       </c>
       <c r="CT22" t="inlineStr">
         <is>
-          <t>87.7</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="CU22" t="inlineStr">
@@ -11175,12 +11175,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>3.08</t>
+          <t>-4.68</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>15899.0</t>
+          <t>23549.0</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -11190,7 +11190,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>92.1</t>
+          <t>87.7</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -11200,17 +11200,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-6.35</t>
+          <t>-3.3</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>38.73</t>
+          <t>53.66</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -11275,7 +11275,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>-22.93</t>
+          <t>-26.61</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -11300,7 +11300,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
@@ -11325,42 +11325,42 @@
       </c>
       <c r="AG23" t="inlineStr">
         <is>
+          <t>2026/01/05</t>
+        </is>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>84.9</t>
+        </is>
+      </c>
+      <c r="AI23" t="inlineStr">
+        <is>
           <t>2025/12/16</t>
         </is>
       </c>
-      <c r="AH23" t="inlineStr">
+      <c r="AJ23" t="inlineStr">
         <is>
           <t>86.5</t>
         </is>
       </c>
-      <c r="AI23" t="inlineStr">
-        <is>
-          <t>2025/11/18</t>
-        </is>
-      </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>84.6</t>
-        </is>
-      </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>2025-11-27 00:00:00</t>
+          <t>2025-12-30 00:00:00</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>14.13</t>
+          <t>20.92</t>
         </is>
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>-1.72</t>
+          <t>-7.98</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
@@ -11371,66 +11371,66 @@
       <c r="AP23" t="inlineStr"/>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>125</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>4517</t>
+          <t>5699</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>41.33</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>86.46</t>
+          <t>71.59</t>
         </is>
       </c>
       <c r="AU23" t="n">
-        <v>1.93</v>
+        <v>-2.6</v>
       </c>
       <c r="AV23" t="n">
-        <v>0.47</v>
+        <v>0.38</v>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>-1.83</t>
+          <t>-1.73</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>-9.08</t>
+          <t>-9.04</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>90.36</t>
+          <t>90.03999999999999</t>
         </is>
       </c>
       <c r="AZ23" t="n">
-        <v>89.93000000000001</v>
+        <v>89.7</v>
       </c>
       <c r="BA23" t="n">
-        <v>91.61</v>
+        <v>91.28</v>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>100.76</t>
+          <t>100.36</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>41.41</t>
+          <t>29.37</t>
         </is>
       </c>
       <c r="BD23" t="n">
-        <v>-0.76</v>
+        <v>-0.86</v>
       </c>
       <c r="BE23" t="n">
-        <v>-1.3</v>
+        <v>-1.21</v>
       </c>
       <c r="BF23" t="inlineStr">
         <is>
@@ -11439,7 +11439,7 @@
       </c>
       <c r="BG23" t="inlineStr">
         <is>
-          <t>-110.85</t>
+          <t>-110.10</t>
         </is>
       </c>
       <c r="BH23" t="inlineStr">
@@ -11449,43 +11449,43 @@
       </c>
       <c r="BI23" t="inlineStr">
         <is>
-          <t>1620700.515463918</t>
+          <t>1199847.889655172</t>
         </is>
       </c>
       <c r="BJ23" t="inlineStr">
         <is>
-          <t>1481141.0</t>
+          <t>2122726.0</t>
         </is>
       </c>
       <c r="BK23" t="n">
-        <v>911278.6</v>
+        <v>1271524.8</v>
       </c>
       <c r="BL23" t="inlineStr">
         <is>
-          <t>656854.7</t>
+          <t>827510.9</t>
         </is>
       </c>
       <c r="BM23" t="n">
-        <v>1254226.66</v>
+        <v>1267007.76</v>
       </c>
       <c r="BN23" t="inlineStr">
         <is>
-          <t>254423</t>
+          <t>444013</t>
         </is>
       </c>
       <c r="BO23" t="inlineStr">
         <is>
-          <t>-100528.2055630648</t>
+          <t>-68256.5314190742</t>
         </is>
       </c>
       <c r="BP23" t="inlineStr">
         <is>
-          <t>12525.91088111838</t>
+          <t>109237.6763728742</t>
         </is>
       </c>
       <c r="BQ23" t="inlineStr">
         <is>
-          <t>1481141.0</t>
+          <t>2122726.0</t>
         </is>
       </c>
       <c r="BR23" t="inlineStr">
@@ -11505,7 +11505,7 @@
       </c>
       <c r="BU23" t="inlineStr">
         <is>
-          <t>35.44</t>
+          <t>28.97</t>
         </is>
       </c>
       <c r="BV23" t="inlineStr">
@@ -11535,37 +11535,37 @@
       </c>
       <c r="CA23" t="inlineStr">
         <is>
-          <t>10.52226299517467</t>
+          <t>-10.72295503475104</t>
         </is>
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>27.79118773626352</t>
+          <t>6.089521543140648</t>
         </is>
       </c>
       <c r="CC23" t="inlineStr">
         <is>
-          <t>-2.044940352257788</t>
+          <t>-1.317487052973139</t>
         </is>
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>1.77</t>
         </is>
       </c>
       <c r="CH23" t="inlineStr">
@@ -11575,7 +11575,7 @@
       </c>
       <c r="CI23" t="inlineStr">
         <is>
-          <t>93.12</t>
+          <t>91.29</t>
         </is>
       </c>
       <c r="CJ23" t="inlineStr">
@@ -11590,12 +11590,12 @@
       </c>
       <c r="CL23" t="inlineStr">
         <is>
-          <t>95.21</t>
+          <t>93.1</t>
         </is>
       </c>
       <c r="CM23" t="inlineStr">
         <is>
-          <t>33859</t>
+          <t>33194</t>
         </is>
       </c>
       <c r="CN23" t="inlineStr">
@@ -11615,22 +11615,22 @@
       </c>
       <c r="CQ23" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>94.0</t>
         </is>
       </c>
       <c r="CR23" t="inlineStr">
         <is>
-          <t>94.8</t>
+          <t>95.1</t>
         </is>
       </c>
       <c r="CS23" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>87.3</t>
         </is>
       </c>
       <c r="CT23" t="inlineStr">
         <is>
-          <t>92.1</t>
+          <t>87.7</t>
         </is>
       </c>
       <c r="CU23" t="inlineStr">
@@ -11652,7 +11652,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -11662,12 +11662,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>-0.89</t>
+          <t>3.08</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>4861.0</t>
+          <t>15899.0</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -11677,7 +11677,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>89.3</t>
+          <t>92.1</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -11687,17 +11687,17 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>-3.12</t>
+          <t>-8.48</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>34.32</t>
+          <t>38.73</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -11762,7 +11762,7 @@
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>-25.27</t>
+          <t>-22.93</t>
         </is>
       </c>
       <c r="X24" t="inlineStr">
@@ -11787,7 +11787,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
@@ -11812,42 +11812,42 @@
       </c>
       <c r="AG24" t="inlineStr">
         <is>
+          <t>2026/01/05</t>
+        </is>
+      </c>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>84.9</t>
+        </is>
+      </c>
+      <c r="AI24" t="inlineStr">
+        <is>
           <t>2025/12/16</t>
         </is>
       </c>
-      <c r="AH24" t="inlineStr">
+      <c r="AJ24" t="inlineStr">
         <is>
           <t>86.5</t>
         </is>
       </c>
-      <c r="AI24" t="inlineStr">
-        <is>
-          <t>2025/11/18</t>
-        </is>
-      </c>
-      <c r="AJ24" t="inlineStr">
-        <is>
-          <t>84.6</t>
-        </is>
-      </c>
       <c r="AK24" t="inlineStr">
         <is>
-          <t>2025-11-27 00:00:00</t>
+          <t>2025-12-30 00:00:00</t>
         </is>
       </c>
       <c r="AL24" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="AM24" t="inlineStr">
         <is>
-          <t>4.32</t>
+          <t>14.13</t>
         </is>
       </c>
       <c r="AN24" t="inlineStr">
         <is>
-          <t>-1.00</t>
+          <t>-1.72</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
@@ -11858,17 +11858,17 @@
       <c r="AP24" t="inlineStr"/>
       <c r="AQ24" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>125</t>
         </is>
       </c>
       <c r="AR24" t="inlineStr">
         <is>
-          <t>4517</t>
+          <t>5699</t>
         </is>
       </c>
       <c r="AS24" t="inlineStr">
         <is>
-          <t>73.44</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr">
@@ -11877,47 +11877,47 @@
         </is>
       </c>
       <c r="AU24" t="n">
-        <v>-0.18</v>
+        <v>1.93</v>
       </c>
       <c r="AV24" t="n">
-        <v>-0.58</v>
+        <v>0.47</v>
       </c>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>-2.13</t>
+          <t>-1.83</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>-9.03</t>
+          <t>-9.08</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr">
         <is>
-          <t>89.46</t>
+          <t>90.36</t>
         </is>
       </c>
       <c r="AZ24" t="n">
-        <v>89.98</v>
+        <v>89.94</v>
       </c>
       <c r="BA24" t="n">
-        <v>91.95</v>
+        <v>91.61</v>
       </c>
       <c r="BB24" t="inlineStr">
         <is>
-          <t>101.07</t>
+          <t>100.76</t>
         </is>
       </c>
       <c r="BC24" t="inlineStr">
         <is>
-          <t>24.82</t>
+          <t>41.41</t>
         </is>
       </c>
       <c r="BD24" t="n">
-        <v>-1.08</v>
+        <v>-0.76</v>
       </c>
       <c r="BE24" t="n">
-        <v>-1.44</v>
+        <v>-1.3</v>
       </c>
       <c r="BF24" t="inlineStr">
         <is>
@@ -11926,7 +11926,7 @@
       </c>
       <c r="BG24" t="inlineStr">
         <is>
-          <t>-111.97</t>
+          <t>-110.85</t>
         </is>
       </c>
       <c r="BH24" t="inlineStr">
@@ -11936,43 +11936,43 @@
       </c>
       <c r="BI24" t="inlineStr">
         <is>
-          <t>1620700.515463918</t>
+          <t>1199847.889655172</t>
         </is>
       </c>
       <c r="BJ24" t="inlineStr">
         <is>
-          <t>433980.0</t>
+          <t>1481141.0</t>
         </is>
       </c>
       <c r="BK24" t="n">
-        <v>721245.6</v>
+        <v>911278.6</v>
       </c>
       <c r="BL24" t="inlineStr">
         <is>
-          <t>536973.1</t>
+          <t>656854.7</t>
         </is>
       </c>
       <c r="BM24" t="n">
-        <v>1297321.12</v>
+        <v>1254226.66</v>
       </c>
       <c r="BN24" t="inlineStr">
         <is>
-          <t>184272</t>
+          <t>254423</t>
         </is>
       </c>
       <c r="BO24" t="inlineStr">
         <is>
-          <t>-121083.4994620072</t>
+          <t>-100528.2055630648</t>
         </is>
       </c>
       <c r="BP24" t="inlineStr">
         <is>
-          <t>-57339.85806714394</t>
+          <t>12525.91088111838</t>
         </is>
       </c>
       <c r="BQ24" t="inlineStr">
         <is>
-          <t>433980.0</t>
+          <t>1481141.0</t>
         </is>
       </c>
       <c r="BR24" t="inlineStr">
@@ -11992,7 +11992,7 @@
       </c>
       <c r="BU24" t="inlineStr">
         <is>
-          <t>31.32</t>
+          <t>35.44</t>
         </is>
       </c>
       <c r="BV24" t="inlineStr">
@@ -12022,22 +12022,22 @@
       </c>
       <c r="CA24" t="inlineStr">
         <is>
-          <t>10.52226299517467</t>
+          <t>-10.72295503475104</t>
         </is>
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>27.79118773626352</t>
+          <t>6.089521543140648</t>
         </is>
       </c>
       <c r="CC24" t="inlineStr">
         <is>
-          <t>-2.044940352257788</t>
+          <t>-1.317487052973139</t>
         </is>
       </c>
       <c r="CD24" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE24" t="inlineStr">
@@ -12047,12 +12047,12 @@
       </c>
       <c r="CF24" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="CG24" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>1.77</t>
         </is>
       </c>
       <c r="CH24" t="inlineStr">
@@ -12062,7 +12062,7 @@
       </c>
       <c r="CI24" t="inlineStr">
         <is>
-          <t>93.12</t>
+          <t>91.29</t>
         </is>
       </c>
       <c r="CJ24" t="inlineStr">
@@ -12077,12 +12077,12 @@
       </c>
       <c r="CL24" t="inlineStr">
         <is>
-          <t>95.21</t>
+          <t>93.1</t>
         </is>
       </c>
       <c r="CM24" t="inlineStr">
         <is>
-          <t>33859</t>
+          <t>33194</t>
         </is>
       </c>
       <c r="CN24" t="inlineStr">
@@ -12102,22 +12102,22 @@
       </c>
       <c r="CQ24" t="inlineStr">
         <is>
-          <t>90.3</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="CR24" t="inlineStr">
         <is>
+          <t>94.8</t>
+        </is>
+      </c>
+      <c r="CS24" t="inlineStr">
+        <is>
           <t>91.0</t>
         </is>
       </c>
-      <c r="CS24" t="inlineStr">
-        <is>
-          <t>88.5</t>
-        </is>
-      </c>
       <c r="CT24" t="inlineStr">
         <is>
-          <t>89.3</t>
+          <t>92.1</t>
         </is>
       </c>
       <c r="CU24" t="inlineStr">
@@ -12149,12 +12149,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>-0.99</t>
+          <t>-0.89</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>8620.0</t>
+          <t>4861.0</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -12164,7 +12164,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>90.1</t>
+          <t>89.3</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -12174,17 +12174,17 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>-4.04</t>
+          <t>-5.18</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>27.91</t>
+          <t>34.32</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -12249,7 +12249,7 @@
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>-24.60</t>
+          <t>-25.27</t>
         </is>
       </c>
       <c r="X25" t="inlineStr">
@@ -12274,7 +12274,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
@@ -12299,42 +12299,42 @@
       </c>
       <c r="AG25" t="inlineStr">
         <is>
+          <t>2026/01/05</t>
+        </is>
+      </c>
+      <c r="AH25" t="inlineStr">
+        <is>
+          <t>84.9</t>
+        </is>
+      </c>
+      <c r="AI25" t="inlineStr">
+        <is>
           <t>2025/12/16</t>
         </is>
       </c>
-      <c r="AH25" t="inlineStr">
+      <c r="AJ25" t="inlineStr">
         <is>
           <t>86.5</t>
         </is>
       </c>
-      <c r="AI25" t="inlineStr">
-        <is>
-          <t>2025/11/18</t>
-        </is>
-      </c>
-      <c r="AJ25" t="inlineStr">
-        <is>
-          <t>84.6</t>
-        </is>
-      </c>
       <c r="AK25" t="inlineStr">
         <is>
-          <t>2025-11-27 00:00:00</t>
+          <t>2025-12-30 00:00:00</t>
         </is>
       </c>
       <c r="AL25" t="inlineStr">
         <is>
-          <t>2025-12-24</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>7.66</t>
+          <t>4.32</t>
         </is>
       </c>
       <c r="AN25" t="inlineStr">
         <is>
-          <t>-3.66</t>
+          <t>-1.00</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
@@ -12345,66 +12345,66 @@
       <c r="AP25" t="inlineStr"/>
       <c r="AQ25" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>125</t>
         </is>
       </c>
       <c r="AR25" t="inlineStr">
         <is>
-          <t>4517</t>
+          <t>5699</t>
         </is>
       </c>
       <c r="AS25" t="inlineStr">
         <is>
-          <t>85.94</t>
+          <t>73.44</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr">
         <is>
-          <t>93.31</t>
+          <t>86.46</t>
         </is>
       </c>
       <c r="AU25" t="n">
-        <v>1.78</v>
+        <v>-0.18</v>
       </c>
       <c r="AV25" t="n">
-        <v>-1.93</v>
+        <v>-0.58</v>
       </c>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>-2.12</t>
+          <t>-2.13</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>-9.14</t>
+          <t>-9.03</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr">
         <is>
-          <t>88.52000000000001</t>
+          <t>89.46</t>
         </is>
       </c>
       <c r="AZ25" t="n">
-        <v>90.26000000000001</v>
+        <v>89.98</v>
       </c>
       <c r="BA25" t="n">
-        <v>92.22</v>
+        <v>91.95</v>
       </c>
       <c r="BB25" t="inlineStr">
         <is>
-          <t>101.49</t>
+          <t>101.07</t>
         </is>
       </c>
       <c r="BC25" t="inlineStr">
         <is>
-          <t>22.40</t>
+          <t>24.82</t>
         </is>
       </c>
       <c r="BD25" t="n">
-        <v>-1.18</v>
+        <v>-1.08</v>
       </c>
       <c r="BE25" t="n">
-        <v>-1.53</v>
+        <v>-1.44</v>
       </c>
       <c r="BF25" t="inlineStr">
         <is>
@@ -12413,7 +12413,7 @@
       </c>
       <c r="BG25" t="inlineStr">
         <is>
-          <t>-112.71</t>
+          <t>-111.97</t>
         </is>
       </c>
       <c r="BH25" t="inlineStr">
@@ -12423,43 +12423,43 @@
       </c>
       <c r="BI25" t="inlineStr">
         <is>
-          <t>1620700.515463918</t>
+          <t>1199847.889655172</t>
         </is>
       </c>
       <c r="BJ25" t="inlineStr">
         <is>
-          <t>788803.0</t>
+          <t>433980.0</t>
         </is>
       </c>
       <c r="BK25" t="n">
-        <v>681655.6</v>
+        <v>721245.6</v>
       </c>
       <c r="BL25" t="inlineStr">
         <is>
-          <t>532930.9</t>
+          <t>536973.1</t>
         </is>
       </c>
       <c r="BM25" t="n">
-        <v>1334873.04</v>
+        <v>1297321.12</v>
       </c>
       <c r="BN25" t="inlineStr">
         <is>
-          <t>148724</t>
+          <t>184272</t>
         </is>
       </c>
       <c r="BO25" t="inlineStr">
         <is>
-          <t>-132673.2524428914</t>
+          <t>-121083.4994620072</t>
         </is>
       </c>
       <c r="BP25" t="inlineStr">
         <is>
-          <t>-42904.42591940647</t>
+          <t>-57339.85806714394</t>
         </is>
       </c>
       <c r="BQ25" t="inlineStr">
         <is>
-          <t>788803.0</t>
+          <t>433980.0</t>
         </is>
       </c>
       <c r="BR25" t="inlineStr">
@@ -12479,7 +12479,7 @@
       </c>
       <c r="BU25" t="inlineStr">
         <is>
-          <t>32.50</t>
+          <t>31.32</t>
         </is>
       </c>
       <c r="BV25" t="inlineStr">
@@ -12509,37 +12509,37 @@
       </c>
       <c r="CA25" t="inlineStr">
         <is>
-          <t>10.52226299517467</t>
+          <t>-10.72295503475104</t>
         </is>
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>27.79118773626352</t>
+          <t>6.089521543140648</t>
         </is>
       </c>
       <c r="CC25" t="inlineStr">
         <is>
-          <t>-2.044940352257788</t>
+          <t>-1.317487052973139</t>
         </is>
       </c>
       <c r="CD25" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE25" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CF25" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="CG25" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>1.77</t>
         </is>
       </c>
       <c r="CH25" t="inlineStr">
@@ -12549,7 +12549,7 @@
       </c>
       <c r="CI25" t="inlineStr">
         <is>
-          <t>93.12</t>
+          <t>91.29</t>
         </is>
       </c>
       <c r="CJ25" t="inlineStr">
@@ -12564,12 +12564,12 @@
       </c>
       <c r="CL25" t="inlineStr">
         <is>
-          <t>95.21</t>
+          <t>93.1</t>
         </is>
       </c>
       <c r="CM25" t="inlineStr">
         <is>
-          <t>33859</t>
+          <t>33194</t>
         </is>
       </c>
       <c r="CN25" t="inlineStr">
@@ -12589,22 +12589,22 @@
       </c>
       <c r="CQ25" t="inlineStr">
         <is>
+          <t>90.3</t>
+        </is>
+      </c>
+      <c r="CR25" t="inlineStr">
+        <is>
           <t>91.0</t>
         </is>
       </c>
-      <c r="CR25" t="inlineStr">
-        <is>
-          <t>93.5</t>
-        </is>
-      </c>
       <c r="CS25" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>88.5</t>
         </is>
       </c>
       <c r="CT25" t="inlineStr">
         <is>
-          <t>90.1</t>
+          <t>89.3</t>
         </is>
       </c>
       <c r="CU25" t="inlineStr">
@@ -12636,12 +12636,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>1.89</t>
+          <t>-0.99</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>16680.0</t>
+          <t>8620.0</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -12651,7 +12651,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>90.1</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -12661,17 +12661,17 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>-5.08</t>
+          <t>-6.12</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>11.94</t>
+          <t>27.91</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -12736,7 +12736,7 @@
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>-23.85</t>
+          <t>-24.60</t>
         </is>
       </c>
       <c r="X26" t="inlineStr">
@@ -12761,7 +12761,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>0.27</t>
+          <t>0.11</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
@@ -12786,42 +12786,42 @@
       </c>
       <c r="AG26" t="inlineStr">
         <is>
+          <t>2026/01/05</t>
+        </is>
+      </c>
+      <c r="AH26" t="inlineStr">
+        <is>
+          <t>84.9</t>
+        </is>
+      </c>
+      <c r="AI26" t="inlineStr">
+        <is>
           <t>2025/12/16</t>
         </is>
       </c>
-      <c r="AH26" t="inlineStr">
+      <c r="AJ26" t="inlineStr">
         <is>
           <t>86.5</t>
         </is>
       </c>
-      <c r="AI26" t="inlineStr">
-        <is>
-          <t>2025/11/18</t>
-        </is>
-      </c>
-      <c r="AJ26" t="inlineStr">
-        <is>
-          <t>84.6</t>
-        </is>
-      </c>
       <c r="AK26" t="inlineStr">
         <is>
-          <t>2025-11-27 00:00:00</t>
+          <t>2025-12-30 00:00:00</t>
         </is>
       </c>
       <c r="AL26" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2025-12-24</t>
         </is>
       </c>
       <c r="AM26" t="inlineStr">
         <is>
-          <t>14.82</t>
+          <t>7.66</t>
         </is>
       </c>
       <c r="AN26" t="inlineStr">
         <is>
-          <t>-1.15</t>
+          <t>-3.66</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
@@ -12832,66 +12832,66 @@
       <c r="AP26" t="inlineStr"/>
       <c r="AQ26" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>125</t>
         </is>
       </c>
       <c r="AR26" t="inlineStr">
         <is>
-          <t>4517</t>
+          <t>5699</t>
         </is>
       </c>
       <c r="AS26" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>85.94</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr">
         <is>
-          <t>78.18</t>
+          <t>93.31</t>
         </is>
       </c>
       <c r="AU26" t="n">
-        <v>3.86</v>
+        <v>1.78</v>
       </c>
       <c r="AV26" t="n">
-        <v>-3.46</v>
+        <v>-1.93</v>
       </c>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>-1.9</t>
+          <t>-2.12</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>-9.19</t>
+          <t>-9.14</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr">
         <is>
-          <t>87.61999999999999</t>
+          <t>88.52000000000001</t>
         </is>
       </c>
       <c r="AZ26" t="n">
-        <v>90.76000000000001</v>
+        <v>90.27</v>
       </c>
       <c r="BA26" t="n">
-        <v>92.52</v>
+        <v>92.22</v>
       </c>
       <c r="BB26" t="inlineStr">
         <is>
-          <t>101.88</t>
+          <t>101.49</t>
         </is>
       </c>
       <c r="BC26" t="inlineStr">
         <is>
-          <t>14.28</t>
+          <t>22.40</t>
         </is>
       </c>
       <c r="BD26" t="n">
-        <v>-1.38</v>
+        <v>-1.18</v>
       </c>
       <c r="BE26" t="n">
-        <v>-1.61</v>
+        <v>-1.53</v>
       </c>
       <c r="BF26" t="inlineStr">
         <is>
@@ -12900,7 +12900,7 @@
       </c>
       <c r="BG26" t="inlineStr">
         <is>
-          <t>-113.42</t>
+          <t>-112.71</t>
         </is>
       </c>
       <c r="BH26" t="inlineStr">
@@ -12910,43 +12910,43 @@
       </c>
       <c r="BI26" t="inlineStr">
         <is>
-          <t>1620700.515463918</t>
+          <t>1199847.889655172</t>
         </is>
       </c>
       <c r="BJ26" t="inlineStr">
         <is>
-          <t>1530974.0</t>
+          <t>788803.0</t>
         </is>
       </c>
       <c r="BK26" t="n">
-        <v>579979.6</v>
+        <v>681655.6</v>
       </c>
       <c r="BL26" t="inlineStr">
         <is>
-          <t>518134.7</t>
+          <t>532930.9</t>
         </is>
       </c>
       <c r="BM26" t="n">
-        <v>1377293.78</v>
+        <v>1334873.04</v>
       </c>
       <c r="BN26" t="inlineStr">
         <is>
-          <t>61844</t>
+          <t>148724</t>
         </is>
       </c>
       <c r="BO26" t="inlineStr">
         <is>
-          <t>-148994.8572653433</t>
+          <t>-132673.2524428914</t>
         </is>
       </c>
       <c r="BP26" t="inlineStr">
         <is>
-          <t>-58766.82906837412</t>
+          <t>-42904.42591940647</t>
         </is>
       </c>
       <c r="BQ26" t="inlineStr">
         <is>
-          <t>1530974.0</t>
+          <t>788803.0</t>
         </is>
       </c>
       <c r="BR26" t="inlineStr">
@@ -12966,7 +12966,7 @@
       </c>
       <c r="BU26" t="inlineStr">
         <is>
-          <t>33.82</t>
+          <t>32.50</t>
         </is>
       </c>
       <c r="BV26" t="inlineStr">
@@ -12996,37 +12996,37 @@
       </c>
       <c r="CA26" t="inlineStr">
         <is>
-          <t>10.52226299517467</t>
+          <t>-10.72295503475104</t>
         </is>
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>27.79118773626352</t>
+          <t>6.089521543140648</t>
         </is>
       </c>
       <c r="CC26" t="inlineStr">
         <is>
-          <t>-2.044940352257788</t>
+          <t>-1.317487052973139</t>
         </is>
       </c>
       <c r="CD26" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE26" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CF26" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="CG26" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>1.77</t>
         </is>
       </c>
       <c r="CH26" t="inlineStr">
@@ -13036,7 +13036,7 @@
       </c>
       <c r="CI26" t="inlineStr">
         <is>
-          <t>93.12</t>
+          <t>91.29</t>
         </is>
       </c>
       <c r="CJ26" t="inlineStr">
@@ -13051,12 +13051,12 @@
       </c>
       <c r="CL26" t="inlineStr">
         <is>
-          <t>95.21</t>
+          <t>93.1</t>
         </is>
       </c>
       <c r="CM26" t="inlineStr">
         <is>
-          <t>33859</t>
+          <t>33194</t>
         </is>
       </c>
       <c r="CN26" t="inlineStr">
@@ -13076,22 +13076,22 @@
       </c>
       <c r="CQ26" t="inlineStr">
         <is>
-          <t>89.9</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="CR26" t="inlineStr">
         <is>
-          <t>94.3</t>
+          <t>93.5</t>
         </is>
       </c>
       <c r="CS26" t="inlineStr">
         <is>
-          <t>88.8</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="CT26" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>90.1</t>
         </is>
       </c>
       <c r="CU26" t="inlineStr">
@@ -13113,7 +13113,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d2】</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -13123,12 +13123,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>1.89</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>3593.0</t>
+          <t>16680.0</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -13138,7 +13138,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>89.3</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -13148,17 +13148,17 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>-3.12</t>
+          <t>-7.18</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>-9.08</t>
+          <t>11.94</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -13223,7 +13223,7 @@
       </c>
       <c r="W27" t="inlineStr">
         <is>
-          <t>-25.27</t>
+          <t>-23.85</t>
         </is>
       </c>
       <c r="X27" t="inlineStr">
@@ -13248,7 +13248,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>0.27</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
@@ -13273,42 +13273,42 @@
       </c>
       <c r="AG27" t="inlineStr">
         <is>
+          <t>2026/01/05</t>
+        </is>
+      </c>
+      <c r="AH27" t="inlineStr">
+        <is>
+          <t>84.9</t>
+        </is>
+      </c>
+      <c r="AI27" t="inlineStr">
+        <is>
           <t>2025/12/16</t>
         </is>
       </c>
-      <c r="AH27" t="inlineStr">
+      <c r="AJ27" t="inlineStr">
         <is>
           <t>86.5</t>
         </is>
       </c>
-      <c r="AI27" t="inlineStr">
-        <is>
-          <t>2025/11/18</t>
-        </is>
-      </c>
-      <c r="AJ27" t="inlineStr">
-        <is>
-          <t>84.6</t>
-        </is>
-      </c>
       <c r="AK27" t="inlineStr">
         <is>
-          <t>2025-11-27 00:00:00</t>
+          <t>2025-12-30 00:00:00</t>
         </is>
       </c>
       <c r="AL27" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-23</t>
         </is>
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>3.19</t>
+          <t>14.82</t>
         </is>
       </c>
       <c r="AN27" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>-1.15</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
@@ -13319,66 +13319,66 @@
       <c r="AP27" t="inlineStr"/>
       <c r="AQ27" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>125</t>
         </is>
       </c>
       <c r="AR27" t="inlineStr">
         <is>
-          <t>4517</t>
+          <t>5699</t>
         </is>
       </c>
       <c r="AS27" t="inlineStr">
         <is>
-          <t>94.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr">
         <is>
-          <t>44.85</t>
+          <t>78.18</t>
         </is>
       </c>
       <c r="AU27" t="n">
-        <v>2.98</v>
+        <v>3.86</v>
       </c>
       <c r="AV27" t="n">
-        <v>-4.45</v>
+        <v>-3.46</v>
       </c>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>-2.44</t>
+          <t>-1.9</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>-9.05</t>
+          <t>-9.19</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr">
         <is>
-          <t>86.72</t>
+          <t>87.61999999999999</t>
         </is>
       </c>
       <c r="AZ27" t="n">
         <v>90.76000000000001</v>
       </c>
       <c r="BA27" t="n">
-        <v>93.03</v>
+        <v>92.52</v>
       </c>
       <c r="BB27" t="inlineStr">
         <is>
-          <t>102.29</t>
+          <t>101.88</t>
         </is>
       </c>
       <c r="BC27" t="inlineStr">
         <is>
-          <t>-2.13</t>
+          <t>14.28</t>
         </is>
       </c>
       <c r="BD27" t="n">
-        <v>-1.7</v>
+        <v>-1.38</v>
       </c>
       <c r="BE27" t="n">
-        <v>-1.67</v>
+        <v>-1.61</v>
       </c>
       <c r="BF27" t="inlineStr">
         <is>
@@ -13387,7 +13387,7 @@
       </c>
       <c r="BG27" t="inlineStr">
         <is>
-          <t>-113.90</t>
+          <t>-113.42</t>
         </is>
       </c>
       <c r="BH27" t="inlineStr">
@@ -13397,43 +13397,43 @@
       </c>
       <c r="BI27" t="inlineStr">
         <is>
-          <t>1620700.515463918</t>
+          <t>1199847.889655172</t>
         </is>
       </c>
       <c r="BJ27" t="inlineStr">
         <is>
-          <t>321495.0</t>
+          <t>1530974.0</t>
         </is>
       </c>
       <c r="BK27" t="n">
-        <v>383497</v>
+        <v>579979.6</v>
       </c>
       <c r="BL27" t="inlineStr">
         <is>
-          <t>421816.7</t>
+          <t>518134.7</t>
         </is>
       </c>
       <c r="BM27" t="n">
-        <v>1399030.72</v>
+        <v>1377293.78</v>
       </c>
       <c r="BN27" t="inlineStr">
         <is>
-          <t>-38319</t>
+          <t>61844</t>
         </is>
       </c>
       <c r="BO27" t="inlineStr">
         <is>
-          <t>-165399.9533011559</t>
+          <t>-148994.8572653433</t>
         </is>
       </c>
       <c r="BP27" t="inlineStr">
         <is>
-          <t>-158846.9111001717</t>
+          <t>-58766.82906837412</t>
         </is>
       </c>
       <c r="BQ27" t="inlineStr">
         <is>
-          <t>321495.0</t>
+          <t>1530974.0</t>
         </is>
       </c>
       <c r="BR27" t="inlineStr">
@@ -13453,7 +13453,7 @@
       </c>
       <c r="BU27" t="inlineStr">
         <is>
-          <t>31.32</t>
+          <t>33.82</t>
         </is>
       </c>
       <c r="BV27" t="inlineStr">
@@ -13483,22 +13483,22 @@
       </c>
       <c r="CA27" t="inlineStr">
         <is>
-          <t>10.52226299517467</t>
+          <t>-10.72295503475104</t>
         </is>
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>27.79118773626352</t>
+          <t>6.089521543140648</t>
         </is>
       </c>
       <c r="CC27" t="inlineStr">
         <is>
-          <t>-2.044940352257788</t>
+          <t>-1.317487052973139</t>
         </is>
       </c>
       <c r="CD27" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="CE27" t="inlineStr">
@@ -13508,12 +13508,12 @@
       </c>
       <c r="CF27" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="CG27" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>1.77</t>
         </is>
       </c>
       <c r="CH27" t="inlineStr">
@@ -13523,7 +13523,7 @@
       </c>
       <c r="CI27" t="inlineStr">
         <is>
-          <t>93.12</t>
+          <t>91.29</t>
         </is>
       </c>
       <c r="CJ27" t="inlineStr">
@@ -13538,12 +13538,12 @@
       </c>
       <c r="CL27" t="inlineStr">
         <is>
-          <t>95.21</t>
+          <t>93.1</t>
         </is>
       </c>
       <c r="CM27" t="inlineStr">
         <is>
-          <t>33859</t>
+          <t>33194</t>
         </is>
       </c>
       <c r="CN27" t="inlineStr">
@@ -13563,22 +13563,22 @@
       </c>
       <c r="CQ27" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>89.9</t>
         </is>
       </c>
       <c r="CR27" t="inlineStr">
         <is>
-          <t>90.4</t>
+          <t>94.3</t>
         </is>
       </c>
       <c r="CS27" t="inlineStr">
         <is>
-          <t>88.5</t>
+          <t>88.8</t>
         </is>
       </c>
       <c r="CT27" t="inlineStr">
         <is>
-          <t>89.3</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="CU27" t="inlineStr">
@@ -13610,12 +13610,12 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>6066.0</t>
+          <t>3593.0</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -13625,7 +13625,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>87.6</t>
+          <t>89.3</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -13635,17 +13635,17 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>-1.15</t>
+          <t>-5.18</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>-4.01</t>
+          <t>-9.08</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -13710,7 +13710,7 @@
       </c>
       <c r="W28" t="inlineStr">
         <is>
-          <t>-26.69</t>
+          <t>-25.27</t>
         </is>
       </c>
       <c r="X28" t="inlineStr">
@@ -13735,7 +13735,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>0.22</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
@@ -13760,42 +13760,42 @@
       </c>
       <c r="AG28" t="inlineStr">
         <is>
+          <t>2026/01/05</t>
+        </is>
+      </c>
+      <c r="AH28" t="inlineStr">
+        <is>
+          <t>84.9</t>
+        </is>
+      </c>
+      <c r="AI28" t="inlineStr">
+        <is>
           <t>2025/12/16</t>
         </is>
       </c>
-      <c r="AH28" t="inlineStr">
+      <c r="AJ28" t="inlineStr">
         <is>
           <t>86.5</t>
         </is>
       </c>
-      <c r="AI28" t="inlineStr">
-        <is>
-          <t>2025/11/18</t>
-        </is>
-      </c>
-      <c r="AJ28" t="inlineStr">
-        <is>
-          <t>84.6</t>
-        </is>
-      </c>
       <c r="AK28" t="inlineStr">
         <is>
-          <t>2025-11-27 00:00:00</t>
+          <t>2025-12-30 00:00:00</t>
         </is>
       </c>
       <c r="AL28" t="inlineStr">
         <is>
-          <t>2025-12-19</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="AM28" t="inlineStr">
         <is>
-          <t>5.39</t>
+          <t>3.19</t>
         </is>
       </c>
       <c r="AN28" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
@@ -13806,66 +13806,66 @@
       <c r="AP28" t="inlineStr"/>
       <c r="AQ28" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>125</t>
         </is>
       </c>
       <c r="AR28" t="inlineStr">
         <is>
-          <t>4517</t>
+          <t>5699</t>
         </is>
       </c>
       <c r="AS28" t="inlineStr">
         <is>
-          <t>40.54</t>
+          <t>94.0</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr">
         <is>
-          <t>13.51</t>
+          <t>44.85</t>
         </is>
       </c>
       <c r="AU28" t="n">
-        <v>0.9399999999999999</v>
+        <v>2.98</v>
       </c>
       <c r="AV28" t="n">
-        <v>-4.16</v>
+        <v>-4.45</v>
       </c>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>-3.21</t>
+          <t>-2.44</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>-8.89</t>
+          <t>-9.05</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr">
         <is>
-          <t>86.78</t>
+          <t>86.72</t>
         </is>
       </c>
       <c r="AZ28" t="n">
-        <v>90.55</v>
+        <v>90.76000000000001</v>
       </c>
       <c r="BA28" t="n">
-        <v>93.55</v>
+        <v>93.03</v>
       </c>
       <c r="BB28" t="inlineStr">
         <is>
-          <t>102.68</t>
+          <t>102.29</t>
         </is>
       </c>
       <c r="BC28" t="inlineStr">
         <is>
-          <t>-15.60</t>
+          <t>-2.13</t>
         </is>
       </c>
       <c r="BD28" t="n">
-        <v>-1.92</v>
+        <v>-1.7</v>
       </c>
       <c r="BE28" t="n">
-        <v>-1.66</v>
+        <v>-1.67</v>
       </c>
       <c r="BF28" t="inlineStr">
         <is>
@@ -13874,7 +13874,7 @@
       </c>
       <c r="BG28" t="inlineStr">
         <is>
-          <t>-113.83</t>
+          <t>-113.90</t>
         </is>
       </c>
       <c r="BH28" t="inlineStr">
@@ -13884,43 +13884,43 @@
       </c>
       <c r="BI28" t="inlineStr">
         <is>
-          <t>1620700.515463918</t>
+          <t>1199847.889655172</t>
         </is>
       </c>
       <c r="BJ28" t="inlineStr">
         <is>
-          <t>530976.0</t>
+          <t>321495.0</t>
         </is>
       </c>
       <c r="BK28" t="n">
-        <v>402430.8</v>
+        <v>383497</v>
       </c>
       <c r="BL28" t="inlineStr">
         <is>
-          <t>419263.1</t>
+          <t>421816.7</t>
         </is>
       </c>
       <c r="BM28" t="n">
-        <v>1422552.52</v>
+        <v>1399030.72</v>
       </c>
       <c r="BN28" t="inlineStr">
         <is>
-          <t>-16832</t>
+          <t>-38319</t>
         </is>
       </c>
       <c r="BO28" t="inlineStr">
         <is>
-          <t>-166591.4155195166</t>
+          <t>-165399.9533011559</t>
         </is>
       </c>
       <c r="BP28" t="inlineStr">
         <is>
-          <t>-166558.3171777336</t>
+          <t>-158846.9111001717</t>
         </is>
       </c>
       <c r="BQ28" t="inlineStr">
         <is>
-          <t>530976.0</t>
+          <t>321495.0</t>
         </is>
       </c>
       <c r="BR28" t="inlineStr">
@@ -13940,7 +13940,7 @@
       </c>
       <c r="BU28" t="inlineStr">
         <is>
-          <t>28.82</t>
+          <t>31.32</t>
         </is>
       </c>
       <c r="BV28" t="inlineStr">
@@ -13970,22 +13970,22 @@
       </c>
       <c r="CA28" t="inlineStr">
         <is>
-          <t>10.52226299517467</t>
+          <t>-10.72295503475104</t>
         </is>
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>27.79118773626352</t>
+          <t>6.089521543140648</t>
         </is>
       </c>
       <c r="CC28" t="inlineStr">
         <is>
-          <t>-2.044940352257788</t>
+          <t>-1.317487052973139</t>
         </is>
       </c>
       <c r="CD28" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE28" t="inlineStr">
@@ -13995,12 +13995,12 @@
       </c>
       <c r="CF28" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="CG28" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>1.77</t>
         </is>
       </c>
       <c r="CH28" t="inlineStr">
@@ -14010,7 +14010,7 @@
       </c>
       <c r="CI28" t="inlineStr">
         <is>
-          <t>93.12</t>
+          <t>91.29</t>
         </is>
       </c>
       <c r="CJ28" t="inlineStr">
@@ -14025,12 +14025,12 @@
       </c>
       <c r="CL28" t="inlineStr">
         <is>
-          <t>95.21</t>
+          <t>93.1</t>
         </is>
       </c>
       <c r="CM28" t="inlineStr">
         <is>
-          <t>33859</t>
+          <t>33194</t>
         </is>
       </c>
       <c r="CN28" t="inlineStr">
@@ -14050,22 +14050,22 @@
       </c>
       <c r="CQ28" t="inlineStr">
         <is>
-          <t>85.8</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="CR28" t="inlineStr">
         <is>
-          <t>88.6</t>
+          <t>90.4</t>
         </is>
       </c>
       <c r="CS28" t="inlineStr">
         <is>
-          <t>85.4</t>
+          <t>88.5</t>
         </is>
       </c>
       <c r="CT28" t="inlineStr">
         <is>
-          <t>87.6</t>
+          <t>89.3</t>
         </is>
       </c>
       <c r="CU28" t="inlineStr">

--- a/Result/checksun_type/整體解決方案.xlsx
+++ b/Result/checksun_type/整體解決方案.xlsx
@@ -948,12 +948,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-0.53</t>
+          <t>-1.22</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2138.0</t>
+          <t>3999.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -963,7 +963,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>28.65</t>
+          <t>28.3</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -978,12 +978,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>2.41</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-24.84</t>
+          <t>-44.05</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -993,7 +993,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -1003,7 +1003,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>2026-01-08 00:00:00</t>
+          <t>2026-01-09 00:00:00</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -1043,7 +1043,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>-7.13</t>
+          <t>-8.27</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
@@ -1123,17 +1123,17 @@
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>2026-01-07</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>8.06</t>
+          <t>15.08</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>-4.05</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
@@ -1149,61 +1149,61 @@
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>2138</t>
+          <t>3999</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>58.88</t>
+          <t>21.54</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>53.27</t>
+          <t>47.37</t>
         </is>
       </c>
       <c r="AU2" t="n">
-        <v>-0.93</v>
+        <v>-0.95</v>
       </c>
       <c r="AV2" t="n">
-        <v>10.58</v>
+        <v>7.88</v>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>11.92</t>
+          <t>12.81</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>-1.26</t>
+          <t>-0.92</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>28.92</t>
+          <t>28.57</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>26.15</v>
+        <v>26.48</v>
       </c>
       <c r="BA2" t="n">
-        <v>23.37</v>
+        <v>23.48</v>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>23.66</t>
+          <t>23.69</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>10.97</t>
+          <t>4.06</t>
         </is>
       </c>
       <c r="BD2" t="n">
-        <v>1.83</v>
+        <v>1.73</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="BF2" t="inlineStr">
         <is>
@@ -1212,7 +1212,7 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>-1.49</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -1222,48 +1222,48 @@
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>44150.30225409836</t>
+          <t>44417.10736196319</t>
         </is>
       </c>
       <c r="BJ2" t="inlineStr">
         <is>
-          <t>61007.0</t>
+          <t>116412.0</t>
         </is>
       </c>
       <c r="BK2" t="n">
-        <v>136238.8</v>
+        <v>97389.39999999999</v>
       </c>
       <c r="BL2" t="inlineStr">
         <is>
-          <t>181255.6</t>
+          <t>174067.0</t>
         </is>
       </c>
       <c r="BM2" t="n">
-        <v>47685.44</v>
+        <v>49892.26</v>
       </c>
       <c r="BN2" t="inlineStr">
         <is>
-          <t>-45016</t>
+          <t>-76677</t>
         </is>
       </c>
       <c r="BO2" t="inlineStr">
         <is>
-          <t>23465.33738344641</t>
+          <t>20717.8097349553</t>
         </is>
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>8376.633245774749</t>
+          <t>5606.407668254164</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>61007.0</t>
+          <t>116412.0</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-01-09</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
@@ -1278,7 +1278,7 @@
       </c>
       <c r="BU2" t="inlineStr">
         <is>
-          <t>9.35</t>
+          <t>8.02</t>
         </is>
       </c>
       <c r="BV2" t="inlineStr">
@@ -1323,22 +1323,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1363,12 +1363,12 @@
       </c>
       <c r="CL2" t="inlineStr">
         <is>
-          <t>94.08</t>
+          <t>93.31</t>
         </is>
       </c>
       <c r="CM2" t="inlineStr">
         <is>
-          <t>2876</t>
+          <t>2841</t>
         </is>
       </c>
       <c r="CN2" t="inlineStr">
@@ -1388,22 +1388,22 @@
       </c>
       <c r="CQ2" t="inlineStr">
         <is>
-          <t>28.5</t>
+          <t>28.8</t>
         </is>
       </c>
       <c r="CR2" t="inlineStr">
         <is>
-          <t>28.95</t>
+          <t>29.75</t>
         </is>
       </c>
       <c r="CS2" t="inlineStr">
         <is>
-          <t>27.95</t>
+          <t>28.0</t>
         </is>
       </c>
       <c r="CT2" t="inlineStr">
         <is>
-          <t>28.65</t>
+          <t>28.3</t>
         </is>
       </c>
       <c r="CU2" t="inlineStr">
@@ -1435,12 +1435,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>4.26</t>
+          <t>-0.53</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>3015.0</t>
+          <t>2138.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1450,7 +1450,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>28.8</t>
+          <t>28.65</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1460,17 +1460,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>-1.24</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>2.41</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>5.22</t>
+          <t>-24.84</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1480,7 +1480,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -1490,7 +1490,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>2026-01-08 00:00:00</t>
+          <t>2026-01-09 00:00:00</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>-6.65</t>
+          <t>-7.13</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -1610,17 +1610,17 @@
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>2026-01-06</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>11.37</t>
+          <t>8.06</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>-1.34</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
@@ -1636,61 +1636,61 @@
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>2138</t>
+          <t>3999</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>61.68</t>
+          <t>58.88</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>60.55</t>
+          <t>53.27</t>
         </is>
       </c>
       <c r="AU3" t="n">
-        <v>-1.71</v>
+        <v>-0.93</v>
       </c>
       <c r="AV3" t="n">
-        <v>13.6</v>
+        <v>10.58</v>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>10.9</t>
+          <t>11.92</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>-1.56</t>
+          <t>-1.26</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>29.3</t>
+          <t>28.92</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>25.79</v>
+        <v>26.15</v>
       </c>
       <c r="BA3" t="n">
-        <v>23.26</v>
+        <v>23.37</v>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>23.63</t>
+          <t>23.66</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>17.89</t>
+          <t>10.97</t>
         </is>
       </c>
       <c r="BD3" t="n">
-        <v>1.89</v>
+        <v>1.83</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="BF3" t="inlineStr">
         <is>
@@ -1699,7 +1699,7 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>-4.19</t>
+          <t>-1.49</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -1709,48 +1709,48 @@
       </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>44150.30225409836</t>
+          <t>44417.10736196319</t>
         </is>
       </c>
       <c r="BJ3" t="inlineStr">
         <is>
-          <t>87143.0</t>
+          <t>61007.0</t>
         </is>
       </c>
       <c r="BK3" t="n">
-        <v>197614.2</v>
+        <v>136238.8</v>
       </c>
       <c r="BL3" t="inlineStr">
         <is>
-          <t>187809.1</t>
+          <t>181255.6</t>
         </is>
       </c>
       <c r="BM3" t="n">
-        <v>46536.16</v>
+        <v>47685.44</v>
       </c>
       <c r="BN3" t="inlineStr">
         <is>
-          <t>9805</t>
+          <t>-45016</t>
         </is>
       </c>
       <c r="BO3" t="inlineStr">
         <is>
-          <t>26208.73813575035</t>
+          <t>23465.33738344641</t>
         </is>
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>17971.1828834551</t>
+          <t>8376.633245774749</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>87143.0</t>
+          <t>61007.0</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-01-09</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
@@ -1765,7 +1765,7 @@
       </c>
       <c r="BU3" t="inlineStr">
         <is>
-          <t>9.92</t>
+          <t>9.35</t>
         </is>
       </c>
       <c r="BV3" t="inlineStr">
@@ -1810,12 +1810,12 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>價漲量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
@@ -1825,7 +1825,7 @@
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1850,12 +1850,12 @@
       </c>
       <c r="CL3" t="inlineStr">
         <is>
-          <t>94.08</t>
+          <t>93.31</t>
         </is>
       </c>
       <c r="CM3" t="inlineStr">
         <is>
-          <t>2876</t>
+          <t>2841</t>
         </is>
       </c>
       <c r="CN3" t="inlineStr">
@@ -1875,22 +1875,22 @@
       </c>
       <c r="CQ3" t="inlineStr">
         <is>
-          <t>28.2</t>
+          <t>28.5</t>
         </is>
       </c>
       <c r="CR3" t="inlineStr">
         <is>
-          <t>29.8</t>
+          <t>28.95</t>
         </is>
       </c>
       <c r="CS3" t="inlineStr">
         <is>
-          <t>28.2</t>
+          <t>27.95</t>
         </is>
       </c>
       <c r="CT3" t="inlineStr">
         <is>
-          <t>28.8</t>
+          <t>28.65</t>
         </is>
       </c>
       <c r="CU3" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-6.42</t>
+          <t>4.26</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>3771.0</t>
+          <t>3015.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1937,7 +1937,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>27.6</t>
+          <t>28.8</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1947,17 +1947,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>3.66</t>
+          <t>-1.77</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>2.41</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>44.84</t>
+          <t>5.22</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1967,7 +1967,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -1977,7 +1977,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>2026-01-08 00:00:00</t>
+          <t>2026-01-09 00:00:00</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -2017,7 +2017,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>-10.53</t>
+          <t>-6.65</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -2047,7 +2047,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -2097,17 +2097,17 @@
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-06</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>14.22</t>
+          <t>11.37</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>-6.87</t>
+          <t>-1.34</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
@@ -2123,61 +2123,61 @@
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>2138</t>
+          <t>3999</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>39.25</t>
+          <t>61.68</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>69.54</t>
+          <t>60.55</t>
         </is>
       </c>
       <c r="AU4" t="n">
-        <v>-7.1</v>
+        <v>-1.71</v>
       </c>
       <c r="AV4" t="n">
-        <v>16.89</v>
+        <v>13.6</v>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>9.77</t>
+          <t>10.9</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>-1.84</t>
+          <t>-1.56</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>29.71</t>
+          <t>29.3</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>25.42</v>
+        <v>25.79</v>
       </c>
       <c r="BA4" t="n">
-        <v>23.16</v>
+        <v>23.26</v>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>23.59</t>
+          <t>23.63</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>25.69</t>
+          <t>17.89</t>
         </is>
       </c>
       <c r="BD4" t="n">
-        <v>1.92</v>
+        <v>1.89</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="BF4" t="inlineStr">
         <is>
@@ -2186,7 +2186,7 @@
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>-8.48</t>
+          <t>-4.19</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -2196,48 +2196,48 @@
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>44150.30225409836</t>
+          <t>44417.10736196319</t>
         </is>
       </c>
       <c r="BJ4" t="inlineStr">
         <is>
-          <t>106092.0</t>
+          <t>87143.0</t>
         </is>
       </c>
       <c r="BK4" t="n">
-        <v>262320</v>
+        <v>197614.2</v>
       </c>
       <c r="BL4" t="inlineStr">
         <is>
-          <t>181116.4</t>
+          <t>187809.1</t>
         </is>
       </c>
       <c r="BM4" t="n">
-        <v>44883.2</v>
+        <v>46536.16</v>
       </c>
       <c r="BN4" t="inlineStr">
         <is>
-          <t>81203</t>
+          <t>9805</t>
         </is>
       </c>
       <c r="BO4" t="inlineStr">
         <is>
-          <t>27706.47545434949</t>
+          <t>26208.73813575035</t>
         </is>
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>28235.56869144645</t>
+          <t>17971.1828834551</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>106092.0</t>
+          <t>87143.0</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-01-09</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
@@ -2252,7 +2252,7 @@
       </c>
       <c r="BU4" t="inlineStr">
         <is>
-          <t>5.34</t>
+          <t>9.92</t>
         </is>
       </c>
       <c r="BV4" t="inlineStr">
@@ -2297,22 +2297,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>價跌量縮</t>
+          <t>價漲量縮</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="CL4" t="inlineStr">
         <is>
-          <t>94.08</t>
+          <t>93.31</t>
         </is>
       </c>
       <c r="CM4" t="inlineStr">
         <is>
-          <t>2876</t>
+          <t>2841</t>
         </is>
       </c>
       <c r="CN4" t="inlineStr">
@@ -2362,22 +2362,22 @@
       </c>
       <c r="CQ4" t="inlineStr">
         <is>
-          <t>29.6</t>
+          <t>28.2</t>
         </is>
       </c>
       <c r="CR4" t="inlineStr">
         <is>
-          <t>29.85</t>
+          <t>29.8</t>
         </is>
       </c>
       <c r="CS4" t="inlineStr">
         <is>
-          <t>27.25</t>
+          <t>28.2</t>
         </is>
       </c>
       <c r="CT4" t="inlineStr">
         <is>
-          <t>27.6</t>
+          <t>28.8</t>
         </is>
       </c>
       <c r="CU4" t="inlineStr">
@@ -2409,12 +2409,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-1.83</t>
+          <t>-6.42</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>3877.0</t>
+          <t>3771.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2424,7 +2424,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>29.5</t>
+          <t>27.6</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2434,17 +2434,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-2.97</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>2.41</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>52.64</t>
+          <t>44.84</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2454,7 +2454,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>2026-01-08 00:00:00</t>
+          <t>2026-01-09 00:00:00</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>-4.38</t>
+          <t>-10.53</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -2534,7 +2534,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -2584,17 +2584,17 @@
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>2026-01-02</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>14.62</t>
+          <t>14.22</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>-4.24</t>
+          <t>-6.87</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
@@ -2610,61 +2610,61 @@
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>2138</t>
+          <t>3999</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>80.71</t>
+          <t>39.25</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>88.37</t>
+          <t>69.54</t>
         </is>
       </c>
       <c r="AU5" t="n">
-        <v>-1.01</v>
+        <v>-7.1</v>
       </c>
       <c r="AV5" t="n">
-        <v>18.7</v>
+        <v>16.89</v>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>8.81</t>
+          <t>9.77</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>-2.09</t>
+          <t>-1.84</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>29.8</t>
+          <t>29.71</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>25.1</v>
+        <v>25.42</v>
       </c>
       <c r="BA5" t="n">
-        <v>23.07</v>
+        <v>23.16</v>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>23.56</t>
+          <t>23.59</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>43.99</t>
+          <t>25.69</t>
         </is>
       </c>
       <c r="BD5" t="n">
-        <v>2.06</v>
+        <v>1.92</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="BF5" t="inlineStr">
         <is>
@@ -2673,7 +2673,7 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>-14.36</t>
+          <t>-8.48</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
@@ -2683,48 +2683,48 @@
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>44150.30225409836</t>
+          <t>44417.10736196319</t>
         </is>
       </c>
       <c r="BJ5" t="inlineStr">
         <is>
-          <t>116293.0</t>
+          <t>106092.0</t>
         </is>
       </c>
       <c r="BK5" t="n">
-        <v>262896.2</v>
+        <v>262320</v>
       </c>
       <c r="BL5" t="inlineStr">
         <is>
-          <t>172236.8</t>
+          <t>181116.4</t>
         </is>
       </c>
       <c r="BM5" t="n">
-        <v>42873.58</v>
+        <v>44883.2</v>
       </c>
       <c r="BN5" t="inlineStr">
         <is>
-          <t>90659</t>
+          <t>81203</t>
         </is>
       </c>
       <c r="BO5" t="inlineStr">
         <is>
-          <t>27610.27668396823</t>
+          <t>27706.47545434949</t>
         </is>
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>39860.31382102531</t>
+          <t>28235.56869144645</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>116293.0</t>
+          <t>106092.0</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-01-09</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
@@ -2739,7 +2739,7 @@
       </c>
       <c r="BU5" t="inlineStr">
         <is>
-          <t>12.60</t>
+          <t>5.34</t>
         </is>
       </c>
       <c r="BV5" t="inlineStr">
@@ -2794,12 +2794,12 @@
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2824,12 +2824,12 @@
       </c>
       <c r="CL5" t="inlineStr">
         <is>
-          <t>94.08</t>
+          <t>93.31</t>
         </is>
       </c>
       <c r="CM5" t="inlineStr">
         <is>
-          <t>2876</t>
+          <t>2841</t>
         </is>
       </c>
       <c r="CN5" t="inlineStr">
@@ -2849,22 +2849,22 @@
       </c>
       <c r="CQ5" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>29.6</t>
         </is>
       </c>
       <c r="CR5" t="inlineStr">
         <is>
-          <t>30.75</t>
+          <t>29.85</t>
         </is>
       </c>
       <c r="CS5" t="inlineStr">
         <is>
-          <t>29.5</t>
+          <t>27.25</t>
         </is>
       </c>
       <c r="CT5" t="inlineStr">
         <is>
-          <t>29.5</t>
+          <t>27.6</t>
         </is>
       </c>
       <c r="CU5" t="inlineStr">
@@ -2896,12 +2896,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-1.63</t>
+          <t>-1.83</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>10117.0</t>
+          <t>3877.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>30.05</t>
+          <t>29.5</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2921,17 +2921,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-4.89</t>
+          <t>-4.24</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>2.41</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>51.98</t>
+          <t>52.64</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2941,7 +2941,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -2951,7 +2951,7 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>2026-01-08 00:00:00</t>
+          <t>2026-01-09 00:00:00</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -2991,7 +2991,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>-2.59</t>
+          <t>-4.38</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -3021,7 +3021,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -3071,17 +3071,17 @@
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2026-01-02</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>38.15</t>
+          <t>14.62</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>-3.79</t>
+          <t>-4.24</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
@@ -3097,61 +3097,61 @@
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>2138</t>
+          <t>3999</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>88.65</t>
+          <t>80.71</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>94.8</t>
+          <t>88.37</t>
         </is>
       </c>
       <c r="AU6" t="n">
-        <v>3.62</v>
+        <v>-1.01</v>
       </c>
       <c r="AV6" t="n">
-        <v>17.43</v>
+        <v>18.7</v>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>7.61</t>
+          <t>8.81</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>-2.44</t>
+          <t>-2.09</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>29.0</t>
+          <t>29.8</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>24.7</v>
+        <v>25.1</v>
       </c>
       <c r="BA6" t="n">
-        <v>22.95</v>
+        <v>23.07</v>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>23.52</t>
+          <t>23.56</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>58.13</t>
+          <t>43.99</t>
         </is>
       </c>
       <c r="BD6" t="n">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.28</v>
+        <v>1.43</v>
       </c>
       <c r="BF6" t="inlineStr">
         <is>
@@ -3160,7 +3160,7 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>-23.77</t>
+          <t>-14.36</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
@@ -3170,48 +3170,48 @@
       </c>
       <c r="BI6" t="inlineStr">
         <is>
-          <t>44150.30225409836</t>
+          <t>44417.10736196319</t>
         </is>
       </c>
       <c r="BJ6" t="inlineStr">
         <is>
-          <t>310659.0</t>
+          <t>116293.0</t>
         </is>
       </c>
       <c r="BK6" t="n">
-        <v>250744.6</v>
+        <v>262896.2</v>
       </c>
       <c r="BL6" t="inlineStr">
         <is>
-          <t>164984.5</t>
+          <t>172236.8</t>
         </is>
       </c>
       <c r="BM6" t="n">
-        <v>40749.4</v>
+        <v>42873.58</v>
       </c>
       <c r="BN6" t="inlineStr">
         <is>
-          <t>85760</t>
+          <t>90659</t>
         </is>
       </c>
       <c r="BO6" t="inlineStr">
         <is>
-          <t>25382.9972045033</t>
+          <t>27610.27668396823</t>
         </is>
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>53950.54565538705</t>
+          <t>39860.31382102531</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>310659.0</t>
+          <t>116293.0</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-01-09</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="BU6" t="inlineStr">
         <is>
-          <t>14.69</t>
+          <t>12.60</t>
         </is>
       </c>
       <c r="BV6" t="inlineStr">
@@ -3271,22 +3271,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價跌量縮</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3311,12 +3311,12 @@
       </c>
       <c r="CL6" t="inlineStr">
         <is>
-          <t>94.08</t>
+          <t>93.31</t>
         </is>
       </c>
       <c r="CM6" t="inlineStr">
         <is>
-          <t>2876</t>
+          <t>2841</t>
         </is>
       </c>
       <c r="CN6" t="inlineStr">
@@ -3336,22 +3336,22 @@
       </c>
       <c r="CQ6" t="inlineStr">
         <is>
+          <t>30.0</t>
+        </is>
+      </c>
+      <c r="CR6" t="inlineStr">
+        <is>
           <t>30.75</t>
         </is>
       </c>
-      <c r="CR6" t="inlineStr">
-        <is>
-          <t>31.8</t>
-        </is>
-      </c>
       <c r="CS6" t="inlineStr">
         <is>
-          <t>29.45</t>
+          <t>29.5</t>
         </is>
       </c>
       <c r="CT6" t="inlineStr">
         <is>
-          <t>30.05</t>
+          <t>29.5</t>
         </is>
       </c>
       <c r="CU6" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-0.97</t>
+          <t>-1.63</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>12182.0</t>
+          <t>10117.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3398,7 +3398,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>30.55</t>
+          <t>30.05</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3408,17 +3408,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-6.63</t>
+          <t>-6.18</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>2.41</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>60.09</t>
+          <t>51.98</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3428,7 +3428,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -3438,7 +3438,7 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>2026-01-08 00:00:00</t>
+          <t>2026-01-09 00:00:00</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>-0.97</t>
+          <t>-2.59</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -3508,7 +3508,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -3558,17 +3558,17 @@
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>45.93</t>
+          <t>38.15</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>2.97</t>
+          <t>-3.79</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
@@ -3584,61 +3584,61 @@
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>2138</t>
+          <t>3999</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>95.74</t>
+          <t>88.65</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>98.58</t>
+          <t>94.8</t>
         </is>
       </c>
       <c r="AU7" t="n">
-        <v>8.140000000000001</v>
+        <v>3.62</v>
       </c>
       <c r="AV7" t="n">
-        <v>16.53</v>
+        <v>17.43</v>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>6.33</t>
+          <t>7.61</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>-2.87</t>
+          <t>-2.44</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>28.25</t>
+          <t>29.0</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>24.24</v>
+        <v>24.7</v>
       </c>
       <c r="BA7" t="n">
-        <v>22.8</v>
+        <v>22.95</v>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>23.47</t>
+          <t>23.52</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>71.73</t>
+          <t>58.13</t>
         </is>
       </c>
       <c r="BD7" t="n">
-        <v>1.87</v>
+        <v>2.02</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.09</v>
+        <v>1.28</v>
       </c>
       <c r="BF7" t="inlineStr">
         <is>
@@ -3647,7 +3647,7 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>-34.85</t>
+          <t>-23.77</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -3657,48 +3657,48 @@
       </c>
       <c r="BI7" t="inlineStr">
         <is>
-          <t>44150.30225409836</t>
+          <t>44417.10736196319</t>
         </is>
       </c>
       <c r="BJ7" t="inlineStr">
         <is>
-          <t>367884.0</t>
+          <t>310659.0</t>
         </is>
       </c>
       <c r="BK7" t="n">
-        <v>226272.4</v>
+        <v>250744.6</v>
       </c>
       <c r="BL7" t="inlineStr">
         <is>
-          <t>141340.3</t>
+          <t>164984.5</t>
         </is>
       </c>
       <c r="BM7" t="n">
-        <v>34625.74</v>
+        <v>40749.4</v>
       </c>
       <c r="BN7" t="inlineStr">
         <is>
-          <t>84932</t>
+          <t>85760</t>
         </is>
       </c>
       <c r="BO7" t="inlineStr">
         <is>
-          <t>20188.8974861608</t>
+          <t>25382.9972045033</t>
         </is>
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>51327.71450249714</t>
+          <t>53950.54565538705</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>367884.0</t>
+          <t>310659.0</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-01-09</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
@@ -3713,7 +3713,7 @@
       </c>
       <c r="BU7" t="inlineStr">
         <is>
-          <t>16.60</t>
+          <t>14.69</t>
         </is>
       </c>
       <c r="BV7" t="inlineStr">
@@ -3758,22 +3758,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3798,12 +3798,12 @@
       </c>
       <c r="CL7" t="inlineStr">
         <is>
-          <t>94.08</t>
+          <t>93.31</t>
         </is>
       </c>
       <c r="CM7" t="inlineStr">
         <is>
-          <t>2876</t>
+          <t>2841</t>
         </is>
       </c>
       <c r="CN7" t="inlineStr">
@@ -3823,22 +3823,22 @@
       </c>
       <c r="CQ7" t="inlineStr">
         <is>
-          <t>30.85</t>
+          <t>30.75</t>
         </is>
       </c>
       <c r="CR7" t="inlineStr">
         <is>
-          <t>31.0</t>
+          <t>31.8</t>
         </is>
       </c>
       <c r="CS7" t="inlineStr">
         <is>
-          <t>29.25</t>
+          <t>29.45</t>
         </is>
       </c>
       <c r="CT7" t="inlineStr">
         <is>
-          <t>30.55</t>
+          <t>30.05</t>
         </is>
       </c>
       <c r="CU7" t="inlineStr">
@@ -3870,12 +3870,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>9.49</t>
+          <t>-0.97</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>13687.0</t>
+          <t>12182.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3885,74 +3885,74 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
+          <t>30.55</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>-7.95</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2.41</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>60.09</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>2025-12-29</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>65.0</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>2025-12-29 00:00:00</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>2026-01-09 00:00:00</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>2025-07-28 00:00:00</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>2025-08-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
           <t>30.85</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>-7.68</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>-0.01</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>67.00</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>2025-12-29</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>90.0</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>2025-12-29 00:00:00</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>2026-01-08 00:00:00</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>2025-07-28 00:00:00</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>2025-08-14 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
         <is>
           <t>30.85</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>30.85</t>
-        </is>
-      </c>
       <c r="T8" t="inlineStr">
         <is>
           <t>25.6</t>
@@ -3965,7 +3965,7 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.97</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
@@ -3995,7 +3995,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -4045,17 +4045,17 @@
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>51.61</t>
+          <t>45.93</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>8.06</t>
+          <t>2.97</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
@@ -4071,61 +4071,61 @@
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>2138</t>
+          <t>3999</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>95.74</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>89.74</t>
+          <t>98.58</t>
         </is>
       </c>
       <c r="AU8" t="n">
-        <v>12.67</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="AV8" t="n">
-        <v>15.21</v>
+        <v>16.53</v>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>4.96</t>
+          <t>6.33</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>-3.29</t>
+          <t>-2.87</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>27.38</t>
+          <t>28.25</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>23.76</v>
+        <v>24.24</v>
       </c>
       <c r="BA8" t="n">
-        <v>22.64</v>
+        <v>22.8</v>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>23.41</t>
+          <t>23.47</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>79.85</t>
+          <t>71.73</t>
         </is>
       </c>
       <c r="BD8" t="n">
-        <v>1.61</v>
+        <v>1.87</v>
       </c>
       <c r="BE8" t="n">
-        <v>0.89</v>
+        <v>1.09</v>
       </c>
       <c r="BF8" t="inlineStr">
         <is>
@@ -4134,7 +4134,7 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>-46.53</t>
+          <t>-34.85</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -4144,48 +4144,48 @@
       </c>
       <c r="BI8" t="inlineStr">
         <is>
-          <t>44150.30225409836</t>
+          <t>44417.10736196319</t>
         </is>
       </c>
       <c r="BJ8" t="inlineStr">
         <is>
-          <t>410672.0</t>
+          <t>367884.0</t>
         </is>
       </c>
       <c r="BK8" t="n">
-        <v>178004</v>
+        <v>226272.4</v>
       </c>
       <c r="BL8" t="inlineStr">
         <is>
-          <t>106592.2</t>
+          <t>141340.3</t>
         </is>
       </c>
       <c r="BM8" t="n">
-        <v>27334.72</v>
+        <v>34625.74</v>
       </c>
       <c r="BN8" t="inlineStr">
         <is>
-          <t>71411</t>
+          <t>84932</t>
         </is>
       </c>
       <c r="BO8" t="inlineStr">
         <is>
-          <t>14527.29439228146</t>
+          <t>20188.8974861608</t>
         </is>
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>39616.43019470811</t>
+          <t>51327.71450249714</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>410672.0</t>
+          <t>367884.0</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-01-09</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
@@ -4200,7 +4200,7 @@
       </c>
       <c r="BU8" t="inlineStr">
         <is>
-          <t>17.75</t>
+          <t>16.60</t>
         </is>
       </c>
       <c r="BV8" t="inlineStr">
@@ -4245,7 +4245,7 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -4285,12 +4285,12 @@
       </c>
       <c r="CL8" t="inlineStr">
         <is>
-          <t>94.08</t>
+          <t>93.31</t>
         </is>
       </c>
       <c r="CM8" t="inlineStr">
         <is>
-          <t>2876</t>
+          <t>2841</t>
         </is>
       </c>
       <c r="CN8" t="inlineStr">
@@ -4310,22 +4310,22 @@
       </c>
       <c r="CQ8" t="inlineStr">
         <is>
-          <t>29.5</t>
+          <t>30.85</t>
         </is>
       </c>
       <c r="CR8" t="inlineStr">
         <is>
-          <t>30.85</t>
+          <t>31.0</t>
         </is>
       </c>
       <c r="CS8" t="inlineStr">
         <is>
-          <t>28.55</t>
+          <t>29.25</t>
         </is>
       </c>
       <c r="CT8" t="inlineStr">
         <is>
-          <t>30.85</t>
+          <t>30.55</t>
         </is>
       </c>
       <c r="CU8" t="inlineStr">
@@ -4357,12 +4357,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>9.85</t>
+          <t>9.49</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>3968.0</t>
+          <t>13687.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -4372,7 +4372,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>28.05</t>
+          <t>30.85</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -4382,27 +4382,27 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2.09</t>
+          <t>-9.01</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>2.41</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>40.41</t>
+          <t>67.00</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -4412,7 +4412,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>2026-01-08 00:00:00</t>
+          <t>2026-01-09 00:00:00</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -4437,7 +4437,7 @@
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>30.85</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
@@ -4452,7 +4452,7 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
@@ -4482,7 +4482,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -4532,17 +4532,17 @@
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>14.96</t>
+          <t>51.61</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>11.09</t>
+          <t>8.06</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
@@ -4558,7 +4558,7 @@
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>2138</t>
+          <t>3999</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4572,47 +4572,47 @@
         </is>
       </c>
       <c r="AU9" t="n">
-        <v>7.97</v>
+        <v>12.67</v>
       </c>
       <c r="AV9" t="n">
-        <v>11.48</v>
+        <v>15.21</v>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>3.68</t>
+          <t>4.96</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>-3.74</t>
+          <t>-3.29</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>25.98</t>
+          <t>27.38</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>23.3</v>
+        <v>23.76</v>
       </c>
       <c r="BA9" t="n">
-        <v>22.48</v>
+        <v>22.64</v>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>23.35</t>
+          <t>23.41</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>70.30</t>
+          <t>79.85</t>
         </is>
       </c>
       <c r="BD9" t="n">
-        <v>1.22</v>
+        <v>1.61</v>
       </c>
       <c r="BE9" t="n">
-        <v>0.72</v>
+        <v>0.89</v>
       </c>
       <c r="BF9" t="inlineStr">
         <is>
@@ -4621,7 +4621,7 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>-57.21</t>
+          <t>-46.53</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -4631,48 +4631,48 @@
       </c>
       <c r="BI9" t="inlineStr">
         <is>
-          <t>44150.30225409836</t>
+          <t>44417.10736196319</t>
         </is>
       </c>
       <c r="BJ9" t="inlineStr">
         <is>
-          <t>108973.0</t>
+          <t>410672.0</t>
         </is>
       </c>
       <c r="BK9" t="n">
-        <v>99912.8</v>
+        <v>178004</v>
       </c>
       <c r="BL9" t="inlineStr">
         <is>
-          <t>71156.8</t>
+          <t>106592.2</t>
         </is>
       </c>
       <c r="BM9" t="n">
-        <v>19249.48</v>
+        <v>27334.72</v>
       </c>
       <c r="BN9" t="inlineStr">
         <is>
-          <t>28756</t>
+          <t>71411</t>
         </is>
       </c>
       <c r="BO9" t="inlineStr">
         <is>
-          <t>9965.6333372948</t>
+          <t>14527.29439228146</t>
         </is>
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>16886.72296234135</t>
+          <t>39616.43019470811</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>108973.0</t>
+          <t>410672.0</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2026-01-09</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
@@ -4687,7 +4687,7 @@
       </c>
       <c r="BU9" t="inlineStr">
         <is>
-          <t>7.06</t>
+          <t>17.75</t>
         </is>
       </c>
       <c r="BV9" t="inlineStr">
@@ -4732,7 +4732,7 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議關注買點&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;2&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
@@ -4742,12 +4742,12 @@
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4772,12 +4772,12 @@
       </c>
       <c r="CL9" t="inlineStr">
         <is>
-          <t>94.08</t>
+          <t>93.31</t>
         </is>
       </c>
       <c r="CM9" t="inlineStr">
         <is>
-          <t>2876</t>
+          <t>2841</t>
         </is>
       </c>
       <c r="CN9" t="inlineStr">
@@ -4797,22 +4797,22 @@
       </c>
       <c r="CQ9" t="inlineStr">
         <is>
-          <t>25.9</t>
+          <t>29.5</t>
         </is>
       </c>
       <c r="CR9" t="inlineStr">
         <is>
-          <t>28.05</t>
+          <t>30.85</t>
         </is>
       </c>
       <c r="CS9" t="inlineStr">
         <is>
-          <t>25.25</t>
+          <t>28.55</t>
         </is>
       </c>
       <c r="CT9" t="inlineStr">
         <is>
-          <t>28.05</t>
+          <t>30.85</t>
         </is>
       </c>
       <c r="CU9" t="inlineStr">
@@ -4844,12 +4844,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-3.09</t>
+          <t>9.85</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2162.0</t>
+          <t>3968.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4859,7 +4859,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>25.5</t>
+          <t>28.05</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4869,17 +4869,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>10.99</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>2.41</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>26.73</t>
+          <t>40.41</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4889,7 +4889,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -4899,7 +4899,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>2026-01-08 00:00:00</t>
+          <t>2026-01-09 00:00:00</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -4969,7 +4969,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -5019,22 +5019,22 @@
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>2025-12-24</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>14.96</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>-2.35</t>
+          <t>11.09</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr"/>
@@ -5045,12 +5045,12 @@
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>2138</t>
+          <t>3999</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>69.23</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr">
@@ -5059,47 +5059,47 @@
         </is>
       </c>
       <c r="AU10" t="n">
-        <v>1.47</v>
+        <v>7.97</v>
       </c>
       <c r="AV10" t="n">
-        <v>9.42</v>
+        <v>11.48</v>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>2.68</t>
+          <t>3.68</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>-4.17</t>
+          <t>-3.74</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>25.13</t>
+          <t>25.98</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>22.97</v>
+        <v>23.3</v>
       </c>
       <c r="BA10" t="n">
-        <v>22.37</v>
+        <v>22.48</v>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>23.34</t>
+          <t>23.35</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>67.67</t>
+          <t>70.30</t>
         </is>
       </c>
       <c r="BD10" t="n">
-        <v>0.99</v>
+        <v>1.22</v>
       </c>
       <c r="BE10" t="n">
-        <v>0.59</v>
+        <v>0.72</v>
       </c>
       <c r="BF10" t="inlineStr">
         <is>
@@ -5108,7 +5108,7 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>-64.73</t>
+          <t>-57.21</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -5118,43 +5118,43 @@
       </c>
       <c r="BI10" t="inlineStr">
         <is>
-          <t>44150.30225409836</t>
+          <t>44417.10736196319</t>
         </is>
       </c>
       <c r="BJ10" t="inlineStr">
         <is>
-          <t>55535.0</t>
+          <t>108973.0</t>
         </is>
       </c>
       <c r="BK10" t="n">
-        <v>81577.39999999999</v>
+        <v>99912.8</v>
       </c>
       <c r="BL10" t="inlineStr">
         <is>
-          <t>64373.5</t>
+          <t>71156.8</t>
         </is>
       </c>
       <c r="BM10" t="n">
-        <v>17193.38</v>
+        <v>19249.48</v>
       </c>
       <c r="BN10" t="inlineStr">
         <is>
-          <t>17203</t>
+          <t>28756</t>
         </is>
       </c>
       <c r="BO10" t="inlineStr">
         <is>
-          <t>8707.253405468153</t>
+          <t>9965.6333372948</t>
         </is>
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>16137.50823887664</t>
+          <t>16886.72296234135</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>55535.0</t>
+          <t>108973.0</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -5174,7 +5174,7 @@
       </c>
       <c r="BU10" t="inlineStr">
         <is>
-          <t>-2.67</t>
+          <t>7.06</t>
         </is>
       </c>
       <c r="BV10" t="inlineStr">
@@ -5219,7 +5219,7 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議關注買點&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;2&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
@@ -5229,12 +5229,12 @@
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -5259,12 +5259,12 @@
       </c>
       <c r="CL10" t="inlineStr">
         <is>
-          <t>94.08</t>
+          <t>93.31</t>
         </is>
       </c>
       <c r="CM10" t="inlineStr">
         <is>
-          <t>2876</t>
+          <t>2841</t>
         </is>
       </c>
       <c r="CN10" t="inlineStr">
@@ -5284,22 +5284,22 @@
       </c>
       <c r="CQ10" t="inlineStr">
         <is>
-          <t>25.85</t>
+          <t>25.9</t>
         </is>
       </c>
       <c r="CR10" t="inlineStr">
         <is>
-          <t>26.2</t>
+          <t>28.05</t>
         </is>
       </c>
       <c r="CS10" t="inlineStr">
         <is>
-          <t>25.4</t>
+          <t>25.25</t>
         </is>
       </c>
       <c r="CT10" t="inlineStr">
         <is>
-          <t>25.5</t>
+          <t>28.05</t>
         </is>
       </c>
       <c r="CU10" t="inlineStr">
@@ -5321,7 +5321,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>價_量;【b1】</t>
+          <t>【b1】</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -5331,12 +5331,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>3.37</t>
+          <t>-5.53</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>10744.0</t>
+          <t>5061.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -5346,7 +5346,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>74.7</t>
+          <t>70.5</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -5361,12 +5361,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-6.45</t>
+          <t>14.77</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -5376,7 +5376,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -5431,7 +5431,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-3.86</t>
+          <t>-9.27</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -5506,17 +5506,17 @@
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>2026-01-07</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>24.75</t>
+          <t>27.77</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>-3.34</t>
+          <t>-7.52</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
@@ -5527,17 +5527,17 @@
       <c r="AP11" t="inlineStr"/>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>65</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>10744</t>
+          <t>5061</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr">
@@ -5546,47 +5546,47 @@
         </is>
       </c>
       <c r="AU11" t="n">
-        <v>3.38</v>
+        <v>-2</v>
       </c>
       <c r="AV11" t="n">
-        <v>4.6</v>
+        <v>3.67</v>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>3.47</t>
+          <t>3.93</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>-4.51</t>
+          <t>-4.39</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>72.26</t>
+          <t>71.94</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>69.09</v>
+        <v>69.39</v>
       </c>
       <c r="BA11" t="n">
         <v>66.77</v>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>69.92</t>
+          <t>69.83</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>29.20</t>
+          <t>12.28</t>
         </is>
       </c>
       <c r="BD11" t="n">
-        <v>2.02</v>
+        <v>1.81</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.56</v>
+        <v>1.61</v>
       </c>
       <c r="BF11" t="inlineStr">
         <is>
@@ -5595,7 +5595,7 @@
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>-81.37</t>
+          <t>-80.78</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
@@ -5605,43 +5605,43 @@
       </c>
       <c r="BI11" t="inlineStr">
         <is>
-          <t>1277721.845286885</t>
+          <t>1276231.26993865</t>
         </is>
       </c>
       <c r="BJ11" t="inlineStr">
         <is>
-          <t>810212.0</t>
+          <t>365887.0</t>
         </is>
       </c>
       <c r="BK11" t="n">
-        <v>356009.4</v>
+        <v>383681.2</v>
       </c>
       <c r="BL11" t="inlineStr">
         <is>
-          <t>380538.6</t>
+          <t>334298.2</t>
         </is>
       </c>
       <c r="BM11" t="n">
-        <v>157522.02</v>
+        <v>163244.72</v>
       </c>
       <c r="BN11" t="inlineStr">
         <is>
-          <t>-24529</t>
+          <t>49383</t>
         </is>
       </c>
       <c r="BO11" t="inlineStr">
         <is>
-          <t>29042.05609019929</t>
+          <t>31791.93918599866</t>
         </is>
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>55516.64369527216</t>
+          <t>46916.29621289513</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>810212.0</t>
+          <t>365887.0</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5661,7 +5661,7 @@
       </c>
       <c r="BU11" t="inlineStr">
         <is>
-          <t>2.33</t>
+          <t>-3.42</t>
         </is>
       </c>
       <c r="BV11" t="inlineStr">
@@ -5706,22 +5706,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>4.43</t>
+          <t>4.18</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5731,7 +5731,7 @@
       </c>
       <c r="CI11" t="inlineStr">
         <is>
-          <t>574.62</t>
+          <t>542.31</t>
         </is>
       </c>
       <c r="CJ11" t="inlineStr">
@@ -5746,12 +5746,12 @@
       </c>
       <c r="CL11" t="inlineStr">
         <is>
-          <t>94.08</t>
+          <t>93.31</t>
         </is>
       </c>
       <c r="CM11" t="inlineStr">
         <is>
-          <t>19348</t>
+          <t>18260</t>
         </is>
       </c>
       <c r="CN11" t="inlineStr">
@@ -5766,27 +5766,27 @@
       </c>
       <c r="CP11" t="inlineStr">
         <is>
-          <t>光電業平上櫃</t>
+          <t>光電業右下上櫃</t>
         </is>
       </c>
       <c r="CQ11" t="inlineStr">
         <is>
-          <t>74.1</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="CR11" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="CS11" t="inlineStr">
         <is>
-          <t>73.9</t>
+          <t>70.3</t>
         </is>
       </c>
       <c r="CT11" t="inlineStr">
         <is>
-          <t>74.7</t>
+          <t>70.5</t>
         </is>
       </c>
       <c r="CU11" t="inlineStr">
@@ -5818,12 +5818,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>3.37</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>5680.0</t>
+          <t>10744.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5833,7 +5833,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>72.2</t>
+          <t>74.7</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5843,17 +5843,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>3.35</t>
+          <t>-5.96</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-14.81</t>
+          <t>-6.45</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5863,7 +5863,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -5918,7 +5918,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-7.08</t>
+          <t>-3.86</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5943,7 +5943,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -5993,17 +5993,17 @@
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>2026-01-06</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>13.08</t>
+          <t>58.96</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>1.16</t>
+          <t>-3.34</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
@@ -6014,66 +6014,66 @@
       <c r="AP12" t="inlineStr"/>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>65</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>10744</t>
+          <t>5061</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>52.17</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>41.47</t>
+          <t>50.72</t>
         </is>
       </c>
       <c r="AU12" t="n">
-        <v>0.39</v>
+        <v>3.38</v>
       </c>
       <c r="AV12" t="n">
-        <v>4.92</v>
+        <v>4.6</v>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>2.78</t>
+          <t>3.47</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>-4.66</t>
+          <t>-4.51</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>71.91999999999999</t>
+          <t>72.26</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>68.55</v>
+        <v>69.09</v>
       </c>
       <c r="BA12" t="n">
-        <v>66.7</v>
+        <v>66.77</v>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>69.96</t>
+          <t>69.92</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>26.19</t>
+          <t>29.20</t>
         </is>
       </c>
       <c r="BD12" t="n">
-        <v>1.83</v>
+        <v>2.02</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.45</v>
+        <v>1.56</v>
       </c>
       <c r="BF12" t="inlineStr">
         <is>
@@ -6082,7 +6082,7 @@
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>-82.73</t>
+          <t>-81.37</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
@@ -6092,43 +6092,43 @@
       </c>
       <c r="BI12" t="inlineStr">
         <is>
-          <t>1277721.845286885</t>
+          <t>1276231.26993865</t>
         </is>
       </c>
       <c r="BJ12" t="inlineStr">
         <is>
-          <t>409062.0</t>
+          <t>810212.0</t>
         </is>
       </c>
       <c r="BK12" t="n">
-        <v>281077.6</v>
+        <v>356009.4</v>
       </c>
       <c r="BL12" t="inlineStr">
         <is>
-          <t>329927.0</t>
+          <t>380538.6</t>
         </is>
       </c>
       <c r="BM12" t="n">
-        <v>143794.86</v>
+        <v>157522.02</v>
       </c>
       <c r="BN12" t="inlineStr">
         <is>
-          <t>-48849</t>
+          <t>-24529</t>
         </is>
       </c>
       <c r="BO12" t="inlineStr">
         <is>
-          <t>24228.49470745877</t>
+          <t>29042.05609019929</t>
         </is>
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>18213.86710955098</t>
+          <t>55516.64369527216</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>409062.0</t>
+          <t>810212.0</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -6148,7 +6148,7 @@
       </c>
       <c r="BU12" t="inlineStr">
         <is>
-          <t>-1.10</t>
+          <t>2.33</t>
         </is>
       </c>
       <c r="BV12" t="inlineStr">
@@ -6193,22 +6193,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>4.28</t>
+          <t>4.43</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
@@ -6218,7 +6218,7 @@
       </c>
       <c r="CI12" t="inlineStr">
         <is>
-          <t>574.62</t>
+          <t>542.31</t>
         </is>
       </c>
       <c r="CJ12" t="inlineStr">
@@ -6233,12 +6233,12 @@
       </c>
       <c r="CL12" t="inlineStr">
         <is>
-          <t>94.08</t>
+          <t>93.31</t>
         </is>
       </c>
       <c r="CM12" t="inlineStr">
         <is>
-          <t>19348</t>
+          <t>18260</t>
         </is>
       </c>
       <c r="CN12" t="inlineStr">
@@ -6253,27 +6253,27 @@
       </c>
       <c r="CP12" t="inlineStr">
         <is>
-          <t>光電業平上櫃</t>
+          <t>光電業右下上櫃</t>
         </is>
       </c>
       <c r="CQ12" t="inlineStr">
         <is>
-          <t>71.3</t>
+          <t>74.1</t>
         </is>
       </c>
       <c r="CR12" t="inlineStr">
         <is>
-          <t>73.1</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="CS12" t="inlineStr">
         <is>
-          <t>70.5</t>
+          <t>73.9</t>
         </is>
       </c>
       <c r="CT12" t="inlineStr">
         <is>
-          <t>72.2</t>
+          <t>74.7</t>
         </is>
       </c>
       <c r="CU12" t="inlineStr">
@@ -6305,12 +6305,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-0.42</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>3194.0</t>
+          <t>5680.0</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -6320,7 +6320,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>72.2</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -6330,17 +6330,17 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>4.95</t>
+          <t>-2.41</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-20.34</t>
+          <t>-14.81</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -6350,7 +6350,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -6405,7 +6405,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>-8.62</t>
+          <t>-7.08</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -6430,7 +6430,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
@@ -6480,17 +6480,17 @@
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-06</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>7.36</t>
+          <t>31.17</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>1.16</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
@@ -6501,66 +6501,66 @@
       <c r="AP13" t="inlineStr"/>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>65</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>10744</t>
+          <t>5061</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>52.17</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>53.28</t>
+          <t>41.47</t>
         </is>
       </c>
       <c r="AU13" t="n">
-        <v>-1.28</v>
+        <v>0.39</v>
       </c>
       <c r="AV13" t="n">
-        <v>5.46</v>
+        <v>4.92</v>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>2.78</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>-4.74</t>
+          <t>-4.66</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>71.92</t>
+          <t>71.91999999999999</t>
         </is>
       </c>
       <c r="AZ13" t="n">
-        <v>68.2</v>
+        <v>68.55</v>
       </c>
       <c r="BA13" t="n">
-        <v>66.69</v>
+        <v>66.7</v>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>70.01</t>
+          <t>69.96</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>33.90</t>
+          <t>26.19</t>
         </is>
       </c>
       <c r="BD13" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.35</v>
+        <v>1.45</v>
       </c>
       <c r="BF13" t="inlineStr">
         <is>
@@ -6569,7 +6569,7 @@
       </c>
       <c r="BG13" t="inlineStr">
         <is>
-          <t>-83.86</t>
+          <t>-82.73</t>
         </is>
       </c>
       <c r="BH13" t="inlineStr">
@@ -6579,43 +6579,43 @@
       </c>
       <c r="BI13" t="inlineStr">
         <is>
-          <t>1277721.845286885</t>
+          <t>1276231.26993865</t>
         </is>
       </c>
       <c r="BJ13" t="inlineStr">
         <is>
-          <t>224648.0</t>
+          <t>409062.0</t>
         </is>
       </c>
       <c r="BK13" t="n">
-        <v>244234.8</v>
+        <v>281077.6</v>
       </c>
       <c r="BL13" t="inlineStr">
         <is>
-          <t>306587.9</t>
+          <t>329927.0</t>
         </is>
       </c>
       <c r="BM13" t="n">
-        <v>138785.12</v>
+        <v>143794.86</v>
       </c>
       <c r="BN13" t="inlineStr">
         <is>
-          <t>-62353</t>
+          <t>-48849</t>
         </is>
       </c>
       <c r="BO13" t="inlineStr">
         <is>
-          <t>25322.06336162383</t>
+          <t>24228.49470745877</t>
         </is>
       </c>
       <c r="BP13" t="inlineStr">
         <is>
-          <t>7254.048161751067</t>
+          <t>18213.86710955098</t>
         </is>
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>224648.0</t>
+          <t>409062.0</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
@@ -6635,7 +6635,7 @@
       </c>
       <c r="BU13" t="inlineStr">
         <is>
-          <t>-2.74</t>
+          <t>-1.10</t>
         </is>
       </c>
       <c r="BV13" t="inlineStr">
@@ -6680,22 +6680,22 @@
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>4.21</t>
+          <t>4.28</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="CH13" t="inlineStr">
@@ -6705,7 +6705,7 @@
       </c>
       <c r="CI13" t="inlineStr">
         <is>
-          <t>574.62</t>
+          <t>542.31</t>
         </is>
       </c>
       <c r="CJ13" t="inlineStr">
@@ -6720,12 +6720,12 @@
       </c>
       <c r="CL13" t="inlineStr">
         <is>
-          <t>94.08</t>
+          <t>93.31</t>
         </is>
       </c>
       <c r="CM13" t="inlineStr">
         <is>
-          <t>19348</t>
+          <t>18260</t>
         </is>
       </c>
       <c r="CN13" t="inlineStr">
@@ -6740,7 +6740,7 @@
       </c>
       <c r="CP13" t="inlineStr">
         <is>
-          <t>光電業平上櫃</t>
+          <t>光電業右下上櫃</t>
         </is>
       </c>
       <c r="CQ13" t="inlineStr">
@@ -6750,17 +6750,17 @@
       </c>
       <c r="CR13" t="inlineStr">
         <is>
-          <t>71.5</t>
+          <t>73.1</t>
         </is>
       </c>
       <c r="CS13" t="inlineStr">
         <is>
-          <t>69.4</t>
+          <t>70.5</t>
         </is>
       </c>
       <c r="CT13" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>72.2</t>
         </is>
       </c>
       <c r="CU13" t="inlineStr">
@@ -6792,12 +6792,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-1.11</t>
+          <t>-0.42</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1512.0</t>
+          <t>3194.0</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6807,7 +6807,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>71.3</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6817,17 +6817,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>4.55</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>-17.80</t>
+          <t>-20.34</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6837,7 +6837,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -6892,7 +6892,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>-8.24</t>
+          <t>-8.62</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6917,7 +6917,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
@@ -6967,17 +6967,17 @@
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>2026-01-02</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>3.48</t>
+          <t>17.53</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>-1.40</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
@@ -6988,66 +6988,66 @@
       <c r="AP14" t="inlineStr"/>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>65</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>10744</t>
+          <t>5061</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
         <is>
-          <t>72.22</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>85.63</t>
+          <t>53.28</t>
         </is>
       </c>
       <c r="AU14" t="n">
-        <v>-1.08</v>
+        <v>-1.28</v>
       </c>
       <c r="AV14" t="n">
-        <v>6.23</v>
+        <v>5.46</v>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>-4.72</t>
+          <t>-4.74</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>72.08000000000001</t>
+          <t>71.92</t>
         </is>
       </c>
       <c r="AZ14" t="n">
-        <v>67.84999999999999</v>
+        <v>68.2</v>
       </c>
       <c r="BA14" t="n">
-        <v>66.76000000000001</v>
+        <v>66.69</v>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>70.07</t>
+          <t>70.01</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>52.45</t>
+          <t>33.90</t>
         </is>
       </c>
       <c r="BD14" t="n">
-        <v>1.89</v>
+        <v>1.81</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.24</v>
+        <v>1.35</v>
       </c>
       <c r="BF14" t="inlineStr">
         <is>
@@ -7056,7 +7056,7 @@
       </c>
       <c r="BG14" t="inlineStr">
         <is>
-          <t>-85.23</t>
+          <t>-83.86</t>
         </is>
       </c>
       <c r="BH14" t="inlineStr">
@@ -7066,43 +7066,43 @@
       </c>
       <c r="BI14" t="inlineStr">
         <is>
-          <t>1277721.845286885</t>
+          <t>1276231.26993865</t>
         </is>
       </c>
       <c r="BJ14" t="inlineStr">
         <is>
-          <t>108597.0</t>
+          <t>224648.0</t>
         </is>
       </c>
       <c r="BK14" t="n">
-        <v>240458.2</v>
+        <v>244234.8</v>
       </c>
       <c r="BL14" t="inlineStr">
         <is>
-          <t>292538.0</t>
+          <t>306587.9</t>
         </is>
       </c>
       <c r="BM14" t="n">
-        <v>136053.42</v>
+        <v>138785.12</v>
       </c>
       <c r="BN14" t="inlineStr">
         <is>
-          <t>-52079</t>
+          <t>-62353</t>
         </is>
       </c>
       <c r="BO14" t="inlineStr">
         <is>
-          <t>28607.15703432796</t>
+          <t>25322.06336162383</t>
         </is>
       </c>
       <c r="BP14" t="inlineStr">
         <is>
-          <t>11096.73365911728</t>
+          <t>7254.048161751067</t>
         </is>
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>108597.0</t>
+          <t>224648.0</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
@@ -7122,7 +7122,7 @@
       </c>
       <c r="BU14" t="inlineStr">
         <is>
-          <t>-2.33</t>
+          <t>-2.74</t>
         </is>
       </c>
       <c r="BV14" t="inlineStr">
@@ -7167,22 +7167,22 @@
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>4.22</t>
+          <t>4.21</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="CH14" t="inlineStr">
@@ -7192,7 +7192,7 @@
       </c>
       <c r="CI14" t="inlineStr">
         <is>
-          <t>574.62</t>
+          <t>542.31</t>
         </is>
       </c>
       <c r="CJ14" t="inlineStr">
@@ -7207,12 +7207,12 @@
       </c>
       <c r="CL14" t="inlineStr">
         <is>
-          <t>94.08</t>
+          <t>93.31</t>
         </is>
       </c>
       <c r="CM14" t="inlineStr">
         <is>
-          <t>19348</t>
+          <t>18260</t>
         </is>
       </c>
       <c r="CN14" t="inlineStr">
@@ -7227,27 +7227,27 @@
       </c>
       <c r="CP14" t="inlineStr">
         <is>
-          <t>光電業平上櫃</t>
+          <t>光電業右下上櫃</t>
         </is>
       </c>
       <c r="CQ14" t="inlineStr">
         <is>
-          <t>71.8</t>
+          <t>71.3</t>
         </is>
       </c>
       <c r="CR14" t="inlineStr">
         <is>
-          <t>72.3</t>
+          <t>71.5</t>
         </is>
       </c>
       <c r="CS14" t="inlineStr">
         <is>
-          <t>71.3</t>
+          <t>69.4</t>
         </is>
       </c>
       <c r="CT14" t="inlineStr">
         <is>
-          <t>71.3</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="CU14" t="inlineStr">
@@ -7279,12 +7279,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>-1.11</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>3170.0</t>
+          <t>1512.0</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -7294,7 +7294,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>72.1</t>
+          <t>71.3</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -7304,17 +7304,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>3.48</t>
+          <t>-1.13</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>-0.68</t>
+          <t>-17.80</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -7324,7 +7324,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -7379,7 +7379,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>-7.21</t>
+          <t>-8.24</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -7404,7 +7404,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>-0.2</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
@@ -7454,17 +7454,17 @@
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2026-01-02</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>7.30</t>
+          <t>8.30</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>-1.40</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
@@ -7475,266 +7475,266 @@
       <c r="AP15" t="inlineStr"/>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>65</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>10744</t>
+          <t>5061</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
         <is>
-          <t>87.63</t>
+          <t>72.22</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>91.29</t>
+          <t>85.63</t>
         </is>
       </c>
       <c r="AU15" t="n">
-        <v>-0.28</v>
+        <v>-1.08</v>
       </c>
       <c r="AV15" t="n">
-        <v>7.18</v>
+        <v>6.23</v>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>-4.74</t>
+          <t>-4.72</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
+          <t>72.08000000000001</t>
+        </is>
+      </c>
+      <c r="AZ15" t="n">
+        <v>67.84999999999999</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>66.76000000000001</v>
+      </c>
+      <c r="BB15" t="inlineStr">
+        <is>
+          <t>70.07</t>
+        </is>
+      </c>
+      <c r="BC15" t="inlineStr">
+        <is>
+          <t>52.45</t>
+        </is>
+      </c>
+      <c r="BD15" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="BF15" t="inlineStr">
+        <is>
+          <t>8.38</t>
+        </is>
+      </c>
+      <c r="BG15" t="inlineStr">
+        <is>
+          <t>-85.23</t>
+        </is>
+      </c>
+      <c r="BH15" t="inlineStr">
+        <is>
+          <t>2025/11/27</t>
+        </is>
+      </c>
+      <c r="BI15" t="inlineStr">
+        <is>
+          <t>1276231.26993865</t>
+        </is>
+      </c>
+      <c r="BJ15" t="inlineStr">
+        <is>
+          <t>108597.0</t>
+        </is>
+      </c>
+      <c r="BK15" t="n">
+        <v>240458.2</v>
+      </c>
+      <c r="BL15" t="inlineStr">
+        <is>
+          <t>292538.0</t>
+        </is>
+      </c>
+      <c r="BM15" t="n">
+        <v>136053.42</v>
+      </c>
+      <c r="BN15" t="inlineStr">
+        <is>
+          <t>-52079</t>
+        </is>
+      </c>
+      <c r="BO15" t="inlineStr">
+        <is>
+          <t>28607.15703432796</t>
+        </is>
+      </c>
+      <c r="BP15" t="inlineStr">
+        <is>
+          <t>11096.73365911728</t>
+        </is>
+      </c>
+      <c r="BQ15" t="inlineStr">
+        <is>
+          <t>108597.0</t>
+        </is>
+      </c>
+      <c r="BR15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BS15" t="inlineStr">
+        <is>
+          <t>73.0</t>
+        </is>
+      </c>
+      <c r="BT15" t="inlineStr">
+        <is>
+          <t>2025/12/30</t>
+        </is>
+      </c>
+      <c r="BU15" t="inlineStr">
+        <is>
+          <t>-2.33</t>
+        </is>
+      </c>
+      <c r="BV15" t="inlineStr">
+        <is>
+          <t>廣運</t>
+        </is>
+      </c>
+      <c r="BW15" t="inlineStr">
+        <is>
+          <t>廣運</t>
+        </is>
+      </c>
+      <c r="BX15" t="inlineStr">
+        <is>
+          <t>光電業</t>
+        </is>
+      </c>
+      <c r="BY15" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BZ15" t="inlineStr">
+        <is>
+          <t>1.25</t>
+        </is>
+      </c>
+      <c r="CA15" t="inlineStr">
+        <is>
+          <t>8.126510269834878</t>
+        </is>
+      </c>
+      <c r="CB15" t="inlineStr">
+        <is>
+          <t>71.54723574191938</t>
+        </is>
+      </c>
+      <c r="CC15" t="inlineStr">
+        <is>
+          <t>22.92929018430961</t>
+        </is>
+      </c>
+      <c r="CD15" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+        </is>
+      </c>
+      <c r="CE15" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="CF15" t="inlineStr">
+        <is>
+          <t>4.22</t>
+        </is>
+      </c>
+      <c r="CG15" t="inlineStr">
+        <is>
+          <t>0.99</t>
+        </is>
+      </c>
+      <c r="CH15" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="CI15" t="inlineStr">
+        <is>
+          <t>542.31</t>
+        </is>
+      </c>
+      <c r="CJ15" t="inlineStr">
+        <is>
+          <t>17.69%</t>
+        </is>
+      </c>
+      <c r="CK15" t="inlineStr">
+        <is>
+          <t>-6.67%</t>
+        </is>
+      </c>
+      <c r="CL15" t="inlineStr">
+        <is>
+          <t>93.31</t>
+        </is>
+      </c>
+      <c r="CM15" t="inlineStr">
+        <is>
+          <t>18260</t>
+        </is>
+      </c>
+      <c r="CN15" t="inlineStr">
+        <is>
+          <t>自動化設備74.11%、太陽能產品12.33%、電子零組件8.12%、建材營建4.02%、其他1.41% (2024年)</t>
+        </is>
+      </c>
+      <c r="CO15" t="inlineStr">
+        <is>
+          <t>廣運-光電業-上櫃</t>
+        </is>
+      </c>
+      <c r="CP15" t="inlineStr">
+        <is>
+          <t>光電業右下上櫃</t>
+        </is>
+      </c>
+      <c r="CQ15" t="inlineStr">
+        <is>
+          <t>71.8</t>
+        </is>
+      </c>
+      <c r="CR15" t="inlineStr">
+        <is>
           <t>72.3</t>
         </is>
       </c>
-      <c r="AZ15" t="n">
-        <v>67.45999999999999</v>
-      </c>
-      <c r="BA15" t="n">
-        <v>66.81</v>
-      </c>
-      <c r="BB15" t="inlineStr">
-        <is>
-          <t>70.14</t>
-        </is>
-      </c>
-      <c r="BC15" t="inlineStr">
-        <is>
-          <t>79.09</t>
-        </is>
-      </c>
-      <c r="BD15" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="BE15" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="BF15" t="inlineStr">
-        <is>
-          <t>8.38</t>
-        </is>
-      </c>
-      <c r="BG15" t="inlineStr">
-        <is>
-          <t>-87.17</t>
-        </is>
-      </c>
-      <c r="BH15" t="inlineStr">
-        <is>
-          <t>2025/11/27</t>
-        </is>
-      </c>
-      <c r="BI15" t="inlineStr">
-        <is>
-          <t>1277721.845286885</t>
-        </is>
-      </c>
-      <c r="BJ15" t="inlineStr">
-        <is>
-          <t>227528.0</t>
-        </is>
-      </c>
-      <c r="BK15" t="n">
-        <v>284915.2</v>
-      </c>
-      <c r="BL15" t="inlineStr">
-        <is>
-          <t>286862.6</t>
-        </is>
-      </c>
-      <c r="BM15" t="n">
-        <v>136315.58</v>
-      </c>
-      <c r="BN15" t="inlineStr">
-        <is>
-          <t>-1947</t>
-        </is>
-      </c>
-      <c r="BO15" t="inlineStr">
-        <is>
-          <t>31790.87037527536</t>
-        </is>
-      </c>
-      <c r="BP15" t="inlineStr">
-        <is>
-          <t>28624.00816752913</t>
-        </is>
-      </c>
-      <c r="BQ15" t="inlineStr">
-        <is>
-          <t>227528.0</t>
-        </is>
-      </c>
-      <c r="BR15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BS15" t="inlineStr">
-        <is>
-          <t>73.0</t>
-        </is>
-      </c>
-      <c r="BT15" t="inlineStr">
-        <is>
-          <t>2025/12/30</t>
-        </is>
-      </c>
-      <c r="BU15" t="inlineStr">
-        <is>
-          <t>-1.23</t>
-        </is>
-      </c>
-      <c r="BV15" t="inlineStr">
-        <is>
-          <t>廣運</t>
-        </is>
-      </c>
-      <c r="BW15" t="inlineStr">
-        <is>
-          <t>廣運</t>
-        </is>
-      </c>
-      <c r="BX15" t="inlineStr">
-        <is>
-          <t>光電業</t>
-        </is>
-      </c>
-      <c r="BY15" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BZ15" t="inlineStr">
-        <is>
-          <t>1.25</t>
-        </is>
-      </c>
-      <c r="CA15" t="inlineStr">
-        <is>
-          <t>8.126510269834878</t>
-        </is>
-      </c>
-      <c r="CB15" t="inlineStr">
-        <is>
-          <t>71.54723574191938</t>
-        </is>
-      </c>
-      <c r="CC15" t="inlineStr">
-        <is>
-          <t>22.92929018430961</t>
-        </is>
-      </c>
-      <c r="CD15" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="CE15" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="CF15" t="inlineStr">
-        <is>
-          <t>4.27</t>
-        </is>
-      </c>
-      <c r="CG15" t="inlineStr">
-        <is>
-          <t>0.94</t>
-        </is>
-      </c>
-      <c r="CH15" t="inlineStr">
-        <is>
-          <t>4.00</t>
-        </is>
-      </c>
-      <c r="CI15" t="inlineStr">
-        <is>
-          <t>574.62</t>
-        </is>
-      </c>
-      <c r="CJ15" t="inlineStr">
-        <is>
-          <t>17.69%</t>
-        </is>
-      </c>
-      <c r="CK15" t="inlineStr">
-        <is>
-          <t>-6.67%</t>
-        </is>
-      </c>
-      <c r="CL15" t="inlineStr">
-        <is>
-          <t>94.08</t>
-        </is>
-      </c>
-      <c r="CM15" t="inlineStr">
-        <is>
-          <t>19348</t>
-        </is>
-      </c>
-      <c r="CN15" t="inlineStr">
-        <is>
-          <t>自動化設備74.11%、太陽能產品12.33%、電子零組件8.12%、建材營建4.02%、其他1.41% (2024年)</t>
-        </is>
-      </c>
-      <c r="CO15" t="inlineStr">
-        <is>
-          <t>廣運-光電業-上櫃</t>
-        </is>
-      </c>
-      <c r="CP15" t="inlineStr">
-        <is>
-          <t>光電業平上櫃</t>
-        </is>
-      </c>
-      <c r="CQ15" t="inlineStr">
-        <is>
-          <t>72.2</t>
-        </is>
-      </c>
-      <c r="CR15" t="inlineStr">
-        <is>
-          <t>72.7</t>
-        </is>
-      </c>
       <c r="CS15" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>71.3</t>
         </is>
       </c>
       <c r="CT15" t="inlineStr">
         <is>
-          <t>72.1</t>
+          <t>71.3</t>
         </is>
       </c>
       <c r="CU15" t="inlineStr">
@@ -7766,12 +7766,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>6029.0</t>
+          <t>3170.0</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -7781,7 +7781,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>72.1</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -7791,17 +7791,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2.28</t>
+          <t>-2.27</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>46.27</t>
+          <t>-0.68</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -7811,7 +7811,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -7866,7 +7866,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>-6.05</t>
+          <t>-7.21</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7891,7 +7891,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
@@ -7941,17 +7941,17 @@
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>13.89</t>
+          <t>17.40</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>1.86</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
@@ -7962,66 +7962,66 @@
       <c r="AP16" t="inlineStr"/>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>65</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>10744</t>
+          <t>5061</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
-          <t>97.03</t>
+          <t>87.63</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>90.51</t>
+          <t>91.29</t>
         </is>
       </c>
       <c r="AU16" t="n">
-        <v>0.63</v>
+        <v>-0.28</v>
       </c>
       <c r="AV16" t="n">
-        <v>8.380000000000001</v>
+        <v>7.18</v>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>-4.81</t>
+          <t>-4.74</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>72.54</t>
+          <t>72.3</t>
         </is>
       </c>
       <c r="AZ16" t="n">
-        <v>66.93000000000001</v>
+        <v>67.45999999999999</v>
       </c>
       <c r="BA16" t="n">
         <v>66.81</v>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>70.19</t>
+          <t>70.14</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>116.34</t>
+          <t>79.09</t>
         </is>
       </c>
       <c r="BD16" t="n">
-        <v>1.87</v>
+        <v>1.93</v>
       </c>
       <c r="BE16" t="n">
-        <v>0.86</v>
+        <v>1.08</v>
       </c>
       <c r="BF16" t="inlineStr">
         <is>
@@ -8030,7 +8030,7 @@
       </c>
       <c r="BG16" t="inlineStr">
         <is>
-          <t>-89.70</t>
+          <t>-87.17</t>
         </is>
       </c>
       <c r="BH16" t="inlineStr">
@@ -8040,43 +8040,43 @@
       </c>
       <c r="BI16" t="inlineStr">
         <is>
-          <t>1277721.845286885</t>
+          <t>1276231.26993865</t>
         </is>
       </c>
       <c r="BJ16" t="inlineStr">
         <is>
-          <t>435553.0</t>
+          <t>227528.0</t>
         </is>
       </c>
       <c r="BK16" t="n">
-        <v>405067.8</v>
+        <v>284915.2</v>
       </c>
       <c r="BL16" t="inlineStr">
         <is>
-          <t>276939.0</t>
+          <t>286862.6</t>
         </is>
       </c>
       <c r="BM16" t="n">
-        <v>133176.84</v>
+        <v>136315.58</v>
       </c>
       <c r="BN16" t="inlineStr">
         <is>
-          <t>128128</t>
+          <t>-1947</t>
         </is>
       </c>
       <c r="BO16" t="inlineStr">
         <is>
-          <t>32366.66350395649</t>
+          <t>31790.87037527536</t>
         </is>
       </c>
       <c r="BP16" t="inlineStr">
         <is>
-          <t>39898.07860213425</t>
+          <t>28624.00816752913</t>
         </is>
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>435553.0</t>
+          <t>227528.0</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
@@ -8096,7 +8096,7 @@
       </c>
       <c r="BU16" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-1.23</t>
         </is>
       </c>
       <c r="BV16" t="inlineStr">
@@ -8141,22 +8141,22 @@
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>4.32</t>
+          <t>4.27</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="CH16" t="inlineStr">
@@ -8166,7 +8166,7 @@
       </c>
       <c r="CI16" t="inlineStr">
         <is>
-          <t>574.62</t>
+          <t>542.31</t>
         </is>
       </c>
       <c r="CJ16" t="inlineStr">
@@ -8181,12 +8181,12 @@
       </c>
       <c r="CL16" t="inlineStr">
         <is>
-          <t>94.08</t>
+          <t>93.31</t>
         </is>
       </c>
       <c r="CM16" t="inlineStr">
         <is>
-          <t>19348</t>
+          <t>18260</t>
         </is>
       </c>
       <c r="CN16" t="inlineStr">
@@ -8201,17 +8201,17 @@
       </c>
       <c r="CP16" t="inlineStr">
         <is>
-          <t>光電業平上櫃</t>
+          <t>光電業右下上櫃</t>
         </is>
       </c>
       <c r="CQ16" t="inlineStr">
         <is>
-          <t>73.6</t>
+          <t>72.2</t>
         </is>
       </c>
       <c r="CR16" t="inlineStr">
         <is>
-          <t>73.7</t>
+          <t>72.7</t>
         </is>
       </c>
       <c r="CS16" t="inlineStr">
@@ -8221,7 +8221,7 @@
       </c>
       <c r="CT16" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>72.1</t>
         </is>
       </c>
       <c r="CU16" t="inlineStr">
@@ -8243,7 +8243,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>【d1】</t>
+          <t>【b1】</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -8253,12 +8253,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>3110.0</t>
+          <t>6029.0</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -8268,7 +8268,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>72.2</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -8278,17 +8278,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>3.35</t>
+          <t>-3.55</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>42.29</t>
+          <t>46.27</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -8298,7 +8298,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -8353,7 +8353,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>-7.08</t>
+          <t>-6.05</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -8378,7 +8378,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>-0.06</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
@@ -8428,17 +8428,17 @@
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>7.16</t>
+          <t>33.08</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>1.86</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
@@ -8449,66 +8449,66 @@
       <c r="AP17" t="inlineStr"/>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>65</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>10744</t>
+          <t>5061</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
         <is>
-          <t>89.22</t>
+          <t>97.03</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>88.56</t>
+          <t>90.51</t>
         </is>
       </c>
       <c r="AU17" t="n">
-        <v>-0.39</v>
+        <v>0.63</v>
       </c>
       <c r="AV17" t="n">
-        <v>9.199999999999999</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>-4.87</t>
+          <t>-4.81</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>72.47999999999999</t>
+          <t>72.54</t>
         </is>
       </c>
       <c r="AZ17" t="n">
-        <v>66.38</v>
+        <v>66.93000000000001</v>
       </c>
       <c r="BA17" t="n">
-        <v>66.81999999999999</v>
+        <v>66.81</v>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>70.24</t>
+          <t>70.19</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>173.26</t>
+          <t>116.34</t>
         </is>
       </c>
       <c r="BD17" t="n">
-        <v>1.67</v>
+        <v>1.87</v>
       </c>
       <c r="BE17" t="n">
-        <v>0.61</v>
+        <v>0.86</v>
       </c>
       <c r="BF17" t="inlineStr">
         <is>
@@ -8517,7 +8517,7 @@
       </c>
       <c r="BG17" t="inlineStr">
         <is>
-          <t>-92.70</t>
+          <t>-89.70</t>
         </is>
       </c>
       <c r="BH17" t="inlineStr">
@@ -8527,43 +8527,43 @@
       </c>
       <c r="BI17" t="inlineStr">
         <is>
-          <t>1277721.845286885</t>
+          <t>1276231.26993865</t>
         </is>
       </c>
       <c r="BJ17" t="inlineStr">
         <is>
-          <t>224848.0</t>
+          <t>435553.0</t>
         </is>
       </c>
       <c r="BK17" t="n">
-        <v>378776.4</v>
+        <v>405067.8</v>
       </c>
       <c r="BL17" t="inlineStr">
         <is>
-          <t>266193.0</t>
+          <t>276939.0</t>
         </is>
       </c>
       <c r="BM17" t="n">
-        <v>125841.48</v>
+        <v>133176.84</v>
       </c>
       <c r="BN17" t="inlineStr">
         <is>
-          <t>112583</t>
+          <t>128128</t>
         </is>
       </c>
       <c r="BO17" t="inlineStr">
         <is>
-          <t>30997.31530428781</t>
+          <t>32366.66350395649</t>
         </is>
       </c>
       <c r="BP17" t="inlineStr">
         <is>
-          <t>32290.56927292253</t>
+          <t>39898.07860213425</t>
         </is>
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>224848.0</t>
+          <t>435553.0</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
@@ -8583,7 +8583,7 @@
       </c>
       <c r="BU17" t="inlineStr">
         <is>
-          <t>-1.10</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="BV17" t="inlineStr">
@@ -8628,7 +8628,7 @@
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
@@ -8638,12 +8638,12 @@
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>4.28</t>
+          <t>4.32</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="CH17" t="inlineStr">
@@ -8653,7 +8653,7 @@
       </c>
       <c r="CI17" t="inlineStr">
         <is>
-          <t>574.62</t>
+          <t>542.31</t>
         </is>
       </c>
       <c r="CJ17" t="inlineStr">
@@ -8668,12 +8668,12 @@
       </c>
       <c r="CL17" t="inlineStr">
         <is>
-          <t>94.08</t>
+          <t>93.31</t>
         </is>
       </c>
       <c r="CM17" t="inlineStr">
         <is>
-          <t>19348</t>
+          <t>18260</t>
         </is>
       </c>
       <c r="CN17" t="inlineStr">
@@ -8688,27 +8688,27 @@
       </c>
       <c r="CP17" t="inlineStr">
         <is>
-          <t>光電業平上櫃</t>
+          <t>光電業右下上櫃</t>
         </is>
       </c>
       <c r="CQ17" t="inlineStr">
         <is>
-          <t>71.5</t>
+          <t>73.6</t>
         </is>
       </c>
       <c r="CR17" t="inlineStr">
         <is>
-          <t>73.4</t>
+          <t>73.7</t>
         </is>
       </c>
       <c r="CS17" t="inlineStr">
         <is>
-          <t>70.7</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="CT17" t="inlineStr">
         <is>
-          <t>72.2</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="CU17" t="inlineStr">
@@ -8740,12 +8740,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-0.83</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2854.0</t>
+          <t>3110.0</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -8755,7 +8755,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>71.8</t>
+          <t>72.2</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -8765,17 +8765,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>3.88</t>
+          <t>-2.41</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>30.27</t>
+          <t>42.29</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -8785,7 +8785,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -8840,7 +8840,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>-7.59</t>
+          <t>-7.08</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -8865,7 +8865,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
@@ -8915,17 +8915,17 @@
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>6.57</t>
+          <t>17.07</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>-2.08</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
@@ -8936,66 +8936,66 @@
       <c r="AP18" t="inlineStr"/>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>65</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>10744</t>
+          <t>5061</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
         <is>
-          <t>85.29</t>
+          <t>89.22</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>92.16</t>
+          <t>88.56</t>
         </is>
       </c>
       <c r="AU18" t="n">
-        <v>0.76</v>
+        <v>-0.39</v>
       </c>
       <c r="AV18" t="n">
-        <v>8.17</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>-1.47</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>-4.89</t>
+          <t>-4.87</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>71.25999999999999</t>
+          <t>72.47999999999999</t>
         </is>
       </c>
       <c r="AZ18" t="n">
-        <v>65.88</v>
+        <v>66.38</v>
       </c>
       <c r="BA18" t="n">
-        <v>66.86</v>
+        <v>66.81999999999999</v>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>70.3</t>
+          <t>70.24</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>326.92</t>
+          <t>173.26</t>
         </is>
       </c>
       <c r="BD18" t="n">
-        <v>1.48</v>
+        <v>1.67</v>
       </c>
       <c r="BE18" t="n">
-        <v>0.35</v>
+        <v>0.61</v>
       </c>
       <c r="BF18" t="inlineStr">
         <is>
@@ -9004,7 +9004,7 @@
       </c>
       <c r="BG18" t="inlineStr">
         <is>
-          <t>-95.86</t>
+          <t>-92.70</t>
         </is>
       </c>
       <c r="BH18" t="inlineStr">
@@ -9014,43 +9014,43 @@
       </c>
       <c r="BI18" t="inlineStr">
         <is>
-          <t>1277721.845286885</t>
+          <t>1276231.26993865</t>
         </is>
       </c>
       <c r="BJ18" t="inlineStr">
         <is>
-          <t>205765.0</t>
+          <t>224848.0</t>
         </is>
       </c>
       <c r="BK18" t="n">
-        <v>368941</v>
+        <v>378776.4</v>
       </c>
       <c r="BL18" t="inlineStr">
         <is>
-          <t>283217.3</t>
+          <t>266193.0</t>
         </is>
       </c>
       <c r="BM18" t="n">
-        <v>123456.28</v>
+        <v>125841.48</v>
       </c>
       <c r="BN18" t="inlineStr">
         <is>
-          <t>85723</t>
+          <t>112583</t>
         </is>
       </c>
       <c r="BO18" t="inlineStr">
         <is>
-          <t>30762.1782190815</t>
+          <t>30997.31530428781</t>
         </is>
       </c>
       <c r="BP18" t="inlineStr">
         <is>
-          <t>42844.99990001565</t>
+          <t>32290.56927292253</t>
         </is>
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>205765.0</t>
+          <t>224848.0</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
@@ -9070,7 +9070,7 @@
       </c>
       <c r="BU18" t="inlineStr">
         <is>
-          <t>-1.64</t>
+          <t>-1.10</t>
         </is>
       </c>
       <c r="BV18" t="inlineStr">
@@ -9125,12 +9125,12 @@
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>4.25</t>
+          <t>4.28</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="CH18" t="inlineStr">
@@ -9140,7 +9140,7 @@
       </c>
       <c r="CI18" t="inlineStr">
         <is>
-          <t>574.62</t>
+          <t>542.31</t>
         </is>
       </c>
       <c r="CJ18" t="inlineStr">
@@ -9155,12 +9155,12 @@
       </c>
       <c r="CL18" t="inlineStr">
         <is>
-          <t>94.08</t>
+          <t>93.31</t>
         </is>
       </c>
       <c r="CM18" t="inlineStr">
         <is>
-          <t>19348</t>
+          <t>18260</t>
         </is>
       </c>
       <c r="CN18" t="inlineStr">
@@ -9175,27 +9175,27 @@
       </c>
       <c r="CP18" t="inlineStr">
         <is>
-          <t>光電業平上櫃</t>
+          <t>光電業右下上櫃</t>
         </is>
       </c>
       <c r="CQ18" t="inlineStr">
         <is>
-          <t>72.6</t>
+          <t>71.5</t>
         </is>
       </c>
       <c r="CR18" t="inlineStr">
         <is>
-          <t>73.8</t>
+          <t>73.4</t>
         </is>
       </c>
       <c r="CS18" t="inlineStr">
         <is>
-          <t>71.3</t>
+          <t>70.7</t>
         </is>
       </c>
       <c r="CT18" t="inlineStr">
         <is>
-          <t>71.8</t>
+          <t>72.2</t>
         </is>
       </c>
       <c r="CU18" t="inlineStr">
@@ -9227,12 +9227,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-1.23</t>
+          <t>-0.83</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>4590.0</t>
+          <t>2854.0</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -9242,7 +9242,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>72.4</t>
+          <t>71.8</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -9252,17 +9252,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>3.08</t>
+          <t>-1.84</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>24.41</t>
+          <t>30.27</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -9272,7 +9272,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -9327,7 +9327,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>-6.82</t>
+          <t>-7.59</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -9352,7 +9352,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>-0.06</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
@@ -9402,17 +9402,17 @@
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>2025-12-24</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>10.57</t>
+          <t>15.66</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>-2.08</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
@@ -9423,66 +9423,66 @@
       <c r="AP19" t="inlineStr"/>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>65</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>10744</t>
+          <t>5061</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
         <is>
-          <t>91.18</t>
+          <t>85.29</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>97.06</t>
+          <t>92.16</t>
         </is>
       </c>
       <c r="AU19" t="n">
-        <v>3.99</v>
+        <v>0.76</v>
       </c>
       <c r="AV19" t="n">
-        <v>6.41</v>
+        <v>8.17</v>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>-2.18</t>
+          <t>-1.47</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>-4.99</t>
+          <t>-4.89</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>69.62</t>
+          <t>71.25999999999999</t>
         </is>
       </c>
       <c r="AZ19" t="n">
-        <v>65.42</v>
+        <v>65.88</v>
       </c>
       <c r="BA19" t="n">
-        <v>66.88</v>
+        <v>66.86</v>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>70.39</t>
+          <t>70.3</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>1881.60</t>
+          <t>326.92</t>
         </is>
       </c>
       <c r="BD19" t="n">
-        <v>1.26</v>
+        <v>1.48</v>
       </c>
       <c r="BE19" t="n">
-        <v>0.06</v>
+        <v>0.35</v>
       </c>
       <c r="BF19" t="inlineStr">
         <is>
@@ -9491,7 +9491,7 @@
       </c>
       <c r="BG19" t="inlineStr">
         <is>
-          <t>-99.24</t>
+          <t>-95.86</t>
         </is>
       </c>
       <c r="BH19" t="inlineStr">
@@ -9501,43 +9501,43 @@
       </c>
       <c r="BI19" t="inlineStr">
         <is>
-          <t>1277721.845286885</t>
+          <t>1276231.26993865</t>
         </is>
       </c>
       <c r="BJ19" t="inlineStr">
         <is>
-          <t>330882.0</t>
+          <t>205765.0</t>
         </is>
       </c>
       <c r="BK19" t="n">
-        <v>344617.8</v>
+        <v>368941</v>
       </c>
       <c r="BL19" t="inlineStr">
         <is>
-          <t>277012.5</t>
+          <t>283217.3</t>
         </is>
       </c>
       <c r="BM19" t="n">
-        <v>120544.5</v>
+        <v>123456.28</v>
       </c>
       <c r="BN19" t="inlineStr">
         <is>
-          <t>67605</t>
+          <t>85723</t>
         </is>
       </c>
       <c r="BO19" t="inlineStr">
         <is>
-          <t>28565.30154982075</t>
+          <t>30762.1782190815</t>
         </is>
       </c>
       <c r="BP19" t="inlineStr">
         <is>
-          <t>58437.18651371956</t>
+          <t>42844.99990001565</t>
         </is>
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>330882.0</t>
+          <t>205765.0</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
@@ -9557,7 +9557,7 @@
       </c>
       <c r="BU19" t="inlineStr">
         <is>
-          <t>-0.82</t>
+          <t>-1.64</t>
         </is>
       </c>
       <c r="BV19" t="inlineStr">
@@ -9602,7 +9602,7 @@
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
@@ -9612,12 +9612,12 @@
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>4.29</t>
+          <t>4.25</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="CH19" t="inlineStr">
@@ -9627,7 +9627,7 @@
       </c>
       <c r="CI19" t="inlineStr">
         <is>
-          <t>574.62</t>
+          <t>542.31</t>
         </is>
       </c>
       <c r="CJ19" t="inlineStr">
@@ -9642,12 +9642,12 @@
       </c>
       <c r="CL19" t="inlineStr">
         <is>
-          <t>94.08</t>
+          <t>93.31</t>
         </is>
       </c>
       <c r="CM19" t="inlineStr">
         <is>
-          <t>19348</t>
+          <t>18260</t>
         </is>
       </c>
       <c r="CN19" t="inlineStr">
@@ -9662,12 +9662,12 @@
       </c>
       <c r="CP19" t="inlineStr">
         <is>
-          <t>光電業平上櫃</t>
+          <t>光電業右下上櫃</t>
         </is>
       </c>
       <c r="CQ19" t="inlineStr">
         <is>
-          <t>73.3</t>
+          <t>72.6</t>
         </is>
       </c>
       <c r="CR19" t="inlineStr">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="CS19" t="inlineStr">
         <is>
-          <t>70.9</t>
+          <t>71.3</t>
         </is>
       </c>
       <c r="CT19" t="inlineStr">
         <is>
-          <t>72.4</t>
+          <t>71.8</t>
         </is>
       </c>
       <c r="CU19" t="inlineStr">
@@ -9704,7 +9704,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d2】</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -9714,12 +9714,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>3475.0</t>
+          <t>15262.0</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -9729,7 +9729,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>86.3</t>
+          <t>87.9</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -9744,12 +9744,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>-0.2</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>-48.57</t>
+          <t>-29.74</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -9814,7 +9814,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>-27.78</t>
+          <t>-26.44</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -9839,7 +9839,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
@@ -9889,17 +9889,17 @@
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>2026-01-07</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>3.09</t>
+          <t>13.56</t>
         </is>
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.77</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
@@ -9910,66 +9910,66 @@
       <c r="AP20" t="inlineStr"/>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>117</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>3475</t>
+          <t>15262</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
         <is>
-          <t>19.44</t>
+          <t>41.67</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>13.89</t>
+          <t>27.78</t>
         </is>
       </c>
       <c r="AU20" t="n">
-        <v>0.28</v>
+        <v>1.69</v>
       </c>
       <c r="AV20" t="n">
-        <v>-2.32</v>
+        <v>-1.66</v>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>-1.81</t>
+          <t>-1.92</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>-8.39</t>
+          <t>-7.99</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>86.06</t>
+          <t>86.44</t>
         </is>
       </c>
       <c r="AZ20" t="n">
-        <v>88.09999999999999</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="BA20" t="n">
-        <v>89.73</v>
+        <v>89.62</v>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>97.94</t>
+          <t>97.4</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>-8.29</t>
+          <t>1.93</t>
         </is>
       </c>
       <c r="BD20" t="n">
-        <v>-1.37</v>
+        <v>-1.24</v>
       </c>
       <c r="BE20" t="n">
-        <v>-1.27</v>
+        <v>-1.26</v>
       </c>
       <c r="BF20" t="inlineStr">
         <is>
@@ -9978,53 +9978,53 @@
       </c>
       <c r="BG20" t="inlineStr">
         <is>
-          <t>-110.56</t>
+          <t>-110.51</t>
         </is>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2025/12/23</t>
+          <t>2026/01/08</t>
         </is>
       </c>
       <c r="BI20" t="inlineStr">
         <is>
-          <t>1614423.851434426</t>
+          <t>1615264.972392638</t>
         </is>
       </c>
       <c r="BJ20" t="inlineStr">
         <is>
-          <t>300110.0</t>
+          <t>1350488.0</t>
         </is>
       </c>
       <c r="BK20" t="n">
-        <v>440142</v>
+        <v>588601.2</v>
       </c>
       <c r="BL20" t="inlineStr">
         <is>
-          <t>855833.4</t>
+          <t>837784.8</t>
         </is>
       </c>
       <c r="BM20" t="n">
-        <v>1207701.98</v>
+        <v>1183614</v>
       </c>
       <c r="BN20" t="inlineStr">
         <is>
-          <t>-415691</t>
+          <t>-249183</t>
         </is>
       </c>
       <c r="BO20" t="inlineStr">
         <is>
-          <t>-43205.05203860979</t>
+          <t>-37848.60692057251</t>
         </is>
       </c>
       <c r="BP20" t="inlineStr">
         <is>
-          <t>-71305.34976936108</t>
+          <t>-8388.15877136751</t>
         </is>
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>300110.0</t>
+          <t>1350488.0</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
@@ -10044,7 +10044,7 @@
       </c>
       <c r="BU20" t="inlineStr">
         <is>
-          <t>26.91</t>
+          <t>29.26</t>
         </is>
       </c>
       <c r="BV20" t="inlineStr">
@@ -10089,22 +10089,22 @@
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="CH20" t="inlineStr">
@@ -10114,7 +10114,7 @@
       </c>
       <c r="CI20" t="inlineStr">
         <is>
-          <t>92.8</t>
+          <t>94.52</t>
         </is>
       </c>
       <c r="CJ20" t="inlineStr">
@@ -10129,12 +10129,12 @@
       </c>
       <c r="CL20" t="inlineStr">
         <is>
-          <t>94.08</t>
+          <t>93.31</t>
         </is>
       </c>
       <c r="CM20" t="inlineStr">
         <is>
-          <t>33742</t>
+          <t>34367</t>
         </is>
       </c>
       <c r="CN20" t="inlineStr">
@@ -10154,22 +10154,22 @@
       </c>
       <c r="CQ20" t="inlineStr">
         <is>
-          <t>86.7</t>
+          <t>86.6</t>
         </is>
       </c>
       <c r="CR20" t="inlineStr">
         <is>
-          <t>87.1</t>
+          <t>89.9</t>
         </is>
       </c>
       <c r="CS20" t="inlineStr">
         <is>
-          <t>85.7</t>
+          <t>86.6</t>
         </is>
       </c>
       <c r="CT20" t="inlineStr">
         <is>
-          <t>86.3</t>
+          <t>87.9</t>
         </is>
       </c>
       <c r="CU20" t="inlineStr">
@@ -10201,12 +10201,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>1.86</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>4746.0</t>
+          <t>3475.0</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -10216,177 +10216,177 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
+          <t>86.3</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>1.82</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>-0.2</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>-48.57</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>2025-07-30 00:00:00</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>2025-09-08 00:00:00</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>2025-03-24 00:00:00</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>2025-03-31 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>79.0</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>119.5</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>73.0</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>-27.78</t>
+        </is>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>8.22</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2024/12/10</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>77.2</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>0.02</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>2025/10/22</t>
+        </is>
+      </c>
+      <c r="AD21" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="AE21" t="inlineStr">
+        <is>
+          <t>2025/02/12</t>
+        </is>
+      </c>
+      <c r="AF21" t="inlineStr">
+        <is>
+          <t>78.7</t>
+        </is>
+      </c>
+      <c r="AG21" t="inlineStr">
+        <is>
+          <t>2026/01/05</t>
+        </is>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>84.9</t>
+        </is>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>2025/12/16</t>
+        </is>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
           <t>86.5</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>2025-11-27 00:00:00</t>
+        </is>
+      </c>
+      <c r="AL21" t="inlineStr">
+        <is>
+          <t>2026-01-07</t>
+        </is>
+      </c>
+      <c r="AM21" t="inlineStr">
+        <is>
+          <t>3.09</t>
+        </is>
+      </c>
+      <c r="AN21" t="inlineStr">
         <is>
           <t>-0.23</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>0.6</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>-6.21</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>40.0</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>2025-07-30 00:00:00</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>2025-09-08 00:00:00</t>
-        </is>
-      </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>2025-03-24 00:00:00</t>
-        </is>
-      </c>
-      <c r="P21" t="inlineStr">
-        <is>
-          <t>2025-03-31 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q21" t="inlineStr">
-        <is>
-          <t>79.0</t>
-        </is>
-      </c>
-      <c r="R21" t="inlineStr">
-        <is>
-          <t>119.5</t>
-        </is>
-      </c>
-      <c r="S21" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T21" t="inlineStr">
-        <is>
-          <t>84.0</t>
-        </is>
-      </c>
-      <c r="U21" t="inlineStr">
-        <is>
-          <t>73.0</t>
-        </is>
-      </c>
-      <c r="V21" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W21" t="inlineStr">
-        <is>
-          <t>-27.62</t>
-        </is>
-      </c>
-      <c r="X21" t="inlineStr">
-        <is>
-          <t>8.22</t>
-        </is>
-      </c>
-      <c r="Y21" t="inlineStr">
-        <is>
-          <t>2024/12/10</t>
-        </is>
-      </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>77.2</t>
-        </is>
-      </c>
-      <c r="AA21" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>0.02</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>2025/10/22</t>
-        </is>
-      </c>
-      <c r="AD21" t="inlineStr">
-        <is>
-          <t>100.0</t>
-        </is>
-      </c>
-      <c r="AE21" t="inlineStr">
-        <is>
-          <t>2025/02/12</t>
-        </is>
-      </c>
-      <c r="AF21" t="inlineStr">
-        <is>
-          <t>78.7</t>
-        </is>
-      </c>
-      <c r="AG21" t="inlineStr">
-        <is>
-          <t>2026/01/05</t>
-        </is>
-      </c>
-      <c r="AH21" t="inlineStr">
-        <is>
-          <t>84.9</t>
-        </is>
-      </c>
-      <c r="AI21" t="inlineStr">
-        <is>
-          <t>2025/12/16</t>
-        </is>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>86.5</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>2025-11-27 00:00:00</t>
-        </is>
-      </c>
-      <c r="AL21" t="inlineStr">
-        <is>
-          <t>2026-01-06</t>
-        </is>
-      </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>4.22</t>
-        </is>
-      </c>
-      <c r="AN21" t="inlineStr">
-        <is>
-          <t>-0.22</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
@@ -10397,29 +10397,29 @@
       <c r="AP21" t="inlineStr"/>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>117</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>3475</t>
+          <t>15262</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
         <is>
-          <t>22.22</t>
+          <t>19.44</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>10.69</t>
+          <t>13.89</t>
         </is>
       </c>
       <c r="AU21" t="n">
-        <v>0.19</v>
+        <v>0.28</v>
       </c>
       <c r="AV21" t="n">
-        <v>-2.35</v>
+        <v>-2.32</v>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
@@ -10428,35 +10428,35 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>-8.44</t>
+          <t>-8.39</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>86.34</t>
+          <t>86.06</t>
         </is>
       </c>
       <c r="AZ21" t="n">
-        <v>88.42</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="BA21" t="n">
-        <v>90.05</v>
+        <v>89.73</v>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>98.36</t>
+          <t>97.94</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>-9.79</t>
+          <t>-8.29</t>
         </is>
       </c>
       <c r="BD21" t="n">
-        <v>-1.36</v>
+        <v>-1.37</v>
       </c>
       <c r="BE21" t="n">
-        <v>-1.24</v>
+        <v>-1.27</v>
       </c>
       <c r="BF21" t="inlineStr">
         <is>
@@ -10465,53 +10465,53 @@
       </c>
       <c r="BG21" t="inlineStr">
         <is>
-          <t>-110.34</t>
+          <t>-110.56</t>
         </is>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2025/12/23</t>
+          <t>2026/01/08</t>
         </is>
       </c>
       <c r="BI21" t="inlineStr">
         <is>
-          <t>1614423.851434426</t>
+          <t>1615264.972392638</t>
         </is>
       </c>
       <c r="BJ21" t="inlineStr">
         <is>
-          <t>411093.0</t>
+          <t>300110.0</t>
         </is>
       </c>
       <c r="BK21" t="n">
-        <v>804665.2</v>
+        <v>440142</v>
       </c>
       <c r="BL21" t="inlineStr">
         <is>
-          <t>857971.9</t>
+          <t>855833.4</t>
         </is>
       </c>
       <c r="BM21" t="n">
-        <v>1223916.62</v>
+        <v>1207701.98</v>
       </c>
       <c r="BN21" t="inlineStr">
         <is>
-          <t>-53306</t>
+          <t>-415691</t>
         </is>
       </c>
       <c r="BO21" t="inlineStr">
         <is>
-          <t>-38095.90699665501</t>
+          <t>-43205.05203860979</t>
         </is>
       </c>
       <c r="BP21" t="inlineStr">
         <is>
-          <t>-46099.93156044604</t>
+          <t>-71305.34976936108</t>
         </is>
       </c>
       <c r="BQ21" t="inlineStr">
         <is>
-          <t>411093.0</t>
+          <t>300110.0</t>
         </is>
       </c>
       <c r="BR21" t="inlineStr">
@@ -10531,7 +10531,7 @@
       </c>
       <c r="BU21" t="inlineStr">
         <is>
-          <t>27.21</t>
+          <t>26.91</t>
         </is>
       </c>
       <c r="BV21" t="inlineStr">
@@ -10576,12 +10576,12 @@
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
@@ -10591,7 +10591,7 @@
       </c>
       <c r="CG21" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="CH21" t="inlineStr">
@@ -10601,7 +10601,7 @@
       </c>
       <c r="CI21" t="inlineStr">
         <is>
-          <t>92.8</t>
+          <t>94.52</t>
         </is>
       </c>
       <c r="CJ21" t="inlineStr">
@@ -10616,12 +10616,12 @@
       </c>
       <c r="CL21" t="inlineStr">
         <is>
-          <t>94.08</t>
+          <t>93.31</t>
         </is>
       </c>
       <c r="CM21" t="inlineStr">
         <is>
-          <t>33742</t>
+          <t>34367</t>
         </is>
       </c>
       <c r="CN21" t="inlineStr">
@@ -10641,22 +10641,22 @@
       </c>
       <c r="CQ21" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>86.7</t>
         </is>
       </c>
       <c r="CR21" t="inlineStr">
         <is>
-          <t>87.4</t>
+          <t>87.1</t>
         </is>
       </c>
       <c r="CS21" t="inlineStr">
         <is>
-          <t>85.8</t>
+          <t>85.7</t>
         </is>
       </c>
       <c r="CT21" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>86.3</t>
         </is>
       </c>
       <c r="CU21" t="inlineStr">
@@ -10688,12 +10688,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-1.95</t>
+          <t>1.86</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>5699.0</t>
+          <t>4746.0</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -10703,149 +10703,149 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
+          <t>86.5</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>1.59</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>-0.2</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>-6.21</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>2025-07-30 00:00:00</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>2025-09-08 00:00:00</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>2025-03-24 00:00:00</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>2025-03-31 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>79.0</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>119.5</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>73.0</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>-27.62</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>8.22</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2024/12/10</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>77.2</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>0.02</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>2025/10/22</t>
+        </is>
+      </c>
+      <c r="AD22" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="AE22" t="inlineStr">
+        <is>
+          <t>2025/02/12</t>
+        </is>
+      </c>
+      <c r="AF22" t="inlineStr">
+        <is>
+          <t>78.7</t>
+        </is>
+      </c>
+      <c r="AG22" t="inlineStr">
+        <is>
+          <t>2026/01/05</t>
+        </is>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
           <t>84.9</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>1.62</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>0.6</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>17.09</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>40.0</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>2025-07-30 00:00:00</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>2025-09-08 00:00:00</t>
-        </is>
-      </c>
-      <c r="O22" t="inlineStr">
-        <is>
-          <t>2025-03-24 00:00:00</t>
-        </is>
-      </c>
-      <c r="P22" t="inlineStr">
-        <is>
-          <t>2025-03-31 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q22" t="inlineStr">
-        <is>
-          <t>79.0</t>
-        </is>
-      </c>
-      <c r="R22" t="inlineStr">
-        <is>
-          <t>119.5</t>
-        </is>
-      </c>
-      <c r="S22" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T22" t="inlineStr">
-        <is>
-          <t>84.0</t>
-        </is>
-      </c>
-      <c r="U22" t="inlineStr">
-        <is>
-          <t>73.0</t>
-        </is>
-      </c>
-      <c r="V22" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W22" t="inlineStr">
-        <is>
-          <t>-28.95</t>
-        </is>
-      </c>
-      <c r="X22" t="inlineStr">
-        <is>
-          <t>8.22</t>
-        </is>
-      </c>
-      <c r="Y22" t="inlineStr">
-        <is>
-          <t>2024/12/10</t>
-        </is>
-      </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>77.2</t>
-        </is>
-      </c>
-      <c r="AA22" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>-0.16</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>2025/10/22</t>
-        </is>
-      </c>
-      <c r="AD22" t="inlineStr">
-        <is>
-          <t>100.0</t>
-        </is>
-      </c>
-      <c r="AE22" t="inlineStr">
-        <is>
-          <t>2025/02/12</t>
-        </is>
-      </c>
-      <c r="AF22" t="inlineStr">
-        <is>
-          <t>78.7</t>
-        </is>
-      </c>
-      <c r="AG22" t="inlineStr">
-        <is>
-          <t>2026/01/05</t>
-        </is>
-      </c>
-      <c r="AH22" t="inlineStr">
-        <is>
-          <t>84.9</t>
-        </is>
-      </c>
       <c r="AI22" t="inlineStr">
         <is>
           <t>2025/12/16</t>
@@ -10863,17 +10863,17 @@
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-06</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>5.06</t>
+          <t>4.22</t>
         </is>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>-3.30</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
@@ -10884,66 +10884,66 @@
       <c r="AP22" t="inlineStr"/>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>117</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>3475</t>
+          <t>15262</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>22.22</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>9.5</t>
+          <t>10.69</t>
         </is>
       </c>
       <c r="AU22" t="n">
-        <v>-2.93</v>
+        <v>0.19</v>
       </c>
       <c r="AV22" t="n">
-        <v>-1.39</v>
+        <v>-2.35</v>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>-1.78</t>
+          <t>-1.81</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>-8.57</t>
+          <t>-8.44</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>87.46000000000001</t>
+          <t>86.34</t>
         </is>
       </c>
       <c r="AZ22" t="n">
-        <v>88.7</v>
+        <v>88.42</v>
       </c>
       <c r="BA22" t="n">
-        <v>90.3</v>
+        <v>90.05</v>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>98.77</t>
+          <t>98.36</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>-11.55</t>
+          <t>-9.79</t>
         </is>
       </c>
       <c r="BD22" t="n">
-        <v>-1.35</v>
+        <v>-1.36</v>
       </c>
       <c r="BE22" t="n">
-        <v>-1.21</v>
+        <v>-1.24</v>
       </c>
       <c r="BF22" t="inlineStr">
         <is>
@@ -10952,53 +10952,53 @@
       </c>
       <c r="BG22" t="inlineStr">
         <is>
-          <t>-110.08</t>
+          <t>-110.34</t>
         </is>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2025/12/23</t>
+          <t>2026/01/08</t>
         </is>
       </c>
       <c r="BI22" t="inlineStr">
         <is>
-          <t>1614423.851434426</t>
+          <t>1615264.972392638</t>
         </is>
       </c>
       <c r="BJ22" t="inlineStr">
         <is>
-          <t>488190.0</t>
+          <t>411093.0</t>
         </is>
       </c>
       <c r="BK22" t="n">
-        <v>1018674.8</v>
+        <v>804665.2</v>
       </c>
       <c r="BL22" t="inlineStr">
         <is>
-          <t>869960.2</t>
+          <t>857971.9</t>
         </is>
       </c>
       <c r="BM22" t="n">
-        <v>1235131.72</v>
+        <v>1223916.62</v>
       </c>
       <c r="BN22" t="inlineStr">
         <is>
-          <t>148714</t>
+          <t>-53306</t>
         </is>
       </c>
       <c r="BO22" t="inlineStr">
         <is>
-          <t>-36640.62980323846</t>
+          <t>-38095.90699665501</t>
         </is>
       </c>
       <c r="BP22" t="inlineStr">
         <is>
-          <t>-20336.80084912281</t>
+          <t>-46099.93156044604</t>
         </is>
       </c>
       <c r="BQ22" t="inlineStr">
         <is>
-          <t>488190.0</t>
+          <t>411093.0</t>
         </is>
       </c>
       <c r="BR22" t="inlineStr">
@@ -11018,7 +11018,7 @@
       </c>
       <c r="BU22" t="inlineStr">
         <is>
-          <t>24.85</t>
+          <t>27.21</t>
         </is>
       </c>
       <c r="BV22" t="inlineStr">
@@ -11063,22 +11063,22 @@
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="CH22" t="inlineStr">
@@ -11088,7 +11088,7 @@
       </c>
       <c r="CI22" t="inlineStr">
         <is>
-          <t>92.8</t>
+          <t>94.52</t>
         </is>
       </c>
       <c r="CJ22" t="inlineStr">
@@ -11103,12 +11103,12 @@
       </c>
       <c r="CL22" t="inlineStr">
         <is>
-          <t>94.08</t>
+          <t>93.31</t>
         </is>
       </c>
       <c r="CM22" t="inlineStr">
         <is>
-          <t>33742</t>
+          <t>34367</t>
         </is>
       </c>
       <c r="CN22" t="inlineStr">
@@ -11128,22 +11128,22 @@
       </c>
       <c r="CQ22" t="inlineStr">
         <is>
-          <t>87.1</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="CR22" t="inlineStr">
         <is>
-          <t>87.7</t>
+          <t>87.4</t>
         </is>
       </c>
       <c r="CS22" t="inlineStr">
         <is>
-          <t>84.9</t>
+          <t>85.8</t>
         </is>
       </c>
       <c r="CT22" t="inlineStr">
         <is>
-          <t>84.9</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="CU22" t="inlineStr">
@@ -11165,7 +11165,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>【d2】</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -11175,12 +11175,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>-1.95</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>4517.0</t>
+          <t>5699.0</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -11190,7 +11190,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>86.6</t>
+          <t>84.9</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -11200,17 +11200,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>3.41</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>-0.2</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>19.31</t>
+          <t>17.09</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -11275,7 +11275,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>-27.53</t>
+          <t>-28.95</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -11300,7 +11300,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
@@ -11350,17 +11350,17 @@
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>2026-01-02</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>4.01</t>
+          <t>5.06</t>
         </is>
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>-1.27</t>
+          <t>-3.30</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
@@ -11371,66 +11371,66 @@
       <c r="AP23" t="inlineStr"/>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>117</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>3475</t>
+          <t>15262</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
         <is>
-          <t>9.84</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>23.28</t>
+          <t>9.5</t>
         </is>
       </c>
       <c r="AU23" t="n">
-        <v>-1.97</v>
+        <v>-2.93</v>
       </c>
       <c r="AV23" t="n">
-        <v>-0.86</v>
+        <v>-1.39</v>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>-1.65</t>
+          <t>-1.78</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>-8.74</t>
+          <t>-8.57</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>88.34</t>
+          <t>87.46000000000001</t>
         </is>
       </c>
       <c r="AZ23" t="n">
-        <v>89.09999999999999</v>
+        <v>88.7</v>
       </c>
       <c r="BA23" t="n">
-        <v>90.59999999999999</v>
+        <v>90.3</v>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>99.28</t>
+          <t>98.77</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>1.98</t>
+          <t>-11.55</t>
         </is>
       </c>
       <c r="BD23" t="n">
-        <v>-1.15</v>
+        <v>-1.35</v>
       </c>
       <c r="BE23" t="n">
-        <v>-1.18</v>
+        <v>-1.21</v>
       </c>
       <c r="BF23" t="inlineStr">
         <is>
@@ -11439,53 +11439,53 @@
       </c>
       <c r="BG23" t="inlineStr">
         <is>
-          <t>-109.79</t>
+          <t>-110.08</t>
         </is>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2025/12/23</t>
+          <t>2026/01/08</t>
         </is>
       </c>
       <c r="BI23" t="inlineStr">
         <is>
-          <t>1614423.851434426</t>
+          <t>1615264.972392638</t>
         </is>
       </c>
       <c r="BJ23" t="inlineStr">
         <is>
-          <t>393125.0</t>
+          <t>488190.0</t>
         </is>
       </c>
       <c r="BK23" t="n">
-        <v>1007832.8</v>
+        <v>1018674.8</v>
       </c>
       <c r="BL23" t="inlineStr">
         <is>
-          <t>844744.2</t>
+          <t>869960.2</t>
         </is>
       </c>
       <c r="BM23" t="n">
-        <v>1254190.86</v>
+        <v>1235131.72</v>
       </c>
       <c r="BN23" t="inlineStr">
         <is>
-          <t>163088</t>
+          <t>148714</t>
         </is>
       </c>
       <c r="BO23" t="inlineStr">
         <is>
-          <t>-39604.96234035039</t>
+          <t>-36640.62980323846</t>
         </is>
       </c>
       <c r="BP23" t="inlineStr">
         <is>
-          <t>8933.593054521945</t>
+          <t>-20336.80084912281</t>
         </is>
       </c>
       <c r="BQ23" t="inlineStr">
         <is>
-          <t>393125.0</t>
+          <t>488190.0</t>
         </is>
       </c>
       <c r="BR23" t="inlineStr">
@@ -11505,7 +11505,7 @@
       </c>
       <c r="BU23" t="inlineStr">
         <is>
-          <t>27.35</t>
+          <t>24.85</t>
         </is>
       </c>
       <c r="BV23" t="inlineStr">
@@ -11550,22 +11550,22 @@
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="CH23" t="inlineStr">
@@ -11575,7 +11575,7 @@
       </c>
       <c r="CI23" t="inlineStr">
         <is>
-          <t>92.8</t>
+          <t>94.52</t>
         </is>
       </c>
       <c r="CJ23" t="inlineStr">
@@ -11590,12 +11590,12 @@
       </c>
       <c r="CL23" t="inlineStr">
         <is>
-          <t>94.08</t>
+          <t>93.31</t>
         </is>
       </c>
       <c r="CM23" t="inlineStr">
         <is>
-          <t>33742</t>
+          <t>34367</t>
         </is>
       </c>
       <c r="CN23" t="inlineStr">
@@ -11615,22 +11615,22 @@
       </c>
       <c r="CQ23" t="inlineStr">
         <is>
-          <t>86.8</t>
+          <t>87.1</t>
         </is>
       </c>
       <c r="CR23" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>87.7</t>
         </is>
       </c>
       <c r="CS23" t="inlineStr">
         <is>
-          <t>86.3</t>
+          <t>84.9</t>
         </is>
       </c>
       <c r="CT23" t="inlineStr">
         <is>
-          <t>86.6</t>
+          <t>84.9</t>
         </is>
       </c>
       <c r="CU23" t="inlineStr">
@@ -11662,12 +11662,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>-1.93</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>7033.0</t>
+          <t>4517.0</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -11677,7 +11677,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>86.6</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -11687,17 +11687,17 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>-0.2</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>30.41</t>
+          <t>19.31</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -11762,7 +11762,7 @@
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>-28.03</t>
+          <t>-27.53</t>
         </is>
       </c>
       <c r="X24" t="inlineStr">
@@ -11787,7 +11787,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.1</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
@@ -11837,17 +11837,17 @@
       </c>
       <c r="AL24" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2026-01-02</t>
         </is>
       </c>
       <c r="AM24" t="inlineStr">
         <is>
-          <t>6.25</t>
+          <t>4.01</t>
         </is>
       </c>
       <c r="AN24" t="inlineStr">
         <is>
-          <t>-2.09</t>
+          <t>-1.27</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
@@ -11858,63 +11858,63 @@
       <c r="AP24" t="inlineStr"/>
       <c r="AQ24" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>117</t>
         </is>
       </c>
       <c r="AR24" t="inlineStr">
         <is>
-          <t>3475</t>
+          <t>15262</t>
         </is>
       </c>
       <c r="AS24" t="inlineStr">
         <is>
-          <t>18.67</t>
+          <t>9.84</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr">
         <is>
-          <t>53.33</t>
+          <t>23.28</t>
         </is>
       </c>
       <c r="AU24" t="n">
-        <v>-3.41</v>
+        <v>-1.97</v>
       </c>
       <c r="AV24" t="n">
-        <v>-0.43</v>
+        <v>-0.86</v>
       </c>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>-1.68</t>
+          <t>-1.65</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>-8.86</t>
+          <t>-8.74</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr">
         <is>
-          <t>89.03999999999999</t>
+          <t>88.34</t>
         </is>
       </c>
       <c r="AZ24" t="n">
-        <v>89.42</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="BA24" t="n">
-        <v>90.95</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="BB24" t="inlineStr">
         <is>
-          <t>99.8</t>
+          <t>99.28</t>
         </is>
       </c>
       <c r="BC24" t="inlineStr">
         <is>
-          <t>10.62</t>
+          <t>1.98</t>
         </is>
       </c>
       <c r="BD24" t="n">
-        <v>-1.06</v>
+        <v>-1.15</v>
       </c>
       <c r="BE24" t="n">
         <v>-1.18</v>
@@ -11926,53 +11926,53 @@
       </c>
       <c r="BG24" t="inlineStr">
         <is>
-          <t>-109.84</t>
+          <t>-109.79</t>
         </is>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2025/12/23</t>
+          <t>2026/01/08</t>
         </is>
       </c>
       <c r="BI24" t="inlineStr">
         <is>
-          <t>1614423.851434426</t>
+          <t>1615264.972392638</t>
         </is>
       </c>
       <c r="BJ24" t="inlineStr">
         <is>
-          <t>608192.0</t>
+          <t>393125.0</t>
         </is>
       </c>
       <c r="BK24" t="n">
-        <v>1086968.4</v>
+        <v>1007832.8</v>
       </c>
       <c r="BL24" t="inlineStr">
         <is>
-          <t>833474.0</t>
+          <t>844744.2</t>
         </is>
       </c>
       <c r="BM24" t="n">
-        <v>1262665.78</v>
+        <v>1254190.86</v>
       </c>
       <c r="BN24" t="inlineStr">
         <is>
-          <t>253494</t>
+          <t>163088</t>
         </is>
       </c>
       <c r="BO24" t="inlineStr">
         <is>
-          <t>-48430.15423032719</t>
+          <t>-39604.96234035039</t>
         </is>
       </c>
       <c r="BP24" t="inlineStr">
         <is>
-          <t>60614.92030778143</t>
+          <t>8933.593054521945</t>
         </is>
       </c>
       <c r="BQ24" t="inlineStr">
         <is>
-          <t>608192.0</t>
+          <t>393125.0</t>
         </is>
       </c>
       <c r="BR24" t="inlineStr">
@@ -11992,7 +11992,7 @@
       </c>
       <c r="BU24" t="inlineStr">
         <is>
-          <t>26.47</t>
+          <t>27.35</t>
         </is>
       </c>
       <c r="BV24" t="inlineStr">
@@ -12047,12 +12047,12 @@
       </c>
       <c r="CF24" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="CG24" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="CH24" t="inlineStr">
@@ -12062,7 +12062,7 @@
       </c>
       <c r="CI24" t="inlineStr">
         <is>
-          <t>92.8</t>
+          <t>94.52</t>
         </is>
       </c>
       <c r="CJ24" t="inlineStr">
@@ -12077,12 +12077,12 @@
       </c>
       <c r="CL24" t="inlineStr">
         <is>
-          <t>94.08</t>
+          <t>93.31</t>
         </is>
       </c>
       <c r="CM24" t="inlineStr">
         <is>
-          <t>33742</t>
+          <t>34367</t>
         </is>
       </c>
       <c r="CN24" t="inlineStr">
@@ -12102,22 +12102,22 @@
       </c>
       <c r="CQ24" t="inlineStr">
         <is>
+          <t>86.8</t>
+        </is>
+      </c>
+      <c r="CR24" t="inlineStr">
+        <is>
           <t>88.0</t>
         </is>
       </c>
-      <c r="CR24" t="inlineStr">
-        <is>
-          <t>88.0</t>
-        </is>
-      </c>
       <c r="CS24" t="inlineStr">
         <is>
-          <t>85.8</t>
+          <t>86.3</t>
         </is>
       </c>
       <c r="CT24" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>86.6</t>
         </is>
       </c>
       <c r="CU24" t="inlineStr">
@@ -12139,7 +12139,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>【d1】</t>
+          <t>【d2】</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -12149,12 +12149,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>-4.68</t>
+          <t>-1.93</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>23549.0</t>
+          <t>7033.0</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -12164,7 +12164,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>87.7</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -12174,17 +12174,17 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>-1.62</t>
+          <t>2.16</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>-0.2</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>53.66</t>
+          <t>30.41</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -12249,7 +12249,7 @@
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>-26.61</t>
+          <t>-28.03</t>
         </is>
       </c>
       <c r="X25" t="inlineStr">
@@ -12274,7 +12274,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
@@ -12324,17 +12324,17 @@
       </c>
       <c r="AL25" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>20.92</t>
+          <t>6.25</t>
         </is>
       </c>
       <c r="AN25" t="inlineStr">
         <is>
-          <t>-7.98</t>
+          <t>-2.09</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
@@ -12345,66 +12345,66 @@
       <c r="AP25" t="inlineStr"/>
       <c r="AQ25" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>117</t>
         </is>
       </c>
       <c r="AR25" t="inlineStr">
         <is>
-          <t>3475</t>
+          <t>15262</t>
         </is>
       </c>
       <c r="AS25" t="inlineStr">
         <is>
-          <t>41.33</t>
+          <t>18.67</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr">
         <is>
-          <t>71.59</t>
+          <t>53.33</t>
         </is>
       </c>
       <c r="AU25" t="n">
-        <v>-2.6</v>
+        <v>-3.41</v>
       </c>
       <c r="AV25" t="n">
-        <v>0.38</v>
+        <v>-0.43</v>
       </c>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>-1.73</t>
+          <t>-1.68</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>-9.04</t>
+          <t>-8.86</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr">
         <is>
-          <t>90.03999999999999</t>
+          <t>89.03999999999999</t>
         </is>
       </c>
       <c r="AZ25" t="n">
-        <v>89.7</v>
+        <v>89.42</v>
       </c>
       <c r="BA25" t="n">
-        <v>91.28</v>
+        <v>90.95</v>
       </c>
       <c r="BB25" t="inlineStr">
         <is>
-          <t>100.36</t>
+          <t>99.8</t>
         </is>
       </c>
       <c r="BC25" t="inlineStr">
         <is>
-          <t>29.37</t>
+          <t>10.62</t>
         </is>
       </c>
       <c r="BD25" t="n">
-        <v>-0.86</v>
+        <v>-1.06</v>
       </c>
       <c r="BE25" t="n">
-        <v>-1.21</v>
+        <v>-1.18</v>
       </c>
       <c r="BF25" t="inlineStr">
         <is>
@@ -12413,53 +12413,53 @@
       </c>
       <c r="BG25" t="inlineStr">
         <is>
-          <t>-110.10</t>
+          <t>-109.84</t>
         </is>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2025/12/23</t>
+          <t>2026/01/08</t>
         </is>
       </c>
       <c r="BI25" t="inlineStr">
         <is>
-          <t>1614423.851434426</t>
+          <t>1615264.972392638</t>
         </is>
       </c>
       <c r="BJ25" t="inlineStr">
         <is>
-          <t>2122726.0</t>
+          <t>608192.0</t>
         </is>
       </c>
       <c r="BK25" t="n">
-        <v>1271524.8</v>
+        <v>1086968.4</v>
       </c>
       <c r="BL25" t="inlineStr">
         <is>
-          <t>827510.9</t>
+          <t>833474.0</t>
         </is>
       </c>
       <c r="BM25" t="n">
-        <v>1267007.76</v>
+        <v>1262665.78</v>
       </c>
       <c r="BN25" t="inlineStr">
         <is>
-          <t>444013</t>
+          <t>253494</t>
         </is>
       </c>
       <c r="BO25" t="inlineStr">
         <is>
-          <t>-68256.5314190742</t>
+          <t>-48430.15423032719</t>
         </is>
       </c>
       <c r="BP25" t="inlineStr">
         <is>
-          <t>109237.6763728742</t>
+          <t>60614.92030778143</t>
         </is>
       </c>
       <c r="BQ25" t="inlineStr">
         <is>
-          <t>2122726.0</t>
+          <t>608192.0</t>
         </is>
       </c>
       <c r="BR25" t="inlineStr">
@@ -12479,7 +12479,7 @@
       </c>
       <c r="BU25" t="inlineStr">
         <is>
-          <t>28.97</t>
+          <t>26.47</t>
         </is>
       </c>
       <c r="BV25" t="inlineStr">
@@ -12524,22 +12524,22 @@
       </c>
       <c r="CD25" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE25" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CF25" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="CG25" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="CH25" t="inlineStr">
@@ -12549,7 +12549,7 @@
       </c>
       <c r="CI25" t="inlineStr">
         <is>
-          <t>92.8</t>
+          <t>94.52</t>
         </is>
       </c>
       <c r="CJ25" t="inlineStr">
@@ -12564,12 +12564,12 @@
       </c>
       <c r="CL25" t="inlineStr">
         <is>
-          <t>94.08</t>
+          <t>93.31</t>
         </is>
       </c>
       <c r="CM25" t="inlineStr">
         <is>
-          <t>33742</t>
+          <t>34367</t>
         </is>
       </c>
       <c r="CN25" t="inlineStr">
@@ -12589,22 +12589,22 @@
       </c>
       <c r="CQ25" t="inlineStr">
         <is>
-          <t>94.0</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="CR25" t="inlineStr">
         <is>
-          <t>95.1</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="CS25" t="inlineStr">
         <is>
-          <t>87.3</t>
+          <t>85.8</t>
         </is>
       </c>
       <c r="CT25" t="inlineStr">
         <is>
-          <t>87.7</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="CU25" t="inlineStr">
@@ -12636,12 +12636,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>3.08</t>
+          <t>-4.68</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>15899.0</t>
+          <t>23549.0</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -12651,7 +12651,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>92.1</t>
+          <t>87.7</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -12661,17 +12661,17 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>-6.72</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>-0.2</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>38.73</t>
+          <t>53.66</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -12736,7 +12736,7 @@
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>-22.93</t>
+          <t>-26.61</t>
         </is>
       </c>
       <c r="X26" t="inlineStr">
@@ -12761,7 +12761,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
@@ -12811,17 +12811,17 @@
       </c>
       <c r="AL26" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="AM26" t="inlineStr">
         <is>
-          <t>14.13</t>
+          <t>20.92</t>
         </is>
       </c>
       <c r="AN26" t="inlineStr">
         <is>
-          <t>-1.72</t>
+          <t>-7.98</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
@@ -12832,66 +12832,66 @@
       <c r="AP26" t="inlineStr"/>
       <c r="AQ26" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>117</t>
         </is>
       </c>
       <c r="AR26" t="inlineStr">
         <is>
-          <t>3475</t>
+          <t>15262</t>
         </is>
       </c>
       <c r="AS26" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>41.33</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr">
         <is>
-          <t>86.46</t>
+          <t>71.59</t>
         </is>
       </c>
       <c r="AU26" t="n">
-        <v>1.93</v>
+        <v>-2.6</v>
       </c>
       <c r="AV26" t="n">
-        <v>0.47</v>
+        <v>0.38</v>
       </c>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>-1.83</t>
+          <t>-1.73</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>-9.08</t>
+          <t>-9.04</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr">
         <is>
-          <t>90.36</t>
+          <t>90.03999999999999</t>
         </is>
       </c>
       <c r="AZ26" t="n">
-        <v>89.93000000000001</v>
+        <v>89.7</v>
       </c>
       <c r="BA26" t="n">
-        <v>91.61</v>
+        <v>91.28</v>
       </c>
       <c r="BB26" t="inlineStr">
         <is>
-          <t>100.76</t>
+          <t>100.36</t>
         </is>
       </c>
       <c r="BC26" t="inlineStr">
         <is>
-          <t>41.41</t>
+          <t>29.37</t>
         </is>
       </c>
       <c r="BD26" t="n">
-        <v>-0.76</v>
+        <v>-0.86</v>
       </c>
       <c r="BE26" t="n">
-        <v>-1.3</v>
+        <v>-1.21</v>
       </c>
       <c r="BF26" t="inlineStr">
         <is>
@@ -12900,53 +12900,53 @@
       </c>
       <c r="BG26" t="inlineStr">
         <is>
-          <t>-110.85</t>
+          <t>-110.10</t>
         </is>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2025/12/23</t>
+          <t>2026/01/08</t>
         </is>
       </c>
       <c r="BI26" t="inlineStr">
         <is>
-          <t>1614423.851434426</t>
+          <t>1615264.972392638</t>
         </is>
       </c>
       <c r="BJ26" t="inlineStr">
         <is>
-          <t>1481141.0</t>
+          <t>2122726.0</t>
         </is>
       </c>
       <c r="BK26" t="n">
-        <v>911278.6</v>
+        <v>1271524.8</v>
       </c>
       <c r="BL26" t="inlineStr">
         <is>
-          <t>656854.7</t>
+          <t>827510.9</t>
         </is>
       </c>
       <c r="BM26" t="n">
-        <v>1254226.66</v>
+        <v>1267007.76</v>
       </c>
       <c r="BN26" t="inlineStr">
         <is>
-          <t>254423</t>
+          <t>444013</t>
         </is>
       </c>
       <c r="BO26" t="inlineStr">
         <is>
-          <t>-100528.2055630648</t>
+          <t>-68256.5314190742</t>
         </is>
       </c>
       <c r="BP26" t="inlineStr">
         <is>
-          <t>12525.91088111838</t>
+          <t>109237.6763728742</t>
         </is>
       </c>
       <c r="BQ26" t="inlineStr">
         <is>
-          <t>1481141.0</t>
+          <t>2122726.0</t>
         </is>
       </c>
       <c r="BR26" t="inlineStr">
@@ -12966,7 +12966,7 @@
       </c>
       <c r="BU26" t="inlineStr">
         <is>
-          <t>35.44</t>
+          <t>28.97</t>
         </is>
       </c>
       <c r="BV26" t="inlineStr">
@@ -13011,7 +13011,7 @@
       </c>
       <c r="CD26" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE26" t="inlineStr">
@@ -13021,12 +13021,12 @@
       </c>
       <c r="CF26" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="CG26" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="CH26" t="inlineStr">
@@ -13036,7 +13036,7 @@
       </c>
       <c r="CI26" t="inlineStr">
         <is>
-          <t>92.8</t>
+          <t>94.52</t>
         </is>
       </c>
       <c r="CJ26" t="inlineStr">
@@ -13051,12 +13051,12 @@
       </c>
       <c r="CL26" t="inlineStr">
         <is>
-          <t>94.08</t>
+          <t>93.31</t>
         </is>
       </c>
       <c r="CM26" t="inlineStr">
         <is>
-          <t>33742</t>
+          <t>34367</t>
         </is>
       </c>
       <c r="CN26" t="inlineStr">
@@ -13076,22 +13076,22 @@
       </c>
       <c r="CQ26" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>94.0</t>
         </is>
       </c>
       <c r="CR26" t="inlineStr">
         <is>
-          <t>94.8</t>
+          <t>95.1</t>
         </is>
       </c>
       <c r="CS26" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>87.3</t>
         </is>
       </c>
       <c r="CT26" t="inlineStr">
         <is>
-          <t>92.1</t>
+          <t>87.7</t>
         </is>
       </c>
       <c r="CU26" t="inlineStr">
@@ -13113,7 +13113,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -13123,12 +13123,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>-0.89</t>
+          <t>3.08</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>4861.0</t>
+          <t>15899.0</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -13138,7 +13138,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>89.3</t>
+          <t>92.1</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -13148,17 +13148,17 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>-3.48</t>
+          <t>-4.78</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>-0.2</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>34.32</t>
+          <t>38.73</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -13223,7 +13223,7 @@
       </c>
       <c r="W27" t="inlineStr">
         <is>
-          <t>-25.27</t>
+          <t>-22.93</t>
         </is>
       </c>
       <c r="X27" t="inlineStr">
@@ -13248,7 +13248,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
@@ -13298,17 +13298,17 @@
       </c>
       <c r="AL27" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>4.32</t>
+          <t>14.13</t>
         </is>
       </c>
       <c r="AN27" t="inlineStr">
         <is>
-          <t>-1.00</t>
+          <t>-1.72</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
@@ -13319,17 +13319,17 @@
       <c r="AP27" t="inlineStr"/>
       <c r="AQ27" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>117</t>
         </is>
       </c>
       <c r="AR27" t="inlineStr">
         <is>
-          <t>3475</t>
+          <t>15262</t>
         </is>
       </c>
       <c r="AS27" t="inlineStr">
         <is>
-          <t>73.44</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr">
@@ -13338,47 +13338,47 @@
         </is>
       </c>
       <c r="AU27" t="n">
-        <v>-0.18</v>
+        <v>1.93</v>
       </c>
       <c r="AV27" t="n">
-        <v>-0.58</v>
+        <v>0.47</v>
       </c>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>-2.13</t>
+          <t>-1.83</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>-9.03</t>
+          <t>-9.08</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr">
         <is>
-          <t>89.46</t>
+          <t>90.36</t>
         </is>
       </c>
       <c r="AZ27" t="n">
-        <v>89.98</v>
+        <v>89.93000000000001</v>
       </c>
       <c r="BA27" t="n">
-        <v>91.95</v>
+        <v>91.61</v>
       </c>
       <c r="BB27" t="inlineStr">
         <is>
-          <t>101.07</t>
+          <t>100.76</t>
         </is>
       </c>
       <c r="BC27" t="inlineStr">
         <is>
-          <t>24.82</t>
+          <t>41.41</t>
         </is>
       </c>
       <c r="BD27" t="n">
-        <v>-1.08</v>
+        <v>-0.76</v>
       </c>
       <c r="BE27" t="n">
-        <v>-1.44</v>
+        <v>-1.3</v>
       </c>
       <c r="BF27" t="inlineStr">
         <is>
@@ -13387,53 +13387,53 @@
       </c>
       <c r="BG27" t="inlineStr">
         <is>
-          <t>-111.97</t>
+          <t>-110.85</t>
         </is>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2025/12/23</t>
+          <t>2026/01/08</t>
         </is>
       </c>
       <c r="BI27" t="inlineStr">
         <is>
-          <t>1614423.851434426</t>
+          <t>1615264.972392638</t>
         </is>
       </c>
       <c r="BJ27" t="inlineStr">
         <is>
-          <t>433980.0</t>
+          <t>1481141.0</t>
         </is>
       </c>
       <c r="BK27" t="n">
-        <v>721245.6</v>
+        <v>911278.6</v>
       </c>
       <c r="BL27" t="inlineStr">
         <is>
-          <t>536973.1</t>
+          <t>656854.7</t>
         </is>
       </c>
       <c r="BM27" t="n">
-        <v>1297321.12</v>
+        <v>1254226.66</v>
       </c>
       <c r="BN27" t="inlineStr">
         <is>
-          <t>184272</t>
+          <t>254423</t>
         </is>
       </c>
       <c r="BO27" t="inlineStr">
         <is>
-          <t>-121083.4994620072</t>
+          <t>-100528.2055630648</t>
         </is>
       </c>
       <c r="BP27" t="inlineStr">
         <is>
-          <t>-57339.85806714394</t>
+          <t>12525.91088111838</t>
         </is>
       </c>
       <c r="BQ27" t="inlineStr">
         <is>
-          <t>433980.0</t>
+          <t>1481141.0</t>
         </is>
       </c>
       <c r="BR27" t="inlineStr">
@@ -13453,7 +13453,7 @@
       </c>
       <c r="BU27" t="inlineStr">
         <is>
-          <t>31.32</t>
+          <t>35.44</t>
         </is>
       </c>
       <c r="BV27" t="inlineStr">
@@ -13498,7 +13498,7 @@
       </c>
       <c r="CD27" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE27" t="inlineStr">
@@ -13508,12 +13508,12 @@
       </c>
       <c r="CF27" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="CG27" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="CH27" t="inlineStr">
@@ -13523,7 +13523,7 @@
       </c>
       <c r="CI27" t="inlineStr">
         <is>
-          <t>92.8</t>
+          <t>94.52</t>
         </is>
       </c>
       <c r="CJ27" t="inlineStr">
@@ -13538,12 +13538,12 @@
       </c>
       <c r="CL27" t="inlineStr">
         <is>
-          <t>94.08</t>
+          <t>93.31</t>
         </is>
       </c>
       <c r="CM27" t="inlineStr">
         <is>
-          <t>33742</t>
+          <t>34367</t>
         </is>
       </c>
       <c r="CN27" t="inlineStr">
@@ -13563,22 +13563,22 @@
       </c>
       <c r="CQ27" t="inlineStr">
         <is>
-          <t>90.3</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="CR27" t="inlineStr">
         <is>
+          <t>94.8</t>
+        </is>
+      </c>
+      <c r="CS27" t="inlineStr">
+        <is>
           <t>91.0</t>
         </is>
       </c>
-      <c r="CS27" t="inlineStr">
-        <is>
-          <t>88.5</t>
-        </is>
-      </c>
       <c r="CT27" t="inlineStr">
         <is>
-          <t>89.3</t>
+          <t>92.1</t>
         </is>
       </c>
       <c r="CU27" t="inlineStr">
@@ -13610,12 +13610,12 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>-0.99</t>
+          <t>-0.89</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>8620.0</t>
+          <t>4861.0</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -13625,7 +13625,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>90.1</t>
+          <t>89.3</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -13635,17 +13635,17 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>-4.4</t>
+          <t>-1.59</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>-0.2</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>27.91</t>
+          <t>34.32</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -13710,7 +13710,7 @@
       </c>
       <c r="W28" t="inlineStr">
         <is>
-          <t>-24.60</t>
+          <t>-25.27</t>
         </is>
       </c>
       <c r="X28" t="inlineStr">
@@ -13735,7 +13735,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
@@ -13785,17 +13785,17 @@
       </c>
       <c r="AL28" t="inlineStr">
         <is>
-          <t>2025-12-24</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="AM28" t="inlineStr">
         <is>
-          <t>7.66</t>
+          <t>4.32</t>
         </is>
       </c>
       <c r="AN28" t="inlineStr">
         <is>
-          <t>-3.66</t>
+          <t>-1.00</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
@@ -13806,231 +13806,231 @@
       <c r="AP28" t="inlineStr"/>
       <c r="AQ28" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>117</t>
         </is>
       </c>
       <c r="AR28" t="inlineStr">
         <is>
-          <t>3475</t>
+          <t>15262</t>
         </is>
       </c>
       <c r="AS28" t="inlineStr">
         <is>
-          <t>85.94</t>
+          <t>73.44</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr">
         <is>
+          <t>86.46</t>
+        </is>
+      </c>
+      <c r="AU28" t="n">
+        <v>-0.18</v>
+      </c>
+      <c r="AV28" t="n">
+        <v>-0.58</v>
+      </c>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>-2.13</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>-9.03</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr">
+        <is>
+          <t>89.46</t>
+        </is>
+      </c>
+      <c r="AZ28" t="n">
+        <v>89.98</v>
+      </c>
+      <c r="BA28" t="n">
+        <v>91.95</v>
+      </c>
+      <c r="BB28" t="inlineStr">
+        <is>
+          <t>101.07</t>
+        </is>
+      </c>
+      <c r="BC28" t="inlineStr">
+        <is>
+          <t>24.82</t>
+        </is>
+      </c>
+      <c r="BD28" t="n">
+        <v>-1.08</v>
+      </c>
+      <c r="BE28" t="n">
+        <v>-1.44</v>
+      </c>
+      <c r="BF28" t="inlineStr">
+        <is>
+          <t>12.0</t>
+        </is>
+      </c>
+      <c r="BG28" t="inlineStr">
+        <is>
+          <t>-111.97</t>
+        </is>
+      </c>
+      <c r="BH28" t="inlineStr">
+        <is>
+          <t>2026/01/08</t>
+        </is>
+      </c>
+      <c r="BI28" t="inlineStr">
+        <is>
+          <t>1615264.972392638</t>
+        </is>
+      </c>
+      <c r="BJ28" t="inlineStr">
+        <is>
+          <t>433980.0</t>
+        </is>
+      </c>
+      <c r="BK28" t="n">
+        <v>721245.6</v>
+      </c>
+      <c r="BL28" t="inlineStr">
+        <is>
+          <t>536973.1</t>
+        </is>
+      </c>
+      <c r="BM28" t="n">
+        <v>1297321.12</v>
+      </c>
+      <c r="BN28" t="inlineStr">
+        <is>
+          <t>184272</t>
+        </is>
+      </c>
+      <c r="BO28" t="inlineStr">
+        <is>
+          <t>-121083.4994620072</t>
+        </is>
+      </c>
+      <c r="BP28" t="inlineStr">
+        <is>
+          <t>-57339.85806714394</t>
+        </is>
+      </c>
+      <c r="BQ28" t="inlineStr">
+        <is>
+          <t>433980.0</t>
+        </is>
+      </c>
+      <c r="BR28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BS28" t="inlineStr">
+        <is>
+          <t>68.0</t>
+        </is>
+      </c>
+      <c r="BT28" t="inlineStr">
+        <is>
+          <t>2025/07/28</t>
+        </is>
+      </c>
+      <c r="BU28" t="inlineStr">
+        <is>
+          <t>31.32</t>
+        </is>
+      </c>
+      <c r="BV28" t="inlineStr">
+        <is>
+          <t>中光電</t>
+        </is>
+      </c>
+      <c r="BW28" t="inlineStr">
+        <is>
+          <t>中光電</t>
+        </is>
+      </c>
+      <c r="BX28" t="inlineStr">
+        <is>
+          <t>光電業</t>
+        </is>
+      </c>
+      <c r="BY28" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BZ28" t="inlineStr">
+        <is>
+          <t>1.26</t>
+        </is>
+      </c>
+      <c r="CA28" t="inlineStr">
+        <is>
+          <t>-10.72295503475104</t>
+        </is>
+      </c>
+      <c r="CB28" t="inlineStr">
+        <is>
+          <t>6.089521543140648</t>
+        </is>
+      </c>
+      <c r="CC28" t="inlineStr">
+        <is>
+          <t>-1.317487052973139</t>
+        </is>
+      </c>
+      <c r="CD28" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="CE28" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="CF28" t="inlineStr">
+        <is>
+          <t>1.58</t>
+        </is>
+      </c>
+      <c r="CG28" t="inlineStr">
+        <is>
+          <t>1.71</t>
+        </is>
+      </c>
+      <c r="CH28" t="inlineStr">
+        <is>
+          <t>25.44</t>
+        </is>
+      </c>
+      <c r="CI28" t="inlineStr">
+        <is>
+          <t>94.52</t>
+        </is>
+      </c>
+      <c r="CJ28" t="inlineStr">
+        <is>
+          <t>15.18%</t>
+        </is>
+      </c>
+      <c r="CK28" t="inlineStr">
+        <is>
+          <t>-2.36%</t>
+        </is>
+      </c>
+      <c r="CL28" t="inlineStr">
+        <is>
           <t>93.31</t>
         </is>
       </c>
-      <c r="AU28" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AV28" t="n">
-        <v>-1.93</v>
-      </c>
-      <c r="AW28" t="inlineStr">
-        <is>
-          <t>-2.12</t>
-        </is>
-      </c>
-      <c r="AX28" t="inlineStr">
-        <is>
-          <t>-9.14</t>
-        </is>
-      </c>
-      <c r="AY28" t="inlineStr">
-        <is>
-          <t>88.52000000000001</t>
-        </is>
-      </c>
-      <c r="AZ28" t="n">
-        <v>90.26000000000001</v>
-      </c>
-      <c r="BA28" t="n">
-        <v>92.22</v>
-      </c>
-      <c r="BB28" t="inlineStr">
-        <is>
-          <t>101.49</t>
-        </is>
-      </c>
-      <c r="BC28" t="inlineStr">
-        <is>
-          <t>22.40</t>
-        </is>
-      </c>
-      <c r="BD28" t="n">
-        <v>-1.18</v>
-      </c>
-      <c r="BE28" t="n">
-        <v>-1.53</v>
-      </c>
-      <c r="BF28" t="inlineStr">
-        <is>
-          <t>12.0</t>
-        </is>
-      </c>
-      <c r="BG28" t="inlineStr">
-        <is>
-          <t>-112.71</t>
-        </is>
-      </c>
-      <c r="BH28" t="inlineStr">
-        <is>
-          <t>2025/12/23</t>
-        </is>
-      </c>
-      <c r="BI28" t="inlineStr">
-        <is>
-          <t>1614423.851434426</t>
-        </is>
-      </c>
-      <c r="BJ28" t="inlineStr">
-        <is>
-          <t>788803.0</t>
-        </is>
-      </c>
-      <c r="BK28" t="n">
-        <v>681655.6</v>
-      </c>
-      <c r="BL28" t="inlineStr">
-        <is>
-          <t>532930.9</t>
-        </is>
-      </c>
-      <c r="BM28" t="n">
-        <v>1334873.04</v>
-      </c>
-      <c r="BN28" t="inlineStr">
-        <is>
-          <t>148724</t>
-        </is>
-      </c>
-      <c r="BO28" t="inlineStr">
-        <is>
-          <t>-132673.2524428914</t>
-        </is>
-      </c>
-      <c r="BP28" t="inlineStr">
-        <is>
-          <t>-42904.42591940647</t>
-        </is>
-      </c>
-      <c r="BQ28" t="inlineStr">
-        <is>
-          <t>788803.0</t>
-        </is>
-      </c>
-      <c r="BR28" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BS28" t="inlineStr">
-        <is>
-          <t>68.0</t>
-        </is>
-      </c>
-      <c r="BT28" t="inlineStr">
-        <is>
-          <t>2025/07/28</t>
-        </is>
-      </c>
-      <c r="BU28" t="inlineStr">
-        <is>
-          <t>32.50</t>
-        </is>
-      </c>
-      <c r="BV28" t="inlineStr">
-        <is>
-          <t>中光電</t>
-        </is>
-      </c>
-      <c r="BW28" t="inlineStr">
-        <is>
-          <t>中光電</t>
-        </is>
-      </c>
-      <c r="BX28" t="inlineStr">
-        <is>
-          <t>光電業</t>
-        </is>
-      </c>
-      <c r="BY28" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BZ28" t="inlineStr">
-        <is>
-          <t>1.26</t>
-        </is>
-      </c>
-      <c r="CA28" t="inlineStr">
-        <is>
-          <t>-10.72295503475104</t>
-        </is>
-      </c>
-      <c r="CB28" t="inlineStr">
-        <is>
-          <t>6.089521543140648</t>
-        </is>
-      </c>
-      <c r="CC28" t="inlineStr">
-        <is>
-          <t>-1.317487052973139</t>
-        </is>
-      </c>
-      <c r="CD28" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="CE28" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="CF28" t="inlineStr">
-        <is>
-          <t>1.59</t>
-        </is>
-      </c>
-      <c r="CG28" t="inlineStr">
-        <is>
-          <t>1.74</t>
-        </is>
-      </c>
-      <c r="CH28" t="inlineStr">
-        <is>
-          <t>25.44</t>
-        </is>
-      </c>
-      <c r="CI28" t="inlineStr">
-        <is>
-          <t>92.8</t>
-        </is>
-      </c>
-      <c r="CJ28" t="inlineStr">
-        <is>
-          <t>15.18%</t>
-        </is>
-      </c>
-      <c r="CK28" t="inlineStr">
-        <is>
-          <t>-2.36%</t>
-        </is>
-      </c>
-      <c r="CL28" t="inlineStr">
-        <is>
-          <t>94.08</t>
-        </is>
-      </c>
       <c r="CM28" t="inlineStr">
         <is>
-          <t>33742</t>
+          <t>34367</t>
         </is>
       </c>
       <c r="CN28" t="inlineStr">
@@ -14050,22 +14050,22 @@
       </c>
       <c r="CQ28" t="inlineStr">
         <is>
+          <t>90.3</t>
+        </is>
+      </c>
+      <c r="CR28" t="inlineStr">
+        <is>
           <t>91.0</t>
         </is>
       </c>
-      <c r="CR28" t="inlineStr">
-        <is>
-          <t>93.5</t>
-        </is>
-      </c>
       <c r="CS28" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>88.5</t>
         </is>
       </c>
       <c r="CT28" t="inlineStr">
         <is>
-          <t>90.1</t>
+          <t>89.3</t>
         </is>
       </c>
       <c r="CU28" t="inlineStr">
